--- a/Excel/StoreSellConfig.xlsx
+++ b/Excel/StoreSellConfig.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7780B43-1F03-42F0-86B2-6033891B3673}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80330538-FF91-41B3-A717-86CC96466D56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="166" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="135">
   <si>
     <t>Id</t>
   </si>
@@ -538,6 +538,13 @@
   </si>
   <si>
     <t>坐骑:精灵羊驼</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>远古之核</t>
+  </si>
+  <si>
+    <t>魔能核心</t>
     <phoneticPr fontId="15" type="noConversion"/>
   </si>
 </sst>
@@ -2546,7 +2553,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q262"/>
+  <dimension ref="A1:Q264"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="5" width="14" customWidth="1"/>
@@ -7094,7 +7101,7 @@
         <v>50000022</v>
       </c>
       <c r="D156" s="3">
-        <v>0</v>
+        <v>50000023</v>
       </c>
       <c r="E156" s="2">
         <v>1</v>
@@ -7122,155 +7129,155 @@
       </c>
     </row>
     <row r="157" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A157" s="3"/>
-      <c r="B157" s="3"/>
       <c r="C157" s="3">
+        <v>50000023</v>
+      </c>
+      <c r="D157" s="3">
+        <v>50000024</v>
+      </c>
+      <c r="E157" s="2">
+        <v>1</v>
+      </c>
+      <c r="F157" s="3">
+        <v>100</v>
+      </c>
+      <c r="G157" s="9">
+        <v>10000182</v>
+      </c>
+      <c r="H157" s="2">
+        <v>1</v>
+      </c>
+      <c r="I157" s="9">
+        <v>10000151</v>
+      </c>
+      <c r="J157" s="3">
+        <v>1</v>
+      </c>
+      <c r="K157" s="2">
+        <v>0</v>
+      </c>
+      <c r="M157" s="11" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="158" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C158" s="3">
+        <v>50000024</v>
+      </c>
+      <c r="D158" s="3">
+        <v>0</v>
+      </c>
+      <c r="E158" s="2">
+        <v>1</v>
+      </c>
+      <c r="F158" s="3">
+        <v>100</v>
+      </c>
+      <c r="G158" s="9">
+        <v>10000183</v>
+      </c>
+      <c r="H158" s="2">
+        <v>1</v>
+      </c>
+      <c r="I158" s="9">
+        <v>10000151</v>
+      </c>
+      <c r="J158" s="3">
+        <v>5</v>
+      </c>
+      <c r="K158" s="2">
+        <v>0</v>
+      </c>
+      <c r="M158" s="11" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="159" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A159" s="3"/>
+      <c r="B159" s="3"/>
+      <c r="C159" s="3">
         <v>60000001</v>
       </c>
-      <c r="D157" s="3">
+      <c r="D159" s="3">
         <v>60000002</v>
       </c>
-      <c r="E157" s="3">
-        <v>1</v>
-      </c>
-      <c r="F157" s="3">
-        <v>100</v>
-      </c>
-      <c r="G157" s="3">
+      <c r="E159" s="3">
+        <v>1</v>
+      </c>
+      <c r="F159" s="3">
+        <v>100</v>
+      </c>
+      <c r="G159" s="3">
         <v>10000143</v>
       </c>
-      <c r="H157" s="11" t="s">
+      <c r="H159" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="I157" s="9">
+      <c r="I159" s="9">
         <v>10000157</v>
       </c>
-      <c r="J157" s="3">
-        <v>1</v>
-      </c>
-      <c r="K157" s="2">
-        <v>0</v>
-      </c>
-      <c r="L157" s="3"/>
-      <c r="M157" s="15" t="s">
+      <c r="J159" s="3">
+        <v>1</v>
+      </c>
+      <c r="K159" s="2">
+        <v>0</v>
+      </c>
+      <c r="L159" s="3"/>
+      <c r="M159" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="N157" s="3"/>
-      <c r="O157" s="11" t="s">
+      <c r="N159" s="3"/>
+      <c r="O159" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="P157" s="3"/>
-    </row>
-    <row r="158" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A158" s="3"/>
-      <c r="B158" s="3"/>
-      <c r="C158" s="3">
+      <c r="P159" s="3"/>
+    </row>
+    <row r="160" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A160" s="3"/>
+      <c r="B160" s="3"/>
+      <c r="C160" s="3">
         <v>60000002</v>
       </c>
-      <c r="D158" s="3">
+      <c r="D160" s="3">
         <v>60000003</v>
       </c>
-      <c r="E158" s="3">
-        <v>1</v>
-      </c>
-      <c r="F158" s="3">
-        <v>100</v>
-      </c>
-      <c r="G158" s="3">
+      <c r="E160" s="3">
+        <v>1</v>
+      </c>
+      <c r="F160" s="3">
+        <v>100</v>
+      </c>
+      <c r="G160" s="3">
         <v>10010093</v>
       </c>
-      <c r="H158" s="12">
-        <v>1</v>
-      </c>
-      <c r="I158" s="9">
+      <c r="H160" s="12">
+        <v>1</v>
+      </c>
+      <c r="I160" s="9">
         <v>10000143</v>
       </c>
-      <c r="J158" s="11" t="s">
+      <c r="J160" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="K158" s="2">
-        <v>0</v>
-      </c>
-      <c r="L158" s="3"/>
-      <c r="M158" s="12" t="s">
+      <c r="K160" s="2">
+        <v>0</v>
+      </c>
+      <c r="L160" s="3"/>
+      <c r="M160" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="N158" s="3"/>
-      <c r="O158" s="11" t="s">
+      <c r="N160" s="3"/>
+      <c r="O160" s="11" t="s">
         <v>39</v>
       </c>
-      <c r="P158" s="3"/>
-    </row>
-    <row r="159" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C159" s="3">
-        <v>60000003</v>
-      </c>
-      <c r="D159" s="3">
-        <v>60000004</v>
-      </c>
-      <c r="E159" s="3">
-        <v>1</v>
-      </c>
-      <c r="F159" s="3">
-        <v>100</v>
-      </c>
-      <c r="G159" s="13">
-        <v>10012001</v>
-      </c>
-      <c r="H159" s="3">
-        <v>1</v>
-      </c>
-      <c r="I159" s="3">
-        <v>10010029</v>
-      </c>
-      <c r="J159" s="3">
-        <v>10</v>
-      </c>
-      <c r="K159" s="2">
-        <v>0</v>
-      </c>
-      <c r="M159" s="13" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="160" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C160" s="3">
-        <v>60000004</v>
-      </c>
-      <c r="D160" s="3">
-        <v>60000005</v>
-      </c>
-      <c r="E160" s="3">
-        <v>1</v>
-      </c>
-      <c r="F160" s="3">
-        <v>100</v>
-      </c>
-      <c r="G160" s="13">
-        <v>10012002</v>
-      </c>
-      <c r="H160" s="3">
-        <v>1</v>
-      </c>
-      <c r="I160" s="3">
-        <v>10010029</v>
-      </c>
-      <c r="J160" s="3">
-        <v>10</v>
-      </c>
-      <c r="K160" s="2">
-        <v>0</v>
-      </c>
-      <c r="M160" s="13" t="s">
-        <v>51</v>
-      </c>
+      <c r="P160" s="3"/>
     </row>
     <row r="161" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C161" s="3">
-        <v>60000005</v>
+        <v>60000003</v>
       </c>
       <c r="D161" s="3">
-        <v>60000006</v>
+        <v>60000004</v>
       </c>
       <c r="E161" s="3">
         <v>1</v>
@@ -7279,7 +7286,7 @@
         <v>100</v>
       </c>
       <c r="G161" s="13">
-        <v>10012003</v>
+        <v>10012001</v>
       </c>
       <c r="H161" s="3">
         <v>1</v>
@@ -7294,15 +7301,15 @@
         <v>0</v>
       </c>
       <c r="M161" s="13" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
     </row>
     <row r="162" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C162" s="3">
-        <v>60000006</v>
+        <v>60000004</v>
       </c>
       <c r="D162" s="3">
-        <v>60000007</v>
+        <v>60000005</v>
       </c>
       <c r="E162" s="3">
         <v>1</v>
@@ -7311,7 +7318,7 @@
         <v>100</v>
       </c>
       <c r="G162" s="13">
-        <v>10012004</v>
+        <v>10012002</v>
       </c>
       <c r="H162" s="3">
         <v>1</v>
@@ -7326,15 +7333,15 @@
         <v>0</v>
       </c>
       <c r="M162" s="13" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="163" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C163" s="3">
-        <v>60000007</v>
+        <v>60000005</v>
       </c>
       <c r="D163" s="3">
-        <v>60000008</v>
+        <v>60000006</v>
       </c>
       <c r="E163" s="3">
         <v>1</v>
@@ -7343,7 +7350,7 @@
         <v>100</v>
       </c>
       <c r="G163" s="13">
-        <v>10012005</v>
+        <v>10012003</v>
       </c>
       <c r="H163" s="3">
         <v>1</v>
@@ -7358,15 +7365,15 @@
         <v>0</v>
       </c>
       <c r="M163" s="13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="164" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C164" s="3">
-        <v>60000008</v>
+        <v>60000006</v>
       </c>
       <c r="D164" s="3">
-        <v>60000009</v>
+        <v>60000007</v>
       </c>
       <c r="E164" s="3">
         <v>1</v>
@@ -7375,7 +7382,7 @@
         <v>100</v>
       </c>
       <c r="G164" s="13">
-        <v>10012006</v>
+        <v>10012004</v>
       </c>
       <c r="H164" s="3">
         <v>1</v>
@@ -7390,15 +7397,15 @@
         <v>0</v>
       </c>
       <c r="M164" s="13" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="165" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C165" s="3">
-        <v>60000009</v>
+        <v>60000007</v>
       </c>
       <c r="D165" s="3">
-        <v>60000010</v>
+        <v>60000008</v>
       </c>
       <c r="E165" s="3">
         <v>1</v>
@@ -7407,7 +7414,7 @@
         <v>100</v>
       </c>
       <c r="G165" s="13">
-        <v>10012007</v>
+        <v>10012005</v>
       </c>
       <c r="H165" s="3">
         <v>1</v>
@@ -7422,15 +7429,15 @@
         <v>0</v>
       </c>
       <c r="M165" s="13" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="166" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C166" s="3">
-        <v>60000010</v>
+        <v>60000008</v>
       </c>
       <c r="D166" s="3">
-        <v>60000011</v>
+        <v>60000009</v>
       </c>
       <c r="E166" s="3">
         <v>1</v>
@@ -7439,7 +7446,7 @@
         <v>100</v>
       </c>
       <c r="G166" s="13">
-        <v>10012008</v>
+        <v>10012006</v>
       </c>
       <c r="H166" s="3">
         <v>1</v>
@@ -7454,15 +7461,15 @@
         <v>0</v>
       </c>
       <c r="M166" s="13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="167" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C167" s="3">
-        <v>60000011</v>
+        <v>60000009</v>
       </c>
       <c r="D167" s="3">
-        <v>60000012</v>
+        <v>60000010</v>
       </c>
       <c r="E167" s="3">
         <v>1</v>
@@ -7471,7 +7478,7 @@
         <v>100</v>
       </c>
       <c r="G167" s="13">
-        <v>10012009</v>
+        <v>10012007</v>
       </c>
       <c r="H167" s="3">
         <v>1</v>
@@ -7486,15 +7493,15 @@
         <v>0</v>
       </c>
       <c r="M167" s="13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="168" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C168" s="3">
-        <v>60000012</v>
+        <v>60000010</v>
       </c>
       <c r="D168" s="3">
-        <v>60000013</v>
+        <v>60000011</v>
       </c>
       <c r="E168" s="3">
         <v>1</v>
@@ -7503,7 +7510,7 @@
         <v>100</v>
       </c>
       <c r="G168" s="13">
-        <v>10012010</v>
+        <v>10012008</v>
       </c>
       <c r="H168" s="3">
         <v>1</v>
@@ -7518,15 +7525,15 @@
         <v>0</v>
       </c>
       <c r="M168" s="13" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="169" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C169" s="3">
-        <v>60000013</v>
+        <v>60000011</v>
       </c>
       <c r="D169" s="3">
-        <v>60000014</v>
+        <v>60000012</v>
       </c>
       <c r="E169" s="3">
         <v>1</v>
@@ -7535,7 +7542,7 @@
         <v>100</v>
       </c>
       <c r="G169" s="13">
-        <v>10012011</v>
+        <v>10012009</v>
       </c>
       <c r="H169" s="3">
         <v>1</v>
@@ -7550,15 +7557,15 @@
         <v>0</v>
       </c>
       <c r="M169" s="13" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="170" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C170" s="3">
-        <v>60000014</v>
+        <v>60000012</v>
       </c>
       <c r="D170" s="3">
-        <v>60000015</v>
+        <v>60000013</v>
       </c>
       <c r="E170" s="3">
         <v>1</v>
@@ -7567,7 +7574,7 @@
         <v>100</v>
       </c>
       <c r="G170" s="13">
-        <v>10012012</v>
+        <v>10012010</v>
       </c>
       <c r="H170" s="3">
         <v>1</v>
@@ -7582,15 +7589,15 @@
         <v>0</v>
       </c>
       <c r="M170" s="13" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="171" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C171" s="3">
-        <v>60000015</v>
+        <v>60000013</v>
       </c>
       <c r="D171" s="3">
-        <v>60000016</v>
+        <v>60000014</v>
       </c>
       <c r="E171" s="3">
         <v>1</v>
@@ -7599,7 +7606,7 @@
         <v>100</v>
       </c>
       <c r="G171" s="13">
-        <v>10012013</v>
+        <v>10012011</v>
       </c>
       <c r="H171" s="3">
         <v>1</v>
@@ -7614,15 +7621,15 @@
         <v>0</v>
       </c>
       <c r="M171" s="13" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="172" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C172" s="3">
-        <v>60000016</v>
+        <v>60000014</v>
       </c>
       <c r="D172" s="3">
-        <v>60000017</v>
+        <v>60000015</v>
       </c>
       <c r="E172" s="3">
         <v>1</v>
@@ -7631,7 +7638,7 @@
         <v>100</v>
       </c>
       <c r="G172" s="13">
-        <v>10012014</v>
+        <v>10012012</v>
       </c>
       <c r="H172" s="3">
         <v>1</v>
@@ -7646,15 +7653,15 @@
         <v>0</v>
       </c>
       <c r="M172" s="13" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="173" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C173" s="3">
-        <v>60000017</v>
+        <v>60000015</v>
       </c>
       <c r="D173" s="3">
-        <v>60000018</v>
+        <v>60000016</v>
       </c>
       <c r="E173" s="3">
         <v>1</v>
@@ -7663,7 +7670,7 @@
         <v>100</v>
       </c>
       <c r="G173" s="13">
-        <v>10012015</v>
+        <v>10012013</v>
       </c>
       <c r="H173" s="3">
         <v>1</v>
@@ -7678,15 +7685,15 @@
         <v>0</v>
       </c>
       <c r="M173" s="13" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="174" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C174" s="3">
-        <v>60000018</v>
+        <v>60000016</v>
       </c>
       <c r="D174" s="3">
-        <v>60000019</v>
+        <v>60000017</v>
       </c>
       <c r="E174" s="3">
         <v>1</v>
@@ -7695,7 +7702,7 @@
         <v>100</v>
       </c>
       <c r="G174" s="13">
-        <v>10012016</v>
+        <v>10012014</v>
       </c>
       <c r="H174" s="3">
         <v>1</v>
@@ -7710,15 +7717,15 @@
         <v>0</v>
       </c>
       <c r="M174" s="13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="175" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C175" s="3">
-        <v>60000019</v>
+        <v>60000017</v>
       </c>
       <c r="D175" s="3">
-        <v>60000020</v>
+        <v>60000018</v>
       </c>
       <c r="E175" s="3">
         <v>1</v>
@@ -7727,7 +7734,7 @@
         <v>100</v>
       </c>
       <c r="G175" s="13">
-        <v>10012017</v>
+        <v>10012015</v>
       </c>
       <c r="H175" s="3">
         <v>1</v>
@@ -7742,15 +7749,15 @@
         <v>0</v>
       </c>
       <c r="M175" s="13" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="176" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C176" s="3">
-        <v>60000020</v>
+        <v>60000018</v>
       </c>
       <c r="D176" s="3">
-        <v>60000021</v>
+        <v>60000019</v>
       </c>
       <c r="E176" s="3">
         <v>1</v>
@@ -7759,7 +7766,7 @@
         <v>100</v>
       </c>
       <c r="G176" s="13">
-        <v>10012018</v>
+        <v>10012016</v>
       </c>
       <c r="H176" s="3">
         <v>1</v>
@@ -7774,15 +7781,15 @@
         <v>0</v>
       </c>
       <c r="M176" s="13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="177" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C177" s="3">
-        <v>60000021</v>
+        <v>60000019</v>
       </c>
       <c r="D177" s="3">
-        <v>60000022</v>
+        <v>60000020</v>
       </c>
       <c r="E177" s="3">
         <v>1</v>
@@ -7791,7 +7798,7 @@
         <v>100</v>
       </c>
       <c r="G177" s="13">
-        <v>10012019</v>
+        <v>10012017</v>
       </c>
       <c r="H177" s="3">
         <v>1</v>
@@ -7806,15 +7813,15 @@
         <v>0</v>
       </c>
       <c r="M177" s="13" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="178" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C178" s="3">
-        <v>60000022</v>
+        <v>60000020</v>
       </c>
       <c r="D178" s="3">
-        <v>60000023</v>
+        <v>60000021</v>
       </c>
       <c r="E178" s="3">
         <v>1</v>
@@ -7823,7 +7830,7 @@
         <v>100</v>
       </c>
       <c r="G178" s="13">
-        <v>10012020</v>
+        <v>10012018</v>
       </c>
       <c r="H178" s="3">
         <v>1</v>
@@ -7832,21 +7839,21 @@
         <v>10010029</v>
       </c>
       <c r="J178" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K178" s="2">
         <v>0</v>
       </c>
       <c r="M178" s="13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="179" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C179" s="3">
-        <v>60000023</v>
+        <v>60000021</v>
       </c>
       <c r="D179" s="3">
-        <v>60000024</v>
+        <v>60000022</v>
       </c>
       <c r="E179" s="3">
         <v>1</v>
@@ -7855,7 +7862,7 @@
         <v>100</v>
       </c>
       <c r="G179" s="13">
-        <v>10012021</v>
+        <v>10012019</v>
       </c>
       <c r="H179" s="3">
         <v>1</v>
@@ -7864,21 +7871,21 @@
         <v>10010029</v>
       </c>
       <c r="J179" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K179" s="2">
         <v>0</v>
       </c>
       <c r="M179" s="13" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="180" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C180" s="3">
-        <v>60000024</v>
+        <v>60000022</v>
       </c>
       <c r="D180" s="3">
-        <v>60000025</v>
+        <v>60000023</v>
       </c>
       <c r="E180" s="3">
         <v>1</v>
@@ -7887,7 +7894,7 @@
         <v>100</v>
       </c>
       <c r="G180" s="13">
-        <v>10012022</v>
+        <v>10012020</v>
       </c>
       <c r="H180" s="3">
         <v>1</v>
@@ -7902,15 +7909,15 @@
         <v>0</v>
       </c>
       <c r="M180" s="13" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="181" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C181" s="3">
-        <v>60000025</v>
+        <v>60000023</v>
       </c>
       <c r="D181" s="3">
-        <v>60000026</v>
+        <v>60000024</v>
       </c>
       <c r="E181" s="3">
         <v>1</v>
@@ -7919,7 +7926,7 @@
         <v>100</v>
       </c>
       <c r="G181" s="13">
-        <v>10012023</v>
+        <v>10012021</v>
       </c>
       <c r="H181" s="3">
         <v>1</v>
@@ -7934,15 +7941,15 @@
         <v>0</v>
       </c>
       <c r="M181" s="13" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="182" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C182" s="3">
-        <v>60000026</v>
+        <v>60000024</v>
       </c>
       <c r="D182" s="3">
-        <v>60000027</v>
+        <v>60000025</v>
       </c>
       <c r="E182" s="3">
         <v>1</v>
@@ -7951,7 +7958,7 @@
         <v>100</v>
       </c>
       <c r="G182" s="13">
-        <v>10012024</v>
+        <v>10012022</v>
       </c>
       <c r="H182" s="3">
         <v>1</v>
@@ -7966,15 +7973,15 @@
         <v>0</v>
       </c>
       <c r="M182" s="13" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="183" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C183" s="3">
-        <v>60000027</v>
+        <v>60000025</v>
       </c>
       <c r="D183" s="3">
-        <v>60000028</v>
+        <v>60000026</v>
       </c>
       <c r="E183" s="3">
         <v>1</v>
@@ -7983,7 +7990,7 @@
         <v>100</v>
       </c>
       <c r="G183" s="13">
-        <v>10012025</v>
+        <v>10012023</v>
       </c>
       <c r="H183" s="3">
         <v>1</v>
@@ -7998,15 +8005,15 @@
         <v>0</v>
       </c>
       <c r="M183" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="184" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C184" s="3">
-        <v>60000028</v>
+        <v>60000026</v>
       </c>
       <c r="D184" s="3">
-        <v>60000029</v>
+        <v>60000027</v>
       </c>
       <c r="E184" s="3">
         <v>1</v>
@@ -8015,7 +8022,7 @@
         <v>100</v>
       </c>
       <c r="G184" s="13">
-        <v>10012026</v>
+        <v>10012024</v>
       </c>
       <c r="H184" s="3">
         <v>1</v>
@@ -8030,15 +8037,15 @@
         <v>0</v>
       </c>
       <c r="M184" s="13" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="185" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C185" s="3">
-        <v>60000029</v>
+        <v>60000027</v>
       </c>
       <c r="D185" s="3">
-        <v>60000030</v>
+        <v>60000028</v>
       </c>
       <c r="E185" s="3">
         <v>1</v>
@@ -8047,7 +8054,7 @@
         <v>100</v>
       </c>
       <c r="G185" s="13">
-        <v>10012027</v>
+        <v>10012025</v>
       </c>
       <c r="H185" s="3">
         <v>1</v>
@@ -8062,15 +8069,15 @@
         <v>0</v>
       </c>
       <c r="M185" s="13" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="186" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C186" s="3">
-        <v>60000030</v>
+        <v>60000028</v>
       </c>
       <c r="D186" s="3">
-        <v>60000031</v>
+        <v>60000029</v>
       </c>
       <c r="E186" s="3">
         <v>1</v>
@@ -8079,13 +8086,13 @@
         <v>100</v>
       </c>
       <c r="G186" s="13">
-        <v>10013001</v>
+        <v>10012026</v>
       </c>
       <c r="H186" s="3">
         <v>1</v>
       </c>
       <c r="I186" s="3">
-        <v>10010030</v>
+        <v>10010029</v>
       </c>
       <c r="J186" s="3">
         <v>15</v>
@@ -8093,16 +8100,16 @@
       <c r="K186" s="2">
         <v>0</v>
       </c>
-      <c r="M186" s="17" t="s">
-        <v>77</v>
+      <c r="M186" s="13" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="187" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C187" s="3">
-        <v>60000031</v>
+        <v>60000029</v>
       </c>
       <c r="D187" s="3">
-        <v>60000032</v>
+        <v>60000030</v>
       </c>
       <c r="E187" s="3">
         <v>1</v>
@@ -8111,13 +8118,13 @@
         <v>100</v>
       </c>
       <c r="G187" s="13">
-        <v>10013002</v>
+        <v>10012027</v>
       </c>
       <c r="H187" s="3">
         <v>1</v>
       </c>
       <c r="I187" s="3">
-        <v>10010030</v>
+        <v>10010029</v>
       </c>
       <c r="J187" s="3">
         <v>15</v>
@@ -8125,16 +8132,16 @@
       <c r="K187" s="2">
         <v>0</v>
       </c>
-      <c r="M187" s="17" t="s">
-        <v>78</v>
+      <c r="M187" s="13" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="188" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C188" s="3">
-        <v>60000032</v>
+        <v>60000030</v>
       </c>
       <c r="D188" s="3">
-        <v>60000033</v>
+        <v>60000031</v>
       </c>
       <c r="E188" s="3">
         <v>1</v>
@@ -8143,7 +8150,7 @@
         <v>100</v>
       </c>
       <c r="G188" s="13">
-        <v>10013003</v>
+        <v>10013001</v>
       </c>
       <c r="H188" s="3">
         <v>1</v>
@@ -8158,15 +8165,15 @@
         <v>0</v>
       </c>
       <c r="M188" s="17" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="189" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C189" s="3">
-        <v>60000033</v>
+        <v>60000031</v>
       </c>
       <c r="D189" s="3">
-        <v>60000034</v>
+        <v>60000032</v>
       </c>
       <c r="E189" s="3">
         <v>1</v>
@@ -8175,7 +8182,7 @@
         <v>100</v>
       </c>
       <c r="G189" s="13">
-        <v>10013004</v>
+        <v>10013002</v>
       </c>
       <c r="H189" s="3">
         <v>1</v>
@@ -8190,15 +8197,15 @@
         <v>0</v>
       </c>
       <c r="M189" s="17" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="190" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C190" s="3">
-        <v>60000034</v>
+        <v>60000032</v>
       </c>
       <c r="D190" s="3">
-        <v>60000035</v>
+        <v>60000033</v>
       </c>
       <c r="E190" s="3">
         <v>1</v>
@@ -8207,7 +8214,7 @@
         <v>100</v>
       </c>
       <c r="G190" s="13">
-        <v>10013005</v>
+        <v>10013003</v>
       </c>
       <c r="H190" s="3">
         <v>1</v>
@@ -8222,15 +8229,15 @@
         <v>0</v>
       </c>
       <c r="M190" s="17" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="191" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C191" s="3">
-        <v>60000035</v>
+        <v>60000033</v>
       </c>
       <c r="D191" s="3">
-        <v>60000036</v>
+        <v>60000034</v>
       </c>
       <c r="E191" s="3">
         <v>1</v>
@@ -8239,7 +8246,7 @@
         <v>100</v>
       </c>
       <c r="G191" s="13">
-        <v>10013006</v>
+        <v>10013004</v>
       </c>
       <c r="H191" s="3">
         <v>1</v>
@@ -8254,15 +8261,15 @@
         <v>0</v>
       </c>
       <c r="M191" s="17" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="192" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C192" s="3">
-        <v>60000036</v>
+        <v>60000034</v>
       </c>
       <c r="D192" s="3">
-        <v>60000037</v>
+        <v>60000035</v>
       </c>
       <c r="E192" s="3">
         <v>1</v>
@@ -8271,7 +8278,7 @@
         <v>100</v>
       </c>
       <c r="G192" s="13">
-        <v>10013007</v>
+        <v>10013005</v>
       </c>
       <c r="H192" s="3">
         <v>1</v>
@@ -8286,15 +8293,15 @@
         <v>0</v>
       </c>
       <c r="M192" s="17" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="193" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C193" s="3">
-        <v>60000037</v>
+        <v>60000035</v>
       </c>
       <c r="D193" s="3">
-        <v>60000038</v>
+        <v>60000036</v>
       </c>
       <c r="E193" s="3">
         <v>1</v>
@@ -8303,7 +8310,7 @@
         <v>100</v>
       </c>
       <c r="G193" s="13">
-        <v>10013008</v>
+        <v>10013006</v>
       </c>
       <c r="H193" s="3">
         <v>1</v>
@@ -8318,15 +8325,15 @@
         <v>0</v>
       </c>
       <c r="M193" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="194" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C194" s="3">
-        <v>60000038</v>
+        <v>60000036</v>
       </c>
       <c r="D194" s="3">
-        <v>60000039</v>
+        <v>60000037</v>
       </c>
       <c r="E194" s="3">
         <v>1</v>
@@ -8335,7 +8342,7 @@
         <v>100</v>
       </c>
       <c r="G194" s="13">
-        <v>10013009</v>
+        <v>10013007</v>
       </c>
       <c r="H194" s="3">
         <v>1</v>
@@ -8350,15 +8357,15 @@
         <v>0</v>
       </c>
       <c r="M194" s="17" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="195" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C195" s="3">
-        <v>60000039</v>
+        <v>60000037</v>
       </c>
       <c r="D195" s="3">
-        <v>60000040</v>
+        <v>60000038</v>
       </c>
       <c r="E195" s="3">
         <v>1</v>
@@ -8367,7 +8374,7 @@
         <v>100</v>
       </c>
       <c r="G195" s="13">
-        <v>10013010</v>
+        <v>10013008</v>
       </c>
       <c r="H195" s="3">
         <v>1</v>
@@ -8382,15 +8389,15 @@
         <v>0</v>
       </c>
       <c r="M195" s="17" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="196" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C196" s="3">
-        <v>60000040</v>
+        <v>60000038</v>
       </c>
       <c r="D196" s="3">
-        <v>60000041</v>
+        <v>60000039</v>
       </c>
       <c r="E196" s="3">
         <v>1</v>
@@ -8399,7 +8406,7 @@
         <v>100</v>
       </c>
       <c r="G196" s="13">
-        <v>10013011</v>
+        <v>10013009</v>
       </c>
       <c r="H196" s="3">
         <v>1</v>
@@ -8414,15 +8421,15 @@
         <v>0</v>
       </c>
       <c r="M196" s="17" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="197" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C197" s="3">
-        <v>60000041</v>
+        <v>60000039</v>
       </c>
       <c r="D197" s="3">
-        <v>60000042</v>
+        <v>60000040</v>
       </c>
       <c r="E197" s="3">
         <v>1</v>
@@ -8431,7 +8438,7 @@
         <v>100</v>
       </c>
       <c r="G197" s="13">
-        <v>10013012</v>
+        <v>10013010</v>
       </c>
       <c r="H197" s="3">
         <v>1</v>
@@ -8446,15 +8453,15 @@
         <v>0</v>
       </c>
       <c r="M197" s="17" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="198" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C198" s="3">
-        <v>60000042</v>
+        <v>60000040</v>
       </c>
       <c r="D198" s="3">
-        <v>60000043</v>
+        <v>60000041</v>
       </c>
       <c r="E198" s="3">
         <v>1</v>
@@ -8463,7 +8470,7 @@
         <v>100</v>
       </c>
       <c r="G198" s="13">
-        <v>10013013</v>
+        <v>10013011</v>
       </c>
       <c r="H198" s="3">
         <v>1</v>
@@ -8478,15 +8485,15 @@
         <v>0</v>
       </c>
       <c r="M198" s="17" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="199" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C199" s="3">
-        <v>60000043</v>
+        <v>60000041</v>
       </c>
       <c r="D199" s="3">
-        <v>60000044</v>
+        <v>60000042</v>
       </c>
       <c r="E199" s="3">
         <v>1</v>
@@ -8495,7 +8502,7 @@
         <v>100</v>
       </c>
       <c r="G199" s="13">
-        <v>10013014</v>
+        <v>10013012</v>
       </c>
       <c r="H199" s="3">
         <v>1</v>
@@ -8510,15 +8517,15 @@
         <v>0</v>
       </c>
       <c r="M199" s="17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="200" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C200" s="3">
-        <v>60000044</v>
+        <v>60000042</v>
       </c>
       <c r="D200" s="3">
-        <v>60000045</v>
+        <v>60000043</v>
       </c>
       <c r="E200" s="3">
         <v>1</v>
@@ -8527,7 +8534,7 @@
         <v>100</v>
       </c>
       <c r="G200" s="13">
-        <v>10013015</v>
+        <v>10013013</v>
       </c>
       <c r="H200" s="3">
         <v>1</v>
@@ -8542,15 +8549,15 @@
         <v>0</v>
       </c>
       <c r="M200" s="17" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="201" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C201" s="3">
-        <v>60000045</v>
+        <v>60000043</v>
       </c>
       <c r="D201" s="3">
-        <v>60000046</v>
+        <v>60000044</v>
       </c>
       <c r="E201" s="3">
         <v>1</v>
@@ -8559,7 +8566,7 @@
         <v>100</v>
       </c>
       <c r="G201" s="13">
-        <v>10013016</v>
+        <v>10013014</v>
       </c>
       <c r="H201" s="3">
         <v>1</v>
@@ -8574,15 +8581,15 @@
         <v>0</v>
       </c>
       <c r="M201" s="17" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="202" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C202" s="3">
-        <v>60000046</v>
+        <v>60000044</v>
       </c>
       <c r="D202" s="3">
-        <v>60000047</v>
+        <v>60000045</v>
       </c>
       <c r="E202" s="3">
         <v>1</v>
@@ -8591,7 +8598,7 @@
         <v>100</v>
       </c>
       <c r="G202" s="13">
-        <v>10013017</v>
+        <v>10013015</v>
       </c>
       <c r="H202" s="3">
         <v>1</v>
@@ -8606,15 +8613,15 @@
         <v>0</v>
       </c>
       <c r="M202" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="203" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C203" s="3">
-        <v>60000047</v>
+        <v>60000045</v>
       </c>
       <c r="D203" s="3">
-        <v>60000048</v>
+        <v>60000046</v>
       </c>
       <c r="E203" s="3">
         <v>1</v>
@@ -8623,7 +8630,7 @@
         <v>100</v>
       </c>
       <c r="G203" s="13">
-        <v>10013018</v>
+        <v>10013016</v>
       </c>
       <c r="H203" s="3">
         <v>1</v>
@@ -8638,15 +8645,15 @@
         <v>0</v>
       </c>
       <c r="M203" s="17" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="204" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C204" s="3">
-        <v>60000048</v>
+        <v>60000046</v>
       </c>
       <c r="D204" s="3">
-        <v>60000049</v>
+        <v>60000047</v>
       </c>
       <c r="E204" s="3">
         <v>1</v>
@@ -8655,7 +8662,7 @@
         <v>100</v>
       </c>
       <c r="G204" s="13">
-        <v>10013019</v>
+        <v>10013017</v>
       </c>
       <c r="H204" s="3">
         <v>1</v>
@@ -8670,15 +8677,15 @@
         <v>0</v>
       </c>
       <c r="M204" s="17" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="205" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C205" s="3">
-        <v>60000049</v>
+        <v>60000047</v>
       </c>
       <c r="D205" s="3">
-        <v>60000050</v>
+        <v>60000048</v>
       </c>
       <c r="E205" s="3">
         <v>1</v>
@@ -8687,7 +8694,7 @@
         <v>100</v>
       </c>
       <c r="G205" s="13">
-        <v>10013020</v>
+        <v>10013018</v>
       </c>
       <c r="H205" s="3">
         <v>1</v>
@@ -8696,21 +8703,21 @@
         <v>10010030</v>
       </c>
       <c r="J205" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K205" s="2">
         <v>0</v>
       </c>
       <c r="M205" s="17" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="206" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C206" s="3">
-        <v>60000050</v>
+        <v>60000048</v>
       </c>
       <c r="D206" s="3">
-        <v>60000051</v>
+        <v>60000049</v>
       </c>
       <c r="E206" s="3">
         <v>1</v>
@@ -8719,7 +8726,7 @@
         <v>100</v>
       </c>
       <c r="G206" s="13">
-        <v>10013021</v>
+        <v>10013019</v>
       </c>
       <c r="H206" s="3">
         <v>1</v>
@@ -8728,21 +8735,21 @@
         <v>10010030</v>
       </c>
       <c r="J206" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K206" s="2">
         <v>0</v>
       </c>
       <c r="M206" s="17" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="207" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C207" s="3">
-        <v>60000051</v>
+        <v>60000049</v>
       </c>
       <c r="D207" s="3">
-        <v>60000052</v>
+        <v>60000050</v>
       </c>
       <c r="E207" s="3">
         <v>1</v>
@@ -8751,7 +8758,7 @@
         <v>100</v>
       </c>
       <c r="G207" s="13">
-        <v>10013022</v>
+        <v>10013020</v>
       </c>
       <c r="H207" s="3">
         <v>1</v>
@@ -8766,15 +8773,15 @@
         <v>0</v>
       </c>
       <c r="M207" s="17" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="208" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C208" s="3">
-        <v>60000052</v>
+        <v>60000050</v>
       </c>
       <c r="D208" s="3">
-        <v>60000053</v>
+        <v>60000051</v>
       </c>
       <c r="E208" s="3">
         <v>1</v>
@@ -8783,7 +8790,7 @@
         <v>100</v>
       </c>
       <c r="G208" s="13">
-        <v>10013023</v>
+        <v>10013021</v>
       </c>
       <c r="H208" s="3">
         <v>1</v>
@@ -8798,15 +8805,15 @@
         <v>0</v>
       </c>
       <c r="M208" s="17" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="209" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C209" s="3">
-        <v>60000053</v>
+        <v>60000051</v>
       </c>
       <c r="D209" s="3">
-        <v>60000054</v>
+        <v>60000052</v>
       </c>
       <c r="E209" s="3">
         <v>1</v>
@@ -8815,7 +8822,7 @@
         <v>100</v>
       </c>
       <c r="G209" s="13">
-        <v>10013024</v>
+        <v>10013022</v>
       </c>
       <c r="H209" s="3">
         <v>1</v>
@@ -8830,15 +8837,15 @@
         <v>0</v>
       </c>
       <c r="M209" s="17" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="210" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C210" s="3">
-        <v>60000054</v>
+        <v>60000052</v>
       </c>
       <c r="D210" s="3">
-        <v>60000055</v>
+        <v>60000053</v>
       </c>
       <c r="E210" s="3">
         <v>1</v>
@@ -8847,7 +8854,7 @@
         <v>100</v>
       </c>
       <c r="G210" s="13">
-        <v>10013025</v>
+        <v>10013023</v>
       </c>
       <c r="H210" s="3">
         <v>1</v>
@@ -8862,15 +8869,15 @@
         <v>0</v>
       </c>
       <c r="M210" s="17" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="211" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C211" s="3">
-        <v>60000055</v>
+        <v>60000053</v>
       </c>
       <c r="D211" s="3">
-        <v>60000056</v>
+        <v>60000054</v>
       </c>
       <c r="E211" s="3">
         <v>1</v>
@@ -8879,7 +8886,7 @@
         <v>100</v>
       </c>
       <c r="G211" s="13">
-        <v>10013026</v>
+        <v>10013024</v>
       </c>
       <c r="H211" s="3">
         <v>1</v>
@@ -8894,15 +8901,15 @@
         <v>0</v>
       </c>
       <c r="M211" s="17" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="212" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C212" s="3">
-        <v>60000056</v>
+        <v>60000054</v>
       </c>
       <c r="D212" s="3">
-        <v>0</v>
+        <v>60000055</v>
       </c>
       <c r="E212" s="3">
         <v>1</v>
@@ -8911,7 +8918,7 @@
         <v>100</v>
       </c>
       <c r="G212" s="13">
-        <v>10013027</v>
+        <v>10013025</v>
       </c>
       <c r="H212" s="3">
         <v>1</v>
@@ -8926,15 +8933,15 @@
         <v>0</v>
       </c>
       <c r="M212" s="17" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="213" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C213" s="3">
-        <v>70000001</v>
+        <v>60000055</v>
       </c>
       <c r="D213" s="3">
-        <v>70000002</v>
+        <v>60000056</v>
       </c>
       <c r="E213" s="3">
         <v>1</v>
@@ -8942,31 +8949,31 @@
       <c r="F213" s="3">
         <v>100</v>
       </c>
-      <c r="G213" s="9">
-        <v>10010093</v>
+      <c r="G213" s="13">
+        <v>10013026</v>
       </c>
       <c r="H213" s="3">
         <v>1</v>
       </c>
-      <c r="I213" s="8">
-        <v>10000159</v>
-      </c>
-      <c r="J213" s="8">
-        <v>30</v>
+      <c r="I213" s="3">
+        <v>10010030</v>
+      </c>
+      <c r="J213" s="3">
+        <v>20</v>
       </c>
       <c r="K213" s="2">
         <v>0</v>
       </c>
-      <c r="M213" s="12" t="s">
-        <v>49</v>
+      <c r="M213" s="17" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="214" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C214" s="3">
-        <v>70000002</v>
+        <v>60000056</v>
       </c>
       <c r="D214" s="3">
-        <v>70000003</v>
+        <v>0</v>
       </c>
       <c r="E214" s="3">
         <v>1</v>
@@ -8974,31 +8981,31 @@
       <c r="F214" s="3">
         <v>100</v>
       </c>
-      <c r="G214" s="9">
-        <v>10000162</v>
+      <c r="G214" s="13">
+        <v>10013027</v>
       </c>
       <c r="H214" s="3">
         <v>1</v>
       </c>
-      <c r="I214" s="8">
-        <v>10000159</v>
-      </c>
-      <c r="J214" s="8">
+      <c r="I214" s="3">
+        <v>10010030</v>
+      </c>
+      <c r="J214" s="3">
         <v>20</v>
       </c>
       <c r="K214" s="2">
         <v>0</v>
       </c>
-      <c r="M214" s="11" t="s">
-        <v>104</v>
+      <c r="M214" s="17" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="215" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C215" s="3">
-        <v>70000003</v>
+        <v>70000001</v>
       </c>
       <c r="D215" s="3">
-        <v>70000004</v>
+        <v>70000002</v>
       </c>
       <c r="E215" s="3">
         <v>1</v>
@@ -9007,7 +9014,7 @@
         <v>100</v>
       </c>
       <c r="G215" s="9">
-        <v>10010045</v>
+        <v>10010093</v>
       </c>
       <c r="H215" s="3">
         <v>1</v>
@@ -9021,16 +9028,16 @@
       <c r="K215" s="2">
         <v>0</v>
       </c>
-      <c r="M215" s="11" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="216" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M215" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="216" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C216" s="3">
-        <v>70000004</v>
+        <v>70000002</v>
       </c>
       <c r="D216" s="3">
-        <v>70000005</v>
+        <v>70000003</v>
       </c>
       <c r="E216" s="3">
         <v>1</v>
@@ -9039,7 +9046,7 @@
         <v>100</v>
       </c>
       <c r="G216" s="9">
-        <v>10000158</v>
+        <v>10000162</v>
       </c>
       <c r="H216" s="3">
         <v>1</v>
@@ -9053,16 +9060,16 @@
       <c r="K216" s="2">
         <v>0</v>
       </c>
-      <c r="M216" s="9" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="217" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M216" s="11" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="217" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C217" s="3">
-        <v>70000005</v>
+        <v>70000003</v>
       </c>
       <c r="D217" s="3">
-        <v>70000006</v>
+        <v>70000004</v>
       </c>
       <c r="E217" s="3">
         <v>1</v>
@@ -9071,7 +9078,7 @@
         <v>100</v>
       </c>
       <c r="G217" s="9">
-        <v>10010083</v>
+        <v>10010045</v>
       </c>
       <c r="H217" s="3">
         <v>1</v>
@@ -9080,21 +9087,21 @@
         <v>10000159</v>
       </c>
       <c r="J217" s="8">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="K217" s="2">
         <v>0</v>
       </c>
-      <c r="M217" s="16" t="s">
-        <v>107</v>
+      <c r="M217" s="11" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="218" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C218" s="3">
-        <v>70000006</v>
+        <v>70000004</v>
       </c>
       <c r="D218" s="3">
-        <v>70000007</v>
+        <v>70000005</v>
       </c>
       <c r="E218" s="3">
         <v>1</v>
@@ -9103,7 +9110,7 @@
         <v>100</v>
       </c>
       <c r="G218" s="9">
-        <v>10000143</v>
+        <v>10000158</v>
       </c>
       <c r="H218" s="3">
         <v>1</v>
@@ -9112,21 +9119,21 @@
         <v>10000159</v>
       </c>
       <c r="J218" s="8">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K218" s="2">
         <v>0</v>
       </c>
-      <c r="M218" s="16" t="s">
-        <v>47</v>
+      <c r="M218" s="9" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="219" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C219" s="3">
-        <v>70000007</v>
+        <v>70000005</v>
       </c>
       <c r="D219" s="3">
-        <v>70000008</v>
+        <v>70000006</v>
       </c>
       <c r="E219" s="3">
         <v>1</v>
@@ -9135,7 +9142,7 @@
         <v>100</v>
       </c>
       <c r="G219" s="9">
-        <v>10000152</v>
+        <v>10010083</v>
       </c>
       <c r="H219" s="3">
         <v>1</v>
@@ -9144,21 +9151,21 @@
         <v>10000159</v>
       </c>
       <c r="J219" s="8">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K219" s="2">
         <v>0</v>
       </c>
-      <c r="M219" s="11" t="s">
-        <v>38</v>
+      <c r="M219" s="16" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="220" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C220" s="3">
-        <v>70000008</v>
+        <v>70000006</v>
       </c>
       <c r="D220" s="3">
-        <v>70000009</v>
+        <v>70000007</v>
       </c>
       <c r="E220" s="3">
         <v>1</v>
@@ -9167,7 +9174,7 @@
         <v>100</v>
       </c>
       <c r="G220" s="9">
-        <v>10000157</v>
+        <v>10000143</v>
       </c>
       <c r="H220" s="3">
         <v>1</v>
@@ -9176,21 +9183,21 @@
         <v>10000159</v>
       </c>
       <c r="J220" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K220" s="2">
         <v>0</v>
       </c>
-      <c r="M220" s="11" t="s">
-        <v>39</v>
+      <c r="M220" s="16" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="221" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C221" s="3">
-        <v>70000009</v>
+        <v>70000007</v>
       </c>
       <c r="D221" s="3">
-        <v>70000010</v>
+        <v>70000008</v>
       </c>
       <c r="E221" s="3">
         <v>1</v>
@@ -9199,7 +9206,7 @@
         <v>100</v>
       </c>
       <c r="G221" s="9">
-        <v>10010029</v>
+        <v>10000152</v>
       </c>
       <c r="H221" s="3">
         <v>1</v>
@@ -9208,21 +9215,21 @@
         <v>10000159</v>
       </c>
       <c r="J221" s="8">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K221" s="2">
         <v>0</v>
       </c>
       <c r="M221" s="11" t="s">
-        <v>108</v>
+        <v>38</v>
       </c>
     </row>
     <row r="222" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C222" s="3">
-        <v>70000010</v>
+        <v>70000008</v>
       </c>
       <c r="D222" s="3">
-        <v>70000011</v>
+        <v>70000009</v>
       </c>
       <c r="E222" s="3">
         <v>1</v>
@@ -9231,7 +9238,7 @@
         <v>100</v>
       </c>
       <c r="G222" s="9">
-        <v>10010086</v>
+        <v>10000157</v>
       </c>
       <c r="H222" s="3">
         <v>1</v>
@@ -9245,16 +9252,16 @@
       <c r="K222" s="2">
         <v>0</v>
       </c>
-      <c r="M222" s="12" t="s">
-        <v>27</v>
+      <c r="M222" s="11" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="223" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C223" s="3">
-        <v>70000011</v>
+        <v>70000009</v>
       </c>
       <c r="D223" s="3">
-        <v>70000012</v>
+        <v>70000010</v>
       </c>
       <c r="E223" s="3">
         <v>1</v>
@@ -9262,8 +9269,8 @@
       <c r="F223" s="3">
         <v>100</v>
       </c>
-      <c r="G223" s="18">
-        <v>10010101</v>
+      <c r="G223" s="9">
+        <v>10010029</v>
       </c>
       <c r="H223" s="3">
         <v>1</v>
@@ -9277,16 +9284,16 @@
       <c r="K223" s="2">
         <v>0</v>
       </c>
-      <c r="M223" s="8" t="s">
-        <v>109</v>
+      <c r="M223" s="11" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="224" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C224" s="3">
-        <v>70000012</v>
+        <v>70000010</v>
       </c>
       <c r="D224" s="3">
-        <v>70000013</v>
+        <v>70000011</v>
       </c>
       <c r="E224" s="3">
         <v>1</v>
@@ -9294,8 +9301,8 @@
       <c r="F224" s="3">
         <v>100</v>
       </c>
-      <c r="G224" s="18">
-        <v>10010102</v>
+      <c r="G224" s="9">
+        <v>10010086</v>
       </c>
       <c r="H224" s="3">
         <v>1</v>
@@ -9309,16 +9316,16 @@
       <c r="K224" s="2">
         <v>0</v>
       </c>
-      <c r="M224" s="3" t="s">
-        <v>110</v>
+      <c r="M224" s="12" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="225" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C225" s="3">
-        <v>70000013</v>
+        <v>70000011</v>
       </c>
       <c r="D225" s="3">
-        <v>0</v>
+        <v>70000012</v>
       </c>
       <c r="E225" s="3">
         <v>1</v>
@@ -9327,7 +9334,7 @@
         <v>100</v>
       </c>
       <c r="G225" s="18">
-        <v>10010103</v>
+        <v>10010101</v>
       </c>
       <c r="H225" s="3">
         <v>1</v>
@@ -9336,21 +9343,21 @@
         <v>10000159</v>
       </c>
       <c r="J225" s="8">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="K225" s="2">
         <v>0</v>
       </c>
-      <c r="M225" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="226" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M225" s="8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="226" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C226" s="3">
-        <v>80000001</v>
+        <v>70000012</v>
       </c>
       <c r="D226" s="3">
-        <v>80000002</v>
+        <v>70000013</v>
       </c>
       <c r="E226" s="3">
         <v>1</v>
@@ -9358,31 +9365,31 @@
       <c r="F226" s="3">
         <v>100</v>
       </c>
-      <c r="G226" s="9">
-        <v>10010083</v>
+      <c r="G226" s="18">
+        <v>10010102</v>
       </c>
       <c r="H226" s="3">
         <v>1</v>
       </c>
       <c r="I226" s="8">
-        <v>10000163</v>
+        <v>10000159</v>
       </c>
       <c r="J226" s="8">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K226" s="2">
         <v>0</v>
       </c>
       <c r="M226" s="3" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="227" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="227" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C227" s="3">
-        <v>80000002</v>
+        <v>70000013</v>
       </c>
       <c r="D227" s="3">
-        <v>80000003</v>
+        <v>0</v>
       </c>
       <c r="E227" s="3">
         <v>1</v>
@@ -9390,14 +9397,14 @@
       <c r="F227" s="3">
         <v>100</v>
       </c>
-      <c r="G227" s="9">
-        <v>10010086</v>
+      <c r="G227" s="18">
+        <v>10010103</v>
       </c>
       <c r="H227" s="3">
         <v>1</v>
       </c>
       <c r="I227" s="8">
-        <v>10000163</v>
+        <v>10000159</v>
       </c>
       <c r="J227" s="8">
         <v>20</v>
@@ -9406,15 +9413,15 @@
         <v>0</v>
       </c>
       <c r="M227" s="3" t="s">
-        <v>27</v>
+        <v>111</v>
       </c>
     </row>
     <row r="228" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C228" s="3">
-        <v>80000003</v>
+        <v>80000001</v>
       </c>
       <c r="D228" s="3">
-        <v>80000004</v>
+        <v>80000002</v>
       </c>
       <c r="E228" s="3">
         <v>1</v>
@@ -9423,7 +9430,7 @@
         <v>100</v>
       </c>
       <c r="G228" s="9">
-        <v>10010096</v>
+        <v>10010083</v>
       </c>
       <c r="H228" s="3">
         <v>1</v>
@@ -9432,21 +9439,21 @@
         <v>10000163</v>
       </c>
       <c r="J228" s="8">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="K228" s="2">
         <v>0</v>
       </c>
       <c r="M228" s="3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="229" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="229" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C229" s="3">
-        <v>80000004</v>
+        <v>80000002</v>
       </c>
       <c r="D229" s="3">
-        <v>80000005</v>
+        <v>80000003</v>
       </c>
       <c r="E229" s="3">
         <v>1</v>
@@ -9455,7 +9462,7 @@
         <v>100</v>
       </c>
       <c r="G229" s="9">
-        <v>10000139</v>
+        <v>10010086</v>
       </c>
       <c r="H229" s="3">
         <v>1</v>
@@ -9470,15 +9477,15 @@
         <v>0</v>
       </c>
       <c r="M229" s="3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="230" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="230" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C230" s="3">
-        <v>80000005</v>
+        <v>80000003</v>
       </c>
       <c r="D230" s="3">
-        <v>80000006</v>
+        <v>80000004</v>
       </c>
       <c r="E230" s="3">
         <v>1</v>
@@ -9487,7 +9494,7 @@
         <v>100</v>
       </c>
       <c r="G230" s="9">
-        <v>10000143</v>
+        <v>10010096</v>
       </c>
       <c r="H230" s="3">
         <v>1</v>
@@ -9496,21 +9503,21 @@
         <v>10000163</v>
       </c>
       <c r="J230" s="8">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="K230" s="2">
         <v>0</v>
       </c>
       <c r="M230" s="3" t="s">
-        <v>47</v>
+        <v>112</v>
       </c>
     </row>
     <row r="231" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C231" s="3">
-        <v>80000006</v>
+        <v>80000004</v>
       </c>
       <c r="D231" s="3">
-        <v>80000007</v>
+        <v>80000005</v>
       </c>
       <c r="E231" s="3">
         <v>1</v>
@@ -9519,7 +9526,7 @@
         <v>100</v>
       </c>
       <c r="G231" s="9">
-        <v>10000152</v>
+        <v>10000139</v>
       </c>
       <c r="H231" s="3">
         <v>1</v>
@@ -9528,21 +9535,21 @@
         <v>10000163</v>
       </c>
       <c r="J231" s="8">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="K231" s="2">
         <v>0</v>
       </c>
       <c r="M231" s="3" t="s">
-        <v>38</v>
+        <v>113</v>
       </c>
     </row>
     <row r="232" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C232" s="3">
-        <v>80000007</v>
+        <v>80000005</v>
       </c>
       <c r="D232" s="3">
-        <v>80000008</v>
+        <v>80000006</v>
       </c>
       <c r="E232" s="3">
         <v>1</v>
@@ -9551,7 +9558,7 @@
         <v>100</v>
       </c>
       <c r="G232" s="9">
-        <v>10000155</v>
+        <v>10000143</v>
       </c>
       <c r="H232" s="3">
         <v>1</v>
@@ -9560,21 +9567,21 @@
         <v>10000163</v>
       </c>
       <c r="J232" s="8">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K232" s="2">
         <v>0</v>
       </c>
       <c r="M232" s="3" t="s">
-        <v>114</v>
+        <v>47</v>
       </c>
     </row>
     <row r="233" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C233" s="3">
-        <v>80000008</v>
+        <v>80000006</v>
       </c>
       <c r="D233" s="3">
-        <v>80000009</v>
+        <v>80000007</v>
       </c>
       <c r="E233" s="3">
         <v>1</v>
@@ -9583,7 +9590,7 @@
         <v>100</v>
       </c>
       <c r="G233" s="9">
-        <v>10000158</v>
+        <v>10000152</v>
       </c>
       <c r="H233" s="3">
         <v>1</v>
@@ -9592,21 +9599,21 @@
         <v>10000163</v>
       </c>
       <c r="J233" s="8">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="K233" s="2">
         <v>0</v>
       </c>
       <c r="M233" s="3" t="s">
-        <v>106</v>
+        <v>38</v>
       </c>
     </row>
     <row r="234" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C234" s="3">
-        <v>80000009</v>
+        <v>80000007</v>
       </c>
       <c r="D234" s="3">
-        <v>0</v>
+        <v>80000008</v>
       </c>
       <c r="E234" s="3">
         <v>1</v>
@@ -9615,7 +9622,7 @@
         <v>100</v>
       </c>
       <c r="G234" s="9">
-        <v>10010093</v>
+        <v>10000155</v>
       </c>
       <c r="H234" s="3">
         <v>1</v>
@@ -9624,85 +9631,85 @@
         <v>10000163</v>
       </c>
       <c r="J234" s="8">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="K234" s="2">
         <v>0</v>
       </c>
       <c r="M234" s="3" t="s">
-        <v>49</v>
+        <v>114</v>
       </c>
     </row>
     <row r="235" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C235" s="3">
-        <v>90000001</v>
+        <v>80000008</v>
       </c>
       <c r="D235" s="3">
-        <v>90000002</v>
-      </c>
-      <c r="E235" s="2">
+        <v>80000009</v>
+      </c>
+      <c r="E235" s="3">
         <v>1</v>
       </c>
       <c r="F235" s="3">
         <v>100</v>
       </c>
-      <c r="G235" s="3">
-        <v>10000144</v>
+      <c r="G235" s="9">
+        <v>10000158</v>
       </c>
       <c r="H235" s="3">
         <v>1</v>
       </c>
-      <c r="I235" s="9">
-        <v>10000148</v>
+      <c r="I235" s="8">
+        <v>10000163</v>
       </c>
       <c r="J235" s="8">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K235" s="2">
         <v>0</v>
       </c>
-      <c r="L235" s="2"/>
-      <c r="M235" s="7" t="s">
-        <v>115</v>
+      <c r="M235" s="3" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="236" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C236" s="3">
-        <v>90000002</v>
+        <v>80000009</v>
       </c>
       <c r="D236" s="3">
-        <v>90000003</v>
-      </c>
-      <c r="E236" s="2">
+        <v>0</v>
+      </c>
+      <c r="E236" s="3">
         <v>1</v>
       </c>
       <c r="F236" s="3">
         <v>100</v>
       </c>
-      <c r="G236" s="3">
-        <v>10000145</v>
+      <c r="G236" s="9">
+        <v>10010093</v>
       </c>
       <c r="H236" s="3">
         <v>1</v>
       </c>
-      <c r="I236" s="9">
-        <v>10000148</v>
+      <c r="I236" s="8">
+        <v>10000163</v>
       </c>
       <c r="J236" s="8">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="K236" s="2">
         <v>0</v>
       </c>
-      <c r="L236" s="2"/>
-      <c r="M236" s="2"/>
+      <c r="M236" s="3" t="s">
+        <v>49</v>
+      </c>
     </row>
     <row r="237" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C237" s="3">
-        <v>90000003</v>
+        <v>90000001</v>
       </c>
       <c r="D237" s="3">
-        <v>90000004</v>
+        <v>90000002</v>
       </c>
       <c r="E237" s="2">
         <v>1</v>
@@ -9711,7 +9718,7 @@
         <v>100</v>
       </c>
       <c r="G237" s="3">
-        <v>10000146</v>
+        <v>10000144</v>
       </c>
       <c r="H237" s="3">
         <v>1</v>
@@ -9726,14 +9733,16 @@
         <v>0</v>
       </c>
       <c r="L237" s="2"/>
-      <c r="M237" s="2"/>
+      <c r="M237" s="7" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="238" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C238" s="3">
-        <v>90000004</v>
+        <v>90000002</v>
       </c>
       <c r="D238" s="3">
-        <v>90000005</v>
+        <v>90000003</v>
       </c>
       <c r="E238" s="2">
         <v>1</v>
@@ -9742,7 +9751,7 @@
         <v>100</v>
       </c>
       <c r="G238" s="3">
-        <v>10000147</v>
+        <v>10000145</v>
       </c>
       <c r="H238" s="3">
         <v>1</v>
@@ -9761,10 +9770,10 @@
     </row>
     <row r="239" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C239" s="3">
-        <v>90000005</v>
+        <v>90000003</v>
       </c>
       <c r="D239" s="3">
-        <v>90000006</v>
+        <v>90000004</v>
       </c>
       <c r="E239" s="2">
         <v>1</v>
@@ -9773,7 +9782,7 @@
         <v>100</v>
       </c>
       <c r="G239" s="3">
-        <v>10010033</v>
+        <v>10000146</v>
       </c>
       <c r="H239" s="3">
         <v>1</v>
@@ -9781,8 +9790,8 @@
       <c r="I239" s="9">
         <v>10000148</v>
       </c>
-      <c r="J239" s="10">
-        <v>50</v>
+      <c r="J239" s="8">
+        <v>10</v>
       </c>
       <c r="K239" s="2">
         <v>0</v>
@@ -9792,10 +9801,10 @@
     </row>
     <row r="240" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C240" s="3">
-        <v>90000006</v>
+        <v>90000004</v>
       </c>
       <c r="D240" s="3">
-        <v>90000007</v>
+        <v>90000005</v>
       </c>
       <c r="E240" s="2">
         <v>1</v>
@@ -9804,7 +9813,7 @@
         <v>100</v>
       </c>
       <c r="G240" s="3">
-        <v>10010083</v>
+        <v>10000147</v>
       </c>
       <c r="H240" s="3">
         <v>1</v>
@@ -9812,8 +9821,8 @@
       <c r="I240" s="9">
         <v>10000148</v>
       </c>
-      <c r="J240" s="10">
-        <v>5</v>
+      <c r="J240" s="8">
+        <v>10</v>
       </c>
       <c r="K240" s="2">
         <v>0</v>
@@ -9823,10 +9832,10 @@
     </row>
     <row r="241" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C241" s="3">
-        <v>90000007</v>
+        <v>90000005</v>
       </c>
       <c r="D241" s="3">
-        <v>90000008</v>
+        <v>90000006</v>
       </c>
       <c r="E241" s="2">
         <v>1</v>
@@ -9835,7 +9844,7 @@
         <v>100</v>
       </c>
       <c r="G241" s="3">
-        <v>10010098</v>
+        <v>10010033</v>
       </c>
       <c r="H241" s="3">
         <v>1</v>
@@ -9844,7 +9853,7 @@
         <v>10000148</v>
       </c>
       <c r="J241" s="10">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="K241" s="2">
         <v>0</v>
@@ -9854,10 +9863,10 @@
     </row>
     <row r="242" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C242" s="3">
-        <v>90000008</v>
+        <v>90000006</v>
       </c>
       <c r="D242" s="3">
-        <v>90000009</v>
+        <v>90000007</v>
       </c>
       <c r="E242" s="2">
         <v>1</v>
@@ -9866,7 +9875,7 @@
         <v>100</v>
       </c>
       <c r="G242" s="3">
-        <v>10010085</v>
+        <v>10010083</v>
       </c>
       <c r="H242" s="3">
         <v>1</v>
@@ -9875,7 +9884,7 @@
         <v>10000148</v>
       </c>
       <c r="J242" s="10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K242" s="2">
         <v>0</v>
@@ -9885,10 +9894,10 @@
     </row>
     <row r="243" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C243" s="3">
-        <v>90000009</v>
+        <v>90000007</v>
       </c>
       <c r="D243" s="3">
-        <v>90000010</v>
+        <v>90000008</v>
       </c>
       <c r="E243" s="2">
         <v>1</v>
@@ -9897,7 +9906,7 @@
         <v>100</v>
       </c>
       <c r="G243" s="3">
-        <v>10000131</v>
+        <v>10010098</v>
       </c>
       <c r="H243" s="3">
         <v>1</v>
@@ -9906,19 +9915,20 @@
         <v>10000148</v>
       </c>
       <c r="J243" s="10">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K243" s="2">
         <v>0</v>
       </c>
       <c r="L243" s="2"/>
+      <c r="M243" s="2"/>
     </row>
     <row r="244" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C244" s="3">
-        <v>90000010</v>
+        <v>90000008</v>
       </c>
       <c r="D244" s="3">
-        <v>0</v>
+        <v>90000009</v>
       </c>
       <c r="E244" s="2">
         <v>1</v>
@@ -9927,7 +9937,7 @@
         <v>100</v>
       </c>
       <c r="G244" s="3">
-        <v>10000132</v>
+        <v>10010085</v>
       </c>
       <c r="H244" s="3">
         <v>1</v>
@@ -9936,19 +9946,20 @@
         <v>10000148</v>
       </c>
       <c r="J244" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K244" s="2">
         <v>0</v>
       </c>
       <c r="L244" s="2"/>
+      <c r="M244" s="2"/>
     </row>
     <row r="245" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C245" s="3">
-        <v>91000001</v>
+        <v>90000009</v>
       </c>
       <c r="D245" s="3">
-        <v>91000002</v>
+        <v>90000010</v>
       </c>
       <c r="E245" s="2">
         <v>1</v>
@@ -9957,30 +9968,28 @@
         <v>100</v>
       </c>
       <c r="G245" s="3">
-        <v>10010086</v>
+        <v>10000131</v>
       </c>
       <c r="H245" s="3">
         <v>1</v>
       </c>
-      <c r="I245" s="19">
-        <v>36</v>
-      </c>
-      <c r="J245" s="20">
-        <v>8</v>
+      <c r="I245" s="9">
+        <v>10000148</v>
+      </c>
+      <c r="J245" s="10">
+        <v>3</v>
       </c>
       <c r="K245" s="2">
         <v>0</v>
       </c>
-      <c r="M245" s="3" t="s">
-        <v>27</v>
-      </c>
+      <c r="L245" s="2"/>
     </row>
     <row r="246" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C246" s="3">
-        <v>91000002</v>
+        <v>90000010</v>
       </c>
       <c r="D246" s="3">
-        <v>91000003</v>
+        <v>0</v>
       </c>
       <c r="E246" s="2">
         <v>1</v>
@@ -9989,30 +9998,28 @@
         <v>100</v>
       </c>
       <c r="G246" s="3">
-        <v>10010096</v>
+        <v>10000132</v>
       </c>
       <c r="H246" s="3">
         <v>1</v>
       </c>
-      <c r="I246" s="19">
-        <v>36</v>
-      </c>
-      <c r="J246" s="20">
-        <v>20</v>
+      <c r="I246" s="9">
+        <v>10000148</v>
+      </c>
+      <c r="J246" s="10">
+        <v>3</v>
       </c>
       <c r="K246" s="2">
         <v>0</v>
       </c>
-      <c r="M246" s="3" t="s">
-        <v>112</v>
-      </c>
+      <c r="L246" s="2"/>
     </row>
     <row r="247" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C247" s="3">
-        <v>91000003</v>
+        <v>91000001</v>
       </c>
       <c r="D247" s="3">
-        <v>91000004</v>
+        <v>91000002</v>
       </c>
       <c r="E247" s="2">
         <v>1</v>
@@ -10021,7 +10028,7 @@
         <v>100</v>
       </c>
       <c r="G247" s="3">
-        <v>10010074</v>
+        <v>10010086</v>
       </c>
       <c r="H247" s="3">
         <v>1</v>
@@ -10036,15 +10043,15 @@
         <v>0</v>
       </c>
       <c r="M247" s="3" t="s">
-        <v>116</v>
+        <v>27</v>
       </c>
     </row>
     <row r="248" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C248" s="3">
-        <v>91000004</v>
+        <v>91000002</v>
       </c>
       <c r="D248" s="3">
-        <v>91000005</v>
+        <v>91000003</v>
       </c>
       <c r="E248" s="2">
         <v>1</v>
@@ -10053,7 +10060,7 @@
         <v>100</v>
       </c>
       <c r="G248" s="3">
-        <v>10010075</v>
+        <v>10010096</v>
       </c>
       <c r="H248" s="3">
         <v>1</v>
@@ -10068,15 +10075,15 @@
         <v>0</v>
       </c>
       <c r="M248" s="3" t="s">
-        <v>117</v>
+        <v>112</v>
       </c>
     </row>
     <row r="249" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C249" s="3">
-        <v>91000005</v>
+        <v>91000003</v>
       </c>
       <c r="D249" s="3">
-        <v>91000006</v>
+        <v>91000004</v>
       </c>
       <c r="E249" s="2">
         <v>1</v>
@@ -10084,8 +10091,8 @@
       <c r="F249" s="3">
         <v>100</v>
       </c>
-      <c r="G249" s="2">
-        <v>10010083</v>
+      <c r="G249" s="3">
+        <v>10010074</v>
       </c>
       <c r="H249" s="3">
         <v>1</v>
@@ -10094,21 +10101,21 @@
         <v>36</v>
       </c>
       <c r="J249" s="20">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K249" s="2">
         <v>0</v>
       </c>
-      <c r="M249" s="15" t="s">
-        <v>119</v>
+      <c r="M249" s="3" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="250" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C250" s="3">
-        <v>91000006</v>
+        <v>91000004</v>
       </c>
       <c r="D250" s="3">
-        <v>91000007</v>
+        <v>91000005</v>
       </c>
       <c r="E250" s="2">
         <v>1</v>
@@ -10116,8 +10123,8 @@
       <c r="F250" s="3">
         <v>100</v>
       </c>
-      <c r="G250" s="2">
-        <v>10010098</v>
+      <c r="G250" s="3">
+        <v>10010075</v>
       </c>
       <c r="H250" s="3">
         <v>1</v>
@@ -10126,21 +10133,21 @@
         <v>36</v>
       </c>
       <c r="J250" s="20">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K250" s="2">
         <v>0</v>
       </c>
-      <c r="M250" s="15" t="s">
-        <v>118</v>
+      <c r="M250" s="3" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="251" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C251" s="3">
-        <v>91000007</v>
+        <v>91000005</v>
       </c>
       <c r="D251" s="3">
-        <v>0</v>
+        <v>91000006</v>
       </c>
       <c r="E251" s="2">
         <v>1</v>
@@ -10148,8 +10155,8 @@
       <c r="F251" s="3">
         <v>100</v>
       </c>
-      <c r="G251" s="9">
-        <v>10010040</v>
+      <c r="G251" s="2">
+        <v>10010083</v>
       </c>
       <c r="H251" s="3">
         <v>1</v>
@@ -10158,21 +10165,21 @@
         <v>36</v>
       </c>
       <c r="J251" s="20">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="K251" s="2">
-        <v>1</v>
-      </c>
-      <c r="M251" s="9" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="252" spans="3:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="M251" s="15" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="252" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C252" s="3">
-        <v>92000001</v>
+        <v>91000006</v>
       </c>
       <c r="D252" s="3">
-        <v>92000002</v>
+        <v>91000007</v>
       </c>
       <c r="E252" s="2">
         <v>1</v>
@@ -10180,65 +10187,64 @@
       <c r="F252" s="3">
         <v>100</v>
       </c>
-      <c r="G252" s="3">
-        <v>10060100</v>
+      <c r="G252" s="2">
+        <v>10010098</v>
       </c>
       <c r="H252" s="3">
         <v>1</v>
       </c>
-      <c r="I252" s="9">
-        <v>10000136</v>
-      </c>
-      <c r="J252" s="3">
-        <v>50</v>
+      <c r="I252" s="19">
+        <v>36</v>
+      </c>
+      <c r="J252" s="20">
+        <v>1</v>
       </c>
       <c r="K252" s="2">
         <v>0</v>
       </c>
-      <c r="M252" s="22" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q252" s="7"/>
+      <c r="M252" s="15" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="253" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C253" s="3">
+        <v>91000007</v>
+      </c>
+      <c r="D253" s="3">
+        <v>0</v>
+      </c>
+      <c r="E253" s="2">
+        <v>1</v>
+      </c>
+      <c r="F253" s="3">
+        <v>100</v>
+      </c>
+      <c r="G253" s="9">
+        <v>10010040</v>
+      </c>
+      <c r="H253" s="3">
+        <v>1</v>
+      </c>
+      <c r="I253" s="19">
+        <v>36</v>
+      </c>
+      <c r="J253" s="20">
+        <v>100</v>
+      </c>
+      <c r="K253" s="2">
+        <v>1</v>
+      </c>
+      <c r="M253" s="9" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="254" spans="3:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C254" s="3">
+        <v>92000001</v>
+      </c>
+      <c r="D254" s="3">
         <v>92000002</v>
       </c>
-      <c r="D253" s="3">
-        <v>92000003</v>
-      </c>
-      <c r="E253" s="2">
-        <v>1</v>
-      </c>
-      <c r="F253" s="3">
-        <v>100</v>
-      </c>
-      <c r="G253" s="3">
-        <v>10060200</v>
-      </c>
-      <c r="H253" s="3">
-        <v>1</v>
-      </c>
-      <c r="I253" s="9">
-        <v>10000136</v>
-      </c>
-      <c r="J253" s="3">
-        <v>50</v>
-      </c>
-      <c r="K253" s="2">
-        <v>0</v>
-      </c>
-      <c r="M253" s="22" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="254" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C254" s="3">
-        <v>92000003</v>
-      </c>
-      <c r="D254" s="3">
-        <v>92000004</v>
-      </c>
       <c r="E254" s="2">
         <v>1</v>
       </c>
@@ -10246,7 +10252,7 @@
         <v>100</v>
       </c>
       <c r="G254" s="3">
-        <v>10060300</v>
+        <v>10060100</v>
       </c>
       <c r="H254" s="3">
         <v>1</v>
@@ -10261,15 +10267,16 @@
         <v>0</v>
       </c>
       <c r="M254" s="22" t="s">
-        <v>127</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="Q254" s="7"/>
     </row>
     <row r="255" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C255" s="3">
-        <v>92000004</v>
+        <v>92000002</v>
       </c>
       <c r="D255" s="3">
-        <v>92000005</v>
+        <v>92000003</v>
       </c>
       <c r="E255" s="2">
         <v>1</v>
@@ -10278,7 +10285,7 @@
         <v>100</v>
       </c>
       <c r="G255" s="3">
-        <v>10060400</v>
+        <v>10060200</v>
       </c>
       <c r="H255" s="3">
         <v>1</v>
@@ -10293,15 +10300,15 @@
         <v>0</v>
       </c>
       <c r="M255" s="22" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="256" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C256" s="3">
-        <v>92000005</v>
+        <v>92000003</v>
       </c>
       <c r="D256" s="3">
-        <v>92000006</v>
+        <v>92000004</v>
       </c>
       <c r="E256" s="2">
         <v>1</v>
@@ -10310,7 +10317,7 @@
         <v>100</v>
       </c>
       <c r="G256" s="3">
-        <v>10060500</v>
+        <v>10060300</v>
       </c>
       <c r="H256" s="3">
         <v>1</v>
@@ -10325,15 +10332,15 @@
         <v>0</v>
       </c>
       <c r="M256" s="22" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="257" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C257" s="3">
-        <v>92000006</v>
+        <v>92000004</v>
       </c>
       <c r="D257" s="3">
-        <v>92000007</v>
+        <v>92000005</v>
       </c>
       <c r="E257" s="2">
         <v>1</v>
@@ -10342,7 +10349,7 @@
         <v>100</v>
       </c>
       <c r="G257" s="3">
-        <v>10060600</v>
+        <v>10060400</v>
       </c>
       <c r="H257" s="3">
         <v>1</v>
@@ -10357,15 +10364,15 @@
         <v>0</v>
       </c>
       <c r="M257" s="22" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="258" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C258" s="3">
-        <v>92000007</v>
+        <v>92000005</v>
       </c>
       <c r="D258" s="3">
-        <v>92000008</v>
+        <v>92000006</v>
       </c>
       <c r="E258" s="2">
         <v>1</v>
@@ -10374,7 +10381,7 @@
         <v>100</v>
       </c>
       <c r="G258" s="3">
-        <v>10060700</v>
+        <v>10060500</v>
       </c>
       <c r="H258" s="3">
         <v>1</v>
@@ -10389,15 +10396,15 @@
         <v>0</v>
       </c>
       <c r="M258" s="22" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
     </row>
     <row r="259" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C259" s="3">
-        <v>92000008</v>
+        <v>92000006</v>
       </c>
       <c r="D259" s="3">
-        <v>0</v>
+        <v>92000007</v>
       </c>
       <c r="E259" s="2">
         <v>1</v>
@@ -10406,7 +10413,7 @@
         <v>100</v>
       </c>
       <c r="G259" s="3">
-        <v>10000212</v>
+        <v>10060600</v>
       </c>
       <c r="H259" s="3">
         <v>1</v>
@@ -10415,18 +10422,82 @@
         <v>10000136</v>
       </c>
       <c r="J259" s="3">
+        <v>50</v>
+      </c>
+      <c r="K259" s="2">
+        <v>0</v>
+      </c>
+      <c r="M259" s="22" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="260" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C260" s="3">
+        <v>92000007</v>
+      </c>
+      <c r="D260" s="3">
+        <v>92000008</v>
+      </c>
+      <c r="E260" s="2">
+        <v>1</v>
+      </c>
+      <c r="F260" s="3">
+        <v>100</v>
+      </c>
+      <c r="G260" s="3">
+        <v>10060700</v>
+      </c>
+      <c r="H260" s="3">
+        <v>1</v>
+      </c>
+      <c r="I260" s="9">
+        <v>10000136</v>
+      </c>
+      <c r="J260" s="3">
+        <v>50</v>
+      </c>
+      <c r="K260" s="2">
+        <v>0</v>
+      </c>
+      <c r="M260" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="261" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C261" s="3">
+        <v>92000008</v>
+      </c>
+      <c r="D261" s="3">
+        <v>0</v>
+      </c>
+      <c r="E261" s="2">
+        <v>1</v>
+      </c>
+      <c r="F261" s="3">
+        <v>100</v>
+      </c>
+      <c r="G261" s="3">
+        <v>10000212</v>
+      </c>
+      <c r="H261" s="3">
+        <v>1</v>
+      </c>
+      <c r="I261" s="9">
+        <v>10000136</v>
+      </c>
+      <c r="J261" s="3">
         <v>150</v>
       </c>
-      <c r="K259" s="2">
-        <v>0</v>
-      </c>
-      <c r="M259" s="19" t="s">
+      <c r="K261" s="2">
+        <v>0</v>
+      </c>
+      <c r="M261" s="19" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="260" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="262" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="263" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="264" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StoreSellConfig.xlsx
+++ b/Excel/StoreSellConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80330538-FF91-41B3-A717-86CC96466D56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E064359-42FD-47F8-885D-58DB95129CA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StoreSellProto" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="168" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="136">
   <si>
     <t>Id</t>
   </si>
@@ -545,6 +545,10 @@
   </si>
   <si>
     <t>魔能核心</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>魔能之匙</t>
     <phoneticPr fontId="15" type="noConversion"/>
   </si>
 </sst>
@@ -2553,7 +2557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q264"/>
+  <dimension ref="A1:Q265"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="5" width="14" customWidth="1"/>
@@ -7165,7 +7169,7 @@
         <v>50000024</v>
       </c>
       <c r="D158" s="3">
-        <v>0</v>
+        <v>50000025</v>
       </c>
       <c r="E158" s="2">
         <v>1</v>
@@ -7193,54 +7197,46 @@
       </c>
     </row>
     <row r="159" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A159" s="3"/>
-      <c r="B159" s="3"/>
       <c r="C159" s="3">
-        <v>60000001</v>
+        <v>50000025</v>
       </c>
       <c r="D159" s="3">
-        <v>60000002</v>
-      </c>
-      <c r="E159" s="3">
+        <v>0</v>
+      </c>
+      <c r="E159" s="2">
         <v>1</v>
       </c>
       <c r="F159" s="3">
         <v>100</v>
       </c>
-      <c r="G159" s="3">
-        <v>10000143</v>
-      </c>
-      <c r="H159" s="11" t="s">
-        <v>46</v>
+      <c r="G159" s="9">
+        <v>10000181</v>
+      </c>
+      <c r="H159" s="2">
+        <v>1</v>
       </c>
       <c r="I159" s="9">
-        <v>10000157</v>
+        <v>10000151</v>
       </c>
       <c r="J159" s="3">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="K159" s="2">
         <v>0</v>
       </c>
-      <c r="L159" s="3"/>
-      <c r="M159" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="N159" s="3"/>
-      <c r="O159" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="P159" s="3"/>
+      <c r="M159" s="11" t="s">
+        <v>135</v>
+      </c>
     </row>
     <row r="160" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A160" s="3"/>
       <c r="B160" s="3"/>
       <c r="C160" s="3">
+        <v>60000001</v>
+      </c>
+      <c r="D160" s="3">
         <v>60000002</v>
       </c>
-      <c r="D160" s="3">
-        <v>60000003</v>
-      </c>
       <c r="E160" s="3">
         <v>1</v>
       </c>
@@ -7248,23 +7244,23 @@
         <v>100</v>
       </c>
       <c r="G160" s="3">
-        <v>10010093</v>
-      </c>
-      <c r="H160" s="12">
-        <v>1</v>
+        <v>10000143</v>
+      </c>
+      <c r="H160" s="11" t="s">
+        <v>46</v>
       </c>
       <c r="I160" s="9">
-        <v>10000143</v>
-      </c>
-      <c r="J160" s="11" t="s">
-        <v>48</v>
+        <v>10000157</v>
+      </c>
+      <c r="J160" s="3">
+        <v>1</v>
       </c>
       <c r="K160" s="2">
         <v>0</v>
       </c>
       <c r="L160" s="3"/>
-      <c r="M160" s="12" t="s">
-        <v>49</v>
+      <c r="M160" s="15" t="s">
+        <v>47</v>
       </c>
       <c r="N160" s="3"/>
       <c r="O160" s="11" t="s">
@@ -7272,53 +7268,61 @@
       </c>
       <c r="P160" s="3"/>
     </row>
-    <row r="161" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="161" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A161" s="3"/>
+      <c r="B161" s="3"/>
       <c r="C161" s="3">
+        <v>60000002</v>
+      </c>
+      <c r="D161" s="3">
         <v>60000003</v>
       </c>
-      <c r="D161" s="3">
+      <c r="E161" s="3">
+        <v>1</v>
+      </c>
+      <c r="F161" s="3">
+        <v>100</v>
+      </c>
+      <c r="G161" s="3">
+        <v>10010093</v>
+      </c>
+      <c r="H161" s="12">
+        <v>1</v>
+      </c>
+      <c r="I161" s="9">
+        <v>10000143</v>
+      </c>
+      <c r="J161" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="K161" s="2">
+        <v>0</v>
+      </c>
+      <c r="L161" s="3"/>
+      <c r="M161" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="N161" s="3"/>
+      <c r="O161" s="11" t="s">
+        <v>39</v>
+      </c>
+      <c r="P161" s="3"/>
+    </row>
+    <row r="162" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C162" s="3">
+        <v>60000003</v>
+      </c>
+      <c r="D162" s="3">
         <v>60000004</v>
       </c>
-      <c r="E161" s="3">
-        <v>1</v>
-      </c>
-      <c r="F161" s="3">
-        <v>100</v>
-      </c>
-      <c r="G161" s="13">
+      <c r="E162" s="3">
+        <v>1</v>
+      </c>
+      <c r="F162" s="3">
+        <v>100</v>
+      </c>
+      <c r="G162" s="13">
         <v>10012001</v>
-      </c>
-      <c r="H161" s="3">
-        <v>1</v>
-      </c>
-      <c r="I161" s="3">
-        <v>10010029</v>
-      </c>
-      <c r="J161" s="3">
-        <v>10</v>
-      </c>
-      <c r="K161" s="2">
-        <v>0</v>
-      </c>
-      <c r="M161" s="13" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="162" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C162" s="3">
-        <v>60000004</v>
-      </c>
-      <c r="D162" s="3">
-        <v>60000005</v>
-      </c>
-      <c r="E162" s="3">
-        <v>1</v>
-      </c>
-      <c r="F162" s="3">
-        <v>100</v>
-      </c>
-      <c r="G162" s="13">
-        <v>10012002</v>
       </c>
       <c r="H162" s="3">
         <v>1</v>
@@ -7333,16 +7337,16 @@
         <v>0</v>
       </c>
       <c r="M162" s="13" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="163" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="163" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C163" s="3">
+        <v>60000004</v>
+      </c>
+      <c r="D163" s="3">
         <v>60000005</v>
       </c>
-      <c r="D163" s="3">
-        <v>60000006</v>
-      </c>
       <c r="E163" s="3">
         <v>1</v>
       </c>
@@ -7350,7 +7354,7 @@
         <v>100</v>
       </c>
       <c r="G163" s="13">
-        <v>10012003</v>
+        <v>10012002</v>
       </c>
       <c r="H163" s="3">
         <v>1</v>
@@ -7365,16 +7369,16 @@
         <v>0</v>
       </c>
       <c r="M163" s="13" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="164" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="164" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C164" s="3">
+        <v>60000005</v>
+      </c>
+      <c r="D164" s="3">
         <v>60000006</v>
       </c>
-      <c r="D164" s="3">
-        <v>60000007</v>
-      </c>
       <c r="E164" s="3">
         <v>1</v>
       </c>
@@ -7382,7 +7386,7 @@
         <v>100</v>
       </c>
       <c r="G164" s="13">
-        <v>10012004</v>
+        <v>10012003</v>
       </c>
       <c r="H164" s="3">
         <v>1</v>
@@ -7397,16 +7401,16 @@
         <v>0</v>
       </c>
       <c r="M164" s="13" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="165" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="165" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C165" s="3">
+        <v>60000006</v>
+      </c>
+      <c r="D165" s="3">
         <v>60000007</v>
       </c>
-      <c r="D165" s="3">
-        <v>60000008</v>
-      </c>
       <c r="E165" s="3">
         <v>1</v>
       </c>
@@ -7414,7 +7418,7 @@
         <v>100</v>
       </c>
       <c r="G165" s="13">
-        <v>10012005</v>
+        <v>10012004</v>
       </c>
       <c r="H165" s="3">
         <v>1</v>
@@ -7429,16 +7433,16 @@
         <v>0</v>
       </c>
       <c r="M165" s="13" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="166" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="166" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C166" s="3">
+        <v>60000007</v>
+      </c>
+      <c r="D166" s="3">
         <v>60000008</v>
       </c>
-      <c r="D166" s="3">
-        <v>60000009</v>
-      </c>
       <c r="E166" s="3">
         <v>1</v>
       </c>
@@ -7446,7 +7450,7 @@
         <v>100</v>
       </c>
       <c r="G166" s="13">
-        <v>10012006</v>
+        <v>10012005</v>
       </c>
       <c r="H166" s="3">
         <v>1</v>
@@ -7461,16 +7465,16 @@
         <v>0</v>
       </c>
       <c r="M166" s="13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="167" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="167" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C167" s="3">
+        <v>60000008</v>
+      </c>
+      <c r="D167" s="3">
         <v>60000009</v>
       </c>
-      <c r="D167" s="3">
-        <v>60000010</v>
-      </c>
       <c r="E167" s="3">
         <v>1</v>
       </c>
@@ -7478,7 +7482,7 @@
         <v>100</v>
       </c>
       <c r="G167" s="13">
-        <v>10012007</v>
+        <v>10012006</v>
       </c>
       <c r="H167" s="3">
         <v>1</v>
@@ -7493,16 +7497,16 @@
         <v>0</v>
       </c>
       <c r="M167" s="13" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="168" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="168" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C168" s="3">
+        <v>60000009</v>
+      </c>
+      <c r="D168" s="3">
         <v>60000010</v>
       </c>
-      <c r="D168" s="3">
-        <v>60000011</v>
-      </c>
       <c r="E168" s="3">
         <v>1</v>
       </c>
@@ -7510,7 +7514,7 @@
         <v>100</v>
       </c>
       <c r="G168" s="13">
-        <v>10012008</v>
+        <v>10012007</v>
       </c>
       <c r="H168" s="3">
         <v>1</v>
@@ -7525,16 +7529,16 @@
         <v>0</v>
       </c>
       <c r="M168" s="13" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="169" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="169" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C169" s="3">
+        <v>60000010</v>
+      </c>
+      <c r="D169" s="3">
         <v>60000011</v>
       </c>
-      <c r="D169" s="3">
-        <v>60000012</v>
-      </c>
       <c r="E169" s="3">
         <v>1</v>
       </c>
@@ -7542,7 +7546,7 @@
         <v>100</v>
       </c>
       <c r="G169" s="13">
-        <v>10012009</v>
+        <v>10012008</v>
       </c>
       <c r="H169" s="3">
         <v>1</v>
@@ -7557,16 +7561,16 @@
         <v>0</v>
       </c>
       <c r="M169" s="13" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="170" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="170" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C170" s="3">
+        <v>60000011</v>
+      </c>
+      <c r="D170" s="3">
         <v>60000012</v>
       </c>
-      <c r="D170" s="3">
-        <v>60000013</v>
-      </c>
       <c r="E170" s="3">
         <v>1</v>
       </c>
@@ -7574,7 +7578,7 @@
         <v>100</v>
       </c>
       <c r="G170" s="13">
-        <v>10012010</v>
+        <v>10012009</v>
       </c>
       <c r="H170" s="3">
         <v>1</v>
@@ -7589,16 +7593,16 @@
         <v>0</v>
       </c>
       <c r="M170" s="13" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="171" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="171" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C171" s="3">
+        <v>60000012</v>
+      </c>
+      <c r="D171" s="3">
         <v>60000013</v>
       </c>
-      <c r="D171" s="3">
-        <v>60000014</v>
-      </c>
       <c r="E171" s="3">
         <v>1</v>
       </c>
@@ -7606,7 +7610,7 @@
         <v>100</v>
       </c>
       <c r="G171" s="13">
-        <v>10012011</v>
+        <v>10012010</v>
       </c>
       <c r="H171" s="3">
         <v>1</v>
@@ -7621,16 +7625,16 @@
         <v>0</v>
       </c>
       <c r="M171" s="13" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="172" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="172" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C172" s="3">
+        <v>60000013</v>
+      </c>
+      <c r="D172" s="3">
         <v>60000014</v>
       </c>
-      <c r="D172" s="3">
-        <v>60000015</v>
-      </c>
       <c r="E172" s="3">
         <v>1</v>
       </c>
@@ -7638,7 +7642,7 @@
         <v>100</v>
       </c>
       <c r="G172" s="13">
-        <v>10012012</v>
+        <v>10012011</v>
       </c>
       <c r="H172" s="3">
         <v>1</v>
@@ -7653,16 +7657,16 @@
         <v>0</v>
       </c>
       <c r="M172" s="13" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="173" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="173" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C173" s="3">
+        <v>60000014</v>
+      </c>
+      <c r="D173" s="3">
         <v>60000015</v>
       </c>
-      <c r="D173" s="3">
-        <v>60000016</v>
-      </c>
       <c r="E173" s="3">
         <v>1</v>
       </c>
@@ -7670,7 +7674,7 @@
         <v>100</v>
       </c>
       <c r="G173" s="13">
-        <v>10012013</v>
+        <v>10012012</v>
       </c>
       <c r="H173" s="3">
         <v>1</v>
@@ -7685,16 +7689,16 @@
         <v>0</v>
       </c>
       <c r="M173" s="13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="174" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="174" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C174" s="3">
+        <v>60000015</v>
+      </c>
+      <c r="D174" s="3">
         <v>60000016</v>
       </c>
-      <c r="D174" s="3">
-        <v>60000017</v>
-      </c>
       <c r="E174" s="3">
         <v>1</v>
       </c>
@@ -7702,7 +7706,7 @@
         <v>100</v>
       </c>
       <c r="G174" s="13">
-        <v>10012014</v>
+        <v>10012013</v>
       </c>
       <c r="H174" s="3">
         <v>1</v>
@@ -7717,16 +7721,16 @@
         <v>0</v>
       </c>
       <c r="M174" s="13" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="175" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="175" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C175" s="3">
+        <v>60000016</v>
+      </c>
+      <c r="D175" s="3">
         <v>60000017</v>
       </c>
-      <c r="D175" s="3">
-        <v>60000018</v>
-      </c>
       <c r="E175" s="3">
         <v>1</v>
       </c>
@@ -7734,7 +7738,7 @@
         <v>100</v>
       </c>
       <c r="G175" s="13">
-        <v>10012015</v>
+        <v>10012014</v>
       </c>
       <c r="H175" s="3">
         <v>1</v>
@@ -7749,16 +7753,16 @@
         <v>0</v>
       </c>
       <c r="M175" s="13" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="176" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="176" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C176" s="3">
+        <v>60000017</v>
+      </c>
+      <c r="D176" s="3">
         <v>60000018</v>
       </c>
-      <c r="D176" s="3">
-        <v>60000019</v>
-      </c>
       <c r="E176" s="3">
         <v>1</v>
       </c>
@@ -7766,7 +7770,7 @@
         <v>100</v>
       </c>
       <c r="G176" s="13">
-        <v>10012016</v>
+        <v>10012015</v>
       </c>
       <c r="H176" s="3">
         <v>1</v>
@@ -7781,16 +7785,16 @@
         <v>0</v>
       </c>
       <c r="M176" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="177" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C177" s="3">
+        <v>60000018</v>
+      </c>
+      <c r="D177" s="3">
         <v>60000019</v>
       </c>
-      <c r="D177" s="3">
-        <v>60000020</v>
-      </c>
       <c r="E177" s="3">
         <v>1</v>
       </c>
@@ -7798,7 +7802,7 @@
         <v>100</v>
       </c>
       <c r="G177" s="13">
-        <v>10012017</v>
+        <v>10012016</v>
       </c>
       <c r="H177" s="3">
         <v>1</v>
@@ -7813,16 +7817,16 @@
         <v>0</v>
       </c>
       <c r="M177" s="13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="178" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C178" s="3">
+        <v>60000019</v>
+      </c>
+      <c r="D178" s="3">
         <v>60000020</v>
       </c>
-      <c r="D178" s="3">
-        <v>60000021</v>
-      </c>
       <c r="E178" s="3">
         <v>1</v>
       </c>
@@ -7830,7 +7834,7 @@
         <v>100</v>
       </c>
       <c r="G178" s="13">
-        <v>10012018</v>
+        <v>10012017</v>
       </c>
       <c r="H178" s="3">
         <v>1</v>
@@ -7845,16 +7849,16 @@
         <v>0</v>
       </c>
       <c r="M178" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="179" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C179" s="3">
+        <v>60000020</v>
+      </c>
+      <c r="D179" s="3">
         <v>60000021</v>
       </c>
-      <c r="D179" s="3">
-        <v>60000022</v>
-      </c>
       <c r="E179" s="3">
         <v>1</v>
       </c>
@@ -7862,7 +7866,7 @@
         <v>100</v>
       </c>
       <c r="G179" s="13">
-        <v>10012019</v>
+        <v>10012018</v>
       </c>
       <c r="H179" s="3">
         <v>1</v>
@@ -7877,16 +7881,16 @@
         <v>0</v>
       </c>
       <c r="M179" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="180" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C180" s="3">
+        <v>60000021</v>
+      </c>
+      <c r="D180" s="3">
         <v>60000022</v>
       </c>
-      <c r="D180" s="3">
-        <v>60000023</v>
-      </c>
       <c r="E180" s="3">
         <v>1</v>
       </c>
@@ -7894,7 +7898,7 @@
         <v>100</v>
       </c>
       <c r="G180" s="13">
-        <v>10012020</v>
+        <v>10012019</v>
       </c>
       <c r="H180" s="3">
         <v>1</v>
@@ -7903,22 +7907,22 @@
         <v>10010029</v>
       </c>
       <c r="J180" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K180" s="2">
         <v>0</v>
       </c>
       <c r="M180" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="181" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C181" s="3">
+        <v>60000022</v>
+      </c>
+      <c r="D181" s="3">
         <v>60000023</v>
       </c>
-      <c r="D181" s="3">
-        <v>60000024</v>
-      </c>
       <c r="E181" s="3">
         <v>1</v>
       </c>
@@ -7926,7 +7930,7 @@
         <v>100</v>
       </c>
       <c r="G181" s="13">
-        <v>10012021</v>
+        <v>10012020</v>
       </c>
       <c r="H181" s="3">
         <v>1</v>
@@ -7941,16 +7945,16 @@
         <v>0</v>
       </c>
       <c r="M181" s="13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="182" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C182" s="3">
+        <v>60000023</v>
+      </c>
+      <c r="D182" s="3">
         <v>60000024</v>
       </c>
-      <c r="D182" s="3">
-        <v>60000025</v>
-      </c>
       <c r="E182" s="3">
         <v>1</v>
       </c>
@@ -7958,7 +7962,7 @@
         <v>100</v>
       </c>
       <c r="G182" s="13">
-        <v>10012022</v>
+        <v>10012021</v>
       </c>
       <c r="H182" s="3">
         <v>1</v>
@@ -7973,16 +7977,16 @@
         <v>0</v>
       </c>
       <c r="M182" s="13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="183" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C183" s="3">
+        <v>60000024</v>
+      </c>
+      <c r="D183" s="3">
         <v>60000025</v>
       </c>
-      <c r="D183" s="3">
-        <v>60000026</v>
-      </c>
       <c r="E183" s="3">
         <v>1</v>
       </c>
@@ -7990,7 +7994,7 @@
         <v>100</v>
       </c>
       <c r="G183" s="13">
-        <v>10012023</v>
+        <v>10012022</v>
       </c>
       <c r="H183" s="3">
         <v>1</v>
@@ -8005,16 +8009,16 @@
         <v>0</v>
       </c>
       <c r="M183" s="13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="184" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C184" s="3">
+        <v>60000025</v>
+      </c>
+      <c r="D184" s="3">
         <v>60000026</v>
       </c>
-      <c r="D184" s="3">
-        <v>60000027</v>
-      </c>
       <c r="E184" s="3">
         <v>1</v>
       </c>
@@ -8022,7 +8026,7 @@
         <v>100</v>
       </c>
       <c r="G184" s="13">
-        <v>10012024</v>
+        <v>10012023</v>
       </c>
       <c r="H184" s="3">
         <v>1</v>
@@ -8037,16 +8041,16 @@
         <v>0</v>
       </c>
       <c r="M184" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="185" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C185" s="3">
+        <v>60000026</v>
+      </c>
+      <c r="D185" s="3">
         <v>60000027</v>
       </c>
-      <c r="D185" s="3">
-        <v>60000028</v>
-      </c>
       <c r="E185" s="3">
         <v>1</v>
       </c>
@@ -8054,7 +8058,7 @@
         <v>100</v>
       </c>
       <c r="G185" s="13">
-        <v>10012025</v>
+        <v>10012024</v>
       </c>
       <c r="H185" s="3">
         <v>1</v>
@@ -8069,16 +8073,16 @@
         <v>0</v>
       </c>
       <c r="M185" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="186" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C186" s="3">
+        <v>60000027</v>
+      </c>
+      <c r="D186" s="3">
         <v>60000028</v>
       </c>
-      <c r="D186" s="3">
-        <v>60000029</v>
-      </c>
       <c r="E186" s="3">
         <v>1</v>
       </c>
@@ -8086,7 +8090,7 @@
         <v>100</v>
       </c>
       <c r="G186" s="13">
-        <v>10012026</v>
+        <v>10012025</v>
       </c>
       <c r="H186" s="3">
         <v>1</v>
@@ -8101,16 +8105,16 @@
         <v>0</v>
       </c>
       <c r="M186" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="187" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C187" s="3">
+        <v>60000028</v>
+      </c>
+      <c r="D187" s="3">
         <v>60000029</v>
       </c>
-      <c r="D187" s="3">
-        <v>60000030</v>
-      </c>
       <c r="E187" s="3">
         <v>1</v>
       </c>
@@ -8118,7 +8122,7 @@
         <v>100</v>
       </c>
       <c r="G187" s="13">
-        <v>10012027</v>
+        <v>10012026</v>
       </c>
       <c r="H187" s="3">
         <v>1</v>
@@ -8133,16 +8137,16 @@
         <v>0</v>
       </c>
       <c r="M187" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="188" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C188" s="3">
+        <v>60000029</v>
+      </c>
+      <c r="D188" s="3">
         <v>60000030</v>
       </c>
-      <c r="D188" s="3">
-        <v>60000031</v>
-      </c>
       <c r="E188" s="3">
         <v>1</v>
       </c>
@@ -8150,13 +8154,13 @@
         <v>100</v>
       </c>
       <c r="G188" s="13">
-        <v>10013001</v>
+        <v>10012027</v>
       </c>
       <c r="H188" s="3">
         <v>1</v>
       </c>
       <c r="I188" s="3">
-        <v>10010030</v>
+        <v>10010029</v>
       </c>
       <c r="J188" s="3">
         <v>15</v>
@@ -8164,17 +8168,17 @@
       <c r="K188" s="2">
         <v>0</v>
       </c>
-      <c r="M188" s="17" t="s">
-        <v>77</v>
+      <c r="M188" s="13" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="189" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C189" s="3">
+        <v>60000030</v>
+      </c>
+      <c r="D189" s="3">
         <v>60000031</v>
       </c>
-      <c r="D189" s="3">
-        <v>60000032</v>
-      </c>
       <c r="E189" s="3">
         <v>1</v>
       </c>
@@ -8182,7 +8186,7 @@
         <v>100</v>
       </c>
       <c r="G189" s="13">
-        <v>10013002</v>
+        <v>10013001</v>
       </c>
       <c r="H189" s="3">
         <v>1</v>
@@ -8197,16 +8201,16 @@
         <v>0</v>
       </c>
       <c r="M189" s="17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="190" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C190" s="3">
+        <v>60000031</v>
+      </c>
+      <c r="D190" s="3">
         <v>60000032</v>
       </c>
-      <c r="D190" s="3">
-        <v>60000033</v>
-      </c>
       <c r="E190" s="3">
         <v>1</v>
       </c>
@@ -8214,7 +8218,7 @@
         <v>100</v>
       </c>
       <c r="G190" s="13">
-        <v>10013003</v>
+        <v>10013002</v>
       </c>
       <c r="H190" s="3">
         <v>1</v>
@@ -8229,16 +8233,16 @@
         <v>0</v>
       </c>
       <c r="M190" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="191" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C191" s="3">
+        <v>60000032</v>
+      </c>
+      <c r="D191" s="3">
         <v>60000033</v>
       </c>
-      <c r="D191" s="3">
-        <v>60000034</v>
-      </c>
       <c r="E191" s="3">
         <v>1</v>
       </c>
@@ -8246,7 +8250,7 @@
         <v>100</v>
       </c>
       <c r="G191" s="13">
-        <v>10013004</v>
+        <v>10013003</v>
       </c>
       <c r="H191" s="3">
         <v>1</v>
@@ -8261,16 +8265,16 @@
         <v>0</v>
       </c>
       <c r="M191" s="17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="192" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C192" s="3">
+        <v>60000033</v>
+      </c>
+      <c r="D192" s="3">
         <v>60000034</v>
       </c>
-      <c r="D192" s="3">
-        <v>60000035</v>
-      </c>
       <c r="E192" s="3">
         <v>1</v>
       </c>
@@ -8278,7 +8282,7 @@
         <v>100</v>
       </c>
       <c r="G192" s="13">
-        <v>10013005</v>
+        <v>10013004</v>
       </c>
       <c r="H192" s="3">
         <v>1</v>
@@ -8293,16 +8297,16 @@
         <v>0</v>
       </c>
       <c r="M192" s="17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="193" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C193" s="3">
+        <v>60000034</v>
+      </c>
+      <c r="D193" s="3">
         <v>60000035</v>
       </c>
-      <c r="D193" s="3">
-        <v>60000036</v>
-      </c>
       <c r="E193" s="3">
         <v>1</v>
       </c>
@@ -8310,7 +8314,7 @@
         <v>100</v>
       </c>
       <c r="G193" s="13">
-        <v>10013006</v>
+        <v>10013005</v>
       </c>
       <c r="H193" s="3">
         <v>1</v>
@@ -8325,16 +8329,16 @@
         <v>0</v>
       </c>
       <c r="M193" s="17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="194" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C194" s="3">
+        <v>60000035</v>
+      </c>
+      <c r="D194" s="3">
         <v>60000036</v>
       </c>
-      <c r="D194" s="3">
-        <v>60000037</v>
-      </c>
       <c r="E194" s="3">
         <v>1</v>
       </c>
@@ -8342,7 +8346,7 @@
         <v>100</v>
       </c>
       <c r="G194" s="13">
-        <v>10013007</v>
+        <v>10013006</v>
       </c>
       <c r="H194" s="3">
         <v>1</v>
@@ -8357,16 +8361,16 @@
         <v>0</v>
       </c>
       <c r="M194" s="17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="195" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C195" s="3">
+        <v>60000036</v>
+      </c>
+      <c r="D195" s="3">
         <v>60000037</v>
       </c>
-      <c r="D195" s="3">
-        <v>60000038</v>
-      </c>
       <c r="E195" s="3">
         <v>1</v>
       </c>
@@ -8374,7 +8378,7 @@
         <v>100</v>
       </c>
       <c r="G195" s="13">
-        <v>10013008</v>
+        <v>10013007</v>
       </c>
       <c r="H195" s="3">
         <v>1</v>
@@ -8389,16 +8393,16 @@
         <v>0</v>
       </c>
       <c r="M195" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="196" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C196" s="3">
+        <v>60000037</v>
+      </c>
+      <c r="D196" s="3">
         <v>60000038</v>
       </c>
-      <c r="D196" s="3">
-        <v>60000039</v>
-      </c>
       <c r="E196" s="3">
         <v>1</v>
       </c>
@@ -8406,7 +8410,7 @@
         <v>100</v>
       </c>
       <c r="G196" s="13">
-        <v>10013009</v>
+        <v>10013008</v>
       </c>
       <c r="H196" s="3">
         <v>1</v>
@@ -8421,16 +8425,16 @@
         <v>0</v>
       </c>
       <c r="M196" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="197" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C197" s="3">
+        <v>60000038</v>
+      </c>
+      <c r="D197" s="3">
         <v>60000039</v>
       </c>
-      <c r="D197" s="3">
-        <v>60000040</v>
-      </c>
       <c r="E197" s="3">
         <v>1</v>
       </c>
@@ -8438,7 +8442,7 @@
         <v>100</v>
       </c>
       <c r="G197" s="13">
-        <v>10013010</v>
+        <v>10013009</v>
       </c>
       <c r="H197" s="3">
         <v>1</v>
@@ -8453,16 +8457,16 @@
         <v>0</v>
       </c>
       <c r="M197" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="198" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C198" s="3">
+        <v>60000039</v>
+      </c>
+      <c r="D198" s="3">
         <v>60000040</v>
       </c>
-      <c r="D198" s="3">
-        <v>60000041</v>
-      </c>
       <c r="E198" s="3">
         <v>1</v>
       </c>
@@ -8470,7 +8474,7 @@
         <v>100</v>
       </c>
       <c r="G198" s="13">
-        <v>10013011</v>
+        <v>10013010</v>
       </c>
       <c r="H198" s="3">
         <v>1</v>
@@ -8485,16 +8489,16 @@
         <v>0</v>
       </c>
       <c r="M198" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="199" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C199" s="3">
+        <v>60000040</v>
+      </c>
+      <c r="D199" s="3">
         <v>60000041</v>
       </c>
-      <c r="D199" s="3">
-        <v>60000042</v>
-      </c>
       <c r="E199" s="3">
         <v>1</v>
       </c>
@@ -8502,7 +8506,7 @@
         <v>100</v>
       </c>
       <c r="G199" s="13">
-        <v>10013012</v>
+        <v>10013011</v>
       </c>
       <c r="H199" s="3">
         <v>1</v>
@@ -8517,16 +8521,16 @@
         <v>0</v>
       </c>
       <c r="M199" s="17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="200" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C200" s="3">
+        <v>60000041</v>
+      </c>
+      <c r="D200" s="3">
         <v>60000042</v>
       </c>
-      <c r="D200" s="3">
-        <v>60000043</v>
-      </c>
       <c r="E200" s="3">
         <v>1</v>
       </c>
@@ -8534,7 +8538,7 @@
         <v>100</v>
       </c>
       <c r="G200" s="13">
-        <v>10013013</v>
+        <v>10013012</v>
       </c>
       <c r="H200" s="3">
         <v>1</v>
@@ -8549,16 +8553,16 @@
         <v>0</v>
       </c>
       <c r="M200" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="201" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C201" s="3">
+        <v>60000042</v>
+      </c>
+      <c r="D201" s="3">
         <v>60000043</v>
       </c>
-      <c r="D201" s="3">
-        <v>60000044</v>
-      </c>
       <c r="E201" s="3">
         <v>1</v>
       </c>
@@ -8566,7 +8570,7 @@
         <v>100</v>
       </c>
       <c r="G201" s="13">
-        <v>10013014</v>
+        <v>10013013</v>
       </c>
       <c r="H201" s="3">
         <v>1</v>
@@ -8581,16 +8585,16 @@
         <v>0</v>
       </c>
       <c r="M201" s="17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="202" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C202" s="3">
+        <v>60000043</v>
+      </c>
+      <c r="D202" s="3">
         <v>60000044</v>
       </c>
-      <c r="D202" s="3">
-        <v>60000045</v>
-      </c>
       <c r="E202" s="3">
         <v>1</v>
       </c>
@@ -8598,7 +8602,7 @@
         <v>100</v>
       </c>
       <c r="G202" s="13">
-        <v>10013015</v>
+        <v>10013014</v>
       </c>
       <c r="H202" s="3">
         <v>1</v>
@@ -8613,16 +8617,16 @@
         <v>0</v>
       </c>
       <c r="M202" s="17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="203" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C203" s="3">
+        <v>60000044</v>
+      </c>
+      <c r="D203" s="3">
         <v>60000045</v>
       </c>
-      <c r="D203" s="3">
-        <v>60000046</v>
-      </c>
       <c r="E203" s="3">
         <v>1</v>
       </c>
@@ -8630,7 +8634,7 @@
         <v>100</v>
       </c>
       <c r="G203" s="13">
-        <v>10013016</v>
+        <v>10013015</v>
       </c>
       <c r="H203" s="3">
         <v>1</v>
@@ -8645,16 +8649,16 @@
         <v>0</v>
       </c>
       <c r="M203" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="204" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C204" s="3">
+        <v>60000045</v>
+      </c>
+      <c r="D204" s="3">
         <v>60000046</v>
       </c>
-      <c r="D204" s="3">
-        <v>60000047</v>
-      </c>
       <c r="E204" s="3">
         <v>1</v>
       </c>
@@ -8662,7 +8666,7 @@
         <v>100</v>
       </c>
       <c r="G204" s="13">
-        <v>10013017</v>
+        <v>10013016</v>
       </c>
       <c r="H204" s="3">
         <v>1</v>
@@ -8677,16 +8681,16 @@
         <v>0</v>
       </c>
       <c r="M204" s="17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="205" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C205" s="3">
+        <v>60000046</v>
+      </c>
+      <c r="D205" s="3">
         <v>60000047</v>
       </c>
-      <c r="D205" s="3">
-        <v>60000048</v>
-      </c>
       <c r="E205" s="3">
         <v>1</v>
       </c>
@@ -8694,7 +8698,7 @@
         <v>100</v>
       </c>
       <c r="G205" s="13">
-        <v>10013018</v>
+        <v>10013017</v>
       </c>
       <c r="H205" s="3">
         <v>1</v>
@@ -8709,16 +8713,16 @@
         <v>0</v>
       </c>
       <c r="M205" s="17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="206" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C206" s="3">
+        <v>60000047</v>
+      </c>
+      <c r="D206" s="3">
         <v>60000048</v>
       </c>
-      <c r="D206" s="3">
-        <v>60000049</v>
-      </c>
       <c r="E206" s="3">
         <v>1</v>
       </c>
@@ -8726,7 +8730,7 @@
         <v>100</v>
       </c>
       <c r="G206" s="13">
-        <v>10013019</v>
+        <v>10013018</v>
       </c>
       <c r="H206" s="3">
         <v>1</v>
@@ -8741,16 +8745,16 @@
         <v>0</v>
       </c>
       <c r="M206" s="17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="207" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C207" s="3">
+        <v>60000048</v>
+      </c>
+      <c r="D207" s="3">
         <v>60000049</v>
       </c>
-      <c r="D207" s="3">
-        <v>60000050</v>
-      </c>
       <c r="E207" s="3">
         <v>1</v>
       </c>
@@ -8758,7 +8762,7 @@
         <v>100</v>
       </c>
       <c r="G207" s="13">
-        <v>10013020</v>
+        <v>10013019</v>
       </c>
       <c r="H207" s="3">
         <v>1</v>
@@ -8767,22 +8771,22 @@
         <v>10010030</v>
       </c>
       <c r="J207" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K207" s="2">
         <v>0</v>
       </c>
       <c r="M207" s="17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="208" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C208" s="3">
+        <v>60000049</v>
+      </c>
+      <c r="D208" s="3">
         <v>60000050</v>
       </c>
-      <c r="D208" s="3">
-        <v>60000051</v>
-      </c>
       <c r="E208" s="3">
         <v>1</v>
       </c>
@@ -8790,7 +8794,7 @@
         <v>100</v>
       </c>
       <c r="G208" s="13">
-        <v>10013021</v>
+        <v>10013020</v>
       </c>
       <c r="H208" s="3">
         <v>1</v>
@@ -8805,16 +8809,16 @@
         <v>0</v>
       </c>
       <c r="M208" s="17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="209" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C209" s="3">
+        <v>60000050</v>
+      </c>
+      <c r="D209" s="3">
         <v>60000051</v>
       </c>
-      <c r="D209" s="3">
-        <v>60000052</v>
-      </c>
       <c r="E209" s="3">
         <v>1</v>
       </c>
@@ -8822,7 +8826,7 @@
         <v>100</v>
       </c>
       <c r="G209" s="13">
-        <v>10013022</v>
+        <v>10013021</v>
       </c>
       <c r="H209" s="3">
         <v>1</v>
@@ -8837,16 +8841,16 @@
         <v>0</v>
       </c>
       <c r="M209" s="17" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="210" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C210" s="3">
+        <v>60000051</v>
+      </c>
+      <c r="D210" s="3">
         <v>60000052</v>
       </c>
-      <c r="D210" s="3">
-        <v>60000053</v>
-      </c>
       <c r="E210" s="3">
         <v>1</v>
       </c>
@@ -8854,7 +8858,7 @@
         <v>100</v>
       </c>
       <c r="G210" s="13">
-        <v>10013023</v>
+        <v>10013022</v>
       </c>
       <c r="H210" s="3">
         <v>1</v>
@@ -8869,16 +8873,16 @@
         <v>0</v>
       </c>
       <c r="M210" s="17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="211" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C211" s="3">
+        <v>60000052</v>
+      </c>
+      <c r="D211" s="3">
         <v>60000053</v>
       </c>
-      <c r="D211" s="3">
-        <v>60000054</v>
-      </c>
       <c r="E211" s="3">
         <v>1</v>
       </c>
@@ -8886,7 +8890,7 @@
         <v>100</v>
       </c>
       <c r="G211" s="13">
-        <v>10013024</v>
+        <v>10013023</v>
       </c>
       <c r="H211" s="3">
         <v>1</v>
@@ -8901,16 +8905,16 @@
         <v>0</v>
       </c>
       <c r="M211" s="17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="212" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C212" s="3">
+        <v>60000053</v>
+      </c>
+      <c r="D212" s="3">
         <v>60000054</v>
       </c>
-      <c r="D212" s="3">
-        <v>60000055</v>
-      </c>
       <c r="E212" s="3">
         <v>1</v>
       </c>
@@ -8918,7 +8922,7 @@
         <v>100</v>
       </c>
       <c r="G212" s="13">
-        <v>10013025</v>
+        <v>10013024</v>
       </c>
       <c r="H212" s="3">
         <v>1</v>
@@ -8933,16 +8937,16 @@
         <v>0</v>
       </c>
       <c r="M212" s="17" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="213" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C213" s="3">
+        <v>60000054</v>
+      </c>
+      <c r="D213" s="3">
         <v>60000055</v>
       </c>
-      <c r="D213" s="3">
-        <v>60000056</v>
-      </c>
       <c r="E213" s="3">
         <v>1</v>
       </c>
@@ -8950,7 +8954,7 @@
         <v>100</v>
       </c>
       <c r="G213" s="13">
-        <v>10013026</v>
+        <v>10013025</v>
       </c>
       <c r="H213" s="3">
         <v>1</v>
@@ -8965,16 +8969,16 @@
         <v>0</v>
       </c>
       <c r="M213" s="17" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="214" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C214" s="3">
+        <v>60000055</v>
+      </c>
+      <c r="D214" s="3">
         <v>60000056</v>
       </c>
-      <c r="D214" s="3">
-        <v>0</v>
-      </c>
       <c r="E214" s="3">
         <v>1</v>
       </c>
@@ -8982,7 +8986,7 @@
         <v>100</v>
       </c>
       <c r="G214" s="13">
-        <v>10013027</v>
+        <v>10013026</v>
       </c>
       <c r="H214" s="3">
         <v>1</v>
@@ -8997,15 +9001,15 @@
         <v>0</v>
       </c>
       <c r="M214" s="17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="215" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C215" s="3">
-        <v>70000001</v>
+        <v>60000056</v>
       </c>
       <c r="D215" s="3">
-        <v>70000002</v>
+        <v>0</v>
       </c>
       <c r="E215" s="3">
         <v>1</v>
@@ -9013,32 +9017,32 @@
       <c r="F215" s="3">
         <v>100</v>
       </c>
-      <c r="G215" s="9">
-        <v>10010093</v>
+      <c r="G215" s="13">
+        <v>10013027</v>
       </c>
       <c r="H215" s="3">
         <v>1</v>
       </c>
-      <c r="I215" s="8">
-        <v>10000159</v>
-      </c>
-      <c r="J215" s="8">
-        <v>30</v>
+      <c r="I215" s="3">
+        <v>10010030</v>
+      </c>
+      <c r="J215" s="3">
+        <v>20</v>
       </c>
       <c r="K215" s="2">
         <v>0</v>
       </c>
-      <c r="M215" s="12" t="s">
-        <v>49</v>
+      <c r="M215" s="17" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="216" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C216" s="3">
+        <v>70000001</v>
+      </c>
+      <c r="D216" s="3">
         <v>70000002</v>
       </c>
-      <c r="D216" s="3">
-        <v>70000003</v>
-      </c>
       <c r="E216" s="3">
         <v>1</v>
       </c>
@@ -9046,7 +9050,7 @@
         <v>100</v>
       </c>
       <c r="G216" s="9">
-        <v>10000162</v>
+        <v>10010093</v>
       </c>
       <c r="H216" s="3">
         <v>1</v>
@@ -9055,22 +9059,22 @@
         <v>10000159</v>
       </c>
       <c r="J216" s="8">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K216" s="2">
         <v>0</v>
       </c>
-      <c r="M216" s="11" t="s">
-        <v>104</v>
+      <c r="M216" s="12" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="217" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C217" s="3">
+        <v>70000002</v>
+      </c>
+      <c r="D217" s="3">
         <v>70000003</v>
       </c>
-      <c r="D217" s="3">
-        <v>70000004</v>
-      </c>
       <c r="E217" s="3">
         <v>1</v>
       </c>
@@ -9078,7 +9082,7 @@
         <v>100</v>
       </c>
       <c r="G217" s="9">
-        <v>10010045</v>
+        <v>10000162</v>
       </c>
       <c r="H217" s="3">
         <v>1</v>
@@ -9087,22 +9091,22 @@
         <v>10000159</v>
       </c>
       <c r="J217" s="8">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K217" s="2">
         <v>0</v>
       </c>
       <c r="M217" s="11" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="218" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="218" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C218" s="3">
+        <v>70000003</v>
+      </c>
+      <c r="D218" s="3">
         <v>70000004</v>
       </c>
-      <c r="D218" s="3">
-        <v>70000005</v>
-      </c>
       <c r="E218" s="3">
         <v>1</v>
       </c>
@@ -9110,7 +9114,7 @@
         <v>100</v>
       </c>
       <c r="G218" s="9">
-        <v>10000158</v>
+        <v>10010045</v>
       </c>
       <c r="H218" s="3">
         <v>1</v>
@@ -9119,22 +9123,22 @@
         <v>10000159</v>
       </c>
       <c r="J218" s="8">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K218" s="2">
         <v>0</v>
       </c>
-      <c r="M218" s="9" t="s">
-        <v>106</v>
+      <c r="M218" s="11" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="219" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C219" s="3">
+        <v>70000004</v>
+      </c>
+      <c r="D219" s="3">
         <v>70000005</v>
       </c>
-      <c r="D219" s="3">
-        <v>70000006</v>
-      </c>
       <c r="E219" s="3">
         <v>1</v>
       </c>
@@ -9142,7 +9146,7 @@
         <v>100</v>
       </c>
       <c r="G219" s="9">
-        <v>10010083</v>
+        <v>10000158</v>
       </c>
       <c r="H219" s="3">
         <v>1</v>
@@ -9151,22 +9155,22 @@
         <v>10000159</v>
       </c>
       <c r="J219" s="8">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="K219" s="2">
         <v>0</v>
       </c>
-      <c r="M219" s="16" t="s">
-        <v>107</v>
+      <c r="M219" s="9" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="220" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C220" s="3">
+        <v>70000005</v>
+      </c>
+      <c r="D220" s="3">
         <v>70000006</v>
       </c>
-      <c r="D220" s="3">
-        <v>70000007</v>
-      </c>
       <c r="E220" s="3">
         <v>1</v>
       </c>
@@ -9174,7 +9178,7 @@
         <v>100</v>
       </c>
       <c r="G220" s="9">
-        <v>10000143</v>
+        <v>10010083</v>
       </c>
       <c r="H220" s="3">
         <v>1</v>
@@ -9183,22 +9187,22 @@
         <v>10000159</v>
       </c>
       <c r="J220" s="8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K220" s="2">
         <v>0</v>
       </c>
       <c r="M220" s="16" t="s">
-        <v>47</v>
+        <v>107</v>
       </c>
     </row>
     <row r="221" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C221" s="3">
+        <v>70000006</v>
+      </c>
+      <c r="D221" s="3">
         <v>70000007</v>
       </c>
-      <c r="D221" s="3">
-        <v>70000008</v>
-      </c>
       <c r="E221" s="3">
         <v>1</v>
       </c>
@@ -9206,7 +9210,7 @@
         <v>100</v>
       </c>
       <c r="G221" s="9">
-        <v>10000152</v>
+        <v>10000143</v>
       </c>
       <c r="H221" s="3">
         <v>1</v>
@@ -9215,22 +9219,22 @@
         <v>10000159</v>
       </c>
       <c r="J221" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K221" s="2">
         <v>0</v>
       </c>
-      <c r="M221" s="11" t="s">
-        <v>38</v>
+      <c r="M221" s="16" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="222" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C222" s="3">
+        <v>70000007</v>
+      </c>
+      <c r="D222" s="3">
         <v>70000008</v>
       </c>
-      <c r="D222" s="3">
-        <v>70000009</v>
-      </c>
       <c r="E222" s="3">
         <v>1</v>
       </c>
@@ -9238,7 +9242,7 @@
         <v>100</v>
       </c>
       <c r="G222" s="9">
-        <v>10000157</v>
+        <v>10000152</v>
       </c>
       <c r="H222" s="3">
         <v>1</v>
@@ -9253,16 +9257,16 @@
         <v>0</v>
       </c>
       <c r="M222" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="223" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C223" s="3">
+        <v>70000008</v>
+      </c>
+      <c r="D223" s="3">
         <v>70000009</v>
       </c>
-      <c r="D223" s="3">
-        <v>70000010</v>
-      </c>
       <c r="E223" s="3">
         <v>1</v>
       </c>
@@ -9270,7 +9274,7 @@
         <v>100</v>
       </c>
       <c r="G223" s="9">
-        <v>10010029</v>
+        <v>10000157</v>
       </c>
       <c r="H223" s="3">
         <v>1</v>
@@ -9279,22 +9283,22 @@
         <v>10000159</v>
       </c>
       <c r="J223" s="8">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K223" s="2">
         <v>0</v>
       </c>
       <c r="M223" s="11" t="s">
-        <v>108</v>
+        <v>39</v>
       </c>
     </row>
     <row r="224" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C224" s="3">
+        <v>70000009</v>
+      </c>
+      <c r="D224" s="3">
         <v>70000010</v>
       </c>
-      <c r="D224" s="3">
-        <v>70000011</v>
-      </c>
       <c r="E224" s="3">
         <v>1</v>
       </c>
@@ -9302,7 +9306,7 @@
         <v>100</v>
       </c>
       <c r="G224" s="9">
-        <v>10010086</v>
+        <v>10010029</v>
       </c>
       <c r="H224" s="3">
         <v>1</v>
@@ -9311,30 +9315,30 @@
         <v>10000159</v>
       </c>
       <c r="J224" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K224" s="2">
         <v>0</v>
       </c>
-      <c r="M224" s="12" t="s">
-        <v>27</v>
+      <c r="M224" s="11" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="225" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C225" s="3">
+        <v>70000010</v>
+      </c>
+      <c r="D225" s="3">
         <v>70000011</v>
       </c>
-      <c r="D225" s="3">
-        <v>70000012</v>
-      </c>
       <c r="E225" s="3">
         <v>1</v>
       </c>
       <c r="F225" s="3">
         <v>100</v>
       </c>
-      <c r="G225" s="18">
-        <v>10010101</v>
+      <c r="G225" s="9">
+        <v>10010086</v>
       </c>
       <c r="H225" s="3">
         <v>1</v>
@@ -9343,22 +9347,22 @@
         <v>10000159</v>
       </c>
       <c r="J225" s="8">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K225" s="2">
         <v>0</v>
       </c>
-      <c r="M225" s="8" t="s">
-        <v>109</v>
+      <c r="M225" s="12" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="226" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C226" s="3">
+        <v>70000011</v>
+      </c>
+      <c r="D226" s="3">
         <v>70000012</v>
       </c>
-      <c r="D226" s="3">
-        <v>70000013</v>
-      </c>
       <c r="E226" s="3">
         <v>1</v>
       </c>
@@ -9366,7 +9370,7 @@
         <v>100</v>
       </c>
       <c r="G226" s="18">
-        <v>10010102</v>
+        <v>10010101</v>
       </c>
       <c r="H226" s="3">
         <v>1</v>
@@ -9375,22 +9379,22 @@
         <v>10000159</v>
       </c>
       <c r="J226" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K226" s="2">
         <v>0</v>
       </c>
-      <c r="M226" s="3" t="s">
-        <v>110</v>
+      <c r="M226" s="8" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="227" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C227" s="3">
+        <v>70000012</v>
+      </c>
+      <c r="D227" s="3">
         <v>70000013</v>
       </c>
-      <c r="D227" s="3">
-        <v>0</v>
-      </c>
       <c r="E227" s="3">
         <v>1</v>
       </c>
@@ -9398,7 +9402,7 @@
         <v>100</v>
       </c>
       <c r="G227" s="18">
-        <v>10010103</v>
+        <v>10010102</v>
       </c>
       <c r="H227" s="3">
         <v>1</v>
@@ -9407,54 +9411,54 @@
         <v>10000159</v>
       </c>
       <c r="J227" s="8">
+        <v>10</v>
+      </c>
+      <c r="K227" s="2">
+        <v>0</v>
+      </c>
+      <c r="M227" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="228" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C228" s="3">
+        <v>70000013</v>
+      </c>
+      <c r="D228" s="3">
+        <v>0</v>
+      </c>
+      <c r="E228" s="3">
+        <v>1</v>
+      </c>
+      <c r="F228" s="3">
+        <v>100</v>
+      </c>
+      <c r="G228" s="18">
+        <v>10010103</v>
+      </c>
+      <c r="H228" s="3">
+        <v>1</v>
+      </c>
+      <c r="I228" s="8">
+        <v>10000159</v>
+      </c>
+      <c r="J228" s="8">
         <v>20</v>
       </c>
-      <c r="K227" s="2">
-        <v>0</v>
-      </c>
-      <c r="M227" s="3" t="s">
+      <c r="K228" s="2">
+        <v>0</v>
+      </c>
+      <c r="M228" s="3" t="s">
         <v>111</v>
-      </c>
-    </row>
-    <row r="228" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C228" s="3">
-        <v>80000001</v>
-      </c>
-      <c r="D228" s="3">
-        <v>80000002</v>
-      </c>
-      <c r="E228" s="3">
-        <v>1</v>
-      </c>
-      <c r="F228" s="3">
-        <v>100</v>
-      </c>
-      <c r="G228" s="9">
-        <v>10010083</v>
-      </c>
-      <c r="H228" s="3">
-        <v>1</v>
-      </c>
-      <c r="I228" s="8">
-        <v>10000163</v>
-      </c>
-      <c r="J228" s="8">
-        <v>1</v>
-      </c>
-      <c r="K228" s="2">
-        <v>0</v>
-      </c>
-      <c r="M228" s="3" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="229" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C229" s="3">
+        <v>80000001</v>
+      </c>
+      <c r="D229" s="3">
         <v>80000002</v>
       </c>
-      <c r="D229" s="3">
-        <v>80000003</v>
-      </c>
       <c r="E229" s="3">
         <v>1</v>
       </c>
@@ -9462,7 +9466,7 @@
         <v>100</v>
       </c>
       <c r="G229" s="9">
-        <v>10010086</v>
+        <v>10010083</v>
       </c>
       <c r="H229" s="3">
         <v>1</v>
@@ -9471,22 +9475,22 @@
         <v>10000163</v>
       </c>
       <c r="J229" s="8">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K229" s="2">
         <v>0</v>
       </c>
       <c r="M229" s="3" t="s">
-        <v>27</v>
+        <v>107</v>
       </c>
     </row>
     <row r="230" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C230" s="3">
+        <v>80000002</v>
+      </c>
+      <c r="D230" s="3">
         <v>80000003</v>
       </c>
-      <c r="D230" s="3">
-        <v>80000004</v>
-      </c>
       <c r="E230" s="3">
         <v>1</v>
       </c>
@@ -9494,7 +9498,7 @@
         <v>100</v>
       </c>
       <c r="G230" s="9">
-        <v>10010096</v>
+        <v>10010086</v>
       </c>
       <c r="H230" s="3">
         <v>1</v>
@@ -9503,22 +9507,22 @@
         <v>10000163</v>
       </c>
       <c r="J230" s="8">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="K230" s="2">
         <v>0</v>
       </c>
       <c r="M230" s="3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="231" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="231" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C231" s="3">
+        <v>80000003</v>
+      </c>
+      <c r="D231" s="3">
         <v>80000004</v>
       </c>
-      <c r="D231" s="3">
-        <v>80000005</v>
-      </c>
       <c r="E231" s="3">
         <v>1</v>
       </c>
@@ -9526,7 +9530,7 @@
         <v>100</v>
       </c>
       <c r="G231" s="9">
-        <v>10000139</v>
+        <v>10010096</v>
       </c>
       <c r="H231" s="3">
         <v>1</v>
@@ -9535,22 +9539,22 @@
         <v>10000163</v>
       </c>
       <c r="J231" s="8">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="K231" s="2">
         <v>0</v>
       </c>
       <c r="M231" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="232" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C232" s="3">
+        <v>80000004</v>
+      </c>
+      <c r="D232" s="3">
         <v>80000005</v>
       </c>
-      <c r="D232" s="3">
-        <v>80000006</v>
-      </c>
       <c r="E232" s="3">
         <v>1</v>
       </c>
@@ -9558,7 +9562,7 @@
         <v>100</v>
       </c>
       <c r="G232" s="9">
-        <v>10000143</v>
+        <v>10000139</v>
       </c>
       <c r="H232" s="3">
         <v>1</v>
@@ -9573,16 +9577,16 @@
         <v>0</v>
       </c>
       <c r="M232" s="3" t="s">
-        <v>47</v>
+        <v>113</v>
       </c>
     </row>
     <row r="233" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C233" s="3">
+        <v>80000005</v>
+      </c>
+      <c r="D233" s="3">
         <v>80000006</v>
       </c>
-      <c r="D233" s="3">
-        <v>80000007</v>
-      </c>
       <c r="E233" s="3">
         <v>1</v>
       </c>
@@ -9590,7 +9594,7 @@
         <v>100</v>
       </c>
       <c r="G233" s="9">
-        <v>10000152</v>
+        <v>10000143</v>
       </c>
       <c r="H233" s="3">
         <v>1</v>
@@ -9599,22 +9603,22 @@
         <v>10000163</v>
       </c>
       <c r="J233" s="8">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="K233" s="2">
         <v>0</v>
       </c>
       <c r="M233" s="3" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
     </row>
     <row r="234" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C234" s="3">
+        <v>80000006</v>
+      </c>
+      <c r="D234" s="3">
         <v>80000007</v>
       </c>
-      <c r="D234" s="3">
-        <v>80000008</v>
-      </c>
       <c r="E234" s="3">
         <v>1</v>
       </c>
@@ -9622,7 +9626,7 @@
         <v>100</v>
       </c>
       <c r="G234" s="9">
-        <v>10000155</v>
+        <v>10000152</v>
       </c>
       <c r="H234" s="3">
         <v>1</v>
@@ -9631,22 +9635,22 @@
         <v>10000163</v>
       </c>
       <c r="J234" s="8">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="K234" s="2">
         <v>0</v>
       </c>
       <c r="M234" s="3" t="s">
-        <v>114</v>
+        <v>38</v>
       </c>
     </row>
     <row r="235" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C235" s="3">
+        <v>80000007</v>
+      </c>
+      <c r="D235" s="3">
         <v>80000008</v>
       </c>
-      <c r="D235" s="3">
-        <v>80000009</v>
-      </c>
       <c r="E235" s="3">
         <v>1</v>
       </c>
@@ -9654,7 +9658,7 @@
         <v>100</v>
       </c>
       <c r="G235" s="9">
-        <v>10000158</v>
+        <v>10000155</v>
       </c>
       <c r="H235" s="3">
         <v>1</v>
@@ -9663,22 +9667,22 @@
         <v>10000163</v>
       </c>
       <c r="J235" s="8">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="K235" s="2">
         <v>0</v>
       </c>
       <c r="M235" s="3" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="236" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C236" s="3">
+        <v>80000008</v>
+      </c>
+      <c r="D236" s="3">
         <v>80000009</v>
       </c>
-      <c r="D236" s="3">
-        <v>0</v>
-      </c>
       <c r="E236" s="3">
         <v>1</v>
       </c>
@@ -9686,7 +9690,7 @@
         <v>100</v>
       </c>
       <c r="G236" s="9">
-        <v>10010093</v>
+        <v>10000158</v>
       </c>
       <c r="H236" s="3">
         <v>1</v>
@@ -9695,55 +9699,54 @@
         <v>10000163</v>
       </c>
       <c r="J236" s="8">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="K236" s="2">
         <v>0</v>
       </c>
       <c r="M236" s="3" t="s">
-        <v>49</v>
+        <v>106</v>
       </c>
     </row>
     <row r="237" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C237" s="3">
-        <v>90000001</v>
+        <v>80000009</v>
       </c>
       <c r="D237" s="3">
-        <v>90000002</v>
-      </c>
-      <c r="E237" s="2">
+        <v>0</v>
+      </c>
+      <c r="E237" s="3">
         <v>1</v>
       </c>
       <c r="F237" s="3">
         <v>100</v>
       </c>
-      <c r="G237" s="3">
-        <v>10000144</v>
+      <c r="G237" s="9">
+        <v>10010093</v>
       </c>
       <c r="H237" s="3">
         <v>1</v>
       </c>
-      <c r="I237" s="9">
-        <v>10000148</v>
+      <c r="I237" s="8">
+        <v>10000163</v>
       </c>
       <c r="J237" s="8">
-        <v>10</v>
+        <v>35</v>
       </c>
       <c r="K237" s="2">
         <v>0</v>
       </c>
-      <c r="L237" s="2"/>
-      <c r="M237" s="7" t="s">
-        <v>115</v>
+      <c r="M237" s="3" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="238" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C238" s="3">
+        <v>90000001</v>
+      </c>
+      <c r="D238" s="3">
         <v>90000002</v>
       </c>
-      <c r="D238" s="3">
-        <v>90000003</v>
-      </c>
       <c r="E238" s="2">
         <v>1</v>
       </c>
@@ -9751,7 +9754,7 @@
         <v>100</v>
       </c>
       <c r="G238" s="3">
-        <v>10000145</v>
+        <v>10000144</v>
       </c>
       <c r="H238" s="3">
         <v>1</v>
@@ -9766,15 +9769,17 @@
         <v>0</v>
       </c>
       <c r="L238" s="2"/>
-      <c r="M238" s="2"/>
+      <c r="M238" s="7" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="239" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C239" s="3">
+        <v>90000002</v>
+      </c>
+      <c r="D239" s="3">
         <v>90000003</v>
       </c>
-      <c r="D239" s="3">
-        <v>90000004</v>
-      </c>
       <c r="E239" s="2">
         <v>1</v>
       </c>
@@ -9782,7 +9787,7 @@
         <v>100</v>
       </c>
       <c r="G239" s="3">
-        <v>10000146</v>
+        <v>10000145</v>
       </c>
       <c r="H239" s="3">
         <v>1</v>
@@ -9801,11 +9806,11 @@
     </row>
     <row r="240" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C240" s="3">
+        <v>90000003</v>
+      </c>
+      <c r="D240" s="3">
         <v>90000004</v>
       </c>
-      <c r="D240" s="3">
-        <v>90000005</v>
-      </c>
       <c r="E240" s="2">
         <v>1</v>
       </c>
@@ -9813,7 +9818,7 @@
         <v>100</v>
       </c>
       <c r="G240" s="3">
-        <v>10000147</v>
+        <v>10000146</v>
       </c>
       <c r="H240" s="3">
         <v>1</v>
@@ -9832,11 +9837,11 @@
     </row>
     <row r="241" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C241" s="3">
+        <v>90000004</v>
+      </c>
+      <c r="D241" s="3">
         <v>90000005</v>
       </c>
-      <c r="D241" s="3">
-        <v>90000006</v>
-      </c>
       <c r="E241" s="2">
         <v>1</v>
       </c>
@@ -9844,7 +9849,7 @@
         <v>100</v>
       </c>
       <c r="G241" s="3">
-        <v>10010033</v>
+        <v>10000147</v>
       </c>
       <c r="H241" s="3">
         <v>1</v>
@@ -9852,8 +9857,8 @@
       <c r="I241" s="9">
         <v>10000148</v>
       </c>
-      <c r="J241" s="10">
-        <v>50</v>
+      <c r="J241" s="8">
+        <v>10</v>
       </c>
       <c r="K241" s="2">
         <v>0</v>
@@ -9863,11 +9868,11 @@
     </row>
     <row r="242" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C242" s="3">
+        <v>90000005</v>
+      </c>
+      <c r="D242" s="3">
         <v>90000006</v>
       </c>
-      <c r="D242" s="3">
-        <v>90000007</v>
-      </c>
       <c r="E242" s="2">
         <v>1</v>
       </c>
@@ -9875,7 +9880,7 @@
         <v>100</v>
       </c>
       <c r="G242" s="3">
-        <v>10010083</v>
+        <v>10010033</v>
       </c>
       <c r="H242" s="3">
         <v>1</v>
@@ -9884,7 +9889,7 @@
         <v>10000148</v>
       </c>
       <c r="J242" s="10">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="K242" s="2">
         <v>0</v>
@@ -9894,11 +9899,11 @@
     </row>
     <row r="243" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C243" s="3">
+        <v>90000006</v>
+      </c>
+      <c r="D243" s="3">
         <v>90000007</v>
       </c>
-      <c r="D243" s="3">
-        <v>90000008</v>
-      </c>
       <c r="E243" s="2">
         <v>1</v>
       </c>
@@ -9906,7 +9911,7 @@
         <v>100</v>
       </c>
       <c r="G243" s="3">
-        <v>10010098</v>
+        <v>10010083</v>
       </c>
       <c r="H243" s="3">
         <v>1</v>
@@ -9925,11 +9930,11 @@
     </row>
     <row r="244" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C244" s="3">
+        <v>90000007</v>
+      </c>
+      <c r="D244" s="3">
         <v>90000008</v>
       </c>
-      <c r="D244" s="3">
-        <v>90000009</v>
-      </c>
       <c r="E244" s="2">
         <v>1</v>
       </c>
@@ -9937,7 +9942,7 @@
         <v>100</v>
       </c>
       <c r="G244" s="3">
-        <v>10010085</v>
+        <v>10010098</v>
       </c>
       <c r="H244" s="3">
         <v>1</v>
@@ -9946,7 +9951,7 @@
         <v>10000148</v>
       </c>
       <c r="J244" s="10">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K244" s="2">
         <v>0</v>
@@ -9956,11 +9961,11 @@
     </row>
     <row r="245" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C245" s="3">
+        <v>90000008</v>
+      </c>
+      <c r="D245" s="3">
         <v>90000009</v>
       </c>
-      <c r="D245" s="3">
-        <v>90000010</v>
-      </c>
       <c r="E245" s="2">
         <v>1</v>
       </c>
@@ -9968,7 +9973,7 @@
         <v>100</v>
       </c>
       <c r="G245" s="3">
-        <v>10000131</v>
+        <v>10010085</v>
       </c>
       <c r="H245" s="3">
         <v>1</v>
@@ -9977,20 +9982,21 @@
         <v>10000148</v>
       </c>
       <c r="J245" s="10">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K245" s="2">
         <v>0</v>
       </c>
       <c r="L245" s="2"/>
+      <c r="M245" s="2"/>
     </row>
     <row r="246" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C246" s="3">
+        <v>90000009</v>
+      </c>
+      <c r="D246" s="3">
         <v>90000010</v>
       </c>
-      <c r="D246" s="3">
-        <v>0</v>
-      </c>
       <c r="E246" s="2">
         <v>1</v>
       </c>
@@ -9998,7 +10004,7 @@
         <v>100</v>
       </c>
       <c r="G246" s="3">
-        <v>10000132</v>
+        <v>10000131</v>
       </c>
       <c r="H246" s="3">
         <v>1</v>
@@ -10016,10 +10022,10 @@
     </row>
     <row r="247" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C247" s="3">
-        <v>91000001</v>
+        <v>90000010</v>
       </c>
       <c r="D247" s="3">
-        <v>91000002</v>
+        <v>0</v>
       </c>
       <c r="E247" s="2">
         <v>1</v>
@@ -10028,31 +10034,29 @@
         <v>100</v>
       </c>
       <c r="G247" s="3">
-        <v>10010086</v>
+        <v>10000132</v>
       </c>
       <c r="H247" s="3">
         <v>1</v>
       </c>
-      <c r="I247" s="19">
-        <v>36</v>
-      </c>
-      <c r="J247" s="20">
-        <v>8</v>
+      <c r="I247" s="9">
+        <v>10000148</v>
+      </c>
+      <c r="J247" s="10">
+        <v>3</v>
       </c>
       <c r="K247" s="2">
         <v>0</v>
       </c>
-      <c r="M247" s="3" t="s">
-        <v>27</v>
-      </c>
+      <c r="L247" s="2"/>
     </row>
     <row r="248" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C248" s="3">
+        <v>91000001</v>
+      </c>
+      <c r="D248" s="3">
         <v>91000002</v>
       </c>
-      <c r="D248" s="3">
-        <v>91000003</v>
-      </c>
       <c r="E248" s="2">
         <v>1</v>
       </c>
@@ -10060,7 +10064,7 @@
         <v>100</v>
       </c>
       <c r="G248" s="3">
-        <v>10010096</v>
+        <v>10010086</v>
       </c>
       <c r="H248" s="3">
         <v>1</v>
@@ -10069,22 +10073,22 @@
         <v>36</v>
       </c>
       <c r="J248" s="20">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="K248" s="2">
         <v>0</v>
       </c>
       <c r="M248" s="3" t="s">
-        <v>112</v>
+        <v>27</v>
       </c>
     </row>
     <row r="249" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C249" s="3">
+        <v>91000002</v>
+      </c>
+      <c r="D249" s="3">
         <v>91000003</v>
       </c>
-      <c r="D249" s="3">
-        <v>91000004</v>
-      </c>
       <c r="E249" s="2">
         <v>1</v>
       </c>
@@ -10092,7 +10096,7 @@
         <v>100</v>
       </c>
       <c r="G249" s="3">
-        <v>10010074</v>
+        <v>10010096</v>
       </c>
       <c r="H249" s="3">
         <v>1</v>
@@ -10101,22 +10105,22 @@
         <v>36</v>
       </c>
       <c r="J249" s="20">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="K249" s="2">
         <v>0</v>
       </c>
       <c r="M249" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="250" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C250" s="3">
+        <v>91000003</v>
+      </c>
+      <c r="D250" s="3">
         <v>91000004</v>
       </c>
-      <c r="D250" s="3">
-        <v>91000005</v>
-      </c>
       <c r="E250" s="2">
         <v>1</v>
       </c>
@@ -10124,7 +10128,7 @@
         <v>100</v>
       </c>
       <c r="G250" s="3">
-        <v>10010075</v>
+        <v>10010074</v>
       </c>
       <c r="H250" s="3">
         <v>1</v>
@@ -10133,30 +10137,30 @@
         <v>36</v>
       </c>
       <c r="J250" s="20">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="K250" s="2">
         <v>0</v>
       </c>
       <c r="M250" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
     </row>
     <row r="251" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C251" s="3">
+        <v>91000004</v>
+      </c>
+      <c r="D251" s="3">
         <v>91000005</v>
       </c>
-      <c r="D251" s="3">
-        <v>91000006</v>
-      </c>
       <c r="E251" s="2">
         <v>1</v>
       </c>
       <c r="F251" s="3">
         <v>100</v>
       </c>
-      <c r="G251" s="2">
-        <v>10010083</v>
+      <c r="G251" s="3">
+        <v>10010075</v>
       </c>
       <c r="H251" s="3">
         <v>1</v>
@@ -10165,22 +10169,22 @@
         <v>36</v>
       </c>
       <c r="J251" s="20">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K251" s="2">
         <v>0</v>
       </c>
-      <c r="M251" s="15" t="s">
-        <v>119</v>
+      <c r="M251" s="3" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="252" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C252" s="3">
+        <v>91000005</v>
+      </c>
+      <c r="D252" s="3">
         <v>91000006</v>
       </c>
-      <c r="D252" s="3">
-        <v>91000007</v>
-      </c>
       <c r="E252" s="2">
         <v>1</v>
       </c>
@@ -10188,7 +10192,7 @@
         <v>100</v>
       </c>
       <c r="G252" s="2">
-        <v>10010098</v>
+        <v>10010083</v>
       </c>
       <c r="H252" s="3">
         <v>1</v>
@@ -10203,24 +10207,24 @@
         <v>0</v>
       </c>
       <c r="M252" s="15" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="253" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C253" s="3">
+        <v>91000006</v>
+      </c>
+      <c r="D253" s="3">
         <v>91000007</v>
       </c>
-      <c r="D253" s="3">
-        <v>0</v>
-      </c>
       <c r="E253" s="2">
         <v>1</v>
       </c>
       <c r="F253" s="3">
         <v>100</v>
       </c>
-      <c r="G253" s="9">
-        <v>10010040</v>
+      <c r="G253" s="2">
+        <v>10010098</v>
       </c>
       <c r="H253" s="3">
         <v>1</v>
@@ -10229,63 +10233,62 @@
         <v>36</v>
       </c>
       <c r="J253" s="20">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="K253" s="2">
-        <v>1</v>
-      </c>
-      <c r="M253" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="M253" s="15" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="254" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C254" s="3">
+        <v>91000007</v>
+      </c>
+      <c r="D254" s="3">
+        <v>0</v>
+      </c>
+      <c r="E254" s="2">
+        <v>1</v>
+      </c>
+      <c r="F254" s="3">
+        <v>100</v>
+      </c>
+      <c r="G254" s="9">
+        <v>10010040</v>
+      </c>
+      <c r="H254" s="3">
+        <v>1</v>
+      </c>
+      <c r="I254" s="19">
+        <v>36</v>
+      </c>
+      <c r="J254" s="20">
+        <v>100</v>
+      </c>
+      <c r="K254" s="2">
+        <v>1</v>
+      </c>
+      <c r="M254" s="9" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="254" spans="3:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C254" s="3">
+    <row r="255" spans="3:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C255" s="3">
         <v>92000001</v>
       </c>
-      <c r="D254" s="3">
+      <c r="D255" s="3">
         <v>92000002</v>
       </c>
-      <c r="E254" s="2">
-        <v>1</v>
-      </c>
-      <c r="F254" s="3">
-        <v>100</v>
-      </c>
-      <c r="G254" s="3">
+      <c r="E255" s="2">
+        <v>1</v>
+      </c>
+      <c r="F255" s="3">
+        <v>100</v>
+      </c>
+      <c r="G255" s="3">
         <v>10060100</v>
-      </c>
-      <c r="H254" s="3">
-        <v>1</v>
-      </c>
-      <c r="I254" s="9">
-        <v>10000136</v>
-      </c>
-      <c r="J254" s="3">
-        <v>50</v>
-      </c>
-      <c r="K254" s="2">
-        <v>0</v>
-      </c>
-      <c r="M254" s="22" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q254" s="7"/>
-    </row>
-    <row r="255" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C255" s="3">
-        <v>92000002</v>
-      </c>
-      <c r="D255" s="3">
-        <v>92000003</v>
-      </c>
-      <c r="E255" s="2">
-        <v>1</v>
-      </c>
-      <c r="F255" s="3">
-        <v>100</v>
-      </c>
-      <c r="G255" s="3">
-        <v>10060200</v>
       </c>
       <c r="H255" s="3">
         <v>1</v>
@@ -10300,16 +10303,17 @@
         <v>0</v>
       </c>
       <c r="M255" s="22" t="s">
-        <v>126</v>
-      </c>
+        <v>125</v>
+      </c>
+      <c r="Q255" s="7"/>
     </row>
     <row r="256" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C256" s="3">
+        <v>92000002</v>
+      </c>
+      <c r="D256" s="3">
         <v>92000003</v>
       </c>
-      <c r="D256" s="3">
-        <v>92000004</v>
-      </c>
       <c r="E256" s="2">
         <v>1</v>
       </c>
@@ -10317,7 +10321,7 @@
         <v>100</v>
       </c>
       <c r="G256" s="3">
-        <v>10060300</v>
+        <v>10060200</v>
       </c>
       <c r="H256" s="3">
         <v>1</v>
@@ -10332,16 +10336,16 @@
         <v>0</v>
       </c>
       <c r="M256" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="257" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C257" s="3">
+        <v>92000003</v>
+      </c>
+      <c r="D257" s="3">
         <v>92000004</v>
       </c>
-      <c r="D257" s="3">
-        <v>92000005</v>
-      </c>
       <c r="E257" s="2">
         <v>1</v>
       </c>
@@ -10349,7 +10353,7 @@
         <v>100</v>
       </c>
       <c r="G257" s="3">
-        <v>10060400</v>
+        <v>10060300</v>
       </c>
       <c r="H257" s="3">
         <v>1</v>
@@ -10364,16 +10368,16 @@
         <v>0</v>
       </c>
       <c r="M257" s="22" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="258" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C258" s="3">
+        <v>92000004</v>
+      </c>
+      <c r="D258" s="3">
         <v>92000005</v>
       </c>
-      <c r="D258" s="3">
-        <v>92000006</v>
-      </c>
       <c r="E258" s="2">
         <v>1</v>
       </c>
@@ -10381,7 +10385,7 @@
         <v>100</v>
       </c>
       <c r="G258" s="3">
-        <v>10060500</v>
+        <v>10060400</v>
       </c>
       <c r="H258" s="3">
         <v>1</v>
@@ -10396,16 +10400,16 @@
         <v>0</v>
       </c>
       <c r="M258" s="22" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="259" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C259" s="3">
+        <v>92000005</v>
+      </c>
+      <c r="D259" s="3">
         <v>92000006</v>
       </c>
-      <c r="D259" s="3">
-        <v>92000007</v>
-      </c>
       <c r="E259" s="2">
         <v>1</v>
       </c>
@@ -10413,7 +10417,7 @@
         <v>100</v>
       </c>
       <c r="G259" s="3">
-        <v>10060600</v>
+        <v>10060500</v>
       </c>
       <c r="H259" s="3">
         <v>1</v>
@@ -10428,16 +10432,16 @@
         <v>0</v>
       </c>
       <c r="M259" s="22" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="260" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C260" s="3">
+        <v>92000006</v>
+      </c>
+      <c r="D260" s="3">
         <v>92000007</v>
       </c>
-      <c r="D260" s="3">
-        <v>92000008</v>
-      </c>
       <c r="E260" s="2">
         <v>1</v>
       </c>
@@ -10445,7 +10449,7 @@
         <v>100</v>
       </c>
       <c r="G260" s="3">
-        <v>10060700</v>
+        <v>10060600</v>
       </c>
       <c r="H260" s="3">
         <v>1</v>
@@ -10460,16 +10464,16 @@
         <v>0</v>
       </c>
       <c r="M260" s="22" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="261" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C261" s="3">
+        <v>92000007</v>
+      </c>
+      <c r="D261" s="3">
         <v>92000008</v>
       </c>
-      <c r="D261" s="3">
-        <v>0</v>
-      </c>
       <c r="E261" s="2">
         <v>1</v>
       </c>
@@ -10477,7 +10481,7 @@
         <v>100</v>
       </c>
       <c r="G261" s="3">
-        <v>10000212</v>
+        <v>10060700</v>
       </c>
       <c r="H261" s="3">
         <v>1</v>
@@ -10486,18 +10490,50 @@
         <v>10000136</v>
       </c>
       <c r="J261" s="3">
+        <v>50</v>
+      </c>
+      <c r="K261" s="2">
+        <v>0</v>
+      </c>
+      <c r="M261" s="22" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="262" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C262" s="3">
+        <v>92000008</v>
+      </c>
+      <c r="D262" s="3">
+        <v>0</v>
+      </c>
+      <c r="E262" s="2">
+        <v>1</v>
+      </c>
+      <c r="F262" s="3">
+        <v>100</v>
+      </c>
+      <c r="G262" s="3">
+        <v>10000212</v>
+      </c>
+      <c r="H262" s="3">
+        <v>1</v>
+      </c>
+      <c r="I262" s="9">
+        <v>10000136</v>
+      </c>
+      <c r="J262" s="3">
         <v>150</v>
       </c>
-      <c r="K261" s="2">
-        <v>0</v>
-      </c>
-      <c r="M261" s="19" t="s">
+      <c r="K262" s="2">
+        <v>0</v>
+      </c>
+      <c r="M262" s="19" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="262" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="263" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="264" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="265" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StoreSellConfig.xlsx
+++ b/Excel/StoreSellConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E064359-42FD-47F8-885D-58DB95129CA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EA3FAC0-F6CF-4276-AC99-4362047651F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="169" uniqueCount="136">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="135">
   <si>
     <t>Id</t>
   </si>
@@ -471,9 +471,6 @@
   </si>
   <si>
     <t>大师球</t>
-  </si>
-  <si>
-    <t>活动1商店</t>
   </si>
   <si>
     <t>基础宠物技能袋子</t>
@@ -2557,7 +2554,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q265"/>
+  <dimension ref="A1:Q262"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="5" width="14" customWidth="1"/>
@@ -7033,7 +7030,7 @@
         <v>0</v>
       </c>
       <c r="M153" s="11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="154" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -7065,7 +7062,7 @@
         <v>0</v>
       </c>
       <c r="M154" s="11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="155" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -7097,7 +7094,7 @@
         <v>0</v>
       </c>
       <c r="M155" s="11" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="156" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -7129,7 +7126,7 @@
         <v>0</v>
       </c>
       <c r="M156" s="11" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="157" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -7161,7 +7158,7 @@
         <v>0</v>
       </c>
       <c r="M157" s="11" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="158" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -7193,7 +7190,7 @@
         <v>0</v>
       </c>
       <c r="M158" s="11" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="159" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -7225,7 +7222,7 @@
         <v>0</v>
       </c>
       <c r="M159" s="11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="160" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -9759,18 +9756,18 @@
       <c r="H238" s="3">
         <v>1</v>
       </c>
-      <c r="I238" s="9">
-        <v>10000148</v>
+      <c r="I238" s="8">
+        <v>10000184</v>
       </c>
       <c r="J238" s="8">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="K238" s="2">
         <v>0</v>
       </c>
       <c r="L238" s="2"/>
-      <c r="M238" s="7" t="s">
-        <v>115</v>
+      <c r="M238" s="12" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="239" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
@@ -9792,17 +9789,19 @@
       <c r="H239" s="3">
         <v>1</v>
       </c>
-      <c r="I239" s="9">
-        <v>10000148</v>
+      <c r="I239" s="8">
+        <v>10000184</v>
       </c>
       <c r="J239" s="8">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K239" s="2">
         <v>0</v>
       </c>
       <c r="L239" s="2"/>
-      <c r="M239" s="2"/>
+      <c r="M239" s="16" t="s">
+        <v>107</v>
+      </c>
     </row>
     <row r="240" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C240" s="3">
@@ -9823,17 +9822,19 @@
       <c r="H240" s="3">
         <v>1</v>
       </c>
-      <c r="I240" s="9">
-        <v>10000148</v>
+      <c r="I240" s="8">
+        <v>10000184</v>
       </c>
       <c r="J240" s="8">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="K240" s="2">
         <v>0</v>
       </c>
       <c r="L240" s="2"/>
-      <c r="M240" s="2"/>
+      <c r="M240" s="12" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="241" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C241" s="3">
@@ -9854,17 +9855,19 @@
       <c r="H241" s="3">
         <v>1</v>
       </c>
-      <c r="I241" s="9">
-        <v>10000148</v>
+      <c r="I241" s="8">
+        <v>10000184</v>
       </c>
       <c r="J241" s="8">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="K241" s="2">
         <v>0</v>
       </c>
       <c r="L241" s="2"/>
-      <c r="M241" s="2"/>
+      <c r="M241" s="11" t="s">
+        <v>47</v>
+      </c>
     </row>
     <row r="242" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C242" s="3">
@@ -9885,17 +9888,19 @@
       <c r="H242" s="3">
         <v>1</v>
       </c>
-      <c r="I242" s="9">
-        <v>10000148</v>
-      </c>
-      <c r="J242" s="10">
+      <c r="I242" s="8">
+        <v>10000184</v>
+      </c>
+      <c r="J242" s="8">
         <v>50</v>
       </c>
       <c r="K242" s="2">
         <v>0</v>
       </c>
       <c r="L242" s="2"/>
-      <c r="M242" s="2"/>
+      <c r="M242" s="11" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="243" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C243" s="3">
@@ -9916,24 +9921,26 @@
       <c r="H243" s="3">
         <v>1</v>
       </c>
-      <c r="I243" s="9">
-        <v>10000148</v>
-      </c>
-      <c r="J243" s="10">
-        <v>5</v>
+      <c r="I243" s="8">
+        <v>10000184</v>
+      </c>
+      <c r="J243" s="8">
+        <v>100</v>
       </c>
       <c r="K243" s="2">
         <v>0</v>
       </c>
       <c r="L243" s="2"/>
-      <c r="M243" s="2"/>
+      <c r="M243" s="11" t="s">
+        <v>45</v>
+      </c>
     </row>
     <row r="244" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C244" s="3">
         <v>90000007</v>
       </c>
       <c r="D244" s="3">
-        <v>90000008</v>
+        <v>0</v>
       </c>
       <c r="E244" s="2">
         <v>1</v>
@@ -9947,24 +9954,26 @@
       <c r="H244" s="3">
         <v>1</v>
       </c>
-      <c r="I244" s="9">
-        <v>10000148</v>
-      </c>
-      <c r="J244" s="10">
-        <v>5</v>
+      <c r="I244" s="8">
+        <v>10000184</v>
+      </c>
+      <c r="J244" s="8">
+        <v>45</v>
       </c>
       <c r="K244" s="2">
         <v>0</v>
       </c>
       <c r="L244" s="2"/>
-      <c r="M244" s="2"/>
+      <c r="M244" s="11" t="s">
+        <v>105</v>
+      </c>
     </row>
     <row r="245" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C245" s="3">
-        <v>90000008</v>
+        <v>91000001</v>
       </c>
       <c r="D245" s="3">
-        <v>90000009</v>
+        <v>91000002</v>
       </c>
       <c r="E245" s="2">
         <v>1</v>
@@ -9973,29 +9982,30 @@
         <v>100</v>
       </c>
       <c r="G245" s="3">
-        <v>10010085</v>
+        <v>10010086</v>
       </c>
       <c r="H245" s="3">
         <v>1</v>
       </c>
-      <c r="I245" s="9">
-        <v>10000148</v>
-      </c>
-      <c r="J245" s="10">
-        <v>2</v>
+      <c r="I245" s="19">
+        <v>36</v>
+      </c>
+      <c r="J245" s="20">
+        <v>8</v>
       </c>
       <c r="K245" s="2">
         <v>0</v>
       </c>
-      <c r="L245" s="2"/>
-      <c r="M245" s="2"/>
+      <c r="M245" s="3" t="s">
+        <v>27</v>
+      </c>
     </row>
     <row r="246" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C246" s="3">
-        <v>90000009</v>
+        <v>91000002</v>
       </c>
       <c r="D246" s="3">
-        <v>90000010</v>
+        <v>91000003</v>
       </c>
       <c r="E246" s="2">
         <v>1</v>
@@ -10004,28 +10014,30 @@
         <v>100</v>
       </c>
       <c r="G246" s="3">
-        <v>10000131</v>
+        <v>10010096</v>
       </c>
       <c r="H246" s="3">
         <v>1</v>
       </c>
-      <c r="I246" s="9">
-        <v>10000148</v>
-      </c>
-      <c r="J246" s="10">
-        <v>3</v>
+      <c r="I246" s="19">
+        <v>36</v>
+      </c>
+      <c r="J246" s="20">
+        <v>20</v>
       </c>
       <c r="K246" s="2">
         <v>0</v>
       </c>
-      <c r="L246" s="2"/>
+      <c r="M246" s="3" t="s">
+        <v>112</v>
+      </c>
     </row>
     <row r="247" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C247" s="3">
-        <v>90000010</v>
+        <v>91000003</v>
       </c>
       <c r="D247" s="3">
-        <v>0</v>
+        <v>91000004</v>
       </c>
       <c r="E247" s="2">
         <v>1</v>
@@ -10034,28 +10046,30 @@
         <v>100</v>
       </c>
       <c r="G247" s="3">
-        <v>10000132</v>
+        <v>10010074</v>
       </c>
       <c r="H247" s="3">
         <v>1</v>
       </c>
-      <c r="I247" s="9">
-        <v>10000148</v>
-      </c>
-      <c r="J247" s="10">
-        <v>3</v>
+      <c r="I247" s="19">
+        <v>36</v>
+      </c>
+      <c r="J247" s="20">
+        <v>8</v>
       </c>
       <c r="K247" s="2">
         <v>0</v>
       </c>
-      <c r="L247" s="2"/>
+      <c r="M247" s="3" t="s">
+        <v>115</v>
+      </c>
     </row>
     <row r="248" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C248" s="3">
-        <v>91000001</v>
+        <v>91000004</v>
       </c>
       <c r="D248" s="3">
-        <v>91000002</v>
+        <v>91000005</v>
       </c>
       <c r="E248" s="2">
         <v>1</v>
@@ -10064,7 +10078,7 @@
         <v>100</v>
       </c>
       <c r="G248" s="3">
-        <v>10010086</v>
+        <v>10010075</v>
       </c>
       <c r="H248" s="3">
         <v>1</v>
@@ -10073,21 +10087,21 @@
         <v>36</v>
       </c>
       <c r="J248" s="20">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="K248" s="2">
         <v>0</v>
       </c>
       <c r="M248" s="3" t="s">
-        <v>27</v>
+        <v>116</v>
       </c>
     </row>
     <row r="249" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C249" s="3">
-        <v>91000002</v>
+        <v>91000005</v>
       </c>
       <c r="D249" s="3">
-        <v>91000003</v>
+        <v>91000006</v>
       </c>
       <c r="E249" s="2">
         <v>1</v>
@@ -10095,8 +10109,8 @@
       <c r="F249" s="3">
         <v>100</v>
       </c>
-      <c r="G249" s="3">
-        <v>10010096</v>
+      <c r="G249" s="2">
+        <v>10010083</v>
       </c>
       <c r="H249" s="3">
         <v>1</v>
@@ -10105,21 +10119,21 @@
         <v>36</v>
       </c>
       <c r="J249" s="20">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K249" s="2">
         <v>0</v>
       </c>
-      <c r="M249" s="3" t="s">
-        <v>112</v>
+      <c r="M249" s="15" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="250" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C250" s="3">
-        <v>91000003</v>
+        <v>91000006</v>
       </c>
       <c r="D250" s="3">
-        <v>91000004</v>
+        <v>91000007</v>
       </c>
       <c r="E250" s="2">
         <v>1</v>
@@ -10127,8 +10141,8 @@
       <c r="F250" s="3">
         <v>100</v>
       </c>
-      <c r="G250" s="3">
-        <v>10010074</v>
+      <c r="G250" s="2">
+        <v>10010098</v>
       </c>
       <c r="H250" s="3">
         <v>1</v>
@@ -10137,21 +10151,21 @@
         <v>36</v>
       </c>
       <c r="J250" s="20">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K250" s="2">
         <v>0</v>
       </c>
-      <c r="M250" s="3" t="s">
-        <v>116</v>
+      <c r="M250" s="15" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="251" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C251" s="3">
-        <v>91000004</v>
+        <v>91000007</v>
       </c>
       <c r="D251" s="3">
-        <v>91000005</v>
+        <v>0</v>
       </c>
       <c r="E251" s="2">
         <v>1</v>
@@ -10159,8 +10173,8 @@
       <c r="F251" s="3">
         <v>100</v>
       </c>
-      <c r="G251" s="3">
-        <v>10010075</v>
+      <c r="G251" s="9">
+        <v>10010040</v>
       </c>
       <c r="H251" s="3">
         <v>1</v>
@@ -10169,21 +10183,21 @@
         <v>36</v>
       </c>
       <c r="J251" s="20">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="K251" s="2">
-        <v>0</v>
-      </c>
-      <c r="M251" s="3" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="252" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="M251" s="9" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="252" spans="3:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C252" s="3">
-        <v>91000005</v>
+        <v>92000001</v>
       </c>
       <c r="D252" s="3">
-        <v>91000006</v>
+        <v>92000002</v>
       </c>
       <c r="E252" s="2">
         <v>1</v>
@@ -10191,31 +10205,32 @@
       <c r="F252" s="3">
         <v>100</v>
       </c>
-      <c r="G252" s="2">
-        <v>10010083</v>
+      <c r="G252" s="3">
+        <v>10060100</v>
       </c>
       <c r="H252" s="3">
         <v>1</v>
       </c>
-      <c r="I252" s="19">
-        <v>36</v>
-      </c>
-      <c r="J252" s="20">
-        <v>1</v>
+      <c r="I252" s="9">
+        <v>10000136</v>
+      </c>
+      <c r="J252" s="3">
+        <v>50</v>
       </c>
       <c r="K252" s="2">
         <v>0</v>
       </c>
-      <c r="M252" s="15" t="s">
-        <v>119</v>
-      </c>
+      <c r="M252" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q252" s="7"/>
     </row>
     <row r="253" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C253" s="3">
-        <v>91000006</v>
+        <v>92000002</v>
       </c>
       <c r="D253" s="3">
-        <v>91000007</v>
+        <v>92000003</v>
       </c>
       <c r="E253" s="2">
         <v>1</v>
@@ -10223,31 +10238,31 @@
       <c r="F253" s="3">
         <v>100</v>
       </c>
-      <c r="G253" s="2">
-        <v>10010098</v>
+      <c r="G253" s="3">
+        <v>10060200</v>
       </c>
       <c r="H253" s="3">
         <v>1</v>
       </c>
-      <c r="I253" s="19">
-        <v>36</v>
-      </c>
-      <c r="J253" s="20">
-        <v>1</v>
+      <c r="I253" s="9">
+        <v>10000136</v>
+      </c>
+      <c r="J253" s="3">
+        <v>50</v>
       </c>
       <c r="K253" s="2">
         <v>0</v>
       </c>
-      <c r="M253" s="15" t="s">
-        <v>118</v>
+      <c r="M253" s="22" t="s">
+        <v>125</v>
       </c>
     </row>
     <row r="254" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C254" s="3">
-        <v>91000007</v>
+        <v>92000003</v>
       </c>
       <c r="D254" s="3">
-        <v>0</v>
+        <v>92000004</v>
       </c>
       <c r="E254" s="2">
         <v>1</v>
@@ -10255,31 +10270,31 @@
       <c r="F254" s="3">
         <v>100</v>
       </c>
-      <c r="G254" s="9">
-        <v>10010040</v>
+      <c r="G254" s="3">
+        <v>10060300</v>
       </c>
       <c r="H254" s="3">
         <v>1</v>
       </c>
-      <c r="I254" s="19">
-        <v>36</v>
-      </c>
-      <c r="J254" s="20">
-        <v>100</v>
+      <c r="I254" s="9">
+        <v>10000136</v>
+      </c>
+      <c r="J254" s="3">
+        <v>50</v>
       </c>
       <c r="K254" s="2">
-        <v>1</v>
-      </c>
-      <c r="M254" s="9" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="255" spans="3:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="M254" s="22" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="255" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C255" s="3">
-        <v>92000001</v>
+        <v>92000004</v>
       </c>
       <c r="D255" s="3">
-        <v>92000002</v>
+        <v>92000005</v>
       </c>
       <c r="E255" s="2">
         <v>1</v>
@@ -10288,7 +10303,7 @@
         <v>100</v>
       </c>
       <c r="G255" s="3">
-        <v>10060100</v>
+        <v>10060400</v>
       </c>
       <c r="H255" s="3">
         <v>1</v>
@@ -10303,16 +10318,15 @@
         <v>0</v>
       </c>
       <c r="M255" s="22" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q255" s="7"/>
+        <v>127</v>
+      </c>
     </row>
     <row r="256" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C256" s="3">
-        <v>92000002</v>
+        <v>92000005</v>
       </c>
       <c r="D256" s="3">
-        <v>92000003</v>
+        <v>92000006</v>
       </c>
       <c r="E256" s="2">
         <v>1</v>
@@ -10321,7 +10335,7 @@
         <v>100</v>
       </c>
       <c r="G256" s="3">
-        <v>10060200</v>
+        <v>10060500</v>
       </c>
       <c r="H256" s="3">
         <v>1</v>
@@ -10336,15 +10350,15 @@
         <v>0</v>
       </c>
       <c r="M256" s="22" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
     </row>
     <row r="257" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C257" s="3">
-        <v>92000003</v>
+        <v>92000006</v>
       </c>
       <c r="D257" s="3">
-        <v>92000004</v>
+        <v>92000007</v>
       </c>
       <c r="E257" s="2">
         <v>1</v>
@@ -10353,7 +10367,7 @@
         <v>100</v>
       </c>
       <c r="G257" s="3">
-        <v>10060300</v>
+        <v>10060600</v>
       </c>
       <c r="H257" s="3">
         <v>1</v>
@@ -10368,15 +10382,15 @@
         <v>0</v>
       </c>
       <c r="M257" s="22" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="258" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C258" s="3">
-        <v>92000004</v>
+        <v>92000007</v>
       </c>
       <c r="D258" s="3">
-        <v>92000005</v>
+        <v>92000008</v>
       </c>
       <c r="E258" s="2">
         <v>1</v>
@@ -10385,7 +10399,7 @@
         <v>100</v>
       </c>
       <c r="G258" s="3">
-        <v>10060400</v>
+        <v>10060700</v>
       </c>
       <c r="H258" s="3">
         <v>1</v>
@@ -10400,15 +10414,15 @@
         <v>0</v>
       </c>
       <c r="M258" s="22" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
     </row>
     <row r="259" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C259" s="3">
-        <v>92000005</v>
+        <v>92000008</v>
       </c>
       <c r="D259" s="3">
-        <v>92000006</v>
+        <v>0</v>
       </c>
       <c r="E259" s="2">
         <v>1</v>
@@ -10417,7 +10431,7 @@
         <v>100</v>
       </c>
       <c r="G259" s="3">
-        <v>10060500</v>
+        <v>10000212</v>
       </c>
       <c r="H259" s="3">
         <v>1</v>
@@ -10426,114 +10440,18 @@
         <v>10000136</v>
       </c>
       <c r="J259" s="3">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="K259" s="2">
         <v>0</v>
       </c>
-      <c r="M259" s="22" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="260" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C260" s="3">
-        <v>92000006</v>
-      </c>
-      <c r="D260" s="3">
-        <v>92000007</v>
-      </c>
-      <c r="E260" s="2">
-        <v>1</v>
-      </c>
-      <c r="F260" s="3">
-        <v>100</v>
-      </c>
-      <c r="G260" s="3">
-        <v>10060600</v>
-      </c>
-      <c r="H260" s="3">
-        <v>1</v>
-      </c>
-      <c r="I260" s="9">
-        <v>10000136</v>
-      </c>
-      <c r="J260" s="3">
-        <v>50</v>
-      </c>
-      <c r="K260" s="2">
-        <v>0</v>
-      </c>
-      <c r="M260" s="22" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="261" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C261" s="3">
-        <v>92000007</v>
-      </c>
-      <c r="D261" s="3">
-        <v>92000008</v>
-      </c>
-      <c r="E261" s="2">
-        <v>1</v>
-      </c>
-      <c r="F261" s="3">
-        <v>100</v>
-      </c>
-      <c r="G261" s="3">
-        <v>10060700</v>
-      </c>
-      <c r="H261" s="3">
-        <v>1</v>
-      </c>
-      <c r="I261" s="9">
-        <v>10000136</v>
-      </c>
-      <c r="J261" s="3">
-        <v>50</v>
-      </c>
-      <c r="K261" s="2">
-        <v>0</v>
-      </c>
-      <c r="M261" s="22" t="s">
+      <c r="M259" s="19" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="262" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C262" s="3">
-        <v>92000008</v>
-      </c>
-      <c r="D262" s="3">
-        <v>0</v>
-      </c>
-      <c r="E262" s="2">
-        <v>1</v>
-      </c>
-      <c r="F262" s="3">
-        <v>100</v>
-      </c>
-      <c r="G262" s="3">
-        <v>10000212</v>
-      </c>
-      <c r="H262" s="3">
-        <v>1</v>
-      </c>
-      <c r="I262" s="9">
-        <v>10000136</v>
-      </c>
-      <c r="J262" s="3">
-        <v>150</v>
-      </c>
-      <c r="K262" s="2">
-        <v>0</v>
-      </c>
-      <c r="M262" s="19" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="263" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="260" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="261" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="262" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StoreSellConfig.xlsx
+++ b/Excel/StoreSellConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EA3FAC0-F6CF-4276-AC99-4362047651F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C702BD6-3D72-414E-AD80-F99009EF9B24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="162">
   <si>
     <t>Id</t>
   </si>
@@ -547,6 +547,87 @@
   <si>
     <t>魔能之匙</t>
     <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>远古之神:破晓之盔</t>
+  </si>
+  <si>
+    <t>远古之神:圣辉之盔</t>
+  </si>
+  <si>
+    <t>远古之神:耀世之盔</t>
+  </si>
+  <si>
+    <t>远古之神:破晓之手</t>
+  </si>
+  <si>
+    <t>远古之神:圣辉之手</t>
+  </si>
+  <si>
+    <t>远古之神:耀世之手</t>
+  </si>
+  <si>
+    <t>远古之神:破晓之带</t>
+  </si>
+  <si>
+    <t>远古之神:圣辉之带</t>
+  </si>
+  <si>
+    <t>远古之神:耀世之带</t>
+  </si>
+  <si>
+    <t>远古之神:破晓之靴</t>
+  </si>
+  <si>
+    <t>远古之神:圣辉之靴</t>
+  </si>
+  <si>
+    <t>远古之神:耀世之靴</t>
+  </si>
+  <si>
+    <t>远古之神:破晓之腿</t>
+  </si>
+  <si>
+    <t>远古之神:圣辉之腿</t>
+  </si>
+  <si>
+    <t>远古之神:耀世之腿</t>
+  </si>
+  <si>
+    <t>远古之神:万象之链</t>
+  </si>
+  <si>
+    <t>远古之神:万象之戒</t>
+  </si>
+  <si>
+    <t>远古之神:万象之灵</t>
+  </si>
+  <si>
+    <t>远古之神:万象之符</t>
+  </si>
+  <si>
+    <t>远古之神:万象之剑</t>
+  </si>
+  <si>
+    <t>远古之神:万象战刃</t>
+  </si>
+  <si>
+    <t>远古之神:万象之杖</t>
+  </si>
+  <si>
+    <t>远古之神:万象之书</t>
+  </si>
+  <si>
+    <t>远古之神:万象之弓</t>
+  </si>
+  <si>
+    <t>远古之神:破晓之甲</t>
+  </si>
+  <si>
+    <t>远古之神:圣辉之甲</t>
+  </si>
+  <si>
+    <t>远古之神:耀世之甲</t>
   </si>
 </sst>
 </file>
@@ -2554,7 +2635,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q262"/>
+  <dimension ref="A1:Q289"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="5" width="14" customWidth="1"/>
@@ -2562,6 +2643,7 @@
     <col min="7" max="8" width="17.875" customWidth="1"/>
     <col min="9" max="11" width="13.25" customWidth="1"/>
     <col min="13" max="13" width="23.375" customWidth="1"/>
+    <col min="14" max="14" width="14.375" customWidth="1"/>
     <col min="16" max="16" width="9.375"/>
   </cols>
   <sheetData>
@@ -9006,7 +9088,7 @@
         <v>60000056</v>
       </c>
       <c r="D215" s="3">
-        <v>0</v>
+        <v>60000057</v>
       </c>
       <c r="E215" s="3">
         <v>1</v>
@@ -9035,10 +9117,10 @@
     </row>
     <row r="216" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C216" s="3">
-        <v>70000001</v>
+        <v>60000057</v>
       </c>
       <c r="D216" s="3">
-        <v>70000002</v>
+        <v>60000058</v>
       </c>
       <c r="E216" s="3">
         <v>1</v>
@@ -9046,31 +9128,31 @@
       <c r="F216" s="3">
         <v>100</v>
       </c>
-      <c r="G216" s="9">
-        <v>10010093</v>
+      <c r="G216" s="13">
+        <v>10014001</v>
       </c>
       <c r="H216" s="3">
         <v>1</v>
       </c>
-      <c r="I216" s="8">
-        <v>10000159</v>
-      </c>
-      <c r="J216" s="8">
-        <v>30</v>
+      <c r="I216" s="3">
+        <v>10010031</v>
+      </c>
+      <c r="J216" s="3">
+        <v>20</v>
       </c>
       <c r="K216" s="2">
         <v>0</v>
       </c>
-      <c r="M216" s="12" t="s">
-        <v>49</v>
+      <c r="M216" s="3" t="s">
+        <v>135</v>
       </c>
     </row>
     <row r="217" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C217" s="3">
-        <v>70000002</v>
+        <v>60000058</v>
       </c>
       <c r="D217" s="3">
-        <v>70000003</v>
+        <v>60000059</v>
       </c>
       <c r="E217" s="3">
         <v>1</v>
@@ -9078,31 +9160,31 @@
       <c r="F217" s="3">
         <v>100</v>
       </c>
-      <c r="G217" s="9">
-        <v>10000162</v>
+      <c r="G217" s="13">
+        <v>10014002</v>
       </c>
       <c r="H217" s="3">
         <v>1</v>
       </c>
-      <c r="I217" s="8">
-        <v>10000159</v>
-      </c>
-      <c r="J217" s="8">
+      <c r="I217" s="3">
+        <v>10010031</v>
+      </c>
+      <c r="J217" s="3">
         <v>20</v>
       </c>
       <c r="K217" s="2">
         <v>0</v>
       </c>
-      <c r="M217" s="11" t="s">
-        <v>104</v>
+      <c r="M217" s="3" t="s">
+        <v>136</v>
       </c>
     </row>
     <row r="218" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C218" s="3">
-        <v>70000003</v>
+        <v>60000059</v>
       </c>
       <c r="D218" s="3">
-        <v>70000004</v>
+        <v>60000060</v>
       </c>
       <c r="E218" s="3">
         <v>1</v>
@@ -9110,31 +9192,31 @@
       <c r="F218" s="3">
         <v>100</v>
       </c>
-      <c r="G218" s="9">
-        <v>10010045</v>
+      <c r="G218" s="13">
+        <v>10014003</v>
       </c>
       <c r="H218" s="3">
         <v>1</v>
       </c>
-      <c r="I218" s="8">
-        <v>10000159</v>
-      </c>
-      <c r="J218" s="8">
-        <v>30</v>
+      <c r="I218" s="3">
+        <v>10010031</v>
+      </c>
+      <c r="J218" s="3">
+        <v>20</v>
       </c>
       <c r="K218" s="2">
         <v>0</v>
       </c>
-      <c r="M218" s="11" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="219" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M218" s="3" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="219" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C219" s="3">
-        <v>70000004</v>
+        <v>60000060</v>
       </c>
       <c r="D219" s="3">
-        <v>70000005</v>
+        <v>60000061</v>
       </c>
       <c r="E219" s="3">
         <v>1</v>
@@ -9142,31 +9224,31 @@
       <c r="F219" s="3">
         <v>100</v>
       </c>
-      <c r="G219" s="9">
-        <v>10000158</v>
+      <c r="G219" s="13">
+        <v>10014004</v>
       </c>
       <c r="H219" s="3">
         <v>1</v>
       </c>
-      <c r="I219" s="8">
-        <v>10000159</v>
-      </c>
-      <c r="J219" s="8">
+      <c r="I219" s="3">
+        <v>10010031</v>
+      </c>
+      <c r="J219" s="3">
         <v>20</v>
       </c>
       <c r="K219" s="2">
         <v>0</v>
       </c>
-      <c r="M219" s="9" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="220" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M219" s="3" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="220" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C220" s="3">
-        <v>70000005</v>
+        <v>60000061</v>
       </c>
       <c r="D220" s="3">
-        <v>70000006</v>
+        <v>60000062</v>
       </c>
       <c r="E220" s="3">
         <v>1</v>
@@ -9174,31 +9256,31 @@
       <c r="F220" s="3">
         <v>100</v>
       </c>
-      <c r="G220" s="9">
-        <v>10010083</v>
+      <c r="G220" s="13">
+        <v>10014005</v>
       </c>
       <c r="H220" s="3">
         <v>1</v>
       </c>
-      <c r="I220" s="8">
-        <v>10000159</v>
-      </c>
-      <c r="J220" s="8">
-        <v>2</v>
+      <c r="I220" s="3">
+        <v>10010031</v>
+      </c>
+      <c r="J220" s="3">
+        <v>20</v>
       </c>
       <c r="K220" s="2">
         <v>0</v>
       </c>
-      <c r="M220" s="16" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="221" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M220" s="3" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="221" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C221" s="3">
-        <v>70000006</v>
+        <v>60000062</v>
       </c>
       <c r="D221" s="3">
-        <v>70000007</v>
+        <v>60000063</v>
       </c>
       <c r="E221" s="3">
         <v>1</v>
@@ -9206,31 +9288,31 @@
       <c r="F221" s="3">
         <v>100</v>
       </c>
-      <c r="G221" s="9">
-        <v>10000143</v>
+      <c r="G221" s="13">
+        <v>10014006</v>
       </c>
       <c r="H221" s="3">
         <v>1</v>
       </c>
-      <c r="I221" s="8">
-        <v>10000159</v>
-      </c>
-      <c r="J221" s="8">
-        <v>5</v>
+      <c r="I221" s="3">
+        <v>10010031</v>
+      </c>
+      <c r="J221" s="3">
+        <v>20</v>
       </c>
       <c r="K221" s="2">
         <v>0</v>
       </c>
-      <c r="M221" s="16" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="222" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M221" s="3" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="222" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C222" s="3">
-        <v>70000007</v>
+        <v>60000063</v>
       </c>
       <c r="D222" s="3">
-        <v>70000008</v>
+        <v>60000064</v>
       </c>
       <c r="E222" s="3">
         <v>1</v>
@@ -9238,31 +9320,31 @@
       <c r="F222" s="3">
         <v>100</v>
       </c>
-      <c r="G222" s="9">
-        <v>10000152</v>
+      <c r="G222" s="13">
+        <v>10014007</v>
       </c>
       <c r="H222" s="3">
         <v>1</v>
       </c>
-      <c r="I222" s="8">
-        <v>10000159</v>
-      </c>
-      <c r="J222" s="8">
-        <v>10</v>
+      <c r="I222" s="3">
+        <v>10010031</v>
+      </c>
+      <c r="J222" s="3">
+        <v>20</v>
       </c>
       <c r="K222" s="2">
         <v>0</v>
       </c>
-      <c r="M222" s="11" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="223" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M222" s="3" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="223" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C223" s="3">
-        <v>70000008</v>
+        <v>60000064</v>
       </c>
       <c r="D223" s="3">
-        <v>70000009</v>
+        <v>60000065</v>
       </c>
       <c r="E223" s="3">
         <v>1</v>
@@ -9270,31 +9352,31 @@
       <c r="F223" s="3">
         <v>100</v>
       </c>
-      <c r="G223" s="9">
-        <v>10000157</v>
+      <c r="G223" s="13">
+        <v>10014008</v>
       </c>
       <c r="H223" s="3">
         <v>1</v>
       </c>
-      <c r="I223" s="8">
-        <v>10000159</v>
-      </c>
-      <c r="J223" s="8">
-        <v>10</v>
+      <c r="I223" s="3">
+        <v>10010031</v>
+      </c>
+      <c r="J223" s="3">
+        <v>20</v>
       </c>
       <c r="K223" s="2">
         <v>0</v>
       </c>
-      <c r="M223" s="11" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="224" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M223" s="3" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="224" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C224" s="3">
-        <v>70000009</v>
+        <v>60000065</v>
       </c>
       <c r="D224" s="3">
-        <v>70000010</v>
+        <v>60000066</v>
       </c>
       <c r="E224" s="3">
         <v>1</v>
@@ -9302,31 +9384,31 @@
       <c r="F224" s="3">
         <v>100</v>
       </c>
-      <c r="G224" s="9">
-        <v>10010029</v>
+      <c r="G224" s="13">
+        <v>10014009</v>
       </c>
       <c r="H224" s="3">
         <v>1</v>
       </c>
-      <c r="I224" s="8">
-        <v>10000159</v>
-      </c>
-      <c r="J224" s="8">
-        <v>5</v>
+      <c r="I224" s="3">
+        <v>10010031</v>
+      </c>
+      <c r="J224" s="3">
+        <v>20</v>
       </c>
       <c r="K224" s="2">
         <v>0</v>
       </c>
-      <c r="M224" s="11" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="225" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M224" s="3" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="225" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C225" s="3">
-        <v>70000010</v>
+        <v>60000066</v>
       </c>
       <c r="D225" s="3">
-        <v>70000011</v>
+        <v>60000067</v>
       </c>
       <c r="E225" s="3">
         <v>1</v>
@@ -9334,31 +9416,31 @@
       <c r="F225" s="3">
         <v>100</v>
       </c>
-      <c r="G225" s="9">
-        <v>10010086</v>
+      <c r="G225" s="13">
+        <v>10014010</v>
       </c>
       <c r="H225" s="3">
         <v>1</v>
       </c>
-      <c r="I225" s="8">
-        <v>10000159</v>
-      </c>
-      <c r="J225" s="8">
-        <v>10</v>
+      <c r="I225" s="3">
+        <v>10010031</v>
+      </c>
+      <c r="J225" s="3">
+        <v>20</v>
       </c>
       <c r="K225" s="2">
         <v>0</v>
       </c>
-      <c r="M225" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="226" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M225" s="3" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="226" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C226" s="3">
-        <v>70000011</v>
+        <v>60000067</v>
       </c>
       <c r="D226" s="3">
-        <v>70000012</v>
+        <v>60000068</v>
       </c>
       <c r="E226" s="3">
         <v>1</v>
@@ -9366,31 +9448,31 @@
       <c r="F226" s="3">
         <v>100</v>
       </c>
-      <c r="G226" s="18">
-        <v>10010101</v>
+      <c r="G226" s="13">
+        <v>10014011</v>
       </c>
       <c r="H226" s="3">
         <v>1</v>
       </c>
-      <c r="I226" s="8">
-        <v>10000159</v>
-      </c>
-      <c r="J226" s="8">
-        <v>5</v>
+      <c r="I226" s="3">
+        <v>10010031</v>
+      </c>
+      <c r="J226" s="3">
+        <v>20</v>
       </c>
       <c r="K226" s="2">
         <v>0</v>
       </c>
-      <c r="M226" s="8" t="s">
-        <v>109</v>
-      </c>
-    </row>
-    <row r="227" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M226" s="3" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="227" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C227" s="3">
-        <v>70000012</v>
+        <v>60000068</v>
       </c>
       <c r="D227" s="3">
-        <v>70000013</v>
+        <v>60000069</v>
       </c>
       <c r="E227" s="3">
         <v>1</v>
@@ -9398,31 +9480,31 @@
       <c r="F227" s="3">
         <v>100</v>
       </c>
-      <c r="G227" s="18">
-        <v>10010102</v>
+      <c r="G227" s="13">
+        <v>10014012</v>
       </c>
       <c r="H227" s="3">
         <v>1</v>
       </c>
-      <c r="I227" s="8">
-        <v>10000159</v>
-      </c>
-      <c r="J227" s="8">
-        <v>10</v>
+      <c r="I227" s="3">
+        <v>10010031</v>
+      </c>
+      <c r="J227" s="3">
+        <v>20</v>
       </c>
       <c r="K227" s="2">
         <v>0</v>
       </c>
       <c r="M227" s="3" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="228" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="228" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C228" s="3">
-        <v>70000013</v>
+        <v>60000069</v>
       </c>
       <c r="D228" s="3">
-        <v>0</v>
+        <v>60000070</v>
       </c>
       <c r="E228" s="3">
         <v>1</v>
@@ -9430,31 +9512,31 @@
       <c r="F228" s="3">
         <v>100</v>
       </c>
-      <c r="G228" s="18">
-        <v>10010103</v>
+      <c r="G228" s="13">
+        <v>10014013</v>
       </c>
       <c r="H228" s="3">
         <v>1</v>
       </c>
-      <c r="I228" s="8">
-        <v>10000159</v>
-      </c>
-      <c r="J228" s="8">
+      <c r="I228" s="3">
+        <v>10010031</v>
+      </c>
+      <c r="J228" s="3">
         <v>20</v>
       </c>
       <c r="K228" s="2">
         <v>0</v>
       </c>
       <c r="M228" s="3" t="s">
-        <v>111</v>
+        <v>147</v>
       </c>
     </row>
     <row r="229" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C229" s="3">
-        <v>80000001</v>
+        <v>60000070</v>
       </c>
       <c r="D229" s="3">
-        <v>80000002</v>
+        <v>60000071</v>
       </c>
       <c r="E229" s="3">
         <v>1</v>
@@ -9462,31 +9544,31 @@
       <c r="F229" s="3">
         <v>100</v>
       </c>
-      <c r="G229" s="9">
-        <v>10010083</v>
+      <c r="G229" s="13">
+        <v>10014014</v>
       </c>
       <c r="H229" s="3">
         <v>1</v>
       </c>
-      <c r="I229" s="8">
-        <v>10000163</v>
-      </c>
-      <c r="J229" s="8">
-        <v>1</v>
+      <c r="I229" s="3">
+        <v>10010031</v>
+      </c>
+      <c r="J229" s="3">
+        <v>20</v>
       </c>
       <c r="K229" s="2">
         <v>0</v>
       </c>
       <c r="M229" s="3" t="s">
-        <v>107</v>
+        <v>148</v>
       </c>
     </row>
     <row r="230" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C230" s="3">
-        <v>80000002</v>
+        <v>60000071</v>
       </c>
       <c r="D230" s="3">
-        <v>80000003</v>
+        <v>60000072</v>
       </c>
       <c r="E230" s="3">
         <v>1</v>
@@ -9494,964 +9576,1828 @@
       <c r="F230" s="3">
         <v>100</v>
       </c>
-      <c r="G230" s="9">
-        <v>10010086</v>
+      <c r="G230" s="13">
+        <v>10014015</v>
       </c>
       <c r="H230" s="3">
         <v>1</v>
       </c>
-      <c r="I230" s="8">
-        <v>10000163</v>
-      </c>
-      <c r="J230" s="8">
+      <c r="I230" s="3">
+        <v>10010031</v>
+      </c>
+      <c r="J230" s="3">
         <v>20</v>
       </c>
       <c r="K230" s="2">
         <v>0</v>
       </c>
       <c r="M230" s="3" t="s">
-        <v>27</v>
+        <v>149</v>
       </c>
     </row>
     <row r="231" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C231" s="3">
+        <v>60000072</v>
+      </c>
+      <c r="D231" s="3">
+        <v>60000073</v>
+      </c>
+      <c r="E231" s="3">
+        <v>1</v>
+      </c>
+      <c r="F231" s="3">
+        <v>100</v>
+      </c>
+      <c r="G231" s="13">
+        <v>10014016</v>
+      </c>
+      <c r="H231" s="3">
+        <v>1</v>
+      </c>
+      <c r="I231" s="3">
+        <v>10010031</v>
+      </c>
+      <c r="J231" s="3">
+        <v>20</v>
+      </c>
+      <c r="K231" s="2">
+        <v>0</v>
+      </c>
+      <c r="M231" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="232" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C232" s="3">
+        <v>60000073</v>
+      </c>
+      <c r="D232" s="3">
+        <v>60000074</v>
+      </c>
+      <c r="E232" s="3">
+        <v>1</v>
+      </c>
+      <c r="F232" s="3">
+        <v>100</v>
+      </c>
+      <c r="G232" s="13">
+        <v>10014017</v>
+      </c>
+      <c r="H232" s="3">
+        <v>1</v>
+      </c>
+      <c r="I232" s="3">
+        <v>10010031</v>
+      </c>
+      <c r="J232" s="3">
+        <v>20</v>
+      </c>
+      <c r="K232" s="2">
+        <v>0</v>
+      </c>
+      <c r="M232" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="233" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C233" s="3">
+        <v>60000074</v>
+      </c>
+      <c r="D233" s="3">
+        <v>60000075</v>
+      </c>
+      <c r="E233" s="3">
+        <v>1</v>
+      </c>
+      <c r="F233" s="3">
+        <v>100</v>
+      </c>
+      <c r="G233" s="13">
+        <v>10014018</v>
+      </c>
+      <c r="H233" s="3">
+        <v>1</v>
+      </c>
+      <c r="I233" s="3">
+        <v>10010031</v>
+      </c>
+      <c r="J233" s="3">
+        <v>20</v>
+      </c>
+      <c r="K233" s="2">
+        <v>0</v>
+      </c>
+      <c r="M233" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="234" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C234" s="3">
+        <v>60000075</v>
+      </c>
+      <c r="D234" s="3">
+        <v>60000076</v>
+      </c>
+      <c r="E234" s="3">
+        <v>1</v>
+      </c>
+      <c r="F234" s="3">
+        <v>100</v>
+      </c>
+      <c r="G234" s="13">
+        <v>10014019</v>
+      </c>
+      <c r="H234" s="3">
+        <v>1</v>
+      </c>
+      <c r="I234" s="3">
+        <v>10010031</v>
+      </c>
+      <c r="J234" s="3">
+        <v>20</v>
+      </c>
+      <c r="K234" s="2">
+        <v>0</v>
+      </c>
+      <c r="M234" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="235" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C235" s="3">
+        <v>60000076</v>
+      </c>
+      <c r="D235" s="3">
+        <v>60000077</v>
+      </c>
+      <c r="E235" s="3">
+        <v>1</v>
+      </c>
+      <c r="F235" s="3">
+        <v>100</v>
+      </c>
+      <c r="G235" s="13">
+        <v>10014020</v>
+      </c>
+      <c r="H235" s="3">
+        <v>1</v>
+      </c>
+      <c r="I235" s="3">
+        <v>10010031</v>
+      </c>
+      <c r="J235" s="3">
+        <v>30</v>
+      </c>
+      <c r="K235" s="2">
+        <v>0</v>
+      </c>
+      <c r="M235" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="236" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C236" s="3">
+        <v>60000077</v>
+      </c>
+      <c r="D236" s="3">
+        <v>60000078</v>
+      </c>
+      <c r="E236" s="3">
+        <v>1</v>
+      </c>
+      <c r="F236" s="3">
+        <v>100</v>
+      </c>
+      <c r="G236" s="13">
+        <v>10014021</v>
+      </c>
+      <c r="H236" s="3">
+        <v>1</v>
+      </c>
+      <c r="I236" s="3">
+        <v>10010031</v>
+      </c>
+      <c r="J236" s="3">
+        <v>30</v>
+      </c>
+      <c r="K236" s="2">
+        <v>0</v>
+      </c>
+      <c r="M236" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="237" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C237" s="3">
+        <v>60000078</v>
+      </c>
+      <c r="D237" s="3">
+        <v>60000079</v>
+      </c>
+      <c r="E237" s="3">
+        <v>1</v>
+      </c>
+      <c r="F237" s="3">
+        <v>100</v>
+      </c>
+      <c r="G237" s="13">
+        <v>10014022</v>
+      </c>
+      <c r="H237" s="3">
+        <v>1</v>
+      </c>
+      <c r="I237" s="3">
+        <v>10010031</v>
+      </c>
+      <c r="J237" s="3">
+        <v>30</v>
+      </c>
+      <c r="K237" s="2">
+        <v>0</v>
+      </c>
+      <c r="M237" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="238" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C238" s="3">
+        <v>60000079</v>
+      </c>
+      <c r="D238" s="3">
+        <v>60000080</v>
+      </c>
+      <c r="E238" s="3">
+        <v>1</v>
+      </c>
+      <c r="F238" s="3">
+        <v>100</v>
+      </c>
+      <c r="G238" s="13">
+        <v>10014023</v>
+      </c>
+      <c r="H238" s="3">
+        <v>1</v>
+      </c>
+      <c r="I238" s="3">
+        <v>10010031</v>
+      </c>
+      <c r="J238" s="3">
+        <v>30</v>
+      </c>
+      <c r="K238" s="2">
+        <v>0</v>
+      </c>
+      <c r="M238" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="239" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C239" s="3">
+        <v>60000080</v>
+      </c>
+      <c r="D239" s="3">
+        <v>60000081</v>
+      </c>
+      <c r="E239" s="3">
+        <v>1</v>
+      </c>
+      <c r="F239" s="3">
+        <v>100</v>
+      </c>
+      <c r="G239" s="13">
+        <v>10014024</v>
+      </c>
+      <c r="H239" s="3">
+        <v>1</v>
+      </c>
+      <c r="I239" s="3">
+        <v>10010031</v>
+      </c>
+      <c r="J239" s="3">
+        <v>30</v>
+      </c>
+      <c r="K239" s="2">
+        <v>0</v>
+      </c>
+      <c r="M239" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="240" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C240" s="3">
+        <v>60000081</v>
+      </c>
+      <c r="D240" s="3">
+        <v>60000082</v>
+      </c>
+      <c r="E240" s="3">
+        <v>1</v>
+      </c>
+      <c r="F240" s="3">
+        <v>100</v>
+      </c>
+      <c r="G240" s="13">
+        <v>10014025</v>
+      </c>
+      <c r="H240" s="3">
+        <v>1</v>
+      </c>
+      <c r="I240" s="3">
+        <v>10010031</v>
+      </c>
+      <c r="J240" s="3">
+        <v>30</v>
+      </c>
+      <c r="K240" s="2">
+        <v>0</v>
+      </c>
+      <c r="M240" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="241" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C241" s="3">
+        <v>60000082</v>
+      </c>
+      <c r="D241" s="3">
+        <v>60000083</v>
+      </c>
+      <c r="E241" s="3">
+        <v>1</v>
+      </c>
+      <c r="F241" s="3">
+        <v>100</v>
+      </c>
+      <c r="G241" s="13">
+        <v>10014026</v>
+      </c>
+      <c r="H241" s="3">
+        <v>1</v>
+      </c>
+      <c r="I241" s="3">
+        <v>10010031</v>
+      </c>
+      <c r="J241" s="3">
+        <v>30</v>
+      </c>
+      <c r="K241" s="2">
+        <v>0</v>
+      </c>
+      <c r="M241" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="242" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C242" s="3">
+        <v>60000083</v>
+      </c>
+      <c r="D242" s="3">
+        <v>0</v>
+      </c>
+      <c r="E242" s="3">
+        <v>1</v>
+      </c>
+      <c r="F242" s="3">
+        <v>100</v>
+      </c>
+      <c r="G242" s="13">
+        <v>10014027</v>
+      </c>
+      <c r="H242" s="3">
+        <v>1</v>
+      </c>
+      <c r="I242" s="3">
+        <v>10010031</v>
+      </c>
+      <c r="J242" s="3">
+        <v>30</v>
+      </c>
+      <c r="K242" s="2">
+        <v>0</v>
+      </c>
+      <c r="M242" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="243" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C243" s="3">
+        <v>70000001</v>
+      </c>
+      <c r="D243" s="3">
+        <v>70000002</v>
+      </c>
+      <c r="E243" s="3">
+        <v>1</v>
+      </c>
+      <c r="F243" s="3">
+        <v>100</v>
+      </c>
+      <c r="G243" s="9">
+        <v>10010093</v>
+      </c>
+      <c r="H243" s="3">
+        <v>1</v>
+      </c>
+      <c r="I243" s="8">
+        <v>10000159</v>
+      </c>
+      <c r="J243" s="8">
+        <v>30</v>
+      </c>
+      <c r="K243" s="2">
+        <v>0</v>
+      </c>
+      <c r="M243" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="244" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C244" s="3">
+        <v>70000002</v>
+      </c>
+      <c r="D244" s="3">
+        <v>70000003</v>
+      </c>
+      <c r="E244" s="3">
+        <v>1</v>
+      </c>
+      <c r="F244" s="3">
+        <v>100</v>
+      </c>
+      <c r="G244" s="9">
+        <v>10000162</v>
+      </c>
+      <c r="H244" s="3">
+        <v>1</v>
+      </c>
+      <c r="I244" s="8">
+        <v>10000159</v>
+      </c>
+      <c r="J244" s="8">
+        <v>20</v>
+      </c>
+      <c r="K244" s="2">
+        <v>0</v>
+      </c>
+      <c r="M244" s="11" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="245" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C245" s="3">
+        <v>70000003</v>
+      </c>
+      <c r="D245" s="3">
+        <v>70000004</v>
+      </c>
+      <c r="E245" s="3">
+        <v>1</v>
+      </c>
+      <c r="F245" s="3">
+        <v>100</v>
+      </c>
+      <c r="G245" s="9">
+        <v>10010045</v>
+      </c>
+      <c r="H245" s="3">
+        <v>1</v>
+      </c>
+      <c r="I245" s="8">
+        <v>10000159</v>
+      </c>
+      <c r="J245" s="8">
+        <v>30</v>
+      </c>
+      <c r="K245" s="2">
+        <v>0</v>
+      </c>
+      <c r="M245" s="11" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="246" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C246" s="3">
+        <v>70000004</v>
+      </c>
+      <c r="D246" s="3">
+        <v>70000005</v>
+      </c>
+      <c r="E246" s="3">
+        <v>1</v>
+      </c>
+      <c r="F246" s="3">
+        <v>100</v>
+      </c>
+      <c r="G246" s="9">
+        <v>10000158</v>
+      </c>
+      <c r="H246" s="3">
+        <v>1</v>
+      </c>
+      <c r="I246" s="8">
+        <v>10000159</v>
+      </c>
+      <c r="J246" s="8">
+        <v>20</v>
+      </c>
+      <c r="K246" s="2">
+        <v>0</v>
+      </c>
+      <c r="M246" s="9" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="247" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C247" s="3">
+        <v>70000005</v>
+      </c>
+      <c r="D247" s="3">
+        <v>70000006</v>
+      </c>
+      <c r="E247" s="3">
+        <v>1</v>
+      </c>
+      <c r="F247" s="3">
+        <v>100</v>
+      </c>
+      <c r="G247" s="9">
+        <v>10010083</v>
+      </c>
+      <c r="H247" s="3">
+        <v>1</v>
+      </c>
+      <c r="I247" s="8">
+        <v>10000159</v>
+      </c>
+      <c r="J247" s="8">
+        <v>2</v>
+      </c>
+      <c r="K247" s="2">
+        <v>0</v>
+      </c>
+      <c r="M247" s="16" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="248" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C248" s="3">
+        <v>70000006</v>
+      </c>
+      <c r="D248" s="3">
+        <v>70000007</v>
+      </c>
+      <c r="E248" s="3">
+        <v>1</v>
+      </c>
+      <c r="F248" s="3">
+        <v>100</v>
+      </c>
+      <c r="G248" s="9">
+        <v>10000143</v>
+      </c>
+      <c r="H248" s="3">
+        <v>1</v>
+      </c>
+      <c r="I248" s="8">
+        <v>10000159</v>
+      </c>
+      <c r="J248" s="8">
+        <v>5</v>
+      </c>
+      <c r="K248" s="2">
+        <v>0</v>
+      </c>
+      <c r="M248" s="16" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="249" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C249" s="3">
+        <v>70000007</v>
+      </c>
+      <c r="D249" s="3">
+        <v>70000008</v>
+      </c>
+      <c r="E249" s="3">
+        <v>1</v>
+      </c>
+      <c r="F249" s="3">
+        <v>100</v>
+      </c>
+      <c r="G249" s="9">
+        <v>10000152</v>
+      </c>
+      <c r="H249" s="3">
+        <v>1</v>
+      </c>
+      <c r="I249" s="8">
+        <v>10000159</v>
+      </c>
+      <c r="J249" s="8">
+        <v>10</v>
+      </c>
+      <c r="K249" s="2">
+        <v>0</v>
+      </c>
+      <c r="M249" s="11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="250" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C250" s="3">
+        <v>70000008</v>
+      </c>
+      <c r="D250" s="3">
+        <v>70000009</v>
+      </c>
+      <c r="E250" s="3">
+        <v>1</v>
+      </c>
+      <c r="F250" s="3">
+        <v>100</v>
+      </c>
+      <c r="G250" s="9">
+        <v>10000157</v>
+      </c>
+      <c r="H250" s="3">
+        <v>1</v>
+      </c>
+      <c r="I250" s="8">
+        <v>10000159</v>
+      </c>
+      <c r="J250" s="8">
+        <v>10</v>
+      </c>
+      <c r="K250" s="2">
+        <v>0</v>
+      </c>
+      <c r="M250" s="11" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="251" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C251" s="3">
+        <v>70000009</v>
+      </c>
+      <c r="D251" s="3">
+        <v>70000010</v>
+      </c>
+      <c r="E251" s="3">
+        <v>1</v>
+      </c>
+      <c r="F251" s="3">
+        <v>100</v>
+      </c>
+      <c r="G251" s="9">
+        <v>10010029</v>
+      </c>
+      <c r="H251" s="3">
+        <v>1</v>
+      </c>
+      <c r="I251" s="8">
+        <v>10000159</v>
+      </c>
+      <c r="J251" s="8">
+        <v>5</v>
+      </c>
+      <c r="K251" s="2">
+        <v>0</v>
+      </c>
+      <c r="M251" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="252" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C252" s="3">
+        <v>70000010</v>
+      </c>
+      <c r="D252" s="3">
+        <v>70000011</v>
+      </c>
+      <c r="E252" s="3">
+        <v>1</v>
+      </c>
+      <c r="F252" s="3">
+        <v>100</v>
+      </c>
+      <c r="G252" s="9">
+        <v>10010086</v>
+      </c>
+      <c r="H252" s="3">
+        <v>1</v>
+      </c>
+      <c r="I252" s="8">
+        <v>10000159</v>
+      </c>
+      <c r="J252" s="8">
+        <v>10</v>
+      </c>
+      <c r="K252" s="2">
+        <v>0</v>
+      </c>
+      <c r="M252" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="253" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C253" s="3">
+        <v>70000011</v>
+      </c>
+      <c r="D253" s="3">
+        <v>70000012</v>
+      </c>
+      <c r="E253" s="3">
+        <v>1</v>
+      </c>
+      <c r="F253" s="3">
+        <v>100</v>
+      </c>
+      <c r="G253" s="18">
+        <v>10010101</v>
+      </c>
+      <c r="H253" s="3">
+        <v>1</v>
+      </c>
+      <c r="I253" s="8">
+        <v>10000159</v>
+      </c>
+      <c r="J253" s="8">
+        <v>5</v>
+      </c>
+      <c r="K253" s="2">
+        <v>0</v>
+      </c>
+      <c r="M253" s="8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="254" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C254" s="3">
+        <v>70000012</v>
+      </c>
+      <c r="D254" s="3">
+        <v>70000013</v>
+      </c>
+      <c r="E254" s="3">
+        <v>1</v>
+      </c>
+      <c r="F254" s="3">
+        <v>100</v>
+      </c>
+      <c r="G254" s="18">
+        <v>10010102</v>
+      </c>
+      <c r="H254" s="3">
+        <v>1</v>
+      </c>
+      <c r="I254" s="8">
+        <v>10000159</v>
+      </c>
+      <c r="J254" s="8">
+        <v>10</v>
+      </c>
+      <c r="K254" s="2">
+        <v>0</v>
+      </c>
+      <c r="M254" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="255" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C255" s="3">
+        <v>70000013</v>
+      </c>
+      <c r="D255" s="3">
+        <v>0</v>
+      </c>
+      <c r="E255" s="3">
+        <v>1</v>
+      </c>
+      <c r="F255" s="3">
+        <v>100</v>
+      </c>
+      <c r="G255" s="18">
+        <v>10010103</v>
+      </c>
+      <c r="H255" s="3">
+        <v>1</v>
+      </c>
+      <c r="I255" s="8">
+        <v>10000159</v>
+      </c>
+      <c r="J255" s="8">
+        <v>20</v>
+      </c>
+      <c r="K255" s="2">
+        <v>0</v>
+      </c>
+      <c r="M255" s="3" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="256" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C256" s="3">
+        <v>80000001</v>
+      </c>
+      <c r="D256" s="3">
+        <v>80000002</v>
+      </c>
+      <c r="E256" s="3">
+        <v>1</v>
+      </c>
+      <c r="F256" s="3">
+        <v>100</v>
+      </c>
+      <c r="G256" s="9">
+        <v>10010083</v>
+      </c>
+      <c r="H256" s="3">
+        <v>1</v>
+      </c>
+      <c r="I256" s="8">
+        <v>10000163</v>
+      </c>
+      <c r="J256" s="8">
+        <v>1</v>
+      </c>
+      <c r="K256" s="2">
+        <v>0</v>
+      </c>
+      <c r="M256" s="3" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="257" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C257" s="3">
+        <v>80000002</v>
+      </c>
+      <c r="D257" s="3">
         <v>80000003</v>
       </c>
-      <c r="D231" s="3">
+      <c r="E257" s="3">
+        <v>1</v>
+      </c>
+      <c r="F257" s="3">
+        <v>100</v>
+      </c>
+      <c r="G257" s="9">
+        <v>10010086</v>
+      </c>
+      <c r="H257" s="3">
+        <v>1</v>
+      </c>
+      <c r="I257" s="8">
+        <v>10000163</v>
+      </c>
+      <c r="J257" s="8">
+        <v>20</v>
+      </c>
+      <c r="K257" s="2">
+        <v>0</v>
+      </c>
+      <c r="M257" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="258" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C258" s="3">
+        <v>80000003</v>
+      </c>
+      <c r="D258" s="3">
         <v>80000004</v>
       </c>
-      <c r="E231" s="3">
-        <v>1</v>
-      </c>
-      <c r="F231" s="3">
-        <v>100</v>
-      </c>
-      <c r="G231" s="9">
+      <c r="E258" s="3">
+        <v>1</v>
+      </c>
+      <c r="F258" s="3">
+        <v>100</v>
+      </c>
+      <c r="G258" s="9">
         <v>10010096</v>
       </c>
-      <c r="H231" s="3">
-        <v>1</v>
-      </c>
-      <c r="I231" s="8">
+      <c r="H258" s="3">
+        <v>1</v>
+      </c>
+      <c r="I258" s="8">
         <v>10000163</v>
       </c>
-      <c r="J231" s="8">
+      <c r="J258" s="8">
         <v>35</v>
       </c>
-      <c r="K231" s="2">
-        <v>0</v>
-      </c>
-      <c r="M231" s="3" t="s">
+      <c r="K258" s="2">
+        <v>0</v>
+      </c>
+      <c r="M258" s="3" t="s">
         <v>112</v>
-      </c>
-    </row>
-    <row r="232" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C232" s="3">
-        <v>80000004</v>
-      </c>
-      <c r="D232" s="3">
-        <v>80000005</v>
-      </c>
-      <c r="E232" s="3">
-        <v>1</v>
-      </c>
-      <c r="F232" s="3">
-        <v>100</v>
-      </c>
-      <c r="G232" s="9">
-        <v>10000139</v>
-      </c>
-      <c r="H232" s="3">
-        <v>1</v>
-      </c>
-      <c r="I232" s="8">
-        <v>10000163</v>
-      </c>
-      <c r="J232" s="8">
-        <v>20</v>
-      </c>
-      <c r="K232" s="2">
-        <v>0</v>
-      </c>
-      <c r="M232" s="3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="233" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C233" s="3">
-        <v>80000005</v>
-      </c>
-      <c r="D233" s="3">
-        <v>80000006</v>
-      </c>
-      <c r="E233" s="3">
-        <v>1</v>
-      </c>
-      <c r="F233" s="3">
-        <v>100</v>
-      </c>
-      <c r="G233" s="9">
-        <v>10000143</v>
-      </c>
-      <c r="H233" s="3">
-        <v>1</v>
-      </c>
-      <c r="I233" s="8">
-        <v>10000163</v>
-      </c>
-      <c r="J233" s="8">
-        <v>20</v>
-      </c>
-      <c r="K233" s="2">
-        <v>0</v>
-      </c>
-      <c r="M233" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="234" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C234" s="3">
-        <v>80000006</v>
-      </c>
-      <c r="D234" s="3">
-        <v>80000007</v>
-      </c>
-      <c r="E234" s="3">
-        <v>1</v>
-      </c>
-      <c r="F234" s="3">
-        <v>100</v>
-      </c>
-      <c r="G234" s="9">
-        <v>10000152</v>
-      </c>
-      <c r="H234" s="3">
-        <v>1</v>
-      </c>
-      <c r="I234" s="8">
-        <v>10000163</v>
-      </c>
-      <c r="J234" s="8">
-        <v>35</v>
-      </c>
-      <c r="K234" s="2">
-        <v>0</v>
-      </c>
-      <c r="M234" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="235" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C235" s="3">
-        <v>80000007</v>
-      </c>
-      <c r="D235" s="3">
-        <v>80000008</v>
-      </c>
-      <c r="E235" s="3">
-        <v>1</v>
-      </c>
-      <c r="F235" s="3">
-        <v>100</v>
-      </c>
-      <c r="G235" s="9">
-        <v>10000155</v>
-      </c>
-      <c r="H235" s="3">
-        <v>1</v>
-      </c>
-      <c r="I235" s="8">
-        <v>10000163</v>
-      </c>
-      <c r="J235" s="8">
-        <v>5</v>
-      </c>
-      <c r="K235" s="2">
-        <v>0</v>
-      </c>
-      <c r="M235" s="3" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="236" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C236" s="3">
-        <v>80000008</v>
-      </c>
-      <c r="D236" s="3">
-        <v>80000009</v>
-      </c>
-      <c r="E236" s="3">
-        <v>1</v>
-      </c>
-      <c r="F236" s="3">
-        <v>100</v>
-      </c>
-      <c r="G236" s="9">
-        <v>10000158</v>
-      </c>
-      <c r="H236" s="3">
-        <v>1</v>
-      </c>
-      <c r="I236" s="8">
-        <v>10000163</v>
-      </c>
-      <c r="J236" s="8">
-        <v>20</v>
-      </c>
-      <c r="K236" s="2">
-        <v>0</v>
-      </c>
-      <c r="M236" s="3" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="237" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C237" s="3">
-        <v>80000009</v>
-      </c>
-      <c r="D237" s="3">
-        <v>0</v>
-      </c>
-      <c r="E237" s="3">
-        <v>1</v>
-      </c>
-      <c r="F237" s="3">
-        <v>100</v>
-      </c>
-      <c r="G237" s="9">
-        <v>10010093</v>
-      </c>
-      <c r="H237" s="3">
-        <v>1</v>
-      </c>
-      <c r="I237" s="8">
-        <v>10000163</v>
-      </c>
-      <c r="J237" s="8">
-        <v>35</v>
-      </c>
-      <c r="K237" s="2">
-        <v>0</v>
-      </c>
-      <c r="M237" s="3" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="238" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C238" s="3">
-        <v>90000001</v>
-      </c>
-      <c r="D238" s="3">
-        <v>90000002</v>
-      </c>
-      <c r="E238" s="2">
-        <v>1</v>
-      </c>
-      <c r="F238" s="3">
-        <v>100</v>
-      </c>
-      <c r="G238" s="3">
-        <v>10000144</v>
-      </c>
-      <c r="H238" s="3">
-        <v>1</v>
-      </c>
-      <c r="I238" s="8">
-        <v>10000184</v>
-      </c>
-      <c r="J238" s="8">
-        <v>60</v>
-      </c>
-      <c r="K238" s="2">
-        <v>0</v>
-      </c>
-      <c r="L238" s="2"/>
-      <c r="M238" s="12" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="239" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C239" s="3">
-        <v>90000002</v>
-      </c>
-      <c r="D239" s="3">
-        <v>90000003</v>
-      </c>
-      <c r="E239" s="2">
-        <v>1</v>
-      </c>
-      <c r="F239" s="3">
-        <v>100</v>
-      </c>
-      <c r="G239" s="3">
-        <v>10000145</v>
-      </c>
-      <c r="H239" s="3">
-        <v>1</v>
-      </c>
-      <c r="I239" s="8">
-        <v>10000184</v>
-      </c>
-      <c r="J239" s="8">
-        <v>2</v>
-      </c>
-      <c r="K239" s="2">
-        <v>0</v>
-      </c>
-      <c r="L239" s="2"/>
-      <c r="M239" s="16" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="240" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C240" s="3">
-        <v>90000003</v>
-      </c>
-      <c r="D240" s="3">
-        <v>90000004</v>
-      </c>
-      <c r="E240" s="2">
-        <v>1</v>
-      </c>
-      <c r="F240" s="3">
-        <v>100</v>
-      </c>
-      <c r="G240" s="3">
-        <v>10000146</v>
-      </c>
-      <c r="H240" s="3">
-        <v>1</v>
-      </c>
-      <c r="I240" s="8">
-        <v>10000184</v>
-      </c>
-      <c r="J240" s="8">
-        <v>25</v>
-      </c>
-      <c r="K240" s="2">
-        <v>0</v>
-      </c>
-      <c r="L240" s="2"/>
-      <c r="M240" s="12" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="241" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C241" s="3">
-        <v>90000004</v>
-      </c>
-      <c r="D241" s="3">
-        <v>90000005</v>
-      </c>
-      <c r="E241" s="2">
-        <v>1</v>
-      </c>
-      <c r="F241" s="3">
-        <v>100</v>
-      </c>
-      <c r="G241" s="3">
-        <v>10000147</v>
-      </c>
-      <c r="H241" s="3">
-        <v>1</v>
-      </c>
-      <c r="I241" s="8">
-        <v>10000184</v>
-      </c>
-      <c r="J241" s="8">
-        <v>30</v>
-      </c>
-      <c r="K241" s="2">
-        <v>0</v>
-      </c>
-      <c r="L241" s="2"/>
-      <c r="M241" s="11" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="242" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C242" s="3">
-        <v>90000005</v>
-      </c>
-      <c r="D242" s="3">
-        <v>90000006</v>
-      </c>
-      <c r="E242" s="2">
-        <v>1</v>
-      </c>
-      <c r="F242" s="3">
-        <v>100</v>
-      </c>
-      <c r="G242" s="3">
-        <v>10010033</v>
-      </c>
-      <c r="H242" s="3">
-        <v>1</v>
-      </c>
-      <c r="I242" s="8">
-        <v>10000184</v>
-      </c>
-      <c r="J242" s="8">
-        <v>50</v>
-      </c>
-      <c r="K242" s="2">
-        <v>0</v>
-      </c>
-      <c r="L242" s="2"/>
-      <c r="M242" s="11" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="243" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C243" s="3">
-        <v>90000006</v>
-      </c>
-      <c r="D243" s="3">
-        <v>90000007</v>
-      </c>
-      <c r="E243" s="2">
-        <v>1</v>
-      </c>
-      <c r="F243" s="3">
-        <v>100</v>
-      </c>
-      <c r="G243" s="3">
-        <v>10010083</v>
-      </c>
-      <c r="H243" s="3">
-        <v>1</v>
-      </c>
-      <c r="I243" s="8">
-        <v>10000184</v>
-      </c>
-      <c r="J243" s="8">
-        <v>100</v>
-      </c>
-      <c r="K243" s="2">
-        <v>0</v>
-      </c>
-      <c r="L243" s="2"/>
-      <c r="M243" s="11" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="244" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C244" s="3">
-        <v>90000007</v>
-      </c>
-      <c r="D244" s="3">
-        <v>0</v>
-      </c>
-      <c r="E244" s="2">
-        <v>1</v>
-      </c>
-      <c r="F244" s="3">
-        <v>100</v>
-      </c>
-      <c r="G244" s="3">
-        <v>10010098</v>
-      </c>
-      <c r="H244" s="3">
-        <v>1</v>
-      </c>
-      <c r="I244" s="8">
-        <v>10000184</v>
-      </c>
-      <c r="J244" s="8">
-        <v>45</v>
-      </c>
-      <c r="K244" s="2">
-        <v>0</v>
-      </c>
-      <c r="L244" s="2"/>
-      <c r="M244" s="11" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="245" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C245" s="3">
-        <v>91000001</v>
-      </c>
-      <c r="D245" s="3">
-        <v>91000002</v>
-      </c>
-      <c r="E245" s="2">
-        <v>1</v>
-      </c>
-      <c r="F245" s="3">
-        <v>100</v>
-      </c>
-      <c r="G245" s="3">
-        <v>10010086</v>
-      </c>
-      <c r="H245" s="3">
-        <v>1</v>
-      </c>
-      <c r="I245" s="19">
-        <v>36</v>
-      </c>
-      <c r="J245" s="20">
-        <v>8</v>
-      </c>
-      <c r="K245" s="2">
-        <v>0</v>
-      </c>
-      <c r="M245" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="246" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C246" s="3">
-        <v>91000002</v>
-      </c>
-      <c r="D246" s="3">
-        <v>91000003</v>
-      </c>
-      <c r="E246" s="2">
-        <v>1</v>
-      </c>
-      <c r="F246" s="3">
-        <v>100</v>
-      </c>
-      <c r="G246" s="3">
-        <v>10010096</v>
-      </c>
-      <c r="H246" s="3">
-        <v>1</v>
-      </c>
-      <c r="I246" s="19">
-        <v>36</v>
-      </c>
-      <c r="J246" s="20">
-        <v>20</v>
-      </c>
-      <c r="K246" s="2">
-        <v>0</v>
-      </c>
-      <c r="M246" s="3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="247" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C247" s="3">
-        <v>91000003</v>
-      </c>
-      <c r="D247" s="3">
-        <v>91000004</v>
-      </c>
-      <c r="E247" s="2">
-        <v>1</v>
-      </c>
-      <c r="F247" s="3">
-        <v>100</v>
-      </c>
-      <c r="G247" s="3">
-        <v>10010074</v>
-      </c>
-      <c r="H247" s="3">
-        <v>1</v>
-      </c>
-      <c r="I247" s="19">
-        <v>36</v>
-      </c>
-      <c r="J247" s="20">
-        <v>8</v>
-      </c>
-      <c r="K247" s="2">
-        <v>0</v>
-      </c>
-      <c r="M247" s="3" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="248" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C248" s="3">
-        <v>91000004</v>
-      </c>
-      <c r="D248" s="3">
-        <v>91000005</v>
-      </c>
-      <c r="E248" s="2">
-        <v>1</v>
-      </c>
-      <c r="F248" s="3">
-        <v>100</v>
-      </c>
-      <c r="G248" s="3">
-        <v>10010075</v>
-      </c>
-      <c r="H248" s="3">
-        <v>1</v>
-      </c>
-      <c r="I248" s="19">
-        <v>36</v>
-      </c>
-      <c r="J248" s="20">
-        <v>20</v>
-      </c>
-      <c r="K248" s="2">
-        <v>0</v>
-      </c>
-      <c r="M248" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="249" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C249" s="3">
-        <v>91000005</v>
-      </c>
-      <c r="D249" s="3">
-        <v>91000006</v>
-      </c>
-      <c r="E249" s="2">
-        <v>1</v>
-      </c>
-      <c r="F249" s="3">
-        <v>100</v>
-      </c>
-      <c r="G249" s="2">
-        <v>10010083</v>
-      </c>
-      <c r="H249" s="3">
-        <v>1</v>
-      </c>
-      <c r="I249" s="19">
-        <v>36</v>
-      </c>
-      <c r="J249" s="20">
-        <v>1</v>
-      </c>
-      <c r="K249" s="2">
-        <v>0</v>
-      </c>
-      <c r="M249" s="15" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="250" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C250" s="3">
-        <v>91000006</v>
-      </c>
-      <c r="D250" s="3">
-        <v>91000007</v>
-      </c>
-      <c r="E250" s="2">
-        <v>1</v>
-      </c>
-      <c r="F250" s="3">
-        <v>100</v>
-      </c>
-      <c r="G250" s="2">
-        <v>10010098</v>
-      </c>
-      <c r="H250" s="3">
-        <v>1</v>
-      </c>
-      <c r="I250" s="19">
-        <v>36</v>
-      </c>
-      <c r="J250" s="20">
-        <v>1</v>
-      </c>
-      <c r="K250" s="2">
-        <v>0</v>
-      </c>
-      <c r="M250" s="15" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="251" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C251" s="3">
-        <v>91000007</v>
-      </c>
-      <c r="D251" s="3">
-        <v>0</v>
-      </c>
-      <c r="E251" s="2">
-        <v>1</v>
-      </c>
-      <c r="F251" s="3">
-        <v>100</v>
-      </c>
-      <c r="G251" s="9">
-        <v>10010040</v>
-      </c>
-      <c r="H251" s="3">
-        <v>1</v>
-      </c>
-      <c r="I251" s="19">
-        <v>36</v>
-      </c>
-      <c r="J251" s="20">
-        <v>100</v>
-      </c>
-      <c r="K251" s="2">
-        <v>1</v>
-      </c>
-      <c r="M251" s="9" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="252" spans="3:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C252" s="3">
-        <v>92000001</v>
-      </c>
-      <c r="D252" s="3">
-        <v>92000002</v>
-      </c>
-      <c r="E252" s="2">
-        <v>1</v>
-      </c>
-      <c r="F252" s="3">
-        <v>100</v>
-      </c>
-      <c r="G252" s="3">
-        <v>10060100</v>
-      </c>
-      <c r="H252" s="3">
-        <v>1</v>
-      </c>
-      <c r="I252" s="9">
-        <v>10000136</v>
-      </c>
-      <c r="J252" s="3">
-        <v>50</v>
-      </c>
-      <c r="K252" s="2">
-        <v>0</v>
-      </c>
-      <c r="M252" s="22" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q252" s="7"/>
-    </row>
-    <row r="253" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C253" s="3">
-        <v>92000002</v>
-      </c>
-      <c r="D253" s="3">
-        <v>92000003</v>
-      </c>
-      <c r="E253" s="2">
-        <v>1</v>
-      </c>
-      <c r="F253" s="3">
-        <v>100</v>
-      </c>
-      <c r="G253" s="3">
-        <v>10060200</v>
-      </c>
-      <c r="H253" s="3">
-        <v>1</v>
-      </c>
-      <c r="I253" s="9">
-        <v>10000136</v>
-      </c>
-      <c r="J253" s="3">
-        <v>50</v>
-      </c>
-      <c r="K253" s="2">
-        <v>0</v>
-      </c>
-      <c r="M253" s="22" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="254" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C254" s="3">
-        <v>92000003</v>
-      </c>
-      <c r="D254" s="3">
-        <v>92000004</v>
-      </c>
-      <c r="E254" s="2">
-        <v>1</v>
-      </c>
-      <c r="F254" s="3">
-        <v>100</v>
-      </c>
-      <c r="G254" s="3">
-        <v>10060300</v>
-      </c>
-      <c r="H254" s="3">
-        <v>1</v>
-      </c>
-      <c r="I254" s="9">
-        <v>10000136</v>
-      </c>
-      <c r="J254" s="3">
-        <v>50</v>
-      </c>
-      <c r="K254" s="2">
-        <v>0</v>
-      </c>
-      <c r="M254" s="22" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="255" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C255" s="3">
-        <v>92000004</v>
-      </c>
-      <c r="D255" s="3">
-        <v>92000005</v>
-      </c>
-      <c r="E255" s="2">
-        <v>1</v>
-      </c>
-      <c r="F255" s="3">
-        <v>100</v>
-      </c>
-      <c r="G255" s="3">
-        <v>10060400</v>
-      </c>
-      <c r="H255" s="3">
-        <v>1</v>
-      </c>
-      <c r="I255" s="9">
-        <v>10000136</v>
-      </c>
-      <c r="J255" s="3">
-        <v>50</v>
-      </c>
-      <c r="K255" s="2">
-        <v>0</v>
-      </c>
-      <c r="M255" s="22" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="256" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C256" s="3">
-        <v>92000005</v>
-      </c>
-      <c r="D256" s="3">
-        <v>92000006</v>
-      </c>
-      <c r="E256" s="2">
-        <v>1</v>
-      </c>
-      <c r="F256" s="3">
-        <v>100</v>
-      </c>
-      <c r="G256" s="3">
-        <v>10060500</v>
-      </c>
-      <c r="H256" s="3">
-        <v>1</v>
-      </c>
-      <c r="I256" s="9">
-        <v>10000136</v>
-      </c>
-      <c r="J256" s="3">
-        <v>50</v>
-      </c>
-      <c r="K256" s="2">
-        <v>0</v>
-      </c>
-      <c r="M256" s="22" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="257" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C257" s="3">
-        <v>92000006</v>
-      </c>
-      <c r="D257" s="3">
-        <v>92000007</v>
-      </c>
-      <c r="E257" s="2">
-        <v>1</v>
-      </c>
-      <c r="F257" s="3">
-        <v>100</v>
-      </c>
-      <c r="G257" s="3">
-        <v>10060600</v>
-      </c>
-      <c r="H257" s="3">
-        <v>1</v>
-      </c>
-      <c r="I257" s="9">
-        <v>10000136</v>
-      </c>
-      <c r="J257" s="3">
-        <v>50</v>
-      </c>
-      <c r="K257" s="2">
-        <v>0</v>
-      </c>
-      <c r="M257" s="22" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="258" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C258" s="3">
-        <v>92000007</v>
-      </c>
-      <c r="D258" s="3">
-        <v>92000008</v>
-      </c>
-      <c r="E258" s="2">
-        <v>1</v>
-      </c>
-      <c r="F258" s="3">
-        <v>100</v>
-      </c>
-      <c r="G258" s="3">
-        <v>10060700</v>
-      </c>
-      <c r="H258" s="3">
-        <v>1</v>
-      </c>
-      <c r="I258" s="9">
-        <v>10000136</v>
-      </c>
-      <c r="J258" s="3">
-        <v>50</v>
-      </c>
-      <c r="K258" s="2">
-        <v>0</v>
-      </c>
-      <c r="M258" s="22" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="259" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C259" s="3">
+        <v>80000004</v>
+      </c>
+      <c r="D259" s="3">
+        <v>80000005</v>
+      </c>
+      <c r="E259" s="3">
+        <v>1</v>
+      </c>
+      <c r="F259" s="3">
+        <v>100</v>
+      </c>
+      <c r="G259" s="9">
+        <v>10000139</v>
+      </c>
+      <c r="H259" s="3">
+        <v>1</v>
+      </c>
+      <c r="I259" s="8">
+        <v>10000163</v>
+      </c>
+      <c r="J259" s="8">
+        <v>20</v>
+      </c>
+      <c r="K259" s="2">
+        <v>0</v>
+      </c>
+      <c r="M259" s="3" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="260" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C260" s="3">
+        <v>80000005</v>
+      </c>
+      <c r="D260" s="3">
+        <v>80000006</v>
+      </c>
+      <c r="E260" s="3">
+        <v>1</v>
+      </c>
+      <c r="F260" s="3">
+        <v>100</v>
+      </c>
+      <c r="G260" s="9">
+        <v>10000143</v>
+      </c>
+      <c r="H260" s="3">
+        <v>1</v>
+      </c>
+      <c r="I260" s="8">
+        <v>10000163</v>
+      </c>
+      <c r="J260" s="8">
+        <v>20</v>
+      </c>
+      <c r="K260" s="2">
+        <v>0</v>
+      </c>
+      <c r="M260" s="3" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="261" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C261" s="3">
+        <v>80000006</v>
+      </c>
+      <c r="D261" s="3">
+        <v>80000007</v>
+      </c>
+      <c r="E261" s="3">
+        <v>1</v>
+      </c>
+      <c r="F261" s="3">
+        <v>100</v>
+      </c>
+      <c r="G261" s="9">
+        <v>10000152</v>
+      </c>
+      <c r="H261" s="3">
+        <v>1</v>
+      </c>
+      <c r="I261" s="8">
+        <v>10000163</v>
+      </c>
+      <c r="J261" s="8">
+        <v>35</v>
+      </c>
+      <c r="K261" s="2">
+        <v>0</v>
+      </c>
+      <c r="M261" s="3" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="262" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C262" s="3">
+        <v>80000007</v>
+      </c>
+      <c r="D262" s="3">
+        <v>80000008</v>
+      </c>
+      <c r="E262" s="3">
+        <v>1</v>
+      </c>
+      <c r="F262" s="3">
+        <v>100</v>
+      </c>
+      <c r="G262" s="9">
+        <v>10000155</v>
+      </c>
+      <c r="H262" s="3">
+        <v>1</v>
+      </c>
+      <c r="I262" s="8">
+        <v>10000163</v>
+      </c>
+      <c r="J262" s="8">
+        <v>5</v>
+      </c>
+      <c r="K262" s="2">
+        <v>0</v>
+      </c>
+      <c r="M262" s="3" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="263" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C263" s="3">
+        <v>80000008</v>
+      </c>
+      <c r="D263" s="3">
+        <v>80000009</v>
+      </c>
+      <c r="E263" s="3">
+        <v>1</v>
+      </c>
+      <c r="F263" s="3">
+        <v>100</v>
+      </c>
+      <c r="G263" s="9">
+        <v>10000158</v>
+      </c>
+      <c r="H263" s="3">
+        <v>1</v>
+      </c>
+      <c r="I263" s="8">
+        <v>10000163</v>
+      </c>
+      <c r="J263" s="8">
+        <v>20</v>
+      </c>
+      <c r="K263" s="2">
+        <v>0</v>
+      </c>
+      <c r="M263" s="3" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="264" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C264" s="3">
+        <v>80000009</v>
+      </c>
+      <c r="D264" s="3">
+        <v>0</v>
+      </c>
+      <c r="E264" s="3">
+        <v>1</v>
+      </c>
+      <c r="F264" s="3">
+        <v>100</v>
+      </c>
+      <c r="G264" s="9">
+        <v>10010093</v>
+      </c>
+      <c r="H264" s="3">
+        <v>1</v>
+      </c>
+      <c r="I264" s="8">
+        <v>10000163</v>
+      </c>
+      <c r="J264" s="8">
+        <v>35</v>
+      </c>
+      <c r="K264" s="2">
+        <v>0</v>
+      </c>
+      <c r="M264" s="3" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="265" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C265" s="3">
+        <v>90000001</v>
+      </c>
+      <c r="D265" s="3">
+        <v>90000002</v>
+      </c>
+      <c r="E265" s="2">
+        <v>1</v>
+      </c>
+      <c r="F265" s="3">
+        <v>100</v>
+      </c>
+      <c r="G265" s="3">
+        <v>10000144</v>
+      </c>
+      <c r="H265" s="3">
+        <v>1</v>
+      </c>
+      <c r="I265" s="8">
+        <v>10000184</v>
+      </c>
+      <c r="J265" s="8">
+        <v>60</v>
+      </c>
+      <c r="K265" s="2">
+        <v>0</v>
+      </c>
+      <c r="L265" s="2"/>
+      <c r="M265" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="266" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C266" s="3">
+        <v>90000002</v>
+      </c>
+      <c r="D266" s="3">
+        <v>90000003</v>
+      </c>
+      <c r="E266" s="2">
+        <v>1</v>
+      </c>
+      <c r="F266" s="3">
+        <v>100</v>
+      </c>
+      <c r="G266" s="3">
+        <v>10000145</v>
+      </c>
+      <c r="H266" s="3">
+        <v>1</v>
+      </c>
+      <c r="I266" s="8">
+        <v>10000184</v>
+      </c>
+      <c r="J266" s="8">
+        <v>2</v>
+      </c>
+      <c r="K266" s="2">
+        <v>0</v>
+      </c>
+      <c r="L266" s="2"/>
+      <c r="M266" s="16" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="267" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C267" s="3">
+        <v>90000003</v>
+      </c>
+      <c r="D267" s="3">
+        <v>90000004</v>
+      </c>
+      <c r="E267" s="2">
+        <v>1</v>
+      </c>
+      <c r="F267" s="3">
+        <v>100</v>
+      </c>
+      <c r="G267" s="3">
+        <v>10000146</v>
+      </c>
+      <c r="H267" s="3">
+        <v>1</v>
+      </c>
+      <c r="I267" s="8">
+        <v>10000184</v>
+      </c>
+      <c r="J267" s="8">
+        <v>25</v>
+      </c>
+      <c r="K267" s="2">
+        <v>0</v>
+      </c>
+      <c r="L267" s="2"/>
+      <c r="M267" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="268" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C268" s="3">
+        <v>90000004</v>
+      </c>
+      <c r="D268" s="3">
+        <v>90000005</v>
+      </c>
+      <c r="E268" s="2">
+        <v>1</v>
+      </c>
+      <c r="F268" s="3">
+        <v>100</v>
+      </c>
+      <c r="G268" s="3">
+        <v>10000147</v>
+      </c>
+      <c r="H268" s="3">
+        <v>1</v>
+      </c>
+      <c r="I268" s="8">
+        <v>10000184</v>
+      </c>
+      <c r="J268" s="8">
+        <v>30</v>
+      </c>
+      <c r="K268" s="2">
+        <v>0</v>
+      </c>
+      <c r="L268" s="2"/>
+      <c r="M268" s="11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="269" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C269" s="3">
+        <v>90000005</v>
+      </c>
+      <c r="D269" s="3">
+        <v>90000006</v>
+      </c>
+      <c r="E269" s="2">
+        <v>1</v>
+      </c>
+      <c r="F269" s="3">
+        <v>100</v>
+      </c>
+      <c r="G269" s="3">
+        <v>10010033</v>
+      </c>
+      <c r="H269" s="3">
+        <v>1</v>
+      </c>
+      <c r="I269" s="8">
+        <v>10000184</v>
+      </c>
+      <c r="J269" s="8">
+        <v>50</v>
+      </c>
+      <c r="K269" s="2">
+        <v>0</v>
+      </c>
+      <c r="L269" s="2"/>
+      <c r="M269" s="11" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="270" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C270" s="3">
+        <v>90000006</v>
+      </c>
+      <c r="D270" s="3">
+        <v>90000007</v>
+      </c>
+      <c r="E270" s="2">
+        <v>1</v>
+      </c>
+      <c r="F270" s="3">
+        <v>100</v>
+      </c>
+      <c r="G270" s="3">
+        <v>10010083</v>
+      </c>
+      <c r="H270" s="3">
+        <v>1</v>
+      </c>
+      <c r="I270" s="8">
+        <v>10000184</v>
+      </c>
+      <c r="J270" s="8">
+        <v>100</v>
+      </c>
+      <c r="K270" s="2">
+        <v>0</v>
+      </c>
+      <c r="L270" s="2"/>
+      <c r="M270" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="271" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C271" s="3">
+        <v>90000007</v>
+      </c>
+      <c r="D271" s="3">
+        <v>0</v>
+      </c>
+      <c r="E271" s="2">
+        <v>1</v>
+      </c>
+      <c r="F271" s="3">
+        <v>100</v>
+      </c>
+      <c r="G271" s="3">
+        <v>10010098</v>
+      </c>
+      <c r="H271" s="3">
+        <v>1</v>
+      </c>
+      <c r="I271" s="8">
+        <v>10000184</v>
+      </c>
+      <c r="J271" s="8">
+        <v>45</v>
+      </c>
+      <c r="K271" s="2">
+        <v>0</v>
+      </c>
+      <c r="L271" s="2"/>
+      <c r="M271" s="11" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="272" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C272" s="3">
+        <v>91000001</v>
+      </c>
+      <c r="D272" s="3">
+        <v>91000002</v>
+      </c>
+      <c r="E272" s="2">
+        <v>1</v>
+      </c>
+      <c r="F272" s="3">
+        <v>100</v>
+      </c>
+      <c r="G272" s="3">
+        <v>10010086</v>
+      </c>
+      <c r="H272" s="3">
+        <v>1</v>
+      </c>
+      <c r="I272" s="19">
+        <v>36</v>
+      </c>
+      <c r="J272" s="20">
+        <v>8</v>
+      </c>
+      <c r="K272" s="2">
+        <v>0</v>
+      </c>
+      <c r="M272" s="3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="273" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C273" s="3">
+        <v>91000002</v>
+      </c>
+      <c r="D273" s="3">
+        <v>91000003</v>
+      </c>
+      <c r="E273" s="2">
+        <v>1</v>
+      </c>
+      <c r="F273" s="3">
+        <v>100</v>
+      </c>
+      <c r="G273" s="3">
+        <v>10010096</v>
+      </c>
+      <c r="H273" s="3">
+        <v>1</v>
+      </c>
+      <c r="I273" s="19">
+        <v>36</v>
+      </c>
+      <c r="J273" s="20">
+        <v>20</v>
+      </c>
+      <c r="K273" s="2">
+        <v>0</v>
+      </c>
+      <c r="M273" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="274" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C274" s="3">
+        <v>91000003</v>
+      </c>
+      <c r="D274" s="3">
+        <v>91000004</v>
+      </c>
+      <c r="E274" s="2">
+        <v>1</v>
+      </c>
+      <c r="F274" s="3">
+        <v>100</v>
+      </c>
+      <c r="G274" s="3">
+        <v>10010074</v>
+      </c>
+      <c r="H274" s="3">
+        <v>1</v>
+      </c>
+      <c r="I274" s="19">
+        <v>36</v>
+      </c>
+      <c r="J274" s="20">
+        <v>8</v>
+      </c>
+      <c r="K274" s="2">
+        <v>0</v>
+      </c>
+      <c r="M274" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="275" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C275" s="3">
+        <v>91000004</v>
+      </c>
+      <c r="D275" s="3">
+        <v>91000005</v>
+      </c>
+      <c r="E275" s="2">
+        <v>1</v>
+      </c>
+      <c r="F275" s="3">
+        <v>100</v>
+      </c>
+      <c r="G275" s="3">
+        <v>10010075</v>
+      </c>
+      <c r="H275" s="3">
+        <v>1</v>
+      </c>
+      <c r="I275" s="19">
+        <v>36</v>
+      </c>
+      <c r="J275" s="20">
+        <v>20</v>
+      </c>
+      <c r="K275" s="2">
+        <v>0</v>
+      </c>
+      <c r="M275" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="276" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C276" s="3">
+        <v>91000005</v>
+      </c>
+      <c r="D276" s="3">
+        <v>91000006</v>
+      </c>
+      <c r="E276" s="2">
+        <v>1</v>
+      </c>
+      <c r="F276" s="3">
+        <v>100</v>
+      </c>
+      <c r="G276" s="2">
+        <v>10010083</v>
+      </c>
+      <c r="H276" s="3">
+        <v>1</v>
+      </c>
+      <c r="I276" s="19">
+        <v>36</v>
+      </c>
+      <c r="J276" s="20">
+        <v>1</v>
+      </c>
+      <c r="K276" s="2">
+        <v>0</v>
+      </c>
+      <c r="M276" s="15" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="277" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C277" s="3">
+        <v>91000006</v>
+      </c>
+      <c r="D277" s="3">
+        <v>91000007</v>
+      </c>
+      <c r="E277" s="2">
+        <v>1</v>
+      </c>
+      <c r="F277" s="3">
+        <v>100</v>
+      </c>
+      <c r="G277" s="2">
+        <v>10010098</v>
+      </c>
+      <c r="H277" s="3">
+        <v>1</v>
+      </c>
+      <c r="I277" s="19">
+        <v>36</v>
+      </c>
+      <c r="J277" s="20">
+        <v>1</v>
+      </c>
+      <c r="K277" s="2">
+        <v>0</v>
+      </c>
+      <c r="M277" s="15" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="278" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C278" s="3">
+        <v>91000007</v>
+      </c>
+      <c r="D278" s="3">
+        <v>0</v>
+      </c>
+      <c r="E278" s="2">
+        <v>1</v>
+      </c>
+      <c r="F278" s="3">
+        <v>100</v>
+      </c>
+      <c r="G278" s="9">
+        <v>10010040</v>
+      </c>
+      <c r="H278" s="3">
+        <v>1</v>
+      </c>
+      <c r="I278" s="19">
+        <v>36</v>
+      </c>
+      <c r="J278" s="20">
+        <v>100</v>
+      </c>
+      <c r="K278" s="2">
+        <v>1</v>
+      </c>
+      <c r="M278" s="9" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="279" spans="3:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C279" s="3">
+        <v>92000001</v>
+      </c>
+      <c r="D279" s="3">
+        <v>92000002</v>
+      </c>
+      <c r="E279" s="2">
+        <v>1</v>
+      </c>
+      <c r="F279" s="3">
+        <v>100</v>
+      </c>
+      <c r="G279" s="3">
+        <v>10060100</v>
+      </c>
+      <c r="H279" s="3">
+        <v>1</v>
+      </c>
+      <c r="I279" s="9">
+        <v>10000136</v>
+      </c>
+      <c r="J279" s="3">
+        <v>50</v>
+      </c>
+      <c r="K279" s="2">
+        <v>0</v>
+      </c>
+      <c r="M279" s="22" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q279" s="7"/>
+    </row>
+    <row r="280" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C280" s="3">
+        <v>92000002</v>
+      </c>
+      <c r="D280" s="3">
+        <v>92000003</v>
+      </c>
+      <c r="E280" s="2">
+        <v>1</v>
+      </c>
+      <c r="F280" s="3">
+        <v>100</v>
+      </c>
+      <c r="G280" s="3">
+        <v>10060200</v>
+      </c>
+      <c r="H280" s="3">
+        <v>1</v>
+      </c>
+      <c r="I280" s="9">
+        <v>10000136</v>
+      </c>
+      <c r="J280" s="3">
+        <v>50</v>
+      </c>
+      <c r="K280" s="2">
+        <v>0</v>
+      </c>
+      <c r="M280" s="22" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="281" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C281" s="3">
+        <v>92000003</v>
+      </c>
+      <c r="D281" s="3">
+        <v>92000004</v>
+      </c>
+      <c r="E281" s="2">
+        <v>1</v>
+      </c>
+      <c r="F281" s="3">
+        <v>100</v>
+      </c>
+      <c r="G281" s="3">
+        <v>10060300</v>
+      </c>
+      <c r="H281" s="3">
+        <v>1</v>
+      </c>
+      <c r="I281" s="9">
+        <v>10000136</v>
+      </c>
+      <c r="J281" s="3">
+        <v>50</v>
+      </c>
+      <c r="K281" s="2">
+        <v>0</v>
+      </c>
+      <c r="M281" s="22" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="282" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C282" s="3">
+        <v>92000004</v>
+      </c>
+      <c r="D282" s="3">
+        <v>92000005</v>
+      </c>
+      <c r="E282" s="2">
+        <v>1</v>
+      </c>
+      <c r="F282" s="3">
+        <v>100</v>
+      </c>
+      <c r="G282" s="3">
+        <v>10060400</v>
+      </c>
+      <c r="H282" s="3">
+        <v>1</v>
+      </c>
+      <c r="I282" s="9">
+        <v>10000136</v>
+      </c>
+      <c r="J282" s="3">
+        <v>50</v>
+      </c>
+      <c r="K282" s="2">
+        <v>0</v>
+      </c>
+      <c r="M282" s="22" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="283" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C283" s="3">
+        <v>92000005</v>
+      </c>
+      <c r="D283" s="3">
+        <v>92000006</v>
+      </c>
+      <c r="E283" s="2">
+        <v>1</v>
+      </c>
+      <c r="F283" s="3">
+        <v>100</v>
+      </c>
+      <c r="G283" s="3">
+        <v>10060500</v>
+      </c>
+      <c r="H283" s="3">
+        <v>1</v>
+      </c>
+      <c r="I283" s="9">
+        <v>10000136</v>
+      </c>
+      <c r="J283" s="3">
+        <v>50</v>
+      </c>
+      <c r="K283" s="2">
+        <v>0</v>
+      </c>
+      <c r="M283" s="22" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="284" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C284" s="3">
+        <v>92000006</v>
+      </c>
+      <c r="D284" s="3">
+        <v>92000007</v>
+      </c>
+      <c r="E284" s="2">
+        <v>1</v>
+      </c>
+      <c r="F284" s="3">
+        <v>100</v>
+      </c>
+      <c r="G284" s="3">
+        <v>10060600</v>
+      </c>
+      <c r="H284" s="3">
+        <v>1</v>
+      </c>
+      <c r="I284" s="9">
+        <v>10000136</v>
+      </c>
+      <c r="J284" s="3">
+        <v>50</v>
+      </c>
+      <c r="K284" s="2">
+        <v>0</v>
+      </c>
+      <c r="M284" s="22" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="285" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C285" s="3">
+        <v>92000007</v>
+      </c>
+      <c r="D285" s="3">
         <v>92000008</v>
       </c>
-      <c r="D259" s="3">
-        <v>0</v>
-      </c>
-      <c r="E259" s="2">
-        <v>1</v>
-      </c>
-      <c r="F259" s="3">
-        <v>100</v>
-      </c>
-      <c r="G259" s="3">
+      <c r="E285" s="2">
+        <v>1</v>
+      </c>
+      <c r="F285" s="3">
+        <v>100</v>
+      </c>
+      <c r="G285" s="3">
+        <v>10060700</v>
+      </c>
+      <c r="H285" s="3">
+        <v>1</v>
+      </c>
+      <c r="I285" s="9">
+        <v>10000136</v>
+      </c>
+      <c r="J285" s="3">
+        <v>50</v>
+      </c>
+      <c r="K285" s="2">
+        <v>0</v>
+      </c>
+      <c r="M285" s="22" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="286" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C286" s="3">
+        <v>92000008</v>
+      </c>
+      <c r="D286" s="3">
+        <v>0</v>
+      </c>
+      <c r="E286" s="2">
+        <v>1</v>
+      </c>
+      <c r="F286" s="3">
+        <v>100</v>
+      </c>
+      <c r="G286" s="3">
         <v>10000212</v>
       </c>
-      <c r="H259" s="3">
-        <v>1</v>
-      </c>
-      <c r="I259" s="9">
+      <c r="H286" s="3">
+        <v>1</v>
+      </c>
+      <c r="I286" s="9">
         <v>10000136</v>
       </c>
-      <c r="J259" s="3">
+      <c r="J286" s="3">
         <v>150</v>
       </c>
-      <c r="K259" s="2">
-        <v>0</v>
-      </c>
-      <c r="M259" s="19" t="s">
+      <c r="K286" s="2">
+        <v>0</v>
+      </c>
+      <c r="M286" s="19" t="s">
         <v>131</v>
       </c>
     </row>
-    <row r="260" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="287" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="288" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="289" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StoreSellConfig.xlsx
+++ b/Excel/StoreSellConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C702BD6-3D72-414E-AD80-F99009EF9B24}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F24A0B51-04AF-4CB1-8815-35A52F3BAFDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StoreSellProto" sheetId="1" r:id="rId1"/>
@@ -10697,7 +10697,7 @@
         <v>100</v>
       </c>
       <c r="G265" s="3">
-        <v>10000144</v>
+        <v>10010093</v>
       </c>
       <c r="H265" s="3">
         <v>1</v>
@@ -10730,7 +10730,7 @@
         <v>100</v>
       </c>
       <c r="G266" s="3">
-        <v>10000145</v>
+        <v>10010083</v>
       </c>
       <c r="H266" s="3">
         <v>1</v>
@@ -10763,7 +10763,7 @@
         <v>100</v>
       </c>
       <c r="G267" s="3">
-        <v>10000146</v>
+        <v>10010086</v>
       </c>
       <c r="H267" s="3">
         <v>1</v>
@@ -10796,7 +10796,7 @@
         <v>100</v>
       </c>
       <c r="G268" s="3">
-        <v>10000147</v>
+        <v>10000143</v>
       </c>
       <c r="H268" s="3">
         <v>1</v>
@@ -10829,7 +10829,7 @@
         <v>100</v>
       </c>
       <c r="G269" s="3">
-        <v>10010033</v>
+        <v>10000152</v>
       </c>
       <c r="H269" s="3">
         <v>1</v>
@@ -10862,7 +10862,7 @@
         <v>100</v>
       </c>
       <c r="G270" s="3">
-        <v>10010083</v>
+        <v>10000165</v>
       </c>
       <c r="H270" s="3">
         <v>1</v>
@@ -10895,7 +10895,7 @@
         <v>100</v>
       </c>
       <c r="G271" s="3">
-        <v>10010098</v>
+        <v>10010045</v>
       </c>
       <c r="H271" s="3">
         <v>1</v>

--- a/Excel/StoreSellConfig.xlsx
+++ b/Excel/StoreSellConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F24A0B51-04AF-4CB1-8815-35A52F3BAFDF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A6E3B1E-D0C1-46D0-9D63-8E725FDF936B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="202" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="163">
   <si>
     <t>Id</t>
   </si>
@@ -502,10 +502,6 @@
     <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
-    <t>梦境之核</t>
-    <phoneticPr fontId="15" type="noConversion"/>
-  </si>
-  <si>
     <t>神兽:生命之核</t>
     <phoneticPr fontId="15" type="noConversion"/>
   </si>
@@ -628,6 +624,14 @@
   </si>
   <si>
     <t>远古之神:耀世之甲</t>
+  </si>
+  <si>
+    <t>魔能袋子</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>奇珍兑换币</t>
+    <phoneticPr fontId="15" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -2635,7 +2639,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q289"/>
+  <dimension ref="A1:Q293"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="5" width="14" customWidth="1"/>
@@ -6827,7 +6831,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="145" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="145" spans="3:13" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C145" s="3">
         <v>50000011</v>
       </c>
@@ -6840,8 +6844,8 @@
       <c r="F145" s="3">
         <v>100</v>
       </c>
-      <c r="G145" s="3">
-        <v>10000152</v>
+      <c r="G145" s="9">
+        <v>10000174</v>
       </c>
       <c r="H145" s="2">
         <v>1</v>
@@ -6850,16 +6854,16 @@
         <v>10000151</v>
       </c>
       <c r="J145" s="3">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K145" s="2">
         <v>0</v>
       </c>
-      <c r="M145" s="15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="146" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M145" s="11" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="146" spans="3:13" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C146" s="3">
         <v>50000012</v>
       </c>
@@ -6872,8 +6876,8 @@
       <c r="F146" s="3">
         <v>100</v>
       </c>
-      <c r="G146" s="3">
-        <v>10000157</v>
+      <c r="G146" s="9">
+        <v>10000175</v>
       </c>
       <c r="H146" s="2">
         <v>1</v>
@@ -6882,16 +6886,16 @@
         <v>10000151</v>
       </c>
       <c r="J146" s="3">
-        <v>1</v>
+        <v>30</v>
       </c>
       <c r="K146" s="2">
         <v>0</v>
       </c>
-      <c r="M146" s="15" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="147" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M146" s="11" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="147" spans="3:13" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C147" s="3">
         <v>50000013</v>
       </c>
@@ -6904,8 +6908,8 @@
       <c r="F147" s="3">
         <v>100</v>
       </c>
-      <c r="G147" s="3">
-        <v>10000150</v>
+      <c r="G147" s="9">
+        <v>10000160</v>
       </c>
       <c r="H147" s="2">
         <v>1</v>
@@ -6914,16 +6918,16 @@
         <v>10000151</v>
       </c>
       <c r="J147" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K147" s="2">
         <v>0</v>
       </c>
-      <c r="M147" s="15" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="148" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M147" s="11" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="148" spans="3:13" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C148" s="3">
         <v>50000014</v>
       </c>
@@ -6936,8 +6940,8 @@
       <c r="F148" s="3">
         <v>100</v>
       </c>
-      <c r="G148" s="3">
-        <v>10010078</v>
+      <c r="G148" s="9">
+        <v>10000178</v>
       </c>
       <c r="H148" s="2">
         <v>1</v>
@@ -6946,16 +6950,16 @@
         <v>10000151</v>
       </c>
       <c r="J148" s="3">
-        <v>5</v>
+        <v>50</v>
       </c>
       <c r="K148" s="2">
         <v>0</v>
       </c>
-      <c r="M148" s="12" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="149" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M148" s="11" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="149" spans="3:13" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C149" s="3">
         <v>50000015</v>
       </c>
@@ -6968,8 +6972,8 @@
       <c r="F149" s="3">
         <v>100</v>
       </c>
-      <c r="G149" s="3">
-        <v>10010079</v>
+      <c r="G149" s="9">
+        <v>10000130</v>
       </c>
       <c r="H149" s="2">
         <v>1</v>
@@ -6978,21 +6982,21 @@
         <v>10000151</v>
       </c>
       <c r="J149" s="3">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="K149" s="2">
         <v>0</v>
       </c>
-      <c r="M149" s="16" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="150" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M149" s="11" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="150" spans="3:13" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C150" s="3">
-        <v>50000016</v>
+        <v>50000017</v>
       </c>
       <c r="D150" s="3">
-        <v>50000017</v>
+        <v>50000018</v>
       </c>
       <c r="E150" s="2">
         <v>1</v>
@@ -7001,7 +7005,7 @@
         <v>100</v>
       </c>
       <c r="G150" s="9">
-        <v>10000174</v>
+        <v>10000182</v>
       </c>
       <c r="H150" s="2">
         <v>1</v>
@@ -7010,21 +7014,21 @@
         <v>10000151</v>
       </c>
       <c r="J150" s="3">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K150" s="2">
         <v>0</v>
       </c>
       <c r="M150" s="11" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="151" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="151" spans="3:13" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C151" s="3">
-        <v>50000017</v>
+        <v>50000018</v>
       </c>
       <c r="D151" s="3">
-        <v>50000018</v>
+        <v>50000019</v>
       </c>
       <c r="E151" s="2">
         <v>1</v>
@@ -7033,7 +7037,7 @@
         <v>100</v>
       </c>
       <c r="G151" s="9">
-        <v>10000175</v>
+        <v>10000181</v>
       </c>
       <c r="H151" s="2">
         <v>1</v>
@@ -7042,21 +7046,21 @@
         <v>10000151</v>
       </c>
       <c r="J151" s="3">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="K151" s="2">
         <v>0</v>
       </c>
       <c r="M151" s="11" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="152" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="152" spans="3:13" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C152" s="3">
-        <v>50000018</v>
+        <v>50000019</v>
       </c>
       <c r="D152" s="3">
-        <v>50000019</v>
+        <v>0</v>
       </c>
       <c r="E152" s="2">
         <v>1</v>
@@ -7065,7 +7069,7 @@
         <v>100</v>
       </c>
       <c r="G152" s="9">
-        <v>10000165</v>
+        <v>10000167</v>
       </c>
       <c r="H152" s="2">
         <v>1</v>
@@ -7074,453 +7078,447 @@
         <v>10000151</v>
       </c>
       <c r="J152" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K152" s="2">
         <v>0</v>
       </c>
       <c r="M152" s="11" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="153" spans="3:13" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C153" s="3">
+        <v>51000001</v>
+      </c>
+      <c r="D153" s="3">
+        <v>51000002</v>
+      </c>
+      <c r="E153" s="2">
+        <v>1</v>
+      </c>
+      <c r="F153" s="3">
+        <v>100</v>
+      </c>
+      <c r="G153" s="3">
+        <v>10010094</v>
+      </c>
+      <c r="H153" s="3">
+        <v>1</v>
+      </c>
+      <c r="I153" s="9">
+        <v>10000167</v>
+      </c>
+      <c r="J153" s="3">
+        <v>20</v>
+      </c>
+      <c r="K153" s="2">
+        <v>0</v>
+      </c>
+      <c r="M153" s="12" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="154" spans="3:13" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C154" s="3">
+        <v>51000002</v>
+      </c>
+      <c r="D154" s="3">
+        <v>51000003</v>
+      </c>
+      <c r="E154" s="2">
+        <v>1</v>
+      </c>
+      <c r="F154" s="3">
+        <v>100</v>
+      </c>
+      <c r="G154" s="3">
+        <v>10000105</v>
+      </c>
+      <c r="H154" s="2">
+        <v>1</v>
+      </c>
+      <c r="I154" s="9">
+        <v>10000167</v>
+      </c>
+      <c r="J154" s="3">
+        <v>10</v>
+      </c>
+      <c r="K154" s="2">
+        <v>0</v>
+      </c>
+      <c r="M154" s="15" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="155" spans="3:13" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C155" s="3">
+        <v>51000003</v>
+      </c>
+      <c r="D155" s="3">
+        <v>51000004</v>
+      </c>
+      <c r="E155" s="2">
+        <v>1</v>
+      </c>
+      <c r="F155" s="3">
+        <v>100</v>
+      </c>
+      <c r="G155" s="3">
+        <v>10010026</v>
+      </c>
+      <c r="H155" s="2">
+        <v>1</v>
+      </c>
+      <c r="I155" s="9">
+        <v>10000167</v>
+      </c>
+      <c r="J155" s="3">
+        <v>10</v>
+      </c>
+      <c r="K155" s="2">
+        <v>0</v>
+      </c>
+      <c r="M155" s="15" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="156" spans="3:13" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C156" s="3">
+        <v>51000004</v>
+      </c>
+      <c r="D156" s="3">
+        <v>51000005</v>
+      </c>
+      <c r="E156" s="2">
+        <v>1</v>
+      </c>
+      <c r="F156" s="3">
+        <v>100</v>
+      </c>
+      <c r="G156" s="3">
+        <v>10000152</v>
+      </c>
+      <c r="H156" s="2">
+        <v>1</v>
+      </c>
+      <c r="I156" s="9">
+        <v>10000167</v>
+      </c>
+      <c r="J156" s="3">
+        <v>1</v>
+      </c>
+      <c r="K156" s="2">
+        <v>0</v>
+      </c>
+      <c r="M156" s="15" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="157" spans="3:13" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C157" s="3">
+        <v>51000005</v>
+      </c>
+      <c r="D157" s="3">
+        <v>51000006</v>
+      </c>
+      <c r="E157" s="2">
+        <v>1</v>
+      </c>
+      <c r="F157" s="3">
+        <v>100</v>
+      </c>
+      <c r="G157" s="3">
+        <v>10000157</v>
+      </c>
+      <c r="H157" s="2">
+        <v>1</v>
+      </c>
+      <c r="I157" s="9">
+        <v>10000167</v>
+      </c>
+      <c r="J157" s="3">
+        <v>1</v>
+      </c>
+      <c r="K157" s="2">
+        <v>0</v>
+      </c>
+      <c r="M157" s="15" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="158" spans="3:13" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C158" s="3">
+        <v>51000006</v>
+      </c>
+      <c r="D158" s="3">
+        <v>51000007</v>
+      </c>
+      <c r="E158" s="2">
+        <v>1</v>
+      </c>
+      <c r="F158" s="3">
+        <v>100</v>
+      </c>
+      <c r="G158" s="3">
+        <v>10000150</v>
+      </c>
+      <c r="H158" s="2">
+        <v>1</v>
+      </c>
+      <c r="I158" s="9">
+        <v>10000167</v>
+      </c>
+      <c r="J158" s="3">
+        <v>3</v>
+      </c>
+      <c r="K158" s="2">
+        <v>0</v>
+      </c>
+      <c r="M158" s="15" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="159" spans="3:13" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C159" s="3">
+        <v>51000007</v>
+      </c>
+      <c r="D159" s="3">
+        <v>51000008</v>
+      </c>
+      <c r="E159" s="2">
+        <v>1</v>
+      </c>
+      <c r="F159" s="3">
+        <v>100</v>
+      </c>
+      <c r="G159" s="3">
+        <v>10010078</v>
+      </c>
+      <c r="H159" s="2">
+        <v>1</v>
+      </c>
+      <c r="I159" s="9">
+        <v>10000167</v>
+      </c>
+      <c r="J159" s="3">
+        <v>5</v>
+      </c>
+      <c r="K159" s="2">
+        <v>0</v>
+      </c>
+      <c r="M159" s="12" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="160" spans="3:13" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C160" s="3">
+        <v>51000008</v>
+      </c>
+      <c r="D160" s="3">
+        <v>51000009</v>
+      </c>
+      <c r="E160" s="2">
+        <v>1</v>
+      </c>
+      <c r="F160" s="3">
+        <v>100</v>
+      </c>
+      <c r="G160" s="3">
+        <v>10010079</v>
+      </c>
+      <c r="H160" s="2">
+        <v>1</v>
+      </c>
+      <c r="I160" s="9">
+        <v>10000167</v>
+      </c>
+      <c r="J160" s="3">
+        <v>5</v>
+      </c>
+      <c r="K160" s="2">
+        <v>0</v>
+      </c>
+      <c r="M160" s="16" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="161" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C161" s="3">
+        <v>51000009</v>
+      </c>
+      <c r="D161" s="3">
+        <v>51000010</v>
+      </c>
+      <c r="E161" s="2">
+        <v>1</v>
+      </c>
+      <c r="F161" s="3">
+        <v>100</v>
+      </c>
+      <c r="G161" s="9">
+        <v>10000165</v>
+      </c>
+      <c r="H161" s="2">
+        <v>1</v>
+      </c>
+      <c r="I161" s="9">
+        <v>10000167</v>
+      </c>
+      <c r="J161" s="3">
+        <v>1</v>
+      </c>
+      <c r="K161" s="2">
+        <v>0</v>
+      </c>
+      <c r="M161" s="11" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="153" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C153" s="3">
-        <v>50000019</v>
-      </c>
-      <c r="D153" s="3">
-        <v>50000020</v>
-      </c>
-      <c r="E153" s="2">
-        <v>1</v>
-      </c>
-      <c r="F153" s="3">
-        <v>100</v>
-      </c>
-      <c r="G153" s="9">
-        <v>10000160</v>
-      </c>
-      <c r="H153" s="2">
-        <v>1</v>
-      </c>
-      <c r="I153" s="9">
-        <v>10000151</v>
-      </c>
-      <c r="J153" s="3">
-        <v>1</v>
-      </c>
-      <c r="K153" s="2">
-        <v>0</v>
-      </c>
-      <c r="M153" s="11" t="s">
-        <v>120</v>
-      </c>
-    </row>
-    <row r="154" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C154" s="3">
-        <v>50000020</v>
-      </c>
-      <c r="D154" s="3">
-        <v>50000021</v>
-      </c>
-      <c r="E154" s="2">
-        <v>1</v>
-      </c>
-      <c r="F154" s="3">
-        <v>100</v>
-      </c>
-      <c r="G154" s="9">
-        <v>10000178</v>
-      </c>
-      <c r="H154" s="2">
-        <v>1</v>
-      </c>
-      <c r="I154" s="9">
-        <v>10000151</v>
-      </c>
-      <c r="J154" s="3">
-        <v>50</v>
-      </c>
-      <c r="K154" s="2">
-        <v>0</v>
-      </c>
-      <c r="M154" s="11" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="155" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C155" s="3">
-        <v>50000021</v>
-      </c>
-      <c r="D155" s="3">
-        <v>50000022</v>
-      </c>
-      <c r="E155" s="2">
-        <v>1</v>
-      </c>
-      <c r="F155" s="3">
-        <v>100</v>
-      </c>
-      <c r="G155" s="9">
-        <v>10000130</v>
-      </c>
-      <c r="H155" s="2">
-        <v>1</v>
-      </c>
-      <c r="I155" s="9">
-        <v>10000151</v>
-      </c>
-      <c r="J155" s="3">
-        <v>75</v>
-      </c>
-      <c r="K155" s="2">
-        <v>0</v>
-      </c>
-      <c r="M155" s="11" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="156" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C156" s="3">
-        <v>50000022</v>
-      </c>
-      <c r="D156" s="3">
-        <v>50000023</v>
-      </c>
-      <c r="E156" s="2">
-        <v>1</v>
-      </c>
-      <c r="F156" s="3">
-        <v>100</v>
-      </c>
-      <c r="G156" s="9">
-        <v>10000179</v>
-      </c>
-      <c r="H156" s="2">
-        <v>1</v>
-      </c>
-      <c r="I156" s="9">
-        <v>10000151</v>
-      </c>
-      <c r="J156" s="3">
-        <v>1</v>
-      </c>
-      <c r="K156" s="2">
-        <v>0</v>
-      </c>
-      <c r="M156" s="11" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="157" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C157" s="3">
-        <v>50000023</v>
-      </c>
-      <c r="D157" s="3">
-        <v>50000024</v>
-      </c>
-      <c r="E157" s="2">
-        <v>1</v>
-      </c>
-      <c r="F157" s="3">
-        <v>100</v>
-      </c>
-      <c r="G157" s="9">
-        <v>10000182</v>
-      </c>
-      <c r="H157" s="2">
-        <v>1</v>
-      </c>
-      <c r="I157" s="9">
-        <v>10000151</v>
-      </c>
-      <c r="J157" s="3">
-        <v>1</v>
-      </c>
-      <c r="K157" s="2">
-        <v>0</v>
-      </c>
-      <c r="M157" s="11" t="s">
+    <row r="162" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C162" s="3">
+        <v>51000010</v>
+      </c>
+      <c r="D162" s="3">
+        <v>51000011</v>
+      </c>
+      <c r="E162" s="2">
+        <v>1</v>
+      </c>
+      <c r="F162" s="3">
+        <v>100</v>
+      </c>
+      <c r="G162" s="9">
+        <v>10000183</v>
+      </c>
+      <c r="H162" s="2">
+        <v>1</v>
+      </c>
+      <c r="I162" s="9">
+        <v>10000167</v>
+      </c>
+      <c r="J162" s="3">
+        <v>5</v>
+      </c>
+      <c r="K162" s="2">
+        <v>0</v>
+      </c>
+      <c r="M162" s="11" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="158" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C158" s="3">
-        <v>50000024</v>
-      </c>
-      <c r="D158" s="3">
-        <v>50000025</v>
-      </c>
-      <c r="E158" s="2">
-        <v>1</v>
-      </c>
-      <c r="F158" s="3">
-        <v>100</v>
-      </c>
-      <c r="G158" s="9">
-        <v>10000183</v>
-      </c>
-      <c r="H158" s="2">
-        <v>1</v>
-      </c>
-      <c r="I158" s="9">
-        <v>10000151</v>
-      </c>
-      <c r="J158" s="3">
-        <v>5</v>
-      </c>
-      <c r="K158" s="2">
-        <v>0</v>
-      </c>
-      <c r="M158" s="11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="159" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C159" s="3">
-        <v>50000025</v>
-      </c>
-      <c r="D159" s="3">
-        <v>0</v>
-      </c>
-      <c r="E159" s="2">
-        <v>1</v>
-      </c>
-      <c r="F159" s="3">
-        <v>100</v>
-      </c>
-      <c r="G159" s="9">
-        <v>10000181</v>
-      </c>
-      <c r="H159" s="2">
-        <v>1</v>
-      </c>
-      <c r="I159" s="9">
-        <v>10000151</v>
-      </c>
-      <c r="J159" s="3">
-        <v>50</v>
-      </c>
-      <c r="K159" s="2">
-        <v>0</v>
-      </c>
-      <c r="M159" s="11" t="s">
-        <v>134</v>
-      </c>
-    </row>
-    <row r="160" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A160" s="3"/>
-      <c r="B160" s="3"/>
-      <c r="C160" s="3">
+    <row r="163" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C163" s="3">
+        <v>51000011</v>
+      </c>
+      <c r="D163" s="3">
+        <v>0</v>
+      </c>
+      <c r="E163" s="2">
+        <v>1</v>
+      </c>
+      <c r="F163" s="3">
+        <v>100</v>
+      </c>
+      <c r="G163" s="9">
+        <v>10010060</v>
+      </c>
+      <c r="H163" s="2">
+        <v>1</v>
+      </c>
+      <c r="I163" s="9">
+        <v>10000167</v>
+      </c>
+      <c r="J163" s="3">
+        <v>8</v>
+      </c>
+      <c r="K163" s="2">
+        <v>0</v>
+      </c>
+      <c r="M163" s="11" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="164" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A164" s="3"/>
+      <c r="B164" s="3"/>
+      <c r="C164" s="3">
         <v>60000001</v>
       </c>
-      <c r="D160" s="3">
+      <c r="D164" s="3">
         <v>60000002</v>
       </c>
-      <c r="E160" s="3">
-        <v>1</v>
-      </c>
-      <c r="F160" s="3">
-        <v>100</v>
-      </c>
-      <c r="G160" s="3">
+      <c r="E164" s="3">
+        <v>1</v>
+      </c>
+      <c r="F164" s="3">
+        <v>100</v>
+      </c>
+      <c r="G164" s="3">
         <v>10000143</v>
       </c>
-      <c r="H160" s="11" t="s">
+      <c r="H164" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="I160" s="9">
+      <c r="I164" s="9">
         <v>10000157</v>
       </c>
-      <c r="J160" s="3">
-        <v>1</v>
-      </c>
-      <c r="K160" s="2">
-        <v>0</v>
-      </c>
-      <c r="L160" s="3"/>
-      <c r="M160" s="15" t="s">
+      <c r="J164" s="3">
+        <v>1</v>
+      </c>
+      <c r="K164" s="2">
+        <v>0</v>
+      </c>
+      <c r="L164" s="3"/>
+      <c r="M164" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="N160" s="3"/>
-      <c r="O160" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="P160" s="3"/>
-    </row>
-    <row r="161" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A161" s="3"/>
-      <c r="B161" s="3"/>
-      <c r="C161" s="3">
+      <c r="N164" s="3"/>
+      <c r="P164" s="3"/>
+    </row>
+    <row r="165" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A165" s="3"/>
+      <c r="B165" s="3"/>
+      <c r="C165" s="3">
         <v>60000002</v>
       </c>
-      <c r="D161" s="3">
+      <c r="D165" s="3">
         <v>60000003</v>
       </c>
-      <c r="E161" s="3">
-        <v>1</v>
-      </c>
-      <c r="F161" s="3">
-        <v>100</v>
-      </c>
-      <c r="G161" s="3">
+      <c r="E165" s="3">
+        <v>1</v>
+      </c>
+      <c r="F165" s="3">
+        <v>100</v>
+      </c>
+      <c r="G165" s="3">
         <v>10010093</v>
       </c>
-      <c r="H161" s="12">
-        <v>1</v>
-      </c>
-      <c r="I161" s="9">
+      <c r="H165" s="12">
+        <v>1</v>
+      </c>
+      <c r="I165" s="9">
         <v>10000143</v>
       </c>
-      <c r="J161" s="11" t="s">
+      <c r="J165" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="K161" s="2">
-        <v>0</v>
-      </c>
-      <c r="L161" s="3"/>
-      <c r="M161" s="12" t="s">
+      <c r="K165" s="2">
+        <v>0</v>
+      </c>
+      <c r="L165" s="3"/>
+      <c r="M165" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="N161" s="3"/>
-      <c r="O161" s="11" t="s">
-        <v>39</v>
-      </c>
-      <c r="P161" s="3"/>
-    </row>
-    <row r="162" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C162" s="3">
-        <v>60000003</v>
-      </c>
-      <c r="D162" s="3">
-        <v>60000004</v>
-      </c>
-      <c r="E162" s="3">
-        <v>1</v>
-      </c>
-      <c r="F162" s="3">
-        <v>100</v>
-      </c>
-      <c r="G162" s="13">
-        <v>10012001</v>
-      </c>
-      <c r="H162" s="3">
-        <v>1</v>
-      </c>
-      <c r="I162" s="3">
-        <v>10010029</v>
-      </c>
-      <c r="J162" s="3">
-        <v>10</v>
-      </c>
-      <c r="K162" s="2">
-        <v>0</v>
-      </c>
-      <c r="M162" s="13" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="163" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C163" s="3">
-        <v>60000004</v>
-      </c>
-      <c r="D163" s="3">
-        <v>60000005</v>
-      </c>
-      <c r="E163" s="3">
-        <v>1</v>
-      </c>
-      <c r="F163" s="3">
-        <v>100</v>
-      </c>
-      <c r="G163" s="13">
-        <v>10012002</v>
-      </c>
-      <c r="H163" s="3">
-        <v>1</v>
-      </c>
-      <c r="I163" s="3">
-        <v>10010029</v>
-      </c>
-      <c r="J163" s="3">
-        <v>10</v>
-      </c>
-      <c r="K163" s="2">
-        <v>0</v>
-      </c>
-      <c r="M163" s="13" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="164" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C164" s="3">
-        <v>60000005</v>
-      </c>
-      <c r="D164" s="3">
-        <v>60000006</v>
-      </c>
-      <c r="E164" s="3">
-        <v>1</v>
-      </c>
-      <c r="F164" s="3">
-        <v>100</v>
-      </c>
-      <c r="G164" s="13">
-        <v>10012003</v>
-      </c>
-      <c r="H164" s="3">
-        <v>1</v>
-      </c>
-      <c r="I164" s="3">
-        <v>10010029</v>
-      </c>
-      <c r="J164" s="3">
-        <v>10</v>
-      </c>
-      <c r="K164" s="2">
-        <v>0</v>
-      </c>
-      <c r="M164" s="13" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="165" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C165" s="3">
-        <v>60000006</v>
-      </c>
-      <c r="D165" s="3">
-        <v>60000007</v>
-      </c>
-      <c r="E165" s="3">
-        <v>1</v>
-      </c>
-      <c r="F165" s="3">
-        <v>100</v>
-      </c>
-      <c r="G165" s="13">
-        <v>10012004</v>
-      </c>
-      <c r="H165" s="3">
-        <v>1</v>
-      </c>
-      <c r="I165" s="3">
-        <v>10010029</v>
-      </c>
-      <c r="J165" s="3">
-        <v>10</v>
-      </c>
-      <c r="K165" s="2">
-        <v>0</v>
-      </c>
-      <c r="M165" s="13" t="s">
-        <v>53</v>
-      </c>
+      <c r="N165" s="3"/>
+      <c r="P165" s="3"/>
     </row>
     <row r="166" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C166" s="3">
-        <v>60000007</v>
+        <v>60000003</v>
       </c>
       <c r="D166" s="3">
-        <v>60000008</v>
+        <v>60000004</v>
       </c>
       <c r="E166" s="3">
         <v>1</v>
@@ -7529,7 +7527,7 @@
         <v>100</v>
       </c>
       <c r="G166" s="13">
-        <v>10012005</v>
+        <v>10012001</v>
       </c>
       <c r="H166" s="3">
         <v>1</v>
@@ -7544,15 +7542,16 @@
         <v>0</v>
       </c>
       <c r="M166" s="13" t="s">
-        <v>54</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="O166" s="2"/>
     </row>
     <row r="167" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C167" s="3">
-        <v>60000008</v>
+        <v>60000004</v>
       </c>
       <c r="D167" s="3">
-        <v>60000009</v>
+        <v>60000005</v>
       </c>
       <c r="E167" s="3">
         <v>1</v>
@@ -7561,7 +7560,7 @@
         <v>100</v>
       </c>
       <c r="G167" s="13">
-        <v>10012006</v>
+        <v>10012002</v>
       </c>
       <c r="H167" s="3">
         <v>1</v>
@@ -7576,15 +7575,15 @@
         <v>0</v>
       </c>
       <c r="M167" s="13" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
     </row>
     <row r="168" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C168" s="3">
-        <v>60000009</v>
+        <v>60000005</v>
       </c>
       <c r="D168" s="3">
-        <v>60000010</v>
+        <v>60000006</v>
       </c>
       <c r="E168" s="3">
         <v>1</v>
@@ -7593,7 +7592,7 @@
         <v>100</v>
       </c>
       <c r="G168" s="13">
-        <v>10012007</v>
+        <v>10012003</v>
       </c>
       <c r="H168" s="3">
         <v>1</v>
@@ -7608,15 +7607,15 @@
         <v>0</v>
       </c>
       <c r="M168" s="13" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="169" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C169" s="3">
-        <v>60000010</v>
+        <v>60000006</v>
       </c>
       <c r="D169" s="3">
-        <v>60000011</v>
+        <v>60000007</v>
       </c>
       <c r="E169" s="3">
         <v>1</v>
@@ -7625,7 +7624,7 @@
         <v>100</v>
       </c>
       <c r="G169" s="13">
-        <v>10012008</v>
+        <v>10012004</v>
       </c>
       <c r="H169" s="3">
         <v>1</v>
@@ -7640,15 +7639,15 @@
         <v>0</v>
       </c>
       <c r="M169" s="13" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
     </row>
     <row r="170" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C170" s="3">
-        <v>60000011</v>
+        <v>60000007</v>
       </c>
       <c r="D170" s="3">
-        <v>60000012</v>
+        <v>60000008</v>
       </c>
       <c r="E170" s="3">
         <v>1</v>
@@ -7657,7 +7656,7 @@
         <v>100</v>
       </c>
       <c r="G170" s="13">
-        <v>10012009</v>
+        <v>10012005</v>
       </c>
       <c r="H170" s="3">
         <v>1</v>
@@ -7672,15 +7671,15 @@
         <v>0</v>
       </c>
       <c r="M170" s="13" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="171" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C171" s="3">
-        <v>60000012</v>
+        <v>60000008</v>
       </c>
       <c r="D171" s="3">
-        <v>60000013</v>
+        <v>60000009</v>
       </c>
       <c r="E171" s="3">
         <v>1</v>
@@ -7689,7 +7688,7 @@
         <v>100</v>
       </c>
       <c r="G171" s="13">
-        <v>10012010</v>
+        <v>10012006</v>
       </c>
       <c r="H171" s="3">
         <v>1</v>
@@ -7704,15 +7703,15 @@
         <v>0</v>
       </c>
       <c r="M171" s="13" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="172" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C172" s="3">
-        <v>60000013</v>
+        <v>60000009</v>
       </c>
       <c r="D172" s="3">
-        <v>60000014</v>
+        <v>60000010</v>
       </c>
       <c r="E172" s="3">
         <v>1</v>
@@ -7721,7 +7720,7 @@
         <v>100</v>
       </c>
       <c r="G172" s="13">
-        <v>10012011</v>
+        <v>10012007</v>
       </c>
       <c r="H172" s="3">
         <v>1</v>
@@ -7736,15 +7735,15 @@
         <v>0</v>
       </c>
       <c r="M172" s="13" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
     </row>
     <row r="173" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C173" s="3">
-        <v>60000014</v>
+        <v>60000010</v>
       </c>
       <c r="D173" s="3">
-        <v>60000015</v>
+        <v>60000011</v>
       </c>
       <c r="E173" s="3">
         <v>1</v>
@@ -7753,7 +7752,7 @@
         <v>100</v>
       </c>
       <c r="G173" s="13">
-        <v>10012012</v>
+        <v>10012008</v>
       </c>
       <c r="H173" s="3">
         <v>1</v>
@@ -7768,15 +7767,15 @@
         <v>0</v>
       </c>
       <c r="M173" s="13" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
     </row>
     <row r="174" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C174" s="3">
-        <v>60000015</v>
+        <v>60000011</v>
       </c>
       <c r="D174" s="3">
-        <v>60000016</v>
+        <v>60000012</v>
       </c>
       <c r="E174" s="3">
         <v>1</v>
@@ -7785,7 +7784,7 @@
         <v>100</v>
       </c>
       <c r="G174" s="13">
-        <v>10012013</v>
+        <v>10012009</v>
       </c>
       <c r="H174" s="3">
         <v>1</v>
@@ -7800,15 +7799,15 @@
         <v>0</v>
       </c>
       <c r="M174" s="13" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
     </row>
     <row r="175" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C175" s="3">
-        <v>60000016</v>
+        <v>60000012</v>
       </c>
       <c r="D175" s="3">
-        <v>60000017</v>
+        <v>60000013</v>
       </c>
       <c r="E175" s="3">
         <v>1</v>
@@ -7817,7 +7816,7 @@
         <v>100</v>
       </c>
       <c r="G175" s="13">
-        <v>10012014</v>
+        <v>10012010</v>
       </c>
       <c r="H175" s="3">
         <v>1</v>
@@ -7832,15 +7831,15 @@
         <v>0</v>
       </c>
       <c r="M175" s="13" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
     </row>
     <row r="176" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C176" s="3">
-        <v>60000017</v>
+        <v>60000013</v>
       </c>
       <c r="D176" s="3">
-        <v>60000018</v>
+        <v>60000014</v>
       </c>
       <c r="E176" s="3">
         <v>1</v>
@@ -7849,7 +7848,7 @@
         <v>100</v>
       </c>
       <c r="G176" s="13">
-        <v>10012015</v>
+        <v>10012011</v>
       </c>
       <c r="H176" s="3">
         <v>1</v>
@@ -7864,15 +7863,15 @@
         <v>0</v>
       </c>
       <c r="M176" s="13" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="177" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C177" s="3">
-        <v>60000018</v>
+        <v>60000014</v>
       </c>
       <c r="D177" s="3">
-        <v>60000019</v>
+        <v>60000015</v>
       </c>
       <c r="E177" s="3">
         <v>1</v>
@@ -7881,7 +7880,7 @@
         <v>100</v>
       </c>
       <c r="G177" s="13">
-        <v>10012016</v>
+        <v>10012012</v>
       </c>
       <c r="H177" s="3">
         <v>1</v>
@@ -7896,15 +7895,15 @@
         <v>0</v>
       </c>
       <c r="M177" s="13" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
     </row>
     <row r="178" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C178" s="3">
-        <v>60000019</v>
+        <v>60000015</v>
       </c>
       <c r="D178" s="3">
-        <v>60000020</v>
+        <v>60000016</v>
       </c>
       <c r="E178" s="3">
         <v>1</v>
@@ -7913,7 +7912,7 @@
         <v>100</v>
       </c>
       <c r="G178" s="13">
-        <v>10012017</v>
+        <v>10012013</v>
       </c>
       <c r="H178" s="3">
         <v>1</v>
@@ -7928,15 +7927,15 @@
         <v>0</v>
       </c>
       <c r="M178" s="13" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="179" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C179" s="3">
-        <v>60000020</v>
+        <v>60000016</v>
       </c>
       <c r="D179" s="3">
-        <v>60000021</v>
+        <v>60000017</v>
       </c>
       <c r="E179" s="3">
         <v>1</v>
@@ -7945,7 +7944,7 @@
         <v>100</v>
       </c>
       <c r="G179" s="13">
-        <v>10012018</v>
+        <v>10012014</v>
       </c>
       <c r="H179" s="3">
         <v>1</v>
@@ -7960,15 +7959,15 @@
         <v>0</v>
       </c>
       <c r="M179" s="13" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
     </row>
     <row r="180" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C180" s="3">
-        <v>60000021</v>
+        <v>60000017</v>
       </c>
       <c r="D180" s="3">
-        <v>60000022</v>
+        <v>60000018</v>
       </c>
       <c r="E180" s="3">
         <v>1</v>
@@ -7977,7 +7976,7 @@
         <v>100</v>
       </c>
       <c r="G180" s="13">
-        <v>10012019</v>
+        <v>10012015</v>
       </c>
       <c r="H180" s="3">
         <v>1</v>
@@ -7992,15 +7991,15 @@
         <v>0</v>
       </c>
       <c r="M180" s="13" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="181" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C181" s="3">
-        <v>60000022</v>
+        <v>60000018</v>
       </c>
       <c r="D181" s="3">
-        <v>60000023</v>
+        <v>60000019</v>
       </c>
       <c r="E181" s="3">
         <v>1</v>
@@ -8009,7 +8008,7 @@
         <v>100</v>
       </c>
       <c r="G181" s="13">
-        <v>10012020</v>
+        <v>10012016</v>
       </c>
       <c r="H181" s="3">
         <v>1</v>
@@ -8018,21 +8017,21 @@
         <v>10010029</v>
       </c>
       <c r="J181" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K181" s="2">
         <v>0</v>
       </c>
       <c r="M181" s="13" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="182" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C182" s="3">
-        <v>60000023</v>
+        <v>60000019</v>
       </c>
       <c r="D182" s="3">
-        <v>60000024</v>
+        <v>60000020</v>
       </c>
       <c r="E182" s="3">
         <v>1</v>
@@ -8041,7 +8040,7 @@
         <v>100</v>
       </c>
       <c r="G182" s="13">
-        <v>10012021</v>
+        <v>10012017</v>
       </c>
       <c r="H182" s="3">
         <v>1</v>
@@ -8050,21 +8049,21 @@
         <v>10010029</v>
       </c>
       <c r="J182" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K182" s="2">
         <v>0</v>
       </c>
       <c r="M182" s="13" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="183" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C183" s="3">
-        <v>60000024</v>
+        <v>60000020</v>
       </c>
       <c r="D183" s="3">
-        <v>60000025</v>
+        <v>60000021</v>
       </c>
       <c r="E183" s="3">
         <v>1</v>
@@ -8073,7 +8072,7 @@
         <v>100</v>
       </c>
       <c r="G183" s="13">
-        <v>10012022</v>
+        <v>10012018</v>
       </c>
       <c r="H183" s="3">
         <v>1</v>
@@ -8082,21 +8081,21 @@
         <v>10010029</v>
       </c>
       <c r="J183" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K183" s="2">
         <v>0</v>
       </c>
       <c r="M183" s="13" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="184" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C184" s="3">
-        <v>60000025</v>
+        <v>60000021</v>
       </c>
       <c r="D184" s="3">
-        <v>60000026</v>
+        <v>60000022</v>
       </c>
       <c r="E184" s="3">
         <v>1</v>
@@ -8105,7 +8104,7 @@
         <v>100</v>
       </c>
       <c r="G184" s="13">
-        <v>10012023</v>
+        <v>10012019</v>
       </c>
       <c r="H184" s="3">
         <v>1</v>
@@ -8114,21 +8113,21 @@
         <v>10010029</v>
       </c>
       <c r="J184" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K184" s="2">
         <v>0</v>
       </c>
       <c r="M184" s="13" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="185" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C185" s="3">
-        <v>60000026</v>
+        <v>60000022</v>
       </c>
       <c r="D185" s="3">
-        <v>60000027</v>
+        <v>60000023</v>
       </c>
       <c r="E185" s="3">
         <v>1</v>
@@ -8137,7 +8136,7 @@
         <v>100</v>
       </c>
       <c r="G185" s="13">
-        <v>10012024</v>
+        <v>10012020</v>
       </c>
       <c r="H185" s="3">
         <v>1</v>
@@ -8152,15 +8151,15 @@
         <v>0</v>
       </c>
       <c r="M185" s="13" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
     </row>
     <row r="186" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C186" s="3">
-        <v>60000027</v>
+        <v>60000023</v>
       </c>
       <c r="D186" s="3">
-        <v>60000028</v>
+        <v>60000024</v>
       </c>
       <c r="E186" s="3">
         <v>1</v>
@@ -8169,7 +8168,7 @@
         <v>100</v>
       </c>
       <c r="G186" s="13">
-        <v>10012025</v>
+        <v>10012021</v>
       </c>
       <c r="H186" s="3">
         <v>1</v>
@@ -8184,15 +8183,15 @@
         <v>0</v>
       </c>
       <c r="M186" s="13" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="187" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C187" s="3">
-        <v>60000028</v>
+        <v>60000024</v>
       </c>
       <c r="D187" s="3">
-        <v>60000029</v>
+        <v>60000025</v>
       </c>
       <c r="E187" s="3">
         <v>1</v>
@@ -8201,7 +8200,7 @@
         <v>100</v>
       </c>
       <c r="G187" s="13">
-        <v>10012026</v>
+        <v>10012022</v>
       </c>
       <c r="H187" s="3">
         <v>1</v>
@@ -8216,15 +8215,15 @@
         <v>0</v>
       </c>
       <c r="M187" s="13" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
     </row>
     <row r="188" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C188" s="3">
-        <v>60000029</v>
+        <v>60000025</v>
       </c>
       <c r="D188" s="3">
-        <v>60000030</v>
+        <v>60000026</v>
       </c>
       <c r="E188" s="3">
         <v>1</v>
@@ -8233,7 +8232,7 @@
         <v>100</v>
       </c>
       <c r="G188" s="13">
-        <v>10012027</v>
+        <v>10012023</v>
       </c>
       <c r="H188" s="3">
         <v>1</v>
@@ -8248,15 +8247,15 @@
         <v>0</v>
       </c>
       <c r="M188" s="13" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="189" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C189" s="3">
-        <v>60000030</v>
+        <v>60000026</v>
       </c>
       <c r="D189" s="3">
-        <v>60000031</v>
+        <v>60000027</v>
       </c>
       <c r="E189" s="3">
         <v>1</v>
@@ -8265,13 +8264,13 @@
         <v>100</v>
       </c>
       <c r="G189" s="13">
-        <v>10013001</v>
+        <v>10012024</v>
       </c>
       <c r="H189" s="3">
         <v>1</v>
       </c>
       <c r="I189" s="3">
-        <v>10010030</v>
+        <v>10010029</v>
       </c>
       <c r="J189" s="3">
         <v>15</v>
@@ -8279,16 +8278,16 @@
       <c r="K189" s="2">
         <v>0</v>
       </c>
-      <c r="M189" s="17" t="s">
-        <v>77</v>
+      <c r="M189" s="13" t="s">
+        <v>73</v>
       </c>
     </row>
     <row r="190" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C190" s="3">
-        <v>60000031</v>
+        <v>60000027</v>
       </c>
       <c r="D190" s="3">
-        <v>60000032</v>
+        <v>60000028</v>
       </c>
       <c r="E190" s="3">
         <v>1</v>
@@ -8297,13 +8296,13 @@
         <v>100</v>
       </c>
       <c r="G190" s="13">
-        <v>10013002</v>
+        <v>10012025</v>
       </c>
       <c r="H190" s="3">
         <v>1</v>
       </c>
       <c r="I190" s="3">
-        <v>10010030</v>
+        <v>10010029</v>
       </c>
       <c r="J190" s="3">
         <v>15</v>
@@ -8311,16 +8310,16 @@
       <c r="K190" s="2">
         <v>0</v>
       </c>
-      <c r="M190" s="17" t="s">
-        <v>78</v>
+      <c r="M190" s="13" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="191" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C191" s="3">
-        <v>60000032</v>
+        <v>60000028</v>
       </c>
       <c r="D191" s="3">
-        <v>60000033</v>
+        <v>60000029</v>
       </c>
       <c r="E191" s="3">
         <v>1</v>
@@ -8329,13 +8328,13 @@
         <v>100</v>
       </c>
       <c r="G191" s="13">
-        <v>10013003</v>
+        <v>10012026</v>
       </c>
       <c r="H191" s="3">
         <v>1</v>
       </c>
       <c r="I191" s="3">
-        <v>10010030</v>
+        <v>10010029</v>
       </c>
       <c r="J191" s="3">
         <v>15</v>
@@ -8343,16 +8342,16 @@
       <c r="K191" s="2">
         <v>0</v>
       </c>
-      <c r="M191" s="17" t="s">
-        <v>79</v>
+      <c r="M191" s="13" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="192" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C192" s="3">
-        <v>60000033</v>
+        <v>60000029</v>
       </c>
       <c r="D192" s="3">
-        <v>60000034</v>
+        <v>60000030</v>
       </c>
       <c r="E192" s="3">
         <v>1</v>
@@ -8361,13 +8360,13 @@
         <v>100</v>
       </c>
       <c r="G192" s="13">
-        <v>10013004</v>
+        <v>10012027</v>
       </c>
       <c r="H192" s="3">
         <v>1</v>
       </c>
       <c r="I192" s="3">
-        <v>10010030</v>
+        <v>10010029</v>
       </c>
       <c r="J192" s="3">
         <v>15</v>
@@ -8375,16 +8374,16 @@
       <c r="K192" s="2">
         <v>0</v>
       </c>
-      <c r="M192" s="17" t="s">
-        <v>80</v>
+      <c r="M192" s="13" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="193" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C193" s="3">
-        <v>60000034</v>
+        <v>60000030</v>
       </c>
       <c r="D193" s="3">
-        <v>60000035</v>
+        <v>60000031</v>
       </c>
       <c r="E193" s="3">
         <v>1</v>
@@ -8393,7 +8392,7 @@
         <v>100</v>
       </c>
       <c r="G193" s="13">
-        <v>10013005</v>
+        <v>10013001</v>
       </c>
       <c r="H193" s="3">
         <v>1</v>
@@ -8408,15 +8407,15 @@
         <v>0</v>
       </c>
       <c r="M193" s="17" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
     </row>
     <row r="194" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C194" s="3">
-        <v>60000035</v>
+        <v>60000031</v>
       </c>
       <c r="D194" s="3">
-        <v>60000036</v>
+        <v>60000032</v>
       </c>
       <c r="E194" s="3">
         <v>1</v>
@@ -8425,7 +8424,7 @@
         <v>100</v>
       </c>
       <c r="G194" s="13">
-        <v>10013006</v>
+        <v>10013002</v>
       </c>
       <c r="H194" s="3">
         <v>1</v>
@@ -8440,15 +8439,15 @@
         <v>0</v>
       </c>
       <c r="M194" s="17" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
     </row>
     <row r="195" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C195" s="3">
-        <v>60000036</v>
+        <v>60000032</v>
       </c>
       <c r="D195" s="3">
-        <v>60000037</v>
+        <v>60000033</v>
       </c>
       <c r="E195" s="3">
         <v>1</v>
@@ -8457,7 +8456,7 @@
         <v>100</v>
       </c>
       <c r="G195" s="13">
-        <v>10013007</v>
+        <v>10013003</v>
       </c>
       <c r="H195" s="3">
         <v>1</v>
@@ -8472,15 +8471,15 @@
         <v>0</v>
       </c>
       <c r="M195" s="17" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="196" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C196" s="3">
-        <v>60000037</v>
+        <v>60000033</v>
       </c>
       <c r="D196" s="3">
-        <v>60000038</v>
+        <v>60000034</v>
       </c>
       <c r="E196" s="3">
         <v>1</v>
@@ -8489,7 +8488,7 @@
         <v>100</v>
       </c>
       <c r="G196" s="13">
-        <v>10013008</v>
+        <v>10013004</v>
       </c>
       <c r="H196" s="3">
         <v>1</v>
@@ -8504,15 +8503,15 @@
         <v>0</v>
       </c>
       <c r="M196" s="17" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="197" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C197" s="3">
-        <v>60000038</v>
+        <v>60000034</v>
       </c>
       <c r="D197" s="3">
-        <v>60000039</v>
+        <v>60000035</v>
       </c>
       <c r="E197" s="3">
         <v>1</v>
@@ -8521,7 +8520,7 @@
         <v>100</v>
       </c>
       <c r="G197" s="13">
-        <v>10013009</v>
+        <v>10013005</v>
       </c>
       <c r="H197" s="3">
         <v>1</v>
@@ -8536,15 +8535,15 @@
         <v>0</v>
       </c>
       <c r="M197" s="17" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
     </row>
     <row r="198" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C198" s="3">
-        <v>60000039</v>
+        <v>60000035</v>
       </c>
       <c r="D198" s="3">
-        <v>60000040</v>
+        <v>60000036</v>
       </c>
       <c r="E198" s="3">
         <v>1</v>
@@ -8553,7 +8552,7 @@
         <v>100</v>
       </c>
       <c r="G198" s="13">
-        <v>10013010</v>
+        <v>10013006</v>
       </c>
       <c r="H198" s="3">
         <v>1</v>
@@ -8568,15 +8567,15 @@
         <v>0</v>
       </c>
       <c r="M198" s="17" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
     </row>
     <row r="199" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C199" s="3">
-        <v>60000040</v>
+        <v>60000036</v>
       </c>
       <c r="D199" s="3">
-        <v>60000041</v>
+        <v>60000037</v>
       </c>
       <c r="E199" s="3">
         <v>1</v>
@@ -8585,7 +8584,7 @@
         <v>100</v>
       </c>
       <c r="G199" s="13">
-        <v>10013011</v>
+        <v>10013007</v>
       </c>
       <c r="H199" s="3">
         <v>1</v>
@@ -8600,15 +8599,15 @@
         <v>0</v>
       </c>
       <c r="M199" s="17" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
     </row>
     <row r="200" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C200" s="3">
-        <v>60000041</v>
+        <v>60000037</v>
       </c>
       <c r="D200" s="3">
-        <v>60000042</v>
+        <v>60000038</v>
       </c>
       <c r="E200" s="3">
         <v>1</v>
@@ -8617,7 +8616,7 @@
         <v>100</v>
       </c>
       <c r="G200" s="13">
-        <v>10013012</v>
+        <v>10013008</v>
       </c>
       <c r="H200" s="3">
         <v>1</v>
@@ -8632,15 +8631,15 @@
         <v>0</v>
       </c>
       <c r="M200" s="17" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="201" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C201" s="3">
-        <v>60000042</v>
+        <v>60000038</v>
       </c>
       <c r="D201" s="3">
-        <v>60000043</v>
+        <v>60000039</v>
       </c>
       <c r="E201" s="3">
         <v>1</v>
@@ -8649,7 +8648,7 @@
         <v>100</v>
       </c>
       <c r="G201" s="13">
-        <v>10013013</v>
+        <v>10013009</v>
       </c>
       <c r="H201" s="3">
         <v>1</v>
@@ -8664,15 +8663,15 @@
         <v>0</v>
       </c>
       <c r="M201" s="17" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
     </row>
     <row r="202" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C202" s="3">
-        <v>60000043</v>
+        <v>60000039</v>
       </c>
       <c r="D202" s="3">
-        <v>60000044</v>
+        <v>60000040</v>
       </c>
       <c r="E202" s="3">
         <v>1</v>
@@ -8681,7 +8680,7 @@
         <v>100</v>
       </c>
       <c r="G202" s="13">
-        <v>10013014</v>
+        <v>10013010</v>
       </c>
       <c r="H202" s="3">
         <v>1</v>
@@ -8696,15 +8695,15 @@
         <v>0</v>
       </c>
       <c r="M202" s="17" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
     </row>
     <row r="203" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C203" s="3">
-        <v>60000044</v>
+        <v>60000040</v>
       </c>
       <c r="D203" s="3">
-        <v>60000045</v>
+        <v>60000041</v>
       </c>
       <c r="E203" s="3">
         <v>1</v>
@@ -8713,7 +8712,7 @@
         <v>100</v>
       </c>
       <c r="G203" s="13">
-        <v>10013015</v>
+        <v>10013011</v>
       </c>
       <c r="H203" s="3">
         <v>1</v>
@@ -8728,15 +8727,15 @@
         <v>0</v>
       </c>
       <c r="M203" s="17" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="204" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C204" s="3">
-        <v>60000045</v>
+        <v>60000041</v>
       </c>
       <c r="D204" s="3">
-        <v>60000046</v>
+        <v>60000042</v>
       </c>
       <c r="E204" s="3">
         <v>1</v>
@@ -8745,7 +8744,7 @@
         <v>100</v>
       </c>
       <c r="G204" s="13">
-        <v>10013016</v>
+        <v>10013012</v>
       </c>
       <c r="H204" s="3">
         <v>1</v>
@@ -8760,15 +8759,15 @@
         <v>0</v>
       </c>
       <c r="M204" s="17" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
     </row>
     <row r="205" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C205" s="3">
-        <v>60000046</v>
+        <v>60000042</v>
       </c>
       <c r="D205" s="3">
-        <v>60000047</v>
+        <v>60000043</v>
       </c>
       <c r="E205" s="3">
         <v>1</v>
@@ -8777,7 +8776,7 @@
         <v>100</v>
       </c>
       <c r="G205" s="13">
-        <v>10013017</v>
+        <v>10013013</v>
       </c>
       <c r="H205" s="3">
         <v>1</v>
@@ -8792,15 +8791,15 @@
         <v>0</v>
       </c>
       <c r="M205" s="17" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="206" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C206" s="3">
-        <v>60000047</v>
+        <v>60000043</v>
       </c>
       <c r="D206" s="3">
-        <v>60000048</v>
+        <v>60000044</v>
       </c>
       <c r="E206" s="3">
         <v>1</v>
@@ -8809,7 +8808,7 @@
         <v>100</v>
       </c>
       <c r="G206" s="13">
-        <v>10013018</v>
+        <v>10013014</v>
       </c>
       <c r="H206" s="3">
         <v>1</v>
@@ -8824,15 +8823,15 @@
         <v>0</v>
       </c>
       <c r="M206" s="17" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
     <row r="207" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C207" s="3">
-        <v>60000048</v>
+        <v>60000044</v>
       </c>
       <c r="D207" s="3">
-        <v>60000049</v>
+        <v>60000045</v>
       </c>
       <c r="E207" s="3">
         <v>1</v>
@@ -8841,7 +8840,7 @@
         <v>100</v>
       </c>
       <c r="G207" s="13">
-        <v>10013019</v>
+        <v>10013015</v>
       </c>
       <c r="H207" s="3">
         <v>1</v>
@@ -8856,15 +8855,15 @@
         <v>0</v>
       </c>
       <c r="M207" s="17" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
     </row>
     <row r="208" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C208" s="3">
-        <v>60000049</v>
+        <v>60000045</v>
       </c>
       <c r="D208" s="3">
-        <v>60000050</v>
+        <v>60000046</v>
       </c>
       <c r="E208" s="3">
         <v>1</v>
@@ -8873,7 +8872,7 @@
         <v>100</v>
       </c>
       <c r="G208" s="13">
-        <v>10013020</v>
+        <v>10013016</v>
       </c>
       <c r="H208" s="3">
         <v>1</v>
@@ -8882,21 +8881,21 @@
         <v>10010030</v>
       </c>
       <c r="J208" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K208" s="2">
         <v>0</v>
       </c>
       <c r="M208" s="17" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="209" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C209" s="3">
-        <v>60000050</v>
+        <v>60000046</v>
       </c>
       <c r="D209" s="3">
-        <v>60000051</v>
+        <v>60000047</v>
       </c>
       <c r="E209" s="3">
         <v>1</v>
@@ -8905,7 +8904,7 @@
         <v>100</v>
       </c>
       <c r="G209" s="13">
-        <v>10013021</v>
+        <v>10013017</v>
       </c>
       <c r="H209" s="3">
         <v>1</v>
@@ -8914,21 +8913,21 @@
         <v>10010030</v>
       </c>
       <c r="J209" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K209" s="2">
         <v>0</v>
       </c>
       <c r="M209" s="17" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
     </row>
     <row r="210" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C210" s="3">
-        <v>60000051</v>
+        <v>60000047</v>
       </c>
       <c r="D210" s="3">
-        <v>60000052</v>
+        <v>60000048</v>
       </c>
       <c r="E210" s="3">
         <v>1</v>
@@ -8937,7 +8936,7 @@
         <v>100</v>
       </c>
       <c r="G210" s="13">
-        <v>10013022</v>
+        <v>10013018</v>
       </c>
       <c r="H210" s="3">
         <v>1</v>
@@ -8946,21 +8945,21 @@
         <v>10010030</v>
       </c>
       <c r="J210" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K210" s="2">
         <v>0</v>
       </c>
       <c r="M210" s="17" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
     </row>
     <row r="211" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C211" s="3">
-        <v>60000052</v>
+        <v>60000048</v>
       </c>
       <c r="D211" s="3">
-        <v>60000053</v>
+        <v>60000049</v>
       </c>
       <c r="E211" s="3">
         <v>1</v>
@@ -8969,7 +8968,7 @@
         <v>100</v>
       </c>
       <c r="G211" s="13">
-        <v>10013023</v>
+        <v>10013019</v>
       </c>
       <c r="H211" s="3">
         <v>1</v>
@@ -8978,21 +8977,21 @@
         <v>10010030</v>
       </c>
       <c r="J211" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K211" s="2">
         <v>0</v>
       </c>
       <c r="M211" s="17" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="212" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C212" s="3">
-        <v>60000053</v>
+        <v>60000049</v>
       </c>
       <c r="D212" s="3">
-        <v>60000054</v>
+        <v>60000050</v>
       </c>
       <c r="E212" s="3">
         <v>1</v>
@@ -9001,7 +9000,7 @@
         <v>100</v>
       </c>
       <c r="G212" s="13">
-        <v>10013024</v>
+        <v>10013020</v>
       </c>
       <c r="H212" s="3">
         <v>1</v>
@@ -9016,15 +9015,15 @@
         <v>0</v>
       </c>
       <c r="M212" s="17" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="213" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C213" s="3">
-        <v>60000054</v>
+        <v>60000050</v>
       </c>
       <c r="D213" s="3">
-        <v>60000055</v>
+        <v>60000051</v>
       </c>
       <c r="E213" s="3">
         <v>1</v>
@@ -9033,7 +9032,7 @@
         <v>100</v>
       </c>
       <c r="G213" s="13">
-        <v>10013025</v>
+        <v>10013021</v>
       </c>
       <c r="H213" s="3">
         <v>1</v>
@@ -9048,15 +9047,15 @@
         <v>0</v>
       </c>
       <c r="M213" s="17" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
     </row>
     <row r="214" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C214" s="3">
-        <v>60000055</v>
+        <v>60000051</v>
       </c>
       <c r="D214" s="3">
-        <v>60000056</v>
+        <v>60000052</v>
       </c>
       <c r="E214" s="3">
         <v>1</v>
@@ -9065,7 +9064,7 @@
         <v>100</v>
       </c>
       <c r="G214" s="13">
-        <v>10013026</v>
+        <v>10013022</v>
       </c>
       <c r="H214" s="3">
         <v>1</v>
@@ -9080,15 +9079,15 @@
         <v>0</v>
       </c>
       <c r="M214" s="17" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
     </row>
     <row r="215" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C215" s="3">
-        <v>60000056</v>
+        <v>60000052</v>
       </c>
       <c r="D215" s="3">
-        <v>60000057</v>
+        <v>60000053</v>
       </c>
       <c r="E215" s="3">
         <v>1</v>
@@ -9097,7 +9096,7 @@
         <v>100</v>
       </c>
       <c r="G215" s="13">
-        <v>10013027</v>
+        <v>10013023</v>
       </c>
       <c r="H215" s="3">
         <v>1</v>
@@ -9112,15 +9111,15 @@
         <v>0</v>
       </c>
       <c r="M215" s="17" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="216" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C216" s="3">
-        <v>60000057</v>
+        <v>60000053</v>
       </c>
       <c r="D216" s="3">
-        <v>60000058</v>
+        <v>60000054</v>
       </c>
       <c r="E216" s="3">
         <v>1</v>
@@ -9129,13 +9128,13 @@
         <v>100</v>
       </c>
       <c r="G216" s="13">
-        <v>10014001</v>
+        <v>10013024</v>
       </c>
       <c r="H216" s="3">
         <v>1</v>
       </c>
       <c r="I216" s="3">
-        <v>10010031</v>
+        <v>10010030</v>
       </c>
       <c r="J216" s="3">
         <v>20</v>
@@ -9143,16 +9142,16 @@
       <c r="K216" s="2">
         <v>0</v>
       </c>
-      <c r="M216" s="3" t="s">
-        <v>135</v>
+      <c r="M216" s="17" t="s">
+        <v>100</v>
       </c>
     </row>
     <row r="217" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C217" s="3">
-        <v>60000058</v>
+        <v>60000054</v>
       </c>
       <c r="D217" s="3">
-        <v>60000059</v>
+        <v>60000055</v>
       </c>
       <c r="E217" s="3">
         <v>1</v>
@@ -9161,13 +9160,13 @@
         <v>100</v>
       </c>
       <c r="G217" s="13">
-        <v>10014002</v>
+        <v>10013025</v>
       </c>
       <c r="H217" s="3">
         <v>1</v>
       </c>
       <c r="I217" s="3">
-        <v>10010031</v>
+        <v>10010030</v>
       </c>
       <c r="J217" s="3">
         <v>20</v>
@@ -9175,16 +9174,16 @@
       <c r="K217" s="2">
         <v>0</v>
       </c>
-      <c r="M217" s="3" t="s">
-        <v>136</v>
+      <c r="M217" s="17" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="218" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C218" s="3">
-        <v>60000059</v>
+        <v>60000055</v>
       </c>
       <c r="D218" s="3">
-        <v>60000060</v>
+        <v>60000056</v>
       </c>
       <c r="E218" s="3">
         <v>1</v>
@@ -9193,13 +9192,13 @@
         <v>100</v>
       </c>
       <c r="G218" s="13">
-        <v>10014003</v>
+        <v>10013026</v>
       </c>
       <c r="H218" s="3">
         <v>1</v>
       </c>
       <c r="I218" s="3">
-        <v>10010031</v>
+        <v>10010030</v>
       </c>
       <c r="J218" s="3">
         <v>20</v>
@@ -9207,16 +9206,16 @@
       <c r="K218" s="2">
         <v>0</v>
       </c>
-      <c r="M218" s="3" t="s">
-        <v>137</v>
+      <c r="M218" s="17" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="219" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C219" s="3">
-        <v>60000060</v>
+        <v>60000056</v>
       </c>
       <c r="D219" s="3">
-        <v>60000061</v>
+        <v>60000057</v>
       </c>
       <c r="E219" s="3">
         <v>1</v>
@@ -9225,13 +9224,13 @@
         <v>100</v>
       </c>
       <c r="G219" s="13">
-        <v>10014004</v>
+        <v>10013027</v>
       </c>
       <c r="H219" s="3">
         <v>1</v>
       </c>
       <c r="I219" s="3">
-        <v>10010031</v>
+        <v>10010030</v>
       </c>
       <c r="J219" s="3">
         <v>20</v>
@@ -9239,16 +9238,16 @@
       <c r="K219" s="2">
         <v>0</v>
       </c>
-      <c r="M219" s="3" t="s">
-        <v>138</v>
+      <c r="M219" s="17" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="220" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C220" s="3">
-        <v>60000061</v>
+        <v>60000057</v>
       </c>
       <c r="D220" s="3">
-        <v>60000062</v>
+        <v>60000058</v>
       </c>
       <c r="E220" s="3">
         <v>1</v>
@@ -9257,7 +9256,7 @@
         <v>100</v>
       </c>
       <c r="G220" s="13">
-        <v>10014005</v>
+        <v>10014001</v>
       </c>
       <c r="H220" s="3">
         <v>1</v>
@@ -9272,15 +9271,15 @@
         <v>0</v>
       </c>
       <c r="M220" s="3" t="s">
-        <v>139</v>
+        <v>134</v>
       </c>
     </row>
     <row r="221" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C221" s="3">
-        <v>60000062</v>
+        <v>60000058</v>
       </c>
       <c r="D221" s="3">
-        <v>60000063</v>
+        <v>60000059</v>
       </c>
       <c r="E221" s="3">
         <v>1</v>
@@ -9289,7 +9288,7 @@
         <v>100</v>
       </c>
       <c r="G221" s="13">
-        <v>10014006</v>
+        <v>10014002</v>
       </c>
       <c r="H221" s="3">
         <v>1</v>
@@ -9304,15 +9303,15 @@
         <v>0</v>
       </c>
       <c r="M221" s="3" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="222" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C222" s="3">
-        <v>60000063</v>
+        <v>60000059</v>
       </c>
       <c r="D222" s="3">
-        <v>60000064</v>
+        <v>60000060</v>
       </c>
       <c r="E222" s="3">
         <v>1</v>
@@ -9321,7 +9320,7 @@
         <v>100</v>
       </c>
       <c r="G222" s="13">
-        <v>10014007</v>
+        <v>10014003</v>
       </c>
       <c r="H222" s="3">
         <v>1</v>
@@ -9336,15 +9335,15 @@
         <v>0</v>
       </c>
       <c r="M222" s="3" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
     </row>
     <row r="223" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C223" s="3">
-        <v>60000064</v>
+        <v>60000060</v>
       </c>
       <c r="D223" s="3">
-        <v>60000065</v>
+        <v>60000061</v>
       </c>
       <c r="E223" s="3">
         <v>1</v>
@@ -9353,7 +9352,7 @@
         <v>100</v>
       </c>
       <c r="G223" s="13">
-        <v>10014008</v>
+        <v>10014004</v>
       </c>
       <c r="H223" s="3">
         <v>1</v>
@@ -9368,15 +9367,15 @@
         <v>0</v>
       </c>
       <c r="M223" s="3" t="s">
-        <v>142</v>
+        <v>137</v>
       </c>
     </row>
     <row r="224" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C224" s="3">
-        <v>60000065</v>
+        <v>60000061</v>
       </c>
       <c r="D224" s="3">
-        <v>60000066</v>
+        <v>60000062</v>
       </c>
       <c r="E224" s="3">
         <v>1</v>
@@ -9385,7 +9384,7 @@
         <v>100</v>
       </c>
       <c r="G224" s="13">
-        <v>10014009</v>
+        <v>10014005</v>
       </c>
       <c r="H224" s="3">
         <v>1</v>
@@ -9400,15 +9399,15 @@
         <v>0</v>
       </c>
       <c r="M224" s="3" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
     </row>
     <row r="225" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C225" s="3">
-        <v>60000066</v>
+        <v>60000062</v>
       </c>
       <c r="D225" s="3">
-        <v>60000067</v>
+        <v>60000063</v>
       </c>
       <c r="E225" s="3">
         <v>1</v>
@@ -9417,7 +9416,7 @@
         <v>100</v>
       </c>
       <c r="G225" s="13">
-        <v>10014010</v>
+        <v>10014006</v>
       </c>
       <c r="H225" s="3">
         <v>1</v>
@@ -9432,15 +9431,15 @@
         <v>0</v>
       </c>
       <c r="M225" s="3" t="s">
-        <v>144</v>
+        <v>139</v>
       </c>
     </row>
     <row r="226" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C226" s="3">
-        <v>60000067</v>
+        <v>60000063</v>
       </c>
       <c r="D226" s="3">
-        <v>60000068</v>
+        <v>60000064</v>
       </c>
       <c r="E226" s="3">
         <v>1</v>
@@ -9449,7 +9448,7 @@
         <v>100</v>
       </c>
       <c r="G226" s="13">
-        <v>10014011</v>
+        <v>10014007</v>
       </c>
       <c r="H226" s="3">
         <v>1</v>
@@ -9464,15 +9463,15 @@
         <v>0</v>
       </c>
       <c r="M226" s="3" t="s">
-        <v>145</v>
+        <v>140</v>
       </c>
     </row>
     <row r="227" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C227" s="3">
-        <v>60000068</v>
+        <v>60000064</v>
       </c>
       <c r="D227" s="3">
-        <v>60000069</v>
+        <v>60000065</v>
       </c>
       <c r="E227" s="3">
         <v>1</v>
@@ -9481,7 +9480,7 @@
         <v>100</v>
       </c>
       <c r="G227" s="13">
-        <v>10014012</v>
+        <v>10014008</v>
       </c>
       <c r="H227" s="3">
         <v>1</v>
@@ -9496,15 +9495,15 @@
         <v>0</v>
       </c>
       <c r="M227" s="3" t="s">
-        <v>146</v>
+        <v>141</v>
       </c>
     </row>
     <row r="228" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C228" s="3">
-        <v>60000069</v>
+        <v>60000065</v>
       </c>
       <c r="D228" s="3">
-        <v>60000070</v>
+        <v>60000066</v>
       </c>
       <c r="E228" s="3">
         <v>1</v>
@@ -9513,7 +9512,7 @@
         <v>100</v>
       </c>
       <c r="G228" s="13">
-        <v>10014013</v>
+        <v>10014009</v>
       </c>
       <c r="H228" s="3">
         <v>1</v>
@@ -9528,15 +9527,15 @@
         <v>0</v>
       </c>
       <c r="M228" s="3" t="s">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="229" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C229" s="3">
-        <v>60000070</v>
+        <v>60000066</v>
       </c>
       <c r="D229" s="3">
-        <v>60000071</v>
+        <v>60000067</v>
       </c>
       <c r="E229" s="3">
         <v>1</v>
@@ -9545,7 +9544,7 @@
         <v>100</v>
       </c>
       <c r="G229" s="13">
-        <v>10014014</v>
+        <v>10014010</v>
       </c>
       <c r="H229" s="3">
         <v>1</v>
@@ -9560,15 +9559,15 @@
         <v>0</v>
       </c>
       <c r="M229" s="3" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="230" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C230" s="3">
-        <v>60000071</v>
+        <v>60000067</v>
       </c>
       <c r="D230" s="3">
-        <v>60000072</v>
+        <v>60000068</v>
       </c>
       <c r="E230" s="3">
         <v>1</v>
@@ -9577,7 +9576,7 @@
         <v>100</v>
       </c>
       <c r="G230" s="13">
-        <v>10014015</v>
+        <v>10014011</v>
       </c>
       <c r="H230" s="3">
         <v>1</v>
@@ -9592,15 +9591,15 @@
         <v>0</v>
       </c>
       <c r="M230" s="3" t="s">
-        <v>149</v>
+        <v>144</v>
       </c>
     </row>
     <row r="231" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C231" s="3">
-        <v>60000072</v>
+        <v>60000068</v>
       </c>
       <c r="D231" s="3">
-        <v>60000073</v>
+        <v>60000069</v>
       </c>
       <c r="E231" s="3">
         <v>1</v>
@@ -9609,7 +9608,7 @@
         <v>100</v>
       </c>
       <c r="G231" s="13">
-        <v>10014016</v>
+        <v>10014012</v>
       </c>
       <c r="H231" s="3">
         <v>1</v>
@@ -9624,15 +9623,15 @@
         <v>0</v>
       </c>
       <c r="M231" s="3" t="s">
-        <v>150</v>
+        <v>145</v>
       </c>
     </row>
     <row r="232" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C232" s="3">
-        <v>60000073</v>
+        <v>60000069</v>
       </c>
       <c r="D232" s="3">
-        <v>60000074</v>
+        <v>60000070</v>
       </c>
       <c r="E232" s="3">
         <v>1</v>
@@ -9641,7 +9640,7 @@
         <v>100</v>
       </c>
       <c r="G232" s="13">
-        <v>10014017</v>
+        <v>10014013</v>
       </c>
       <c r="H232" s="3">
         <v>1</v>
@@ -9656,15 +9655,15 @@
         <v>0</v>
       </c>
       <c r="M232" s="3" t="s">
-        <v>151</v>
+        <v>146</v>
       </c>
     </row>
     <row r="233" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C233" s="3">
-        <v>60000074</v>
+        <v>60000070</v>
       </c>
       <c r="D233" s="3">
-        <v>60000075</v>
+        <v>60000071</v>
       </c>
       <c r="E233" s="3">
         <v>1</v>
@@ -9673,7 +9672,7 @@
         <v>100</v>
       </c>
       <c r="G233" s="13">
-        <v>10014018</v>
+        <v>10014014</v>
       </c>
       <c r="H233" s="3">
         <v>1</v>
@@ -9688,15 +9687,15 @@
         <v>0</v>
       </c>
       <c r="M233" s="3" t="s">
-        <v>152</v>
+        <v>147</v>
       </c>
     </row>
     <row r="234" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C234" s="3">
-        <v>60000075</v>
+        <v>60000071</v>
       </c>
       <c r="D234" s="3">
-        <v>60000076</v>
+        <v>60000072</v>
       </c>
       <c r="E234" s="3">
         <v>1</v>
@@ -9705,7 +9704,7 @@
         <v>100</v>
       </c>
       <c r="G234" s="13">
-        <v>10014019</v>
+        <v>10014015</v>
       </c>
       <c r="H234" s="3">
         <v>1</v>
@@ -9720,15 +9719,15 @@
         <v>0</v>
       </c>
       <c r="M234" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
     </row>
     <row r="235" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C235" s="3">
-        <v>60000076</v>
+        <v>60000072</v>
       </c>
       <c r="D235" s="3">
-        <v>60000077</v>
+        <v>60000073</v>
       </c>
       <c r="E235" s="3">
         <v>1</v>
@@ -9737,7 +9736,7 @@
         <v>100</v>
       </c>
       <c r="G235" s="13">
-        <v>10014020</v>
+        <v>10014016</v>
       </c>
       <c r="H235" s="3">
         <v>1</v>
@@ -9746,21 +9745,21 @@
         <v>10010031</v>
       </c>
       <c r="J235" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K235" s="2">
         <v>0</v>
       </c>
       <c r="M235" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="236" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C236" s="3">
-        <v>60000077</v>
+        <v>60000073</v>
       </c>
       <c r="D236" s="3">
-        <v>60000078</v>
+        <v>60000074</v>
       </c>
       <c r="E236" s="3">
         <v>1</v>
@@ -9769,7 +9768,7 @@
         <v>100</v>
       </c>
       <c r="G236" s="13">
-        <v>10014021</v>
+        <v>10014017</v>
       </c>
       <c r="H236" s="3">
         <v>1</v>
@@ -9778,21 +9777,21 @@
         <v>10010031</v>
       </c>
       <c r="J236" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K236" s="2">
         <v>0</v>
       </c>
       <c r="M236" s="3" t="s">
-        <v>155</v>
+        <v>150</v>
       </c>
     </row>
     <row r="237" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C237" s="3">
-        <v>60000078</v>
+        <v>60000074</v>
       </c>
       <c r="D237" s="3">
-        <v>60000079</v>
+        <v>60000075</v>
       </c>
       <c r="E237" s="3">
         <v>1</v>
@@ -9801,7 +9800,7 @@
         <v>100</v>
       </c>
       <c r="G237" s="13">
-        <v>10014022</v>
+        <v>10014018</v>
       </c>
       <c r="H237" s="3">
         <v>1</v>
@@ -9810,21 +9809,21 @@
         <v>10010031</v>
       </c>
       <c r="J237" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K237" s="2">
         <v>0</v>
       </c>
       <c r="M237" s="3" t="s">
-        <v>156</v>
+        <v>151</v>
       </c>
     </row>
     <row r="238" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C238" s="3">
-        <v>60000079</v>
+        <v>60000075</v>
       </c>
       <c r="D238" s="3">
-        <v>60000080</v>
+        <v>60000076</v>
       </c>
       <c r="E238" s="3">
         <v>1</v>
@@ -9833,7 +9832,7 @@
         <v>100</v>
       </c>
       <c r="G238" s="13">
-        <v>10014023</v>
+        <v>10014019</v>
       </c>
       <c r="H238" s="3">
         <v>1</v>
@@ -9842,21 +9841,21 @@
         <v>10010031</v>
       </c>
       <c r="J238" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K238" s="2">
         <v>0</v>
       </c>
       <c r="M238" s="3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
     </row>
     <row r="239" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C239" s="3">
-        <v>60000080</v>
+        <v>60000076</v>
       </c>
       <c r="D239" s="3">
-        <v>60000081</v>
+        <v>60000077</v>
       </c>
       <c r="E239" s="3">
         <v>1</v>
@@ -9865,7 +9864,7 @@
         <v>100</v>
       </c>
       <c r="G239" s="13">
-        <v>10014024</v>
+        <v>10014020</v>
       </c>
       <c r="H239" s="3">
         <v>1</v>
@@ -9880,15 +9879,15 @@
         <v>0</v>
       </c>
       <c r="M239" s="3" t="s">
-        <v>158</v>
+        <v>153</v>
       </c>
     </row>
     <row r="240" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C240" s="3">
-        <v>60000081</v>
+        <v>60000077</v>
       </c>
       <c r="D240" s="3">
-        <v>60000082</v>
+        <v>60000078</v>
       </c>
       <c r="E240" s="3">
         <v>1</v>
@@ -9897,7 +9896,7 @@
         <v>100</v>
       </c>
       <c r="G240" s="13">
-        <v>10014025</v>
+        <v>10014021</v>
       </c>
       <c r="H240" s="3">
         <v>1</v>
@@ -9912,15 +9911,15 @@
         <v>0</v>
       </c>
       <c r="M240" s="3" t="s">
-        <v>159</v>
+        <v>154</v>
       </c>
     </row>
     <row r="241" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C241" s="3">
-        <v>60000082</v>
+        <v>60000078</v>
       </c>
       <c r="D241" s="3">
-        <v>60000083</v>
+        <v>60000079</v>
       </c>
       <c r="E241" s="3">
         <v>1</v>
@@ -9929,7 +9928,7 @@
         <v>100</v>
       </c>
       <c r="G241" s="13">
-        <v>10014026</v>
+        <v>10014022</v>
       </c>
       <c r="H241" s="3">
         <v>1</v>
@@ -9944,15 +9943,15 @@
         <v>0</v>
       </c>
       <c r="M241" s="3" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
     </row>
     <row r="242" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C242" s="3">
-        <v>60000083</v>
+        <v>60000079</v>
       </c>
       <c r="D242" s="3">
-        <v>0</v>
+        <v>60000080</v>
       </c>
       <c r="E242" s="3">
         <v>1</v>
@@ -9961,7 +9960,7 @@
         <v>100</v>
       </c>
       <c r="G242" s="13">
-        <v>10014027</v>
+        <v>10014023</v>
       </c>
       <c r="H242" s="3">
         <v>1</v>
@@ -9976,15 +9975,15 @@
         <v>0</v>
       </c>
       <c r="M242" s="3" t="s">
-        <v>161</v>
+        <v>156</v>
       </c>
     </row>
     <row r="243" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C243" s="3">
-        <v>70000001</v>
+        <v>60000080</v>
       </c>
       <c r="D243" s="3">
-        <v>70000002</v>
+        <v>60000081</v>
       </c>
       <c r="E243" s="3">
         <v>1</v>
@@ -9992,31 +9991,31 @@
       <c r="F243" s="3">
         <v>100</v>
       </c>
-      <c r="G243" s="9">
-        <v>10010093</v>
+      <c r="G243" s="13">
+        <v>10014024</v>
       </c>
       <c r="H243" s="3">
         <v>1</v>
       </c>
-      <c r="I243" s="8">
-        <v>10000159</v>
-      </c>
-      <c r="J243" s="8">
+      <c r="I243" s="3">
+        <v>10010031</v>
+      </c>
+      <c r="J243" s="3">
         <v>30</v>
       </c>
       <c r="K243" s="2">
         <v>0</v>
       </c>
-      <c r="M243" s="12" t="s">
-        <v>49</v>
+      <c r="M243" s="3" t="s">
+        <v>157</v>
       </c>
     </row>
     <row r="244" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C244" s="3">
-        <v>70000002</v>
+        <v>60000081</v>
       </c>
       <c r="D244" s="3">
-        <v>70000003</v>
+        <v>60000082</v>
       </c>
       <c r="E244" s="3">
         <v>1</v>
@@ -10024,31 +10023,31 @@
       <c r="F244" s="3">
         <v>100</v>
       </c>
-      <c r="G244" s="9">
-        <v>10000162</v>
+      <c r="G244" s="13">
+        <v>10014025</v>
       </c>
       <c r="H244" s="3">
         <v>1</v>
       </c>
-      <c r="I244" s="8">
-        <v>10000159</v>
-      </c>
-      <c r="J244" s="8">
-        <v>20</v>
+      <c r="I244" s="3">
+        <v>10010031</v>
+      </c>
+      <c r="J244" s="3">
+        <v>30</v>
       </c>
       <c r="K244" s="2">
         <v>0</v>
       </c>
-      <c r="M244" s="11" t="s">
-        <v>104</v>
+      <c r="M244" s="3" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="245" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C245" s="3">
-        <v>70000003</v>
+        <v>60000082</v>
       </c>
       <c r="D245" s="3">
-        <v>70000004</v>
+        <v>60000083</v>
       </c>
       <c r="E245" s="3">
         <v>1</v>
@@ -10056,31 +10055,31 @@
       <c r="F245" s="3">
         <v>100</v>
       </c>
-      <c r="G245" s="9">
-        <v>10010045</v>
+      <c r="G245" s="13">
+        <v>10014026</v>
       </c>
       <c r="H245" s="3">
         <v>1</v>
       </c>
-      <c r="I245" s="8">
-        <v>10000159</v>
-      </c>
-      <c r="J245" s="8">
+      <c r="I245" s="3">
+        <v>10010031</v>
+      </c>
+      <c r="J245" s="3">
         <v>30</v>
       </c>
       <c r="K245" s="2">
         <v>0</v>
       </c>
-      <c r="M245" s="11" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="246" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M245" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="246" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C246" s="3">
-        <v>70000004</v>
+        <v>60000083</v>
       </c>
       <c r="D246" s="3">
-        <v>70000005</v>
+        <v>0</v>
       </c>
       <c r="E246" s="3">
         <v>1</v>
@@ -10088,31 +10087,31 @@
       <c r="F246" s="3">
         <v>100</v>
       </c>
-      <c r="G246" s="9">
-        <v>10000158</v>
+      <c r="G246" s="13">
+        <v>10014027</v>
       </c>
       <c r="H246" s="3">
         <v>1</v>
       </c>
-      <c r="I246" s="8">
-        <v>10000159</v>
-      </c>
-      <c r="J246" s="8">
-        <v>20</v>
+      <c r="I246" s="3">
+        <v>10010031</v>
+      </c>
+      <c r="J246" s="3">
+        <v>30</v>
       </c>
       <c r="K246" s="2">
         <v>0</v>
       </c>
-      <c r="M246" s="9" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="247" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M246" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="247" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C247" s="3">
-        <v>70000005</v>
+        <v>70000001</v>
       </c>
       <c r="D247" s="3">
-        <v>70000006</v>
+        <v>70000002</v>
       </c>
       <c r="E247" s="3">
         <v>1</v>
@@ -10121,7 +10120,7 @@
         <v>100</v>
       </c>
       <c r="G247" s="9">
-        <v>10010083</v>
+        <v>10010093</v>
       </c>
       <c r="H247" s="3">
         <v>1</v>
@@ -10130,21 +10129,21 @@
         <v>10000159</v>
       </c>
       <c r="J247" s="8">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="K247" s="2">
         <v>0</v>
       </c>
-      <c r="M247" s="16" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="248" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M247" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="248" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C248" s="3">
-        <v>70000006</v>
+        <v>70000002</v>
       </c>
       <c r="D248" s="3">
-        <v>70000007</v>
+        <v>70000003</v>
       </c>
       <c r="E248" s="3">
         <v>1</v>
@@ -10153,7 +10152,7 @@
         <v>100</v>
       </c>
       <c r="G248" s="9">
-        <v>10000143</v>
+        <v>10000162</v>
       </c>
       <c r="H248" s="3">
         <v>1</v>
@@ -10162,21 +10161,21 @@
         <v>10000159</v>
       </c>
       <c r="J248" s="8">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K248" s="2">
         <v>0</v>
       </c>
-      <c r="M248" s="16" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="249" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M248" s="11" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="249" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C249" s="3">
-        <v>70000007</v>
+        <v>70000003</v>
       </c>
       <c r="D249" s="3">
-        <v>70000008</v>
+        <v>70000004</v>
       </c>
       <c r="E249" s="3">
         <v>1</v>
@@ -10185,7 +10184,7 @@
         <v>100</v>
       </c>
       <c r="G249" s="9">
-        <v>10000152</v>
+        <v>10010045</v>
       </c>
       <c r="H249" s="3">
         <v>1</v>
@@ -10194,21 +10193,21 @@
         <v>10000159</v>
       </c>
       <c r="J249" s="8">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="K249" s="2">
         <v>0</v>
       </c>
       <c r="M249" s="11" t="s">
-        <v>38</v>
+        <v>105</v>
       </c>
     </row>
     <row r="250" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C250" s="3">
-        <v>70000008</v>
+        <v>70000004</v>
       </c>
       <c r="D250" s="3">
-        <v>70000009</v>
+        <v>70000005</v>
       </c>
       <c r="E250" s="3">
         <v>1</v>
@@ -10217,7 +10216,7 @@
         <v>100</v>
       </c>
       <c r="G250" s="9">
-        <v>10000157</v>
+        <v>10000158</v>
       </c>
       <c r="H250" s="3">
         <v>1</v>
@@ -10226,21 +10225,21 @@
         <v>10000159</v>
       </c>
       <c r="J250" s="8">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K250" s="2">
         <v>0</v>
       </c>
-      <c r="M250" s="11" t="s">
-        <v>39</v>
+      <c r="M250" s="9" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="251" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C251" s="3">
-        <v>70000009</v>
+        <v>70000005</v>
       </c>
       <c r="D251" s="3">
-        <v>70000010</v>
+        <v>70000006</v>
       </c>
       <c r="E251" s="3">
         <v>1</v>
@@ -10249,7 +10248,7 @@
         <v>100</v>
       </c>
       <c r="G251" s="9">
-        <v>10010029</v>
+        <v>10010083</v>
       </c>
       <c r="H251" s="3">
         <v>1</v>
@@ -10258,21 +10257,21 @@
         <v>10000159</v>
       </c>
       <c r="J251" s="8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K251" s="2">
         <v>0</v>
       </c>
-      <c r="M251" s="11" t="s">
-        <v>108</v>
+      <c r="M251" s="16" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="252" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C252" s="3">
-        <v>70000010</v>
+        <v>70000006</v>
       </c>
       <c r="D252" s="3">
-        <v>70000011</v>
+        <v>70000007</v>
       </c>
       <c r="E252" s="3">
         <v>1</v>
@@ -10281,7 +10280,7 @@
         <v>100</v>
       </c>
       <c r="G252" s="9">
-        <v>10010086</v>
+        <v>10000143</v>
       </c>
       <c r="H252" s="3">
         <v>1</v>
@@ -10290,21 +10289,21 @@
         <v>10000159</v>
       </c>
       <c r="J252" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K252" s="2">
         <v>0</v>
       </c>
-      <c r="M252" s="12" t="s">
-        <v>27</v>
+      <c r="M252" s="16" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="253" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C253" s="3">
-        <v>70000011</v>
+        <v>70000007</v>
       </c>
       <c r="D253" s="3">
-        <v>70000012</v>
+        <v>70000008</v>
       </c>
       <c r="E253" s="3">
         <v>1</v>
@@ -10312,8 +10311,8 @@
       <c r="F253" s="3">
         <v>100</v>
       </c>
-      <c r="G253" s="18">
-        <v>10010101</v>
+      <c r="G253" s="9">
+        <v>10000152</v>
       </c>
       <c r="H253" s="3">
         <v>1</v>
@@ -10322,21 +10321,21 @@
         <v>10000159</v>
       </c>
       <c r="J253" s="8">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K253" s="2">
         <v>0</v>
       </c>
-      <c r="M253" s="8" t="s">
-        <v>109</v>
+      <c r="M253" s="11" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="254" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C254" s="3">
-        <v>70000012</v>
+        <v>70000008</v>
       </c>
       <c r="D254" s="3">
-        <v>70000013</v>
+        <v>70000009</v>
       </c>
       <c r="E254" s="3">
         <v>1</v>
@@ -10344,8 +10343,8 @@
       <c r="F254" s="3">
         <v>100</v>
       </c>
-      <c r="G254" s="18">
-        <v>10010102</v>
+      <c r="G254" s="9">
+        <v>10000157</v>
       </c>
       <c r="H254" s="3">
         <v>1</v>
@@ -10359,16 +10358,16 @@
       <c r="K254" s="2">
         <v>0</v>
       </c>
-      <c r="M254" s="3" t="s">
-        <v>110</v>
+      <c r="M254" s="11" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="255" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C255" s="3">
-        <v>70000013</v>
+        <v>70000009</v>
       </c>
       <c r="D255" s="3">
-        <v>0</v>
+        <v>70000010</v>
       </c>
       <c r="E255" s="3">
         <v>1</v>
@@ -10376,8 +10375,8 @@
       <c r="F255" s="3">
         <v>100</v>
       </c>
-      <c r="G255" s="18">
-        <v>10010103</v>
+      <c r="G255" s="9">
+        <v>10010029</v>
       </c>
       <c r="H255" s="3">
         <v>1</v>
@@ -10386,21 +10385,21 @@
         <v>10000159</v>
       </c>
       <c r="J255" s="8">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="K255" s="2">
         <v>0</v>
       </c>
-      <c r="M255" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="256" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M255" s="11" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="256" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C256" s="3">
-        <v>80000001</v>
+        <v>70000010</v>
       </c>
       <c r="D256" s="3">
-        <v>80000002</v>
+        <v>70000011</v>
       </c>
       <c r="E256" s="3">
         <v>1</v>
@@ -10409,30 +10408,30 @@
         <v>100</v>
       </c>
       <c r="G256" s="9">
-        <v>10010083</v>
+        <v>10010086</v>
       </c>
       <c r="H256" s="3">
         <v>1</v>
       </c>
       <c r="I256" s="8">
-        <v>10000163</v>
+        <v>10000159</v>
       </c>
       <c r="J256" s="8">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K256" s="2">
         <v>0</v>
       </c>
-      <c r="M256" s="3" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="257" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M256" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="257" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C257" s="3">
-        <v>80000002</v>
+        <v>70000011</v>
       </c>
       <c r="D257" s="3">
-        <v>80000003</v>
+        <v>70000012</v>
       </c>
       <c r="E257" s="3">
         <v>1</v>
@@ -10440,31 +10439,31 @@
       <c r="F257" s="3">
         <v>100</v>
       </c>
-      <c r="G257" s="9">
-        <v>10010086</v>
+      <c r="G257" s="18">
+        <v>10010101</v>
       </c>
       <c r="H257" s="3">
         <v>1</v>
       </c>
       <c r="I257" s="8">
-        <v>10000163</v>
+        <v>10000159</v>
       </c>
       <c r="J257" s="8">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="K257" s="2">
         <v>0</v>
       </c>
-      <c r="M257" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="258" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M257" s="8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="258" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C258" s="3">
-        <v>80000003</v>
+        <v>70000012</v>
       </c>
       <c r="D258" s="3">
-        <v>80000004</v>
+        <v>70000013</v>
       </c>
       <c r="E258" s="3">
         <v>1</v>
@@ -10472,31 +10471,31 @@
       <c r="F258" s="3">
         <v>100</v>
       </c>
-      <c r="G258" s="9">
-        <v>10010096</v>
+      <c r="G258" s="18">
+        <v>10010102</v>
       </c>
       <c r="H258" s="3">
         <v>1</v>
       </c>
       <c r="I258" s="8">
-        <v>10000163</v>
+        <v>10000159</v>
       </c>
       <c r="J258" s="8">
-        <v>35</v>
+        <v>10</v>
       </c>
       <c r="K258" s="2">
         <v>0</v>
       </c>
       <c r="M258" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="259" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C259" s="3">
-        <v>80000004</v>
+        <v>70000013</v>
       </c>
       <c r="D259" s="3">
-        <v>80000005</v>
+        <v>0</v>
       </c>
       <c r="E259" s="3">
         <v>1</v>
@@ -10504,14 +10503,14 @@
       <c r="F259" s="3">
         <v>100</v>
       </c>
-      <c r="G259" s="9">
-        <v>10000139</v>
+      <c r="G259" s="18">
+        <v>10010103</v>
       </c>
       <c r="H259" s="3">
         <v>1</v>
       </c>
       <c r="I259" s="8">
-        <v>10000163</v>
+        <v>10000159</v>
       </c>
       <c r="J259" s="8">
         <v>20</v>
@@ -10520,15 +10519,15 @@
         <v>0</v>
       </c>
       <c r="M259" s="3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="260" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="260" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C260" s="3">
-        <v>80000005</v>
+        <v>80000001</v>
       </c>
       <c r="D260" s="3">
-        <v>80000006</v>
+        <v>80000002</v>
       </c>
       <c r="E260" s="3">
         <v>1</v>
@@ -10537,7 +10536,7 @@
         <v>100</v>
       </c>
       <c r="G260" s="9">
-        <v>10000143</v>
+        <v>10010083</v>
       </c>
       <c r="H260" s="3">
         <v>1</v>
@@ -10546,21 +10545,21 @@
         <v>10000163</v>
       </c>
       <c r="J260" s="8">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K260" s="2">
         <v>0</v>
       </c>
       <c r="M260" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="261" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="261" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C261" s="3">
-        <v>80000006</v>
+        <v>80000002</v>
       </c>
       <c r="D261" s="3">
-        <v>80000007</v>
+        <v>80000003</v>
       </c>
       <c r="E261" s="3">
         <v>1</v>
@@ -10569,7 +10568,7 @@
         <v>100</v>
       </c>
       <c r="G261" s="9">
-        <v>10000152</v>
+        <v>10010086</v>
       </c>
       <c r="H261" s="3">
         <v>1</v>
@@ -10578,21 +10577,21 @@
         <v>10000163</v>
       </c>
       <c r="J261" s="8">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="K261" s="2">
         <v>0</v>
       </c>
       <c r="M261" s="3" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="262" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="262" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C262" s="3">
-        <v>80000007</v>
+        <v>80000003</v>
       </c>
       <c r="D262" s="3">
-        <v>80000008</v>
+        <v>80000004</v>
       </c>
       <c r="E262" s="3">
         <v>1</v>
@@ -10601,7 +10600,7 @@
         <v>100</v>
       </c>
       <c r="G262" s="9">
-        <v>10000155</v>
+        <v>10010096</v>
       </c>
       <c r="H262" s="3">
         <v>1</v>
@@ -10610,21 +10609,21 @@
         <v>10000163</v>
       </c>
       <c r="J262" s="8">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="K262" s="2">
         <v>0</v>
       </c>
       <c r="M262" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="263" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C263" s="3">
-        <v>80000008</v>
+        <v>80000004</v>
       </c>
       <c r="D263" s="3">
-        <v>80000009</v>
+        <v>80000005</v>
       </c>
       <c r="E263" s="3">
         <v>1</v>
@@ -10633,7 +10632,7 @@
         <v>100</v>
       </c>
       <c r="G263" s="9">
-        <v>10000158</v>
+        <v>10000139</v>
       </c>
       <c r="H263" s="3">
         <v>1</v>
@@ -10648,15 +10647,15 @@
         <v>0</v>
       </c>
       <c r="M263" s="3" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="264" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C264" s="3">
-        <v>80000009</v>
+        <v>80000005</v>
       </c>
       <c r="D264" s="3">
-        <v>0</v>
+        <v>80000006</v>
       </c>
       <c r="E264" s="3">
         <v>1</v>
@@ -10665,7 +10664,7 @@
         <v>100</v>
       </c>
       <c r="G264" s="9">
-        <v>10010093</v>
+        <v>10000143</v>
       </c>
       <c r="H264" s="3">
         <v>1</v>
@@ -10674,153 +10673,149 @@
         <v>10000163</v>
       </c>
       <c r="J264" s="8">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="K264" s="2">
         <v>0</v>
       </c>
       <c r="M264" s="3" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="265" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C265" s="3">
-        <v>90000001</v>
+        <v>80000006</v>
       </c>
       <c r="D265" s="3">
-        <v>90000002</v>
-      </c>
-      <c r="E265" s="2">
+        <v>80000007</v>
+      </c>
+      <c r="E265" s="3">
         <v>1</v>
       </c>
       <c r="F265" s="3">
         <v>100</v>
       </c>
-      <c r="G265" s="3">
-        <v>10010093</v>
+      <c r="G265" s="9">
+        <v>10000152</v>
       </c>
       <c r="H265" s="3">
         <v>1</v>
       </c>
       <c r="I265" s="8">
-        <v>10000184</v>
+        <v>10000163</v>
       </c>
       <c r="J265" s="8">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="K265" s="2">
         <v>0</v>
       </c>
-      <c r="L265" s="2"/>
-      <c r="M265" s="12" t="s">
-        <v>49</v>
+      <c r="M265" s="3" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="266" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C266" s="3">
-        <v>90000002</v>
+        <v>80000007</v>
       </c>
       <c r="D266" s="3">
-        <v>90000003</v>
-      </c>
-      <c r="E266" s="2">
+        <v>80000008</v>
+      </c>
+      <c r="E266" s="3">
         <v>1</v>
       </c>
       <c r="F266" s="3">
         <v>100</v>
       </c>
-      <c r="G266" s="3">
-        <v>10010083</v>
+      <c r="G266" s="9">
+        <v>10000155</v>
       </c>
       <c r="H266" s="3">
         <v>1</v>
       </c>
       <c r="I266" s="8">
-        <v>10000184</v>
+        <v>10000163</v>
       </c>
       <c r="J266" s="8">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K266" s="2">
         <v>0</v>
       </c>
-      <c r="L266" s="2"/>
-      <c r="M266" s="16" t="s">
-        <v>107</v>
+      <c r="M266" s="3" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="267" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C267" s="3">
-        <v>90000003</v>
+        <v>80000008</v>
       </c>
       <c r="D267" s="3">
-        <v>90000004</v>
-      </c>
-      <c r="E267" s="2">
+        <v>80000009</v>
+      </c>
+      <c r="E267" s="3">
         <v>1</v>
       </c>
       <c r="F267" s="3">
         <v>100</v>
       </c>
-      <c r="G267" s="3">
-        <v>10010086</v>
+      <c r="G267" s="9">
+        <v>10000158</v>
       </c>
       <c r="H267" s="3">
         <v>1</v>
       </c>
       <c r="I267" s="8">
-        <v>10000184</v>
+        <v>10000163</v>
       </c>
       <c r="J267" s="8">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="K267" s="2">
         <v>0</v>
       </c>
-      <c r="L267" s="2"/>
-      <c r="M267" s="12" t="s">
-        <v>27</v>
+      <c r="M267" s="3" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="268" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C268" s="3">
-        <v>90000004</v>
+        <v>80000009</v>
       </c>
       <c r="D268" s="3">
-        <v>90000005</v>
-      </c>
-      <c r="E268" s="2">
+        <v>0</v>
+      </c>
+      <c r="E268" s="3">
         <v>1</v>
       </c>
       <c r="F268" s="3">
         <v>100</v>
       </c>
-      <c r="G268" s="3">
-        <v>10000143</v>
+      <c r="G268" s="9">
+        <v>10010093</v>
       </c>
       <c r="H268" s="3">
         <v>1</v>
       </c>
       <c r="I268" s="8">
-        <v>10000184</v>
+        <v>10000163</v>
       </c>
       <c r="J268" s="8">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="K268" s="2">
         <v>0</v>
       </c>
-      <c r="L268" s="2"/>
-      <c r="M268" s="11" t="s">
-        <v>47</v>
+      <c r="M268" s="3" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="269" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C269" s="3">
-        <v>90000005</v>
+        <v>90000001</v>
       </c>
       <c r="D269" s="3">
-        <v>90000006</v>
+        <v>90000002</v>
       </c>
       <c r="E269" s="2">
         <v>1</v>
@@ -10829,7 +10824,7 @@
         <v>100</v>
       </c>
       <c r="G269" s="3">
-        <v>10000152</v>
+        <v>10010093</v>
       </c>
       <c r="H269" s="3">
         <v>1</v>
@@ -10838,22 +10833,22 @@
         <v>10000184</v>
       </c>
       <c r="J269" s="8">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="K269" s="2">
         <v>0</v>
       </c>
       <c r="L269" s="2"/>
-      <c r="M269" s="11" t="s">
-        <v>38</v>
+      <c r="M269" s="12" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="270" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C270" s="3">
-        <v>90000006</v>
+        <v>90000002</v>
       </c>
       <c r="D270" s="3">
-        <v>90000007</v>
+        <v>90000003</v>
       </c>
       <c r="E270" s="2">
         <v>1</v>
@@ -10862,7 +10857,7 @@
         <v>100</v>
       </c>
       <c r="G270" s="3">
-        <v>10000165</v>
+        <v>10010083</v>
       </c>
       <c r="H270" s="3">
         <v>1</v>
@@ -10871,22 +10866,22 @@
         <v>10000184</v>
       </c>
       <c r="J270" s="8">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="K270" s="2">
         <v>0</v>
       </c>
       <c r="L270" s="2"/>
-      <c r="M270" s="11" t="s">
-        <v>45</v>
+      <c r="M270" s="16" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="271" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C271" s="3">
-        <v>90000007</v>
+        <v>90000003</v>
       </c>
       <c r="D271" s="3">
-        <v>0</v>
+        <v>90000004</v>
       </c>
       <c r="E271" s="2">
         <v>1</v>
@@ -10895,7 +10890,7 @@
         <v>100</v>
       </c>
       <c r="G271" s="3">
-        <v>10010045</v>
+        <v>10010086</v>
       </c>
       <c r="H271" s="3">
         <v>1</v>
@@ -10904,22 +10899,22 @@
         <v>10000184</v>
       </c>
       <c r="J271" s="8">
-        <v>45</v>
+        <v>25</v>
       </c>
       <c r="K271" s="2">
         <v>0</v>
       </c>
       <c r="L271" s="2"/>
-      <c r="M271" s="11" t="s">
-        <v>105</v>
+      <c r="M271" s="12" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="272" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C272" s="3">
-        <v>91000001</v>
+        <v>90000004</v>
       </c>
       <c r="D272" s="3">
-        <v>91000002</v>
+        <v>90000005</v>
       </c>
       <c r="E272" s="2">
         <v>1</v>
@@ -10928,30 +10923,31 @@
         <v>100</v>
       </c>
       <c r="G272" s="3">
-        <v>10010086</v>
+        <v>10000143</v>
       </c>
       <c r="H272" s="3">
         <v>1</v>
       </c>
-      <c r="I272" s="19">
-        <v>36</v>
-      </c>
-      <c r="J272" s="20">
-        <v>8</v>
+      <c r="I272" s="8">
+        <v>10000184</v>
+      </c>
+      <c r="J272" s="8">
+        <v>30</v>
       </c>
       <c r="K272" s="2">
         <v>0</v>
       </c>
-      <c r="M272" s="3" t="s">
-        <v>27</v>
+      <c r="L272" s="2"/>
+      <c r="M272" s="11" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="273" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C273" s="3">
-        <v>91000002</v>
+        <v>90000005</v>
       </c>
       <c r="D273" s="3">
-        <v>91000003</v>
+        <v>90000006</v>
       </c>
       <c r="E273" s="2">
         <v>1</v>
@@ -10960,30 +10956,31 @@
         <v>100</v>
       </c>
       <c r="G273" s="3">
-        <v>10010096</v>
+        <v>10000152</v>
       </c>
       <c r="H273" s="3">
         <v>1</v>
       </c>
-      <c r="I273" s="19">
-        <v>36</v>
-      </c>
-      <c r="J273" s="20">
-        <v>20</v>
+      <c r="I273" s="8">
+        <v>10000184</v>
+      </c>
+      <c r="J273" s="8">
+        <v>50</v>
       </c>
       <c r="K273" s="2">
         <v>0</v>
       </c>
-      <c r="M273" s="3" t="s">
-        <v>112</v>
+      <c r="L273" s="2"/>
+      <c r="M273" s="11" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="274" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C274" s="3">
-        <v>91000003</v>
+        <v>90000006</v>
       </c>
       <c r="D274" s="3">
-        <v>91000004</v>
+        <v>90000007</v>
       </c>
       <c r="E274" s="2">
         <v>1</v>
@@ -10992,30 +10989,31 @@
         <v>100</v>
       </c>
       <c r="G274" s="3">
-        <v>10010074</v>
+        <v>10000165</v>
       </c>
       <c r="H274" s="3">
         <v>1</v>
       </c>
-      <c r="I274" s="19">
-        <v>36</v>
-      </c>
-      <c r="J274" s="20">
-        <v>8</v>
+      <c r="I274" s="8">
+        <v>10000184</v>
+      </c>
+      <c r="J274" s="8">
+        <v>100</v>
       </c>
       <c r="K274" s="2">
         <v>0</v>
       </c>
-      <c r="M274" s="3" t="s">
-        <v>115</v>
+      <c r="L274" s="2"/>
+      <c r="M274" s="11" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="275" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C275" s="3">
-        <v>91000004</v>
+        <v>90000007</v>
       </c>
       <c r="D275" s="3">
-        <v>91000005</v>
+        <v>0</v>
       </c>
       <c r="E275" s="2">
         <v>1</v>
@@ -11024,30 +11022,31 @@
         <v>100</v>
       </c>
       <c r="G275" s="3">
-        <v>10010075</v>
+        <v>10010045</v>
       </c>
       <c r="H275" s="3">
         <v>1</v>
       </c>
-      <c r="I275" s="19">
-        <v>36</v>
-      </c>
-      <c r="J275" s="20">
-        <v>20</v>
+      <c r="I275" s="8">
+        <v>10000184</v>
+      </c>
+      <c r="J275" s="8">
+        <v>45</v>
       </c>
       <c r="K275" s="2">
         <v>0</v>
       </c>
-      <c r="M275" s="3" t="s">
-        <v>116</v>
+      <c r="L275" s="2"/>
+      <c r="M275" s="11" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="276" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C276" s="3">
-        <v>91000005</v>
+        <v>91000001</v>
       </c>
       <c r="D276" s="3">
-        <v>91000006</v>
+        <v>91000002</v>
       </c>
       <c r="E276" s="2">
         <v>1</v>
@@ -11055,8 +11054,8 @@
       <c r="F276" s="3">
         <v>100</v>
       </c>
-      <c r="G276" s="2">
-        <v>10010083</v>
+      <c r="G276" s="3">
+        <v>10010086</v>
       </c>
       <c r="H276" s="3">
         <v>1</v>
@@ -11065,21 +11064,21 @@
         <v>36</v>
       </c>
       <c r="J276" s="20">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K276" s="2">
         <v>0</v>
       </c>
-      <c r="M276" s="15" t="s">
-        <v>118</v>
+      <c r="M276" s="3" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="277" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C277" s="3">
-        <v>91000006</v>
+        <v>91000002</v>
       </c>
       <c r="D277" s="3">
-        <v>91000007</v>
+        <v>91000003</v>
       </c>
       <c r="E277" s="2">
         <v>1</v>
@@ -11087,8 +11086,8 @@
       <c r="F277" s="3">
         <v>100</v>
       </c>
-      <c r="G277" s="2">
-        <v>10010098</v>
+      <c r="G277" s="3">
+        <v>10010096</v>
       </c>
       <c r="H277" s="3">
         <v>1</v>
@@ -11097,21 +11096,21 @@
         <v>36</v>
       </c>
       <c r="J277" s="20">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K277" s="2">
         <v>0</v>
       </c>
-      <c r="M277" s="15" t="s">
-        <v>117</v>
+      <c r="M277" s="3" t="s">
+        <v>112</v>
       </c>
     </row>
     <row r="278" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C278" s="3">
-        <v>91000007</v>
+        <v>91000003</v>
       </c>
       <c r="D278" s="3">
-        <v>0</v>
+        <v>91000004</v>
       </c>
       <c r="E278" s="2">
         <v>1</v>
@@ -11119,8 +11118,8 @@
       <c r="F278" s="3">
         <v>100</v>
       </c>
-      <c r="G278" s="9">
-        <v>10010040</v>
+      <c r="G278" s="3">
+        <v>10010074</v>
       </c>
       <c r="H278" s="3">
         <v>1</v>
@@ -11129,21 +11128,21 @@
         <v>36</v>
       </c>
       <c r="J278" s="20">
-        <v>100</v>
+        <v>8</v>
       </c>
       <c r="K278" s="2">
-        <v>1</v>
-      </c>
-      <c r="M278" s="9" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="279" spans="3:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="M278" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="279" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C279" s="3">
-        <v>92000001</v>
+        <v>91000004</v>
       </c>
       <c r="D279" s="3">
-        <v>92000002</v>
+        <v>91000005</v>
       </c>
       <c r="E279" s="2">
         <v>1</v>
@@ -11152,31 +11151,30 @@
         <v>100</v>
       </c>
       <c r="G279" s="3">
-        <v>10060100</v>
+        <v>10010075</v>
       </c>
       <c r="H279" s="3">
         <v>1</v>
       </c>
-      <c r="I279" s="9">
-        <v>10000136</v>
-      </c>
-      <c r="J279" s="3">
-        <v>50</v>
+      <c r="I279" s="19">
+        <v>36</v>
+      </c>
+      <c r="J279" s="20">
+        <v>20</v>
       </c>
       <c r="K279" s="2">
         <v>0</v>
       </c>
-      <c r="M279" s="22" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q279" s="7"/>
+      <c r="M279" s="3" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="280" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C280" s="3">
-        <v>92000002</v>
+        <v>91000005</v>
       </c>
       <c r="D280" s="3">
-        <v>92000003</v>
+        <v>91000006</v>
       </c>
       <c r="E280" s="2">
         <v>1</v>
@@ -11184,31 +11182,31 @@
       <c r="F280" s="3">
         <v>100</v>
       </c>
-      <c r="G280" s="3">
-        <v>10060200</v>
+      <c r="G280" s="2">
+        <v>10010083</v>
       </c>
       <c r="H280" s="3">
         <v>1</v>
       </c>
-      <c r="I280" s="9">
-        <v>10000136</v>
-      </c>
-      <c r="J280" s="3">
-        <v>50</v>
+      <c r="I280" s="19">
+        <v>36</v>
+      </c>
+      <c r="J280" s="20">
+        <v>1</v>
       </c>
       <c r="K280" s="2">
         <v>0</v>
       </c>
-      <c r="M280" s="22" t="s">
-        <v>125</v>
+      <c r="M280" s="15" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="281" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C281" s="3">
-        <v>92000003</v>
+        <v>91000006</v>
       </c>
       <c r="D281" s="3">
-        <v>92000004</v>
+        <v>91000007</v>
       </c>
       <c r="E281" s="2">
         <v>1</v>
@@ -11216,31 +11214,31 @@
       <c r="F281" s="3">
         <v>100</v>
       </c>
-      <c r="G281" s="3">
-        <v>10060300</v>
+      <c r="G281" s="2">
+        <v>10010098</v>
       </c>
       <c r="H281" s="3">
         <v>1</v>
       </c>
-      <c r="I281" s="9">
-        <v>10000136</v>
-      </c>
-      <c r="J281" s="3">
-        <v>50</v>
+      <c r="I281" s="19">
+        <v>36</v>
+      </c>
+      <c r="J281" s="20">
+        <v>1</v>
       </c>
       <c r="K281" s="2">
         <v>0</v>
       </c>
-      <c r="M281" s="22" t="s">
-        <v>126</v>
+      <c r="M281" s="15" t="s">
+        <v>117</v>
       </c>
     </row>
     <row r="282" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C282" s="3">
-        <v>92000004</v>
+        <v>91000007</v>
       </c>
       <c r="D282" s="3">
-        <v>92000005</v>
+        <v>0</v>
       </c>
       <c r="E282" s="2">
         <v>1</v>
@@ -11248,31 +11246,31 @@
       <c r="F282" s="3">
         <v>100</v>
       </c>
-      <c r="G282" s="3">
-        <v>10060400</v>
+      <c r="G282" s="9">
+        <v>10010040</v>
       </c>
       <c r="H282" s="3">
         <v>1</v>
       </c>
-      <c r="I282" s="9">
-        <v>10000136</v>
-      </c>
-      <c r="J282" s="3">
-        <v>50</v>
+      <c r="I282" s="19">
+        <v>36</v>
+      </c>
+      <c r="J282" s="20">
+        <v>100</v>
       </c>
       <c r="K282" s="2">
-        <v>0</v>
-      </c>
-      <c r="M282" s="22" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="283" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>1</v>
+      </c>
+      <c r="M282" s="9" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="283" spans="3:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C283" s="3">
-        <v>92000005</v>
+        <v>92000001</v>
       </c>
       <c r="D283" s="3">
-        <v>92000006</v>
+        <v>92000002</v>
       </c>
       <c r="E283" s="2">
         <v>1</v>
@@ -11281,7 +11279,7 @@
         <v>100</v>
       </c>
       <c r="G283" s="3">
-        <v>10060500</v>
+        <v>10060100</v>
       </c>
       <c r="H283" s="3">
         <v>1</v>
@@ -11296,15 +11294,16 @@
         <v>0</v>
       </c>
       <c r="M283" s="22" t="s">
-        <v>128</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="Q283" s="7"/>
     </row>
     <row r="284" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C284" s="3">
-        <v>92000006</v>
+        <v>92000002</v>
       </c>
       <c r="D284" s="3">
-        <v>92000007</v>
+        <v>92000003</v>
       </c>
       <c r="E284" s="2">
         <v>1</v>
@@ -11313,7 +11312,7 @@
         <v>100</v>
       </c>
       <c r="G284" s="3">
-        <v>10060600</v>
+        <v>10060200</v>
       </c>
       <c r="H284" s="3">
         <v>1</v>
@@ -11328,15 +11327,15 @@
         <v>0</v>
       </c>
       <c r="M284" s="22" t="s">
-        <v>129</v>
+        <v>124</v>
       </c>
     </row>
     <row r="285" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C285" s="3">
-        <v>92000007</v>
+        <v>92000003</v>
       </c>
       <c r="D285" s="3">
-        <v>92000008</v>
+        <v>92000004</v>
       </c>
       <c r="E285" s="2">
         <v>1</v>
@@ -11345,7 +11344,7 @@
         <v>100</v>
       </c>
       <c r="G285" s="3">
-        <v>10060700</v>
+        <v>10060300</v>
       </c>
       <c r="H285" s="3">
         <v>1</v>
@@ -11360,15 +11359,15 @@
         <v>0</v>
       </c>
       <c r="M285" s="22" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="286" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C286" s="3">
-        <v>92000008</v>
+        <v>92000004</v>
       </c>
       <c r="D286" s="3">
-        <v>0</v>
+        <v>92000005</v>
       </c>
       <c r="E286" s="2">
         <v>1</v>
@@ -11377,7 +11376,7 @@
         <v>100</v>
       </c>
       <c r="G286" s="3">
-        <v>10000212</v>
+        <v>10060400</v>
       </c>
       <c r="H286" s="3">
         <v>1</v>
@@ -11386,18 +11385,146 @@
         <v>10000136</v>
       </c>
       <c r="J286" s="3">
+        <v>50</v>
+      </c>
+      <c r="K286" s="2">
+        <v>0</v>
+      </c>
+      <c r="M286" s="22" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="287" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C287" s="3">
+        <v>92000005</v>
+      </c>
+      <c r="D287" s="3">
+        <v>92000006</v>
+      </c>
+      <c r="E287" s="2">
+        <v>1</v>
+      </c>
+      <c r="F287" s="3">
+        <v>100</v>
+      </c>
+      <c r="G287" s="3">
+        <v>10060500</v>
+      </c>
+      <c r="H287" s="3">
+        <v>1</v>
+      </c>
+      <c r="I287" s="9">
+        <v>10000136</v>
+      </c>
+      <c r="J287" s="3">
+        <v>50</v>
+      </c>
+      <c r="K287" s="2">
+        <v>0</v>
+      </c>
+      <c r="M287" s="22" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="288" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C288" s="3">
+        <v>92000006</v>
+      </c>
+      <c r="D288" s="3">
+        <v>92000007</v>
+      </c>
+      <c r="E288" s="2">
+        <v>1</v>
+      </c>
+      <c r="F288" s="3">
+        <v>100</v>
+      </c>
+      <c r="G288" s="3">
+        <v>10060600</v>
+      </c>
+      <c r="H288" s="3">
+        <v>1</v>
+      </c>
+      <c r="I288" s="9">
+        <v>10000136</v>
+      </c>
+      <c r="J288" s="3">
+        <v>50</v>
+      </c>
+      <c r="K288" s="2">
+        <v>0</v>
+      </c>
+      <c r="M288" s="22" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="289" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C289" s="3">
+        <v>92000007</v>
+      </c>
+      <c r="D289" s="3">
+        <v>92000008</v>
+      </c>
+      <c r="E289" s="2">
+        <v>1</v>
+      </c>
+      <c r="F289" s="3">
+        <v>100</v>
+      </c>
+      <c r="G289" s="3">
+        <v>10060700</v>
+      </c>
+      <c r="H289" s="3">
+        <v>1</v>
+      </c>
+      <c r="I289" s="9">
+        <v>10000136</v>
+      </c>
+      <c r="J289" s="3">
+        <v>50</v>
+      </c>
+      <c r="K289" s="2">
+        <v>0</v>
+      </c>
+      <c r="M289" s="22" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="290" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C290" s="3">
+        <v>92000008</v>
+      </c>
+      <c r="D290" s="3">
+        <v>0</v>
+      </c>
+      <c r="E290" s="2">
+        <v>1</v>
+      </c>
+      <c r="F290" s="3">
+        <v>100</v>
+      </c>
+      <c r="G290" s="3">
+        <v>10000212</v>
+      </c>
+      <c r="H290" s="3">
+        <v>1</v>
+      </c>
+      <c r="I290" s="9">
+        <v>10000136</v>
+      </c>
+      <c r="J290" s="3">
         <v>150</v>
       </c>
-      <c r="K286" s="2">
-        <v>0</v>
-      </c>
-      <c r="M286" s="19" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="287" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+      <c r="K290" s="2">
+        <v>0</v>
+      </c>
+      <c r="M290" s="19" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="291" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="292" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="293" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StoreSellConfig.xlsx
+++ b/Excel/StoreSellConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A6E3B1E-D0C1-46D0-9D63-8E725FDF936B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14323C6D-7B5D-40B2-BF59-164A2439DDD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StoreSellProto" sheetId="1" r:id="rId1"/>
@@ -6993,10 +6993,10 @@
     </row>
     <row r="150" spans="3:13" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C150" s="3">
+        <v>50000016</v>
+      </c>
+      <c r="D150" s="3">
         <v>50000017</v>
-      </c>
-      <c r="D150" s="3">
-        <v>50000018</v>
       </c>
       <c r="E150" s="2">
         <v>1</v>
@@ -7025,10 +7025,10 @@
     </row>
     <row r="151" spans="3:13" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C151" s="3">
+        <v>50000017</v>
+      </c>
+      <c r="D151" s="3">
         <v>50000018</v>
-      </c>
-      <c r="D151" s="3">
-        <v>50000019</v>
       </c>
       <c r="E151" s="2">
         <v>1</v>
@@ -7057,7 +7057,7 @@
     </row>
     <row r="152" spans="3:13" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C152" s="3">
-        <v>50000019</v>
+        <v>50000018</v>
       </c>
       <c r="D152" s="3">
         <v>0</v>

--- a/Excel/StoreSellConfig.xlsx
+++ b/Excel/StoreSellConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14323C6D-7B5D-40B2-BF59-164A2439DDD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B8FF29C-8AEC-4A57-A949-84A161BBEE32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="165">
   <si>
     <t>Id</t>
   </si>
@@ -631,6 +631,14 @@
   </si>
   <si>
     <t>奇珍兑换币</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>巨岩使者精灵</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>羚羊坐骑</t>
     <phoneticPr fontId="15" type="noConversion"/>
   </si>
 </sst>
@@ -2639,7 +2647,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q293"/>
+  <dimension ref="A1:Q295"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="5" width="14" customWidth="1"/>
@@ -7060,7 +7068,7 @@
         <v>50000018</v>
       </c>
       <c r="D152" s="3">
-        <v>0</v>
+        <v>50000019</v>
       </c>
       <c r="E152" s="2">
         <v>1</v>
@@ -7089,10 +7097,10 @@
     </row>
     <row r="153" spans="3:13" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C153" s="3">
-        <v>51000001</v>
+        <v>50000019</v>
       </c>
       <c r="D153" s="3">
-        <v>51000002</v>
+        <v>50000020</v>
       </c>
       <c r="E153" s="2">
         <v>1</v>
@@ -7100,31 +7108,31 @@
       <c r="F153" s="3">
         <v>100</v>
       </c>
-      <c r="G153" s="3">
-        <v>10010094</v>
-      </c>
-      <c r="H153" s="3">
+      <c r="G153" s="9">
+        <v>10032016</v>
+      </c>
+      <c r="H153" s="2">
         <v>1</v>
       </c>
       <c r="I153" s="9">
         <v>10000167</v>
       </c>
       <c r="J153" s="3">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="K153" s="2">
         <v>0</v>
       </c>
-      <c r="M153" s="12" t="s">
-        <v>30</v>
+      <c r="M153" s="11" t="s">
+        <v>163</v>
       </c>
     </row>
     <row r="154" spans="3:13" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C154" s="3">
-        <v>51000002</v>
+        <v>50000020</v>
       </c>
       <c r="D154" s="3">
-        <v>51000003</v>
+        <v>0</v>
       </c>
       <c r="E154" s="2">
         <v>1</v>
@@ -7132,8 +7140,8 @@
       <c r="F154" s="3">
         <v>100</v>
       </c>
-      <c r="G154" s="3">
-        <v>10000105</v>
+      <c r="G154" s="9">
+        <v>10000213</v>
       </c>
       <c r="H154" s="2">
         <v>1</v>
@@ -7142,21 +7150,21 @@
         <v>10000167</v>
       </c>
       <c r="J154" s="3">
-        <v>10</v>
+        <v>60</v>
       </c>
       <c r="K154" s="2">
         <v>0</v>
       </c>
-      <c r="M154" s="15" t="s">
-        <v>33</v>
+      <c r="M154" s="11" t="s">
+        <v>164</v>
       </c>
     </row>
     <row r="155" spans="3:13" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C155" s="3">
-        <v>51000003</v>
+        <v>51000001</v>
       </c>
       <c r="D155" s="3">
-        <v>51000004</v>
+        <v>51000002</v>
       </c>
       <c r="E155" s="2">
         <v>1</v>
@@ -7165,30 +7173,30 @@
         <v>100</v>
       </c>
       <c r="G155" s="3">
-        <v>10010026</v>
-      </c>
-      <c r="H155" s="2">
+        <v>10010094</v>
+      </c>
+      <c r="H155" s="3">
         <v>1</v>
       </c>
       <c r="I155" s="9">
         <v>10000167</v>
       </c>
       <c r="J155" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K155" s="2">
         <v>0</v>
       </c>
-      <c r="M155" s="15" t="s">
-        <v>37</v>
+      <c r="M155" s="12" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="156" spans="3:13" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C156" s="3">
-        <v>51000004</v>
+        <v>51000002</v>
       </c>
       <c r="D156" s="3">
-        <v>51000005</v>
+        <v>51000003</v>
       </c>
       <c r="E156" s="2">
         <v>1</v>
@@ -7197,7 +7205,7 @@
         <v>100</v>
       </c>
       <c r="G156" s="3">
-        <v>10000152</v>
+        <v>10000105</v>
       </c>
       <c r="H156" s="2">
         <v>1</v>
@@ -7206,21 +7214,21 @@
         <v>10000167</v>
       </c>
       <c r="J156" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K156" s="2">
         <v>0</v>
       </c>
       <c r="M156" s="15" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="157" spans="3:13" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C157" s="3">
-        <v>51000005</v>
+        <v>51000003</v>
       </c>
       <c r="D157" s="3">
-        <v>51000006</v>
+        <v>51000004</v>
       </c>
       <c r="E157" s="2">
         <v>1</v>
@@ -7229,7 +7237,7 @@
         <v>100</v>
       </c>
       <c r="G157" s="3">
-        <v>10000157</v>
+        <v>10010026</v>
       </c>
       <c r="H157" s="2">
         <v>1</v>
@@ -7238,21 +7246,21 @@
         <v>10000167</v>
       </c>
       <c r="J157" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K157" s="2">
         <v>0</v>
       </c>
       <c r="M157" s="15" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="158" spans="3:13" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C158" s="3">
-        <v>51000006</v>
+        <v>51000004</v>
       </c>
       <c r="D158" s="3">
-        <v>51000007</v>
+        <v>51000005</v>
       </c>
       <c r="E158" s="2">
         <v>1</v>
@@ -7261,7 +7269,7 @@
         <v>100</v>
       </c>
       <c r="G158" s="3">
-        <v>10000150</v>
+        <v>10000152</v>
       </c>
       <c r="H158" s="2">
         <v>1</v>
@@ -7270,21 +7278,21 @@
         <v>10000167</v>
       </c>
       <c r="J158" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K158" s="2">
         <v>0</v>
       </c>
       <c r="M158" s="15" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="159" spans="3:13" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C159" s="3">
-        <v>51000007</v>
+        <v>51000005</v>
       </c>
       <c r="D159" s="3">
-        <v>51000008</v>
+        <v>51000006</v>
       </c>
       <c r="E159" s="2">
         <v>1</v>
@@ -7293,7 +7301,7 @@
         <v>100</v>
       </c>
       <c r="G159" s="3">
-        <v>10010078</v>
+        <v>10000157</v>
       </c>
       <c r="H159" s="2">
         <v>1</v>
@@ -7302,21 +7310,21 @@
         <v>10000167</v>
       </c>
       <c r="J159" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K159" s="2">
         <v>0</v>
       </c>
-      <c r="M159" s="12" t="s">
-        <v>41</v>
+      <c r="M159" s="15" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="160" spans="3:13" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C160" s="3">
-        <v>51000008</v>
+        <v>51000006</v>
       </c>
       <c r="D160" s="3">
-        <v>51000009</v>
+        <v>51000007</v>
       </c>
       <c r="E160" s="2">
         <v>1</v>
@@ -7325,7 +7333,7 @@
         <v>100</v>
       </c>
       <c r="G160" s="3">
-        <v>10010079</v>
+        <v>10000150</v>
       </c>
       <c r="H160" s="2">
         <v>1</v>
@@ -7334,21 +7342,21 @@
         <v>10000167</v>
       </c>
       <c r="J160" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K160" s="2">
         <v>0</v>
       </c>
-      <c r="M160" s="16" t="s">
-        <v>42</v>
+      <c r="M160" s="15" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="161" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C161" s="3">
-        <v>51000009</v>
+        <v>51000007</v>
       </c>
       <c r="D161" s="3">
-        <v>51000010</v>
+        <v>51000008</v>
       </c>
       <c r="E161" s="2">
         <v>1</v>
@@ -7356,8 +7364,8 @@
       <c r="F161" s="3">
         <v>100</v>
       </c>
-      <c r="G161" s="9">
-        <v>10000165</v>
+      <c r="G161" s="3">
+        <v>10010078</v>
       </c>
       <c r="H161" s="2">
         <v>1</v>
@@ -7366,21 +7374,21 @@
         <v>10000167</v>
       </c>
       <c r="J161" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K161" s="2">
         <v>0</v>
       </c>
-      <c r="M161" s="11" t="s">
-        <v>45</v>
+      <c r="M161" s="12" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="162" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C162" s="3">
-        <v>51000010</v>
+        <v>51000008</v>
       </c>
       <c r="D162" s="3">
-        <v>51000011</v>
+        <v>51000009</v>
       </c>
       <c r="E162" s="2">
         <v>1</v>
@@ -7388,8 +7396,8 @@
       <c r="F162" s="3">
         <v>100</v>
       </c>
-      <c r="G162" s="9">
-        <v>10000183</v>
+      <c r="G162" s="3">
+        <v>10010079</v>
       </c>
       <c r="H162" s="2">
         <v>1</v>
@@ -7403,16 +7411,16 @@
       <c r="K162" s="2">
         <v>0</v>
       </c>
-      <c r="M162" s="11" t="s">
-        <v>132</v>
+      <c r="M162" s="16" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="163" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C163" s="3">
-        <v>51000011</v>
+        <v>51000009</v>
       </c>
       <c r="D163" s="3">
-        <v>0</v>
+        <v>51000010</v>
       </c>
       <c r="E163" s="2">
         <v>1</v>
@@ -7421,7 +7429,7 @@
         <v>100</v>
       </c>
       <c r="G163" s="9">
-        <v>10010060</v>
+        <v>10000165</v>
       </c>
       <c r="H163" s="2">
         <v>1</v>
@@ -7430,160 +7438,159 @@
         <v>10000167</v>
       </c>
       <c r="J163" s="3">
+        <v>1</v>
+      </c>
+      <c r="K163" s="2">
+        <v>0</v>
+      </c>
+      <c r="M163" s="11" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="164" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C164" s="3">
+        <v>51000010</v>
+      </c>
+      <c r="D164" s="3">
+        <v>51000011</v>
+      </c>
+      <c r="E164" s="2">
+        <v>1</v>
+      </c>
+      <c r="F164" s="3">
+        <v>100</v>
+      </c>
+      <c r="G164" s="9">
+        <v>10000183</v>
+      </c>
+      <c r="H164" s="2">
+        <v>1</v>
+      </c>
+      <c r="I164" s="9">
+        <v>10000167</v>
+      </c>
+      <c r="J164" s="3">
+        <v>5</v>
+      </c>
+      <c r="K164" s="2">
+        <v>0</v>
+      </c>
+      <c r="M164" s="11" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="165" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C165" s="3">
+        <v>51000011</v>
+      </c>
+      <c r="D165" s="3">
+        <v>0</v>
+      </c>
+      <c r="E165" s="2">
+        <v>1</v>
+      </c>
+      <c r="F165" s="3">
+        <v>100</v>
+      </c>
+      <c r="G165" s="9">
+        <v>10010060</v>
+      </c>
+      <c r="H165" s="2">
+        <v>1</v>
+      </c>
+      <c r="I165" s="9">
+        <v>10000167</v>
+      </c>
+      <c r="J165" s="3">
         <v>8</v>
       </c>
-      <c r="K163" s="2">
-        <v>0</v>
-      </c>
-      <c r="M163" s="11" t="s">
+      <c r="K165" s="2">
+        <v>0</v>
+      </c>
+      <c r="M165" s="11" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="164" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A164" s="3"/>
-      <c r="B164" s="3"/>
-      <c r="C164" s="3">
+    <row r="166" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A166" s="3"/>
+      <c r="B166" s="3"/>
+      <c r="C166" s="3">
         <v>60000001</v>
       </c>
-      <c r="D164" s="3">
+      <c r="D166" s="3">
         <v>60000002</v>
       </c>
-      <c r="E164" s="3">
-        <v>1</v>
-      </c>
-      <c r="F164" s="3">
-        <v>100</v>
-      </c>
-      <c r="G164" s="3">
+      <c r="E166" s="3">
+        <v>1</v>
+      </c>
+      <c r="F166" s="3">
+        <v>100</v>
+      </c>
+      <c r="G166" s="3">
         <v>10000143</v>
       </c>
-      <c r="H164" s="11" t="s">
+      <c r="H166" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="I164" s="9">
+      <c r="I166" s="9">
         <v>10000157</v>
       </c>
-      <c r="J164" s="3">
-        <v>1</v>
-      </c>
-      <c r="K164" s="2">
-        <v>0</v>
-      </c>
-      <c r="L164" s="3"/>
-      <c r="M164" s="15" t="s">
+      <c r="J166" s="3">
+        <v>1</v>
+      </c>
+      <c r="K166" s="2">
+        <v>0</v>
+      </c>
+      <c r="L166" s="3"/>
+      <c r="M166" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="N164" s="3"/>
-      <c r="P164" s="3"/>
-    </row>
-    <row r="165" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A165" s="3"/>
-      <c r="B165" s="3"/>
-      <c r="C165" s="3">
+      <c r="N166" s="3"/>
+      <c r="P166" s="3"/>
+    </row>
+    <row r="167" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A167" s="3"/>
+      <c r="B167" s="3"/>
+      <c r="C167" s="3">
         <v>60000002</v>
       </c>
-      <c r="D165" s="3">
+      <c r="D167" s="3">
         <v>60000003</v>
       </c>
-      <c r="E165" s="3">
-        <v>1</v>
-      </c>
-      <c r="F165" s="3">
-        <v>100</v>
-      </c>
-      <c r="G165" s="3">
+      <c r="E167" s="3">
+        <v>1</v>
+      </c>
+      <c r="F167" s="3">
+        <v>100</v>
+      </c>
+      <c r="G167" s="3">
         <v>10010093</v>
       </c>
-      <c r="H165" s="12">
-        <v>1</v>
-      </c>
-      <c r="I165" s="9">
+      <c r="H167" s="12">
+        <v>1</v>
+      </c>
+      <c r="I167" s="9">
         <v>10000143</v>
       </c>
-      <c r="J165" s="11" t="s">
+      <c r="J167" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="K165" s="2">
-        <v>0</v>
-      </c>
-      <c r="L165" s="3"/>
-      <c r="M165" s="12" t="s">
+      <c r="K167" s="2">
+        <v>0</v>
+      </c>
+      <c r="L167" s="3"/>
+      <c r="M167" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="N165" s="3"/>
-      <c r="P165" s="3"/>
-    </row>
-    <row r="166" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C166" s="3">
-        <v>60000003</v>
-      </c>
-      <c r="D166" s="3">
-        <v>60000004</v>
-      </c>
-      <c r="E166" s="3">
-        <v>1</v>
-      </c>
-      <c r="F166" s="3">
-        <v>100</v>
-      </c>
-      <c r="G166" s="13">
-        <v>10012001</v>
-      </c>
-      <c r="H166" s="3">
-        <v>1</v>
-      </c>
-      <c r="I166" s="3">
-        <v>10010029</v>
-      </c>
-      <c r="J166" s="3">
-        <v>10</v>
-      </c>
-      <c r="K166" s="2">
-        <v>0</v>
-      </c>
-      <c r="M166" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="O166" s="2"/>
-    </row>
-    <row r="167" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C167" s="3">
-        <v>60000004</v>
-      </c>
-      <c r="D167" s="3">
-        <v>60000005</v>
-      </c>
-      <c r="E167" s="3">
-        <v>1</v>
-      </c>
-      <c r="F167" s="3">
-        <v>100</v>
-      </c>
-      <c r="G167" s="13">
-        <v>10012002</v>
-      </c>
-      <c r="H167" s="3">
-        <v>1</v>
-      </c>
-      <c r="I167" s="3">
-        <v>10010029</v>
-      </c>
-      <c r="J167" s="3">
-        <v>10</v>
-      </c>
-      <c r="K167" s="2">
-        <v>0</v>
-      </c>
-      <c r="M167" s="13" t="s">
-        <v>51</v>
-      </c>
+      <c r="N167" s="3"/>
+      <c r="P167" s="3"/>
     </row>
     <row r="168" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C168" s="3">
-        <v>60000005</v>
+        <v>60000003</v>
       </c>
       <c r="D168" s="3">
-        <v>60000006</v>
+        <v>60000004</v>
       </c>
       <c r="E168" s="3">
         <v>1</v>
@@ -7592,7 +7599,7 @@
         <v>100</v>
       </c>
       <c r="G168" s="13">
-        <v>10012003</v>
+        <v>10012001</v>
       </c>
       <c r="H168" s="3">
         <v>1</v>
@@ -7607,15 +7614,16 @@
         <v>0</v>
       </c>
       <c r="M168" s="13" t="s">
-        <v>52</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="O168" s="2"/>
     </row>
     <row r="169" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C169" s="3">
-        <v>60000006</v>
+        <v>60000004</v>
       </c>
       <c r="D169" s="3">
-        <v>60000007</v>
+        <v>60000005</v>
       </c>
       <c r="E169" s="3">
         <v>1</v>
@@ -7624,7 +7632,7 @@
         <v>100</v>
       </c>
       <c r="G169" s="13">
-        <v>10012004</v>
+        <v>10012002</v>
       </c>
       <c r="H169" s="3">
         <v>1</v>
@@ -7639,15 +7647,15 @@
         <v>0</v>
       </c>
       <c r="M169" s="13" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="170" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C170" s="3">
-        <v>60000007</v>
+        <v>60000005</v>
       </c>
       <c r="D170" s="3">
-        <v>60000008</v>
+        <v>60000006</v>
       </c>
       <c r="E170" s="3">
         <v>1</v>
@@ -7656,7 +7664,7 @@
         <v>100</v>
       </c>
       <c r="G170" s="13">
-        <v>10012005</v>
+        <v>10012003</v>
       </c>
       <c r="H170" s="3">
         <v>1</v>
@@ -7671,15 +7679,15 @@
         <v>0</v>
       </c>
       <c r="M170" s="13" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="171" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C171" s="3">
-        <v>60000008</v>
+        <v>60000006</v>
       </c>
       <c r="D171" s="3">
-        <v>60000009</v>
+        <v>60000007</v>
       </c>
       <c r="E171" s="3">
         <v>1</v>
@@ -7688,7 +7696,7 @@
         <v>100</v>
       </c>
       <c r="G171" s="13">
-        <v>10012006</v>
+        <v>10012004</v>
       </c>
       <c r="H171" s="3">
         <v>1</v>
@@ -7703,15 +7711,15 @@
         <v>0</v>
       </c>
       <c r="M171" s="13" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="172" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C172" s="3">
-        <v>60000009</v>
+        <v>60000007</v>
       </c>
       <c r="D172" s="3">
-        <v>60000010</v>
+        <v>60000008</v>
       </c>
       <c r="E172" s="3">
         <v>1</v>
@@ -7720,7 +7728,7 @@
         <v>100</v>
       </c>
       <c r="G172" s="13">
-        <v>10012007</v>
+        <v>10012005</v>
       </c>
       <c r="H172" s="3">
         <v>1</v>
@@ -7735,15 +7743,15 @@
         <v>0</v>
       </c>
       <c r="M172" s="13" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="173" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C173" s="3">
-        <v>60000010</v>
+        <v>60000008</v>
       </c>
       <c r="D173" s="3">
-        <v>60000011</v>
+        <v>60000009</v>
       </c>
       <c r="E173" s="3">
         <v>1</v>
@@ -7752,7 +7760,7 @@
         <v>100</v>
       </c>
       <c r="G173" s="13">
-        <v>10012008</v>
+        <v>10012006</v>
       </c>
       <c r="H173" s="3">
         <v>1</v>
@@ -7767,15 +7775,15 @@
         <v>0</v>
       </c>
       <c r="M173" s="13" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="174" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C174" s="3">
-        <v>60000011</v>
+        <v>60000009</v>
       </c>
       <c r="D174" s="3">
-        <v>60000012</v>
+        <v>60000010</v>
       </c>
       <c r="E174" s="3">
         <v>1</v>
@@ -7784,7 +7792,7 @@
         <v>100</v>
       </c>
       <c r="G174" s="13">
-        <v>10012009</v>
+        <v>10012007</v>
       </c>
       <c r="H174" s="3">
         <v>1</v>
@@ -7799,15 +7807,15 @@
         <v>0</v>
       </c>
       <c r="M174" s="13" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="175" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C175" s="3">
-        <v>60000012</v>
+        <v>60000010</v>
       </c>
       <c r="D175" s="3">
-        <v>60000013</v>
+        <v>60000011</v>
       </c>
       <c r="E175" s="3">
         <v>1</v>
@@ -7816,7 +7824,7 @@
         <v>100</v>
       </c>
       <c r="G175" s="13">
-        <v>10012010</v>
+        <v>10012008</v>
       </c>
       <c r="H175" s="3">
         <v>1</v>
@@ -7831,15 +7839,15 @@
         <v>0</v>
       </c>
       <c r="M175" s="13" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="176" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C176" s="3">
-        <v>60000013</v>
+        <v>60000011</v>
       </c>
       <c r="D176" s="3">
-        <v>60000014</v>
+        <v>60000012</v>
       </c>
       <c r="E176" s="3">
         <v>1</v>
@@ -7848,7 +7856,7 @@
         <v>100</v>
       </c>
       <c r="G176" s="13">
-        <v>10012011</v>
+        <v>10012009</v>
       </c>
       <c r="H176" s="3">
         <v>1</v>
@@ -7863,15 +7871,15 @@
         <v>0</v>
       </c>
       <c r="M176" s="13" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="177" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C177" s="3">
-        <v>60000014</v>
+        <v>60000012</v>
       </c>
       <c r="D177" s="3">
-        <v>60000015</v>
+        <v>60000013</v>
       </c>
       <c r="E177" s="3">
         <v>1</v>
@@ -7880,7 +7888,7 @@
         <v>100</v>
       </c>
       <c r="G177" s="13">
-        <v>10012012</v>
+        <v>10012010</v>
       </c>
       <c r="H177" s="3">
         <v>1</v>
@@ -7895,15 +7903,15 @@
         <v>0</v>
       </c>
       <c r="M177" s="13" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="178" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C178" s="3">
-        <v>60000015</v>
+        <v>60000013</v>
       </c>
       <c r="D178" s="3">
-        <v>60000016</v>
+        <v>60000014</v>
       </c>
       <c r="E178" s="3">
         <v>1</v>
@@ -7912,7 +7920,7 @@
         <v>100</v>
       </c>
       <c r="G178" s="13">
-        <v>10012013</v>
+        <v>10012011</v>
       </c>
       <c r="H178" s="3">
         <v>1</v>
@@ -7927,15 +7935,15 @@
         <v>0</v>
       </c>
       <c r="M178" s="13" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="179" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C179" s="3">
-        <v>60000016</v>
+        <v>60000014</v>
       </c>
       <c r="D179" s="3">
-        <v>60000017</v>
+        <v>60000015</v>
       </c>
       <c r="E179" s="3">
         <v>1</v>
@@ -7944,7 +7952,7 @@
         <v>100</v>
       </c>
       <c r="G179" s="13">
-        <v>10012014</v>
+        <v>10012012</v>
       </c>
       <c r="H179" s="3">
         <v>1</v>
@@ -7959,15 +7967,15 @@
         <v>0</v>
       </c>
       <c r="M179" s="13" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="180" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C180" s="3">
-        <v>60000017</v>
+        <v>60000015</v>
       </c>
       <c r="D180" s="3">
-        <v>60000018</v>
+        <v>60000016</v>
       </c>
       <c r="E180" s="3">
         <v>1</v>
@@ -7976,7 +7984,7 @@
         <v>100</v>
       </c>
       <c r="G180" s="13">
-        <v>10012015</v>
+        <v>10012013</v>
       </c>
       <c r="H180" s="3">
         <v>1</v>
@@ -7991,15 +7999,15 @@
         <v>0</v>
       </c>
       <c r="M180" s="13" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="181" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C181" s="3">
-        <v>60000018</v>
+        <v>60000016</v>
       </c>
       <c r="D181" s="3">
-        <v>60000019</v>
+        <v>60000017</v>
       </c>
       <c r="E181" s="3">
         <v>1</v>
@@ -8008,7 +8016,7 @@
         <v>100</v>
       </c>
       <c r="G181" s="13">
-        <v>10012016</v>
+        <v>10012014</v>
       </c>
       <c r="H181" s="3">
         <v>1</v>
@@ -8023,15 +8031,15 @@
         <v>0</v>
       </c>
       <c r="M181" s="13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="182" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C182" s="3">
-        <v>60000019</v>
+        <v>60000017</v>
       </c>
       <c r="D182" s="3">
-        <v>60000020</v>
+        <v>60000018</v>
       </c>
       <c r="E182" s="3">
         <v>1</v>
@@ -8040,7 +8048,7 @@
         <v>100</v>
       </c>
       <c r="G182" s="13">
-        <v>10012017</v>
+        <v>10012015</v>
       </c>
       <c r="H182" s="3">
         <v>1</v>
@@ -8055,15 +8063,15 @@
         <v>0</v>
       </c>
       <c r="M182" s="13" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="183" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C183" s="3">
-        <v>60000020</v>
+        <v>60000018</v>
       </c>
       <c r="D183" s="3">
-        <v>60000021</v>
+        <v>60000019</v>
       </c>
       <c r="E183" s="3">
         <v>1</v>
@@ -8072,7 +8080,7 @@
         <v>100</v>
       </c>
       <c r="G183" s="13">
-        <v>10012018</v>
+        <v>10012016</v>
       </c>
       <c r="H183" s="3">
         <v>1</v>
@@ -8087,15 +8095,15 @@
         <v>0</v>
       </c>
       <c r="M183" s="13" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="184" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C184" s="3">
-        <v>60000021</v>
+        <v>60000019</v>
       </c>
       <c r="D184" s="3">
-        <v>60000022</v>
+        <v>60000020</v>
       </c>
       <c r="E184" s="3">
         <v>1</v>
@@ -8104,7 +8112,7 @@
         <v>100</v>
       </c>
       <c r="G184" s="13">
-        <v>10012019</v>
+        <v>10012017</v>
       </c>
       <c r="H184" s="3">
         <v>1</v>
@@ -8119,15 +8127,15 @@
         <v>0</v>
       </c>
       <c r="M184" s="13" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="185" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C185" s="3">
-        <v>60000022</v>
+        <v>60000020</v>
       </c>
       <c r="D185" s="3">
-        <v>60000023</v>
+        <v>60000021</v>
       </c>
       <c r="E185" s="3">
         <v>1</v>
@@ -8136,7 +8144,7 @@
         <v>100</v>
       </c>
       <c r="G185" s="13">
-        <v>10012020</v>
+        <v>10012018</v>
       </c>
       <c r="H185" s="3">
         <v>1</v>
@@ -8145,21 +8153,21 @@
         <v>10010029</v>
       </c>
       <c r="J185" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K185" s="2">
         <v>0</v>
       </c>
       <c r="M185" s="13" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="186" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C186" s="3">
-        <v>60000023</v>
+        <v>60000021</v>
       </c>
       <c r="D186" s="3">
-        <v>60000024</v>
+        <v>60000022</v>
       </c>
       <c r="E186" s="3">
         <v>1</v>
@@ -8168,7 +8176,7 @@
         <v>100</v>
       </c>
       <c r="G186" s="13">
-        <v>10012021</v>
+        <v>10012019</v>
       </c>
       <c r="H186" s="3">
         <v>1</v>
@@ -8177,21 +8185,21 @@
         <v>10010029</v>
       </c>
       <c r="J186" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K186" s="2">
         <v>0</v>
       </c>
       <c r="M186" s="13" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
     </row>
     <row r="187" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C187" s="3">
-        <v>60000024</v>
+        <v>60000022</v>
       </c>
       <c r="D187" s="3">
-        <v>60000025</v>
+        <v>60000023</v>
       </c>
       <c r="E187" s="3">
         <v>1</v>
@@ -8200,7 +8208,7 @@
         <v>100</v>
       </c>
       <c r="G187" s="13">
-        <v>10012022</v>
+        <v>10012020</v>
       </c>
       <c r="H187" s="3">
         <v>1</v>
@@ -8215,15 +8223,15 @@
         <v>0</v>
       </c>
       <c r="M187" s="13" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="188" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C188" s="3">
-        <v>60000025</v>
+        <v>60000023</v>
       </c>
       <c r="D188" s="3">
-        <v>60000026</v>
+        <v>60000024</v>
       </c>
       <c r="E188" s="3">
         <v>1</v>
@@ -8232,7 +8240,7 @@
         <v>100</v>
       </c>
       <c r="G188" s="13">
-        <v>10012023</v>
+        <v>10012021</v>
       </c>
       <c r="H188" s="3">
         <v>1</v>
@@ -8247,15 +8255,15 @@
         <v>0</v>
       </c>
       <c r="M188" s="13" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="189" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C189" s="3">
-        <v>60000026</v>
+        <v>60000024</v>
       </c>
       <c r="D189" s="3">
-        <v>60000027</v>
+        <v>60000025</v>
       </c>
       <c r="E189" s="3">
         <v>1</v>
@@ -8264,7 +8272,7 @@
         <v>100</v>
       </c>
       <c r="G189" s="13">
-        <v>10012024</v>
+        <v>10012022</v>
       </c>
       <c r="H189" s="3">
         <v>1</v>
@@ -8279,15 +8287,15 @@
         <v>0</v>
       </c>
       <c r="M189" s="13" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
     <row r="190" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C190" s="3">
-        <v>60000027</v>
+        <v>60000025</v>
       </c>
       <c r="D190" s="3">
-        <v>60000028</v>
+        <v>60000026</v>
       </c>
       <c r="E190" s="3">
         <v>1</v>
@@ -8296,7 +8304,7 @@
         <v>100</v>
       </c>
       <c r="G190" s="13">
-        <v>10012025</v>
+        <v>10012023</v>
       </c>
       <c r="H190" s="3">
         <v>1</v>
@@ -8311,15 +8319,15 @@
         <v>0</v>
       </c>
       <c r="M190" s="13" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
     </row>
     <row r="191" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C191" s="3">
-        <v>60000028</v>
+        <v>60000026</v>
       </c>
       <c r="D191" s="3">
-        <v>60000029</v>
+        <v>60000027</v>
       </c>
       <c r="E191" s="3">
         <v>1</v>
@@ -8328,7 +8336,7 @@
         <v>100</v>
       </c>
       <c r="G191" s="13">
-        <v>10012026</v>
+        <v>10012024</v>
       </c>
       <c r="H191" s="3">
         <v>1</v>
@@ -8343,15 +8351,15 @@
         <v>0</v>
       </c>
       <c r="M191" s="13" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="192" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C192" s="3">
-        <v>60000029</v>
+        <v>60000027</v>
       </c>
       <c r="D192" s="3">
-        <v>60000030</v>
+        <v>60000028</v>
       </c>
       <c r="E192" s="3">
         <v>1</v>
@@ -8360,7 +8368,7 @@
         <v>100</v>
       </c>
       <c r="G192" s="13">
-        <v>10012027</v>
+        <v>10012025</v>
       </c>
       <c r="H192" s="3">
         <v>1</v>
@@ -8375,15 +8383,15 @@
         <v>0</v>
       </c>
       <c r="M192" s="13" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="193" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C193" s="3">
-        <v>60000030</v>
+        <v>60000028</v>
       </c>
       <c r="D193" s="3">
-        <v>60000031</v>
+        <v>60000029</v>
       </c>
       <c r="E193" s="3">
         <v>1</v>
@@ -8392,13 +8400,13 @@
         <v>100</v>
       </c>
       <c r="G193" s="13">
-        <v>10013001</v>
+        <v>10012026</v>
       </c>
       <c r="H193" s="3">
         <v>1</v>
       </c>
       <c r="I193" s="3">
-        <v>10010030</v>
+        <v>10010029</v>
       </c>
       <c r="J193" s="3">
         <v>15</v>
@@ -8406,16 +8414,16 @@
       <c r="K193" s="2">
         <v>0</v>
       </c>
-      <c r="M193" s="17" t="s">
-        <v>77</v>
+      <c r="M193" s="13" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="194" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C194" s="3">
-        <v>60000031</v>
+        <v>60000029</v>
       </c>
       <c r="D194" s="3">
-        <v>60000032</v>
+        <v>60000030</v>
       </c>
       <c r="E194" s="3">
         <v>1</v>
@@ -8424,13 +8432,13 @@
         <v>100</v>
       </c>
       <c r="G194" s="13">
-        <v>10013002</v>
+        <v>10012027</v>
       </c>
       <c r="H194" s="3">
         <v>1</v>
       </c>
       <c r="I194" s="3">
-        <v>10010030</v>
+        <v>10010029</v>
       </c>
       <c r="J194" s="3">
         <v>15</v>
@@ -8438,16 +8446,16 @@
       <c r="K194" s="2">
         <v>0</v>
       </c>
-      <c r="M194" s="17" t="s">
-        <v>78</v>
+      <c r="M194" s="13" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="195" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C195" s="3">
-        <v>60000032</v>
+        <v>60000030</v>
       </c>
       <c r="D195" s="3">
-        <v>60000033</v>
+        <v>60000031</v>
       </c>
       <c r="E195" s="3">
         <v>1</v>
@@ -8456,7 +8464,7 @@
         <v>100</v>
       </c>
       <c r="G195" s="13">
-        <v>10013003</v>
+        <v>10013001</v>
       </c>
       <c r="H195" s="3">
         <v>1</v>
@@ -8471,15 +8479,15 @@
         <v>0</v>
       </c>
       <c r="M195" s="17" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="196" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C196" s="3">
-        <v>60000033</v>
+        <v>60000031</v>
       </c>
       <c r="D196" s="3">
-        <v>60000034</v>
+        <v>60000032</v>
       </c>
       <c r="E196" s="3">
         <v>1</v>
@@ -8488,7 +8496,7 @@
         <v>100</v>
       </c>
       <c r="G196" s="13">
-        <v>10013004</v>
+        <v>10013002</v>
       </c>
       <c r="H196" s="3">
         <v>1</v>
@@ -8503,15 +8511,15 @@
         <v>0</v>
       </c>
       <c r="M196" s="17" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="197" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C197" s="3">
-        <v>60000034</v>
+        <v>60000032</v>
       </c>
       <c r="D197" s="3">
-        <v>60000035</v>
+        <v>60000033</v>
       </c>
       <c r="E197" s="3">
         <v>1</v>
@@ -8520,7 +8528,7 @@
         <v>100</v>
       </c>
       <c r="G197" s="13">
-        <v>10013005</v>
+        <v>10013003</v>
       </c>
       <c r="H197" s="3">
         <v>1</v>
@@ -8535,15 +8543,15 @@
         <v>0</v>
       </c>
       <c r="M197" s="17" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="198" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C198" s="3">
-        <v>60000035</v>
+        <v>60000033</v>
       </c>
       <c r="D198" s="3">
-        <v>60000036</v>
+        <v>60000034</v>
       </c>
       <c r="E198" s="3">
         <v>1</v>
@@ -8552,7 +8560,7 @@
         <v>100</v>
       </c>
       <c r="G198" s="13">
-        <v>10013006</v>
+        <v>10013004</v>
       </c>
       <c r="H198" s="3">
         <v>1</v>
@@ -8567,15 +8575,15 @@
         <v>0</v>
       </c>
       <c r="M198" s="17" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="199" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C199" s="3">
-        <v>60000036</v>
+        <v>60000034</v>
       </c>
       <c r="D199" s="3">
-        <v>60000037</v>
+        <v>60000035</v>
       </c>
       <c r="E199" s="3">
         <v>1</v>
@@ -8584,7 +8592,7 @@
         <v>100</v>
       </c>
       <c r="G199" s="13">
-        <v>10013007</v>
+        <v>10013005</v>
       </c>
       <c r="H199" s="3">
         <v>1</v>
@@ -8599,15 +8607,15 @@
         <v>0</v>
       </c>
       <c r="M199" s="17" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="200" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C200" s="3">
-        <v>60000037</v>
+        <v>60000035</v>
       </c>
       <c r="D200" s="3">
-        <v>60000038</v>
+        <v>60000036</v>
       </c>
       <c r="E200" s="3">
         <v>1</v>
@@ -8616,7 +8624,7 @@
         <v>100</v>
       </c>
       <c r="G200" s="13">
-        <v>10013008</v>
+        <v>10013006</v>
       </c>
       <c r="H200" s="3">
         <v>1</v>
@@ -8631,15 +8639,15 @@
         <v>0</v>
       </c>
       <c r="M200" s="17" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="201" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C201" s="3">
-        <v>60000038</v>
+        <v>60000036</v>
       </c>
       <c r="D201" s="3">
-        <v>60000039</v>
+        <v>60000037</v>
       </c>
       <c r="E201" s="3">
         <v>1</v>
@@ -8648,7 +8656,7 @@
         <v>100</v>
       </c>
       <c r="G201" s="13">
-        <v>10013009</v>
+        <v>10013007</v>
       </c>
       <c r="H201" s="3">
         <v>1</v>
@@ -8663,15 +8671,15 @@
         <v>0</v>
       </c>
       <c r="M201" s="17" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="202" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C202" s="3">
-        <v>60000039</v>
+        <v>60000037</v>
       </c>
       <c r="D202" s="3">
-        <v>60000040</v>
+        <v>60000038</v>
       </c>
       <c r="E202" s="3">
         <v>1</v>
@@ -8680,7 +8688,7 @@
         <v>100</v>
       </c>
       <c r="G202" s="13">
-        <v>10013010</v>
+        <v>10013008</v>
       </c>
       <c r="H202" s="3">
         <v>1</v>
@@ -8695,15 +8703,15 @@
         <v>0</v>
       </c>
       <c r="M202" s="17" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="203" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C203" s="3">
-        <v>60000040</v>
+        <v>60000038</v>
       </c>
       <c r="D203" s="3">
-        <v>60000041</v>
+        <v>60000039</v>
       </c>
       <c r="E203" s="3">
         <v>1</v>
@@ -8712,7 +8720,7 @@
         <v>100</v>
       </c>
       <c r="G203" s="13">
-        <v>10013011</v>
+        <v>10013009</v>
       </c>
       <c r="H203" s="3">
         <v>1</v>
@@ -8727,15 +8735,15 @@
         <v>0</v>
       </c>
       <c r="M203" s="17" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="204" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C204" s="3">
-        <v>60000041</v>
+        <v>60000039</v>
       </c>
       <c r="D204" s="3">
-        <v>60000042</v>
+        <v>60000040</v>
       </c>
       <c r="E204" s="3">
         <v>1</v>
@@ -8744,7 +8752,7 @@
         <v>100</v>
       </c>
       <c r="G204" s="13">
-        <v>10013012</v>
+        <v>10013010</v>
       </c>
       <c r="H204" s="3">
         <v>1</v>
@@ -8759,15 +8767,15 @@
         <v>0</v>
       </c>
       <c r="M204" s="17" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="205" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C205" s="3">
-        <v>60000042</v>
+        <v>60000040</v>
       </c>
       <c r="D205" s="3">
-        <v>60000043</v>
+        <v>60000041</v>
       </c>
       <c r="E205" s="3">
         <v>1</v>
@@ -8776,7 +8784,7 @@
         <v>100</v>
       </c>
       <c r="G205" s="13">
-        <v>10013013</v>
+        <v>10013011</v>
       </c>
       <c r="H205" s="3">
         <v>1</v>
@@ -8791,15 +8799,15 @@
         <v>0</v>
       </c>
       <c r="M205" s="17" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="206" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C206" s="3">
-        <v>60000043</v>
+        <v>60000041</v>
       </c>
       <c r="D206" s="3">
-        <v>60000044</v>
+        <v>60000042</v>
       </c>
       <c r="E206" s="3">
         <v>1</v>
@@ -8808,7 +8816,7 @@
         <v>100</v>
       </c>
       <c r="G206" s="13">
-        <v>10013014</v>
+        <v>10013012</v>
       </c>
       <c r="H206" s="3">
         <v>1</v>
@@ -8823,15 +8831,15 @@
         <v>0</v>
       </c>
       <c r="M206" s="17" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="207" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C207" s="3">
-        <v>60000044</v>
+        <v>60000042</v>
       </c>
       <c r="D207" s="3">
-        <v>60000045</v>
+        <v>60000043</v>
       </c>
       <c r="E207" s="3">
         <v>1</v>
@@ -8840,7 +8848,7 @@
         <v>100</v>
       </c>
       <c r="G207" s="13">
-        <v>10013015</v>
+        <v>10013013</v>
       </c>
       <c r="H207" s="3">
         <v>1</v>
@@ -8855,15 +8863,15 @@
         <v>0</v>
       </c>
       <c r="M207" s="17" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="208" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C208" s="3">
-        <v>60000045</v>
+        <v>60000043</v>
       </c>
       <c r="D208" s="3">
-        <v>60000046</v>
+        <v>60000044</v>
       </c>
       <c r="E208" s="3">
         <v>1</v>
@@ -8872,7 +8880,7 @@
         <v>100</v>
       </c>
       <c r="G208" s="13">
-        <v>10013016</v>
+        <v>10013014</v>
       </c>
       <c r="H208" s="3">
         <v>1</v>
@@ -8887,15 +8895,15 @@
         <v>0</v>
       </c>
       <c r="M208" s="17" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
     </row>
     <row r="209" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C209" s="3">
-        <v>60000046</v>
+        <v>60000044</v>
       </c>
       <c r="D209" s="3">
-        <v>60000047</v>
+        <v>60000045</v>
       </c>
       <c r="E209" s="3">
         <v>1</v>
@@ -8904,7 +8912,7 @@
         <v>100</v>
       </c>
       <c r="G209" s="13">
-        <v>10013017</v>
+        <v>10013015</v>
       </c>
       <c r="H209" s="3">
         <v>1</v>
@@ -8919,15 +8927,15 @@
         <v>0</v>
       </c>
       <c r="M209" s="17" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="210" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C210" s="3">
-        <v>60000047</v>
+        <v>60000045</v>
       </c>
       <c r="D210" s="3">
-        <v>60000048</v>
+        <v>60000046</v>
       </c>
       <c r="E210" s="3">
         <v>1</v>
@@ -8936,7 +8944,7 @@
         <v>100</v>
       </c>
       <c r="G210" s="13">
-        <v>10013018</v>
+        <v>10013016</v>
       </c>
       <c r="H210" s="3">
         <v>1</v>
@@ -8951,15 +8959,15 @@
         <v>0</v>
       </c>
       <c r="M210" s="17" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="211" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C211" s="3">
-        <v>60000048</v>
+        <v>60000046</v>
       </c>
       <c r="D211" s="3">
-        <v>60000049</v>
+        <v>60000047</v>
       </c>
       <c r="E211" s="3">
         <v>1</v>
@@ -8968,7 +8976,7 @@
         <v>100</v>
       </c>
       <c r="G211" s="13">
-        <v>10013019</v>
+        <v>10013017</v>
       </c>
       <c r="H211" s="3">
         <v>1</v>
@@ -8983,15 +8991,15 @@
         <v>0</v>
       </c>
       <c r="M211" s="17" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
     </row>
     <row r="212" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C212" s="3">
-        <v>60000049</v>
+        <v>60000047</v>
       </c>
       <c r="D212" s="3">
-        <v>60000050</v>
+        <v>60000048</v>
       </c>
       <c r="E212" s="3">
         <v>1</v>
@@ -9000,7 +9008,7 @@
         <v>100</v>
       </c>
       <c r="G212" s="13">
-        <v>10013020</v>
+        <v>10013018</v>
       </c>
       <c r="H212" s="3">
         <v>1</v>
@@ -9009,21 +9017,21 @@
         <v>10010030</v>
       </c>
       <c r="J212" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K212" s="2">
         <v>0</v>
       </c>
       <c r="M212" s="17" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="213" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C213" s="3">
-        <v>60000050</v>
+        <v>60000048</v>
       </c>
       <c r="D213" s="3">
-        <v>60000051</v>
+        <v>60000049</v>
       </c>
       <c r="E213" s="3">
         <v>1</v>
@@ -9032,7 +9040,7 @@
         <v>100</v>
       </c>
       <c r="G213" s="13">
-        <v>10013021</v>
+        <v>10013019</v>
       </c>
       <c r="H213" s="3">
         <v>1</v>
@@ -9041,21 +9049,21 @@
         <v>10010030</v>
       </c>
       <c r="J213" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K213" s="2">
         <v>0</v>
       </c>
       <c r="M213" s="17" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
     </row>
     <row r="214" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C214" s="3">
-        <v>60000051</v>
+        <v>60000049</v>
       </c>
       <c r="D214" s="3">
-        <v>60000052</v>
+        <v>60000050</v>
       </c>
       <c r="E214" s="3">
         <v>1</v>
@@ -9064,7 +9072,7 @@
         <v>100</v>
       </c>
       <c r="G214" s="13">
-        <v>10013022</v>
+        <v>10013020</v>
       </c>
       <c r="H214" s="3">
         <v>1</v>
@@ -9079,15 +9087,15 @@
         <v>0</v>
       </c>
       <c r="M214" s="17" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="215" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C215" s="3">
-        <v>60000052</v>
+        <v>60000050</v>
       </c>
       <c r="D215" s="3">
-        <v>60000053</v>
+        <v>60000051</v>
       </c>
       <c r="E215" s="3">
         <v>1</v>
@@ -9096,7 +9104,7 @@
         <v>100</v>
       </c>
       <c r="G215" s="13">
-        <v>10013023</v>
+        <v>10013021</v>
       </c>
       <c r="H215" s="3">
         <v>1</v>
@@ -9111,15 +9119,15 @@
         <v>0</v>
       </c>
       <c r="M215" s="17" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="216" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C216" s="3">
-        <v>60000053</v>
+        <v>60000051</v>
       </c>
       <c r="D216" s="3">
-        <v>60000054</v>
+        <v>60000052</v>
       </c>
       <c r="E216" s="3">
         <v>1</v>
@@ -9128,7 +9136,7 @@
         <v>100</v>
       </c>
       <c r="G216" s="13">
-        <v>10013024</v>
+        <v>10013022</v>
       </c>
       <c r="H216" s="3">
         <v>1</v>
@@ -9143,15 +9151,15 @@
         <v>0</v>
       </c>
       <c r="M216" s="17" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
     </row>
     <row r="217" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C217" s="3">
-        <v>60000054</v>
+        <v>60000052</v>
       </c>
       <c r="D217" s="3">
-        <v>60000055</v>
+        <v>60000053</v>
       </c>
       <c r="E217" s="3">
         <v>1</v>
@@ -9160,7 +9168,7 @@
         <v>100</v>
       </c>
       <c r="G217" s="13">
-        <v>10013025</v>
+        <v>10013023</v>
       </c>
       <c r="H217" s="3">
         <v>1</v>
@@ -9175,15 +9183,15 @@
         <v>0</v>
       </c>
       <c r="M217" s="17" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="218" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C218" s="3">
-        <v>60000055</v>
+        <v>60000053</v>
       </c>
       <c r="D218" s="3">
-        <v>60000056</v>
+        <v>60000054</v>
       </c>
       <c r="E218" s="3">
         <v>1</v>
@@ -9192,7 +9200,7 @@
         <v>100</v>
       </c>
       <c r="G218" s="13">
-        <v>10013026</v>
+        <v>10013024</v>
       </c>
       <c r="H218" s="3">
         <v>1</v>
@@ -9207,15 +9215,15 @@
         <v>0</v>
       </c>
       <c r="M218" s="17" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
     </row>
     <row r="219" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C219" s="3">
-        <v>60000056</v>
+        <v>60000054</v>
       </c>
       <c r="D219" s="3">
-        <v>60000057</v>
+        <v>60000055</v>
       </c>
       <c r="E219" s="3">
         <v>1</v>
@@ -9224,7 +9232,7 @@
         <v>100</v>
       </c>
       <c r="G219" s="13">
-        <v>10013027</v>
+        <v>10013025</v>
       </c>
       <c r="H219" s="3">
         <v>1</v>
@@ -9239,15 +9247,15 @@
         <v>0</v>
       </c>
       <c r="M219" s="17" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="220" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C220" s="3">
-        <v>60000057</v>
+        <v>60000055</v>
       </c>
       <c r="D220" s="3">
-        <v>60000058</v>
+        <v>60000056</v>
       </c>
       <c r="E220" s="3">
         <v>1</v>
@@ -9256,13 +9264,13 @@
         <v>100</v>
       </c>
       <c r="G220" s="13">
-        <v>10014001</v>
+        <v>10013026</v>
       </c>
       <c r="H220" s="3">
         <v>1</v>
       </c>
       <c r="I220" s="3">
-        <v>10010031</v>
+        <v>10010030</v>
       </c>
       <c r="J220" s="3">
         <v>20</v>
@@ -9270,16 +9278,16 @@
       <c r="K220" s="2">
         <v>0</v>
       </c>
-      <c r="M220" s="3" t="s">
-        <v>134</v>
+      <c r="M220" s="17" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="221" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C221" s="3">
-        <v>60000058</v>
+        <v>60000056</v>
       </c>
       <c r="D221" s="3">
-        <v>60000059</v>
+        <v>60000057</v>
       </c>
       <c r="E221" s="3">
         <v>1</v>
@@ -9288,13 +9296,13 @@
         <v>100</v>
       </c>
       <c r="G221" s="13">
-        <v>10014002</v>
+        <v>10013027</v>
       </c>
       <c r="H221" s="3">
         <v>1</v>
       </c>
       <c r="I221" s="3">
-        <v>10010031</v>
+        <v>10010030</v>
       </c>
       <c r="J221" s="3">
         <v>20</v>
@@ -9302,16 +9310,16 @@
       <c r="K221" s="2">
         <v>0</v>
       </c>
-      <c r="M221" s="3" t="s">
-        <v>135</v>
+      <c r="M221" s="17" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="222" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C222" s="3">
-        <v>60000059</v>
+        <v>60000057</v>
       </c>
       <c r="D222" s="3">
-        <v>60000060</v>
+        <v>60000058</v>
       </c>
       <c r="E222" s="3">
         <v>1</v>
@@ -9320,7 +9328,7 @@
         <v>100</v>
       </c>
       <c r="G222" s="13">
-        <v>10014003</v>
+        <v>10014001</v>
       </c>
       <c r="H222" s="3">
         <v>1</v>
@@ -9335,15 +9343,15 @@
         <v>0</v>
       </c>
       <c r="M222" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="223" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C223" s="3">
-        <v>60000060</v>
+        <v>60000058</v>
       </c>
       <c r="D223" s="3">
-        <v>60000061</v>
+        <v>60000059</v>
       </c>
       <c r="E223" s="3">
         <v>1</v>
@@ -9352,7 +9360,7 @@
         <v>100</v>
       </c>
       <c r="G223" s="13">
-        <v>10014004</v>
+        <v>10014002</v>
       </c>
       <c r="H223" s="3">
         <v>1</v>
@@ -9367,15 +9375,15 @@
         <v>0</v>
       </c>
       <c r="M223" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
     </row>
     <row r="224" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C224" s="3">
-        <v>60000061</v>
+        <v>60000059</v>
       </c>
       <c r="D224" s="3">
-        <v>60000062</v>
+        <v>60000060</v>
       </c>
       <c r="E224" s="3">
         <v>1</v>
@@ -9384,7 +9392,7 @@
         <v>100</v>
       </c>
       <c r="G224" s="13">
-        <v>10014005</v>
+        <v>10014003</v>
       </c>
       <c r="H224" s="3">
         <v>1</v>
@@ -9399,15 +9407,15 @@
         <v>0</v>
       </c>
       <c r="M224" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
     </row>
     <row r="225" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C225" s="3">
-        <v>60000062</v>
+        <v>60000060</v>
       </c>
       <c r="D225" s="3">
-        <v>60000063</v>
+        <v>60000061</v>
       </c>
       <c r="E225" s="3">
         <v>1</v>
@@ -9416,7 +9424,7 @@
         <v>100</v>
       </c>
       <c r="G225" s="13">
-        <v>10014006</v>
+        <v>10014004</v>
       </c>
       <c r="H225" s="3">
         <v>1</v>
@@ -9431,15 +9439,15 @@
         <v>0</v>
       </c>
       <c r="M225" s="3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
     </row>
     <row r="226" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C226" s="3">
-        <v>60000063</v>
+        <v>60000061</v>
       </c>
       <c r="D226" s="3">
-        <v>60000064</v>
+        <v>60000062</v>
       </c>
       <c r="E226" s="3">
         <v>1</v>
@@ -9448,7 +9456,7 @@
         <v>100</v>
       </c>
       <c r="G226" s="13">
-        <v>10014007</v>
+        <v>10014005</v>
       </c>
       <c r="H226" s="3">
         <v>1</v>
@@ -9463,15 +9471,15 @@
         <v>0</v>
       </c>
       <c r="M226" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="227" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C227" s="3">
-        <v>60000064</v>
+        <v>60000062</v>
       </c>
       <c r="D227" s="3">
-        <v>60000065</v>
+        <v>60000063</v>
       </c>
       <c r="E227" s="3">
         <v>1</v>
@@ -9480,7 +9488,7 @@
         <v>100</v>
       </c>
       <c r="G227" s="13">
-        <v>10014008</v>
+        <v>10014006</v>
       </c>
       <c r="H227" s="3">
         <v>1</v>
@@ -9495,15 +9503,15 @@
         <v>0</v>
       </c>
       <c r="M227" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="228" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C228" s="3">
-        <v>60000065</v>
+        <v>60000063</v>
       </c>
       <c r="D228" s="3">
-        <v>60000066</v>
+        <v>60000064</v>
       </c>
       <c r="E228" s="3">
         <v>1</v>
@@ -9512,7 +9520,7 @@
         <v>100</v>
       </c>
       <c r="G228" s="13">
-        <v>10014009</v>
+        <v>10014007</v>
       </c>
       <c r="H228" s="3">
         <v>1</v>
@@ -9527,15 +9535,15 @@
         <v>0</v>
       </c>
       <c r="M228" s="3" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
     </row>
     <row r="229" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C229" s="3">
-        <v>60000066</v>
+        <v>60000064</v>
       </c>
       <c r="D229" s="3">
-        <v>60000067</v>
+        <v>60000065</v>
       </c>
       <c r="E229" s="3">
         <v>1</v>
@@ -9544,7 +9552,7 @@
         <v>100</v>
       </c>
       <c r="G229" s="13">
-        <v>10014010</v>
+        <v>10014008</v>
       </c>
       <c r="H229" s="3">
         <v>1</v>
@@ -9559,15 +9567,15 @@
         <v>0</v>
       </c>
       <c r="M229" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
     </row>
     <row r="230" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C230" s="3">
-        <v>60000067</v>
+        <v>60000065</v>
       </c>
       <c r="D230" s="3">
-        <v>60000068</v>
+        <v>60000066</v>
       </c>
       <c r="E230" s="3">
         <v>1</v>
@@ -9576,7 +9584,7 @@
         <v>100</v>
       </c>
       <c r="G230" s="13">
-        <v>10014011</v>
+        <v>10014009</v>
       </c>
       <c r="H230" s="3">
         <v>1</v>
@@ -9591,15 +9599,15 @@
         <v>0</v>
       </c>
       <c r="M230" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="231" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C231" s="3">
-        <v>60000068</v>
+        <v>60000066</v>
       </c>
       <c r="D231" s="3">
-        <v>60000069</v>
+        <v>60000067</v>
       </c>
       <c r="E231" s="3">
         <v>1</v>
@@ -9608,7 +9616,7 @@
         <v>100</v>
       </c>
       <c r="G231" s="13">
-        <v>10014012</v>
+        <v>10014010</v>
       </c>
       <c r="H231" s="3">
         <v>1</v>
@@ -9623,15 +9631,15 @@
         <v>0</v>
       </c>
       <c r="M231" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
     </row>
     <row r="232" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C232" s="3">
-        <v>60000069</v>
+        <v>60000067</v>
       </c>
       <c r="D232" s="3">
-        <v>60000070</v>
+        <v>60000068</v>
       </c>
       <c r="E232" s="3">
         <v>1</v>
@@ -9640,7 +9648,7 @@
         <v>100</v>
       </c>
       <c r="G232" s="13">
-        <v>10014013</v>
+        <v>10014011</v>
       </c>
       <c r="H232" s="3">
         <v>1</v>
@@ -9655,15 +9663,15 @@
         <v>0</v>
       </c>
       <c r="M232" s="3" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
     </row>
     <row r="233" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C233" s="3">
-        <v>60000070</v>
+        <v>60000068</v>
       </c>
       <c r="D233" s="3">
-        <v>60000071</v>
+        <v>60000069</v>
       </c>
       <c r="E233" s="3">
         <v>1</v>
@@ -9672,7 +9680,7 @@
         <v>100</v>
       </c>
       <c r="G233" s="13">
-        <v>10014014</v>
+        <v>10014012</v>
       </c>
       <c r="H233" s="3">
         <v>1</v>
@@ -9687,15 +9695,15 @@
         <v>0</v>
       </c>
       <c r="M233" s="3" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="234" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C234" s="3">
-        <v>60000071</v>
+        <v>60000069</v>
       </c>
       <c r="D234" s="3">
-        <v>60000072</v>
+        <v>60000070</v>
       </c>
       <c r="E234" s="3">
         <v>1</v>
@@ -9704,7 +9712,7 @@
         <v>100</v>
       </c>
       <c r="G234" s="13">
-        <v>10014015</v>
+        <v>10014013</v>
       </c>
       <c r="H234" s="3">
         <v>1</v>
@@ -9719,15 +9727,15 @@
         <v>0</v>
       </c>
       <c r="M234" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="235" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C235" s="3">
-        <v>60000072</v>
+        <v>60000070</v>
       </c>
       <c r="D235" s="3">
-        <v>60000073</v>
+        <v>60000071</v>
       </c>
       <c r="E235" s="3">
         <v>1</v>
@@ -9736,7 +9744,7 @@
         <v>100</v>
       </c>
       <c r="G235" s="13">
-        <v>10014016</v>
+        <v>10014014</v>
       </c>
       <c r="H235" s="3">
         <v>1</v>
@@ -9751,15 +9759,15 @@
         <v>0</v>
       </c>
       <c r="M235" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="236" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C236" s="3">
-        <v>60000073</v>
+        <v>60000071</v>
       </c>
       <c r="D236" s="3">
-        <v>60000074</v>
+        <v>60000072</v>
       </c>
       <c r="E236" s="3">
         <v>1</v>
@@ -9768,7 +9776,7 @@
         <v>100</v>
       </c>
       <c r="G236" s="13">
-        <v>10014017</v>
+        <v>10014015</v>
       </c>
       <c r="H236" s="3">
         <v>1</v>
@@ -9783,15 +9791,15 @@
         <v>0</v>
       </c>
       <c r="M236" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="237" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C237" s="3">
-        <v>60000074</v>
+        <v>60000072</v>
       </c>
       <c r="D237" s="3">
-        <v>60000075</v>
+        <v>60000073</v>
       </c>
       <c r="E237" s="3">
         <v>1</v>
@@ -9800,7 +9808,7 @@
         <v>100</v>
       </c>
       <c r="G237" s="13">
-        <v>10014018</v>
+        <v>10014016</v>
       </c>
       <c r="H237" s="3">
         <v>1</v>
@@ -9815,15 +9823,15 @@
         <v>0</v>
       </c>
       <c r="M237" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
     </row>
     <row r="238" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C238" s="3">
-        <v>60000075</v>
+        <v>60000073</v>
       </c>
       <c r="D238" s="3">
-        <v>60000076</v>
+        <v>60000074</v>
       </c>
       <c r="E238" s="3">
         <v>1</v>
@@ -9832,7 +9840,7 @@
         <v>100</v>
       </c>
       <c r="G238" s="13">
-        <v>10014019</v>
+        <v>10014017</v>
       </c>
       <c r="H238" s="3">
         <v>1</v>
@@ -9847,15 +9855,15 @@
         <v>0</v>
       </c>
       <c r="M238" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
     </row>
     <row r="239" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C239" s="3">
-        <v>60000076</v>
+        <v>60000074</v>
       </c>
       <c r="D239" s="3">
-        <v>60000077</v>
+        <v>60000075</v>
       </c>
       <c r="E239" s="3">
         <v>1</v>
@@ -9864,7 +9872,7 @@
         <v>100</v>
       </c>
       <c r="G239" s="13">
-        <v>10014020</v>
+        <v>10014018</v>
       </c>
       <c r="H239" s="3">
         <v>1</v>
@@ -9873,21 +9881,21 @@
         <v>10010031</v>
       </c>
       <c r="J239" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K239" s="2">
         <v>0</v>
       </c>
       <c r="M239" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="240" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C240" s="3">
-        <v>60000077</v>
+        <v>60000075</v>
       </c>
       <c r="D240" s="3">
-        <v>60000078</v>
+        <v>60000076</v>
       </c>
       <c r="E240" s="3">
         <v>1</v>
@@ -9896,7 +9904,7 @@
         <v>100</v>
       </c>
       <c r="G240" s="13">
-        <v>10014021</v>
+        <v>10014019</v>
       </c>
       <c r="H240" s="3">
         <v>1</v>
@@ -9905,21 +9913,21 @@
         <v>10010031</v>
       </c>
       <c r="J240" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K240" s="2">
         <v>0</v>
       </c>
       <c r="M240" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="241" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C241" s="3">
-        <v>60000078</v>
+        <v>60000076</v>
       </c>
       <c r="D241" s="3">
-        <v>60000079</v>
+        <v>60000077</v>
       </c>
       <c r="E241" s="3">
         <v>1</v>
@@ -9928,7 +9936,7 @@
         <v>100</v>
       </c>
       <c r="G241" s="13">
-        <v>10014022</v>
+        <v>10014020</v>
       </c>
       <c r="H241" s="3">
         <v>1</v>
@@ -9943,15 +9951,15 @@
         <v>0</v>
       </c>
       <c r="M241" s="3" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="242" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C242" s="3">
-        <v>60000079</v>
+        <v>60000077</v>
       </c>
       <c r="D242" s="3">
-        <v>60000080</v>
+        <v>60000078</v>
       </c>
       <c r="E242" s="3">
         <v>1</v>
@@ -9960,7 +9968,7 @@
         <v>100</v>
       </c>
       <c r="G242" s="13">
-        <v>10014023</v>
+        <v>10014021</v>
       </c>
       <c r="H242" s="3">
         <v>1</v>
@@ -9975,15 +9983,15 @@
         <v>0</v>
       </c>
       <c r="M242" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="243" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C243" s="3">
-        <v>60000080</v>
+        <v>60000078</v>
       </c>
       <c r="D243" s="3">
-        <v>60000081</v>
+        <v>60000079</v>
       </c>
       <c r="E243" s="3">
         <v>1</v>
@@ -9992,7 +10000,7 @@
         <v>100</v>
       </c>
       <c r="G243" s="13">
-        <v>10014024</v>
+        <v>10014022</v>
       </c>
       <c r="H243" s="3">
         <v>1</v>
@@ -10007,15 +10015,15 @@
         <v>0</v>
       </c>
       <c r="M243" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="244" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C244" s="3">
-        <v>60000081</v>
+        <v>60000079</v>
       </c>
       <c r="D244" s="3">
-        <v>60000082</v>
+        <v>60000080</v>
       </c>
       <c r="E244" s="3">
         <v>1</v>
@@ -10024,7 +10032,7 @@
         <v>100</v>
       </c>
       <c r="G244" s="13">
-        <v>10014025</v>
+        <v>10014023</v>
       </c>
       <c r="H244" s="3">
         <v>1</v>
@@ -10039,15 +10047,15 @@
         <v>0</v>
       </c>
       <c r="M244" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="245" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C245" s="3">
-        <v>60000082</v>
+        <v>60000080</v>
       </c>
       <c r="D245" s="3">
-        <v>60000083</v>
+        <v>60000081</v>
       </c>
       <c r="E245" s="3">
         <v>1</v>
@@ -10056,7 +10064,7 @@
         <v>100</v>
       </c>
       <c r="G245" s="13">
-        <v>10014026</v>
+        <v>10014024</v>
       </c>
       <c r="H245" s="3">
         <v>1</v>
@@ -10071,15 +10079,15 @@
         <v>0</v>
       </c>
       <c r="M245" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="246" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C246" s="3">
-        <v>60000083</v>
+        <v>60000081</v>
       </c>
       <c r="D246" s="3">
-        <v>0</v>
+        <v>60000082</v>
       </c>
       <c r="E246" s="3">
         <v>1</v>
@@ -10088,7 +10096,7 @@
         <v>100</v>
       </c>
       <c r="G246" s="13">
-        <v>10014027</v>
+        <v>10014025</v>
       </c>
       <c r="H246" s="3">
         <v>1</v>
@@ -10103,15 +10111,15 @@
         <v>0</v>
       </c>
       <c r="M246" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
     </row>
     <row r="247" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C247" s="3">
-        <v>70000001</v>
+        <v>60000082</v>
       </c>
       <c r="D247" s="3">
-        <v>70000002</v>
+        <v>60000083</v>
       </c>
       <c r="E247" s="3">
         <v>1</v>
@@ -10119,31 +10127,31 @@
       <c r="F247" s="3">
         <v>100</v>
       </c>
-      <c r="G247" s="9">
-        <v>10010093</v>
+      <c r="G247" s="13">
+        <v>10014026</v>
       </c>
       <c r="H247" s="3">
         <v>1</v>
       </c>
-      <c r="I247" s="8">
-        <v>10000159</v>
-      </c>
-      <c r="J247" s="8">
+      <c r="I247" s="3">
+        <v>10010031</v>
+      </c>
+      <c r="J247" s="3">
         <v>30</v>
       </c>
       <c r="K247" s="2">
         <v>0</v>
       </c>
-      <c r="M247" s="12" t="s">
-        <v>49</v>
+      <c r="M247" s="3" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="248" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C248" s="3">
-        <v>70000002</v>
+        <v>60000083</v>
       </c>
       <c r="D248" s="3">
-        <v>70000003</v>
+        <v>0</v>
       </c>
       <c r="E248" s="3">
         <v>1</v>
@@ -10151,31 +10159,31 @@
       <c r="F248" s="3">
         <v>100</v>
       </c>
-      <c r="G248" s="9">
-        <v>10000162</v>
+      <c r="G248" s="13">
+        <v>10014027</v>
       </c>
       <c r="H248" s="3">
         <v>1</v>
       </c>
-      <c r="I248" s="8">
-        <v>10000159</v>
-      </c>
-      <c r="J248" s="8">
-        <v>20</v>
+      <c r="I248" s="3">
+        <v>10010031</v>
+      </c>
+      <c r="J248" s="3">
+        <v>30</v>
       </c>
       <c r="K248" s="2">
         <v>0</v>
       </c>
-      <c r="M248" s="11" t="s">
-        <v>104</v>
+      <c r="M248" s="3" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="249" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C249" s="3">
-        <v>70000003</v>
+        <v>70000001</v>
       </c>
       <c r="D249" s="3">
-        <v>70000004</v>
+        <v>70000002</v>
       </c>
       <c r="E249" s="3">
         <v>1</v>
@@ -10184,7 +10192,7 @@
         <v>100</v>
       </c>
       <c r="G249" s="9">
-        <v>10010045</v>
+        <v>10010093</v>
       </c>
       <c r="H249" s="3">
         <v>1</v>
@@ -10198,16 +10206,16 @@
       <c r="K249" s="2">
         <v>0</v>
       </c>
-      <c r="M249" s="11" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="250" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M249" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="250" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C250" s="3">
-        <v>70000004</v>
+        <v>70000002</v>
       </c>
       <c r="D250" s="3">
-        <v>70000005</v>
+        <v>70000003</v>
       </c>
       <c r="E250" s="3">
         <v>1</v>
@@ -10216,7 +10224,7 @@
         <v>100</v>
       </c>
       <c r="G250" s="9">
-        <v>10000158</v>
+        <v>10000162</v>
       </c>
       <c r="H250" s="3">
         <v>1</v>
@@ -10230,16 +10238,16 @@
       <c r="K250" s="2">
         <v>0</v>
       </c>
-      <c r="M250" s="9" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="251" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M250" s="11" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="251" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C251" s="3">
-        <v>70000005</v>
+        <v>70000003</v>
       </c>
       <c r="D251" s="3">
-        <v>70000006</v>
+        <v>70000004</v>
       </c>
       <c r="E251" s="3">
         <v>1</v>
@@ -10248,7 +10256,7 @@
         <v>100</v>
       </c>
       <c r="G251" s="9">
-        <v>10010083</v>
+        <v>10010045</v>
       </c>
       <c r="H251" s="3">
         <v>1</v>
@@ -10257,21 +10265,21 @@
         <v>10000159</v>
       </c>
       <c r="J251" s="8">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="K251" s="2">
         <v>0</v>
       </c>
-      <c r="M251" s="16" t="s">
-        <v>107</v>
+      <c r="M251" s="11" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="252" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C252" s="3">
-        <v>70000006</v>
+        <v>70000004</v>
       </c>
       <c r="D252" s="3">
-        <v>70000007</v>
+        <v>70000005</v>
       </c>
       <c r="E252" s="3">
         <v>1</v>
@@ -10280,7 +10288,7 @@
         <v>100</v>
       </c>
       <c r="G252" s="9">
-        <v>10000143</v>
+        <v>10000158</v>
       </c>
       <c r="H252" s="3">
         <v>1</v>
@@ -10289,21 +10297,21 @@
         <v>10000159</v>
       </c>
       <c r="J252" s="8">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K252" s="2">
         <v>0</v>
       </c>
-      <c r="M252" s="16" t="s">
-        <v>47</v>
+      <c r="M252" s="9" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="253" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C253" s="3">
-        <v>70000007</v>
+        <v>70000005</v>
       </c>
       <c r="D253" s="3">
-        <v>70000008</v>
+        <v>70000006</v>
       </c>
       <c r="E253" s="3">
         <v>1</v>
@@ -10312,7 +10320,7 @@
         <v>100</v>
       </c>
       <c r="G253" s="9">
-        <v>10000152</v>
+        <v>10010083</v>
       </c>
       <c r="H253" s="3">
         <v>1</v>
@@ -10321,21 +10329,21 @@
         <v>10000159</v>
       </c>
       <c r="J253" s="8">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K253" s="2">
         <v>0</v>
       </c>
-      <c r="M253" s="11" t="s">
-        <v>38</v>
+      <c r="M253" s="16" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="254" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C254" s="3">
-        <v>70000008</v>
+        <v>70000006</v>
       </c>
       <c r="D254" s="3">
-        <v>70000009</v>
+        <v>70000007</v>
       </c>
       <c r="E254" s="3">
         <v>1</v>
@@ -10344,7 +10352,7 @@
         <v>100</v>
       </c>
       <c r="G254" s="9">
-        <v>10000157</v>
+        <v>10000143</v>
       </c>
       <c r="H254" s="3">
         <v>1</v>
@@ -10353,21 +10361,21 @@
         <v>10000159</v>
       </c>
       <c r="J254" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K254" s="2">
         <v>0</v>
       </c>
-      <c r="M254" s="11" t="s">
-        <v>39</v>
+      <c r="M254" s="16" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="255" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C255" s="3">
-        <v>70000009</v>
+        <v>70000007</v>
       </c>
       <c r="D255" s="3">
-        <v>70000010</v>
+        <v>70000008</v>
       </c>
       <c r="E255" s="3">
         <v>1</v>
@@ -10376,7 +10384,7 @@
         <v>100</v>
       </c>
       <c r="G255" s="9">
-        <v>10010029</v>
+        <v>10000152</v>
       </c>
       <c r="H255" s="3">
         <v>1</v>
@@ -10385,21 +10393,21 @@
         <v>10000159</v>
       </c>
       <c r="J255" s="8">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K255" s="2">
         <v>0</v>
       </c>
       <c r="M255" s="11" t="s">
-        <v>108</v>
+        <v>38</v>
       </c>
     </row>
     <row r="256" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C256" s="3">
-        <v>70000010</v>
+        <v>70000008</v>
       </c>
       <c r="D256" s="3">
-        <v>70000011</v>
+        <v>70000009</v>
       </c>
       <c r="E256" s="3">
         <v>1</v>
@@ -10408,7 +10416,7 @@
         <v>100</v>
       </c>
       <c r="G256" s="9">
-        <v>10010086</v>
+        <v>10000157</v>
       </c>
       <c r="H256" s="3">
         <v>1</v>
@@ -10422,16 +10430,16 @@
       <c r="K256" s="2">
         <v>0</v>
       </c>
-      <c r="M256" s="12" t="s">
-        <v>27</v>
+      <c r="M256" s="11" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="257" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C257" s="3">
-        <v>70000011</v>
+        <v>70000009</v>
       </c>
       <c r="D257" s="3">
-        <v>70000012</v>
+        <v>70000010</v>
       </c>
       <c r="E257" s="3">
         <v>1</v>
@@ -10439,8 +10447,8 @@
       <c r="F257" s="3">
         <v>100</v>
       </c>
-      <c r="G257" s="18">
-        <v>10010101</v>
+      <c r="G257" s="9">
+        <v>10010029</v>
       </c>
       <c r="H257" s="3">
         <v>1</v>
@@ -10454,16 +10462,16 @@
       <c r="K257" s="2">
         <v>0</v>
       </c>
-      <c r="M257" s="8" t="s">
-        <v>109</v>
+      <c r="M257" s="11" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="258" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C258" s="3">
-        <v>70000012</v>
+        <v>70000010</v>
       </c>
       <c r="D258" s="3">
-        <v>70000013</v>
+        <v>70000011</v>
       </c>
       <c r="E258" s="3">
         <v>1</v>
@@ -10471,8 +10479,8 @@
       <c r="F258" s="3">
         <v>100</v>
       </c>
-      <c r="G258" s="18">
-        <v>10010102</v>
+      <c r="G258" s="9">
+        <v>10010086</v>
       </c>
       <c r="H258" s="3">
         <v>1</v>
@@ -10486,16 +10494,16 @@
       <c r="K258" s="2">
         <v>0</v>
       </c>
-      <c r="M258" s="3" t="s">
-        <v>110</v>
+      <c r="M258" s="12" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="259" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C259" s="3">
-        <v>70000013</v>
+        <v>70000011</v>
       </c>
       <c r="D259" s="3">
-        <v>0</v>
+        <v>70000012</v>
       </c>
       <c r="E259" s="3">
         <v>1</v>
@@ -10504,7 +10512,7 @@
         <v>100</v>
       </c>
       <c r="G259" s="18">
-        <v>10010103</v>
+        <v>10010101</v>
       </c>
       <c r="H259" s="3">
         <v>1</v>
@@ -10513,21 +10521,21 @@
         <v>10000159</v>
       </c>
       <c r="J259" s="8">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="K259" s="2">
         <v>0</v>
       </c>
-      <c r="M259" s="3" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="260" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M259" s="8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="260" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C260" s="3">
-        <v>80000001</v>
+        <v>70000012</v>
       </c>
       <c r="D260" s="3">
-        <v>80000002</v>
+        <v>70000013</v>
       </c>
       <c r="E260" s="3">
         <v>1</v>
@@ -10535,31 +10543,31 @@
       <c r="F260" s="3">
         <v>100</v>
       </c>
-      <c r="G260" s="9">
-        <v>10010083</v>
+      <c r="G260" s="18">
+        <v>10010102</v>
       </c>
       <c r="H260" s="3">
         <v>1</v>
       </c>
       <c r="I260" s="8">
-        <v>10000163</v>
+        <v>10000159</v>
       </c>
       <c r="J260" s="8">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K260" s="2">
         <v>0</v>
       </c>
       <c r="M260" s="3" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="261" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="261" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C261" s="3">
-        <v>80000002</v>
+        <v>70000013</v>
       </c>
       <c r="D261" s="3">
-        <v>80000003</v>
+        <v>0</v>
       </c>
       <c r="E261" s="3">
         <v>1</v>
@@ -10567,14 +10575,14 @@
       <c r="F261" s="3">
         <v>100</v>
       </c>
-      <c r="G261" s="9">
-        <v>10010086</v>
+      <c r="G261" s="18">
+        <v>10010103</v>
       </c>
       <c r="H261" s="3">
         <v>1</v>
       </c>
       <c r="I261" s="8">
-        <v>10000163</v>
+        <v>10000159</v>
       </c>
       <c r="J261" s="8">
         <v>20</v>
@@ -10583,15 +10591,15 @@
         <v>0</v>
       </c>
       <c r="M261" s="3" t="s">
-        <v>27</v>
+        <v>111</v>
       </c>
     </row>
     <row r="262" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C262" s="3">
-        <v>80000003</v>
+        <v>80000001</v>
       </c>
       <c r="D262" s="3">
-        <v>80000004</v>
+        <v>80000002</v>
       </c>
       <c r="E262" s="3">
         <v>1</v>
@@ -10600,7 +10608,7 @@
         <v>100</v>
       </c>
       <c r="G262" s="9">
-        <v>10010096</v>
+        <v>10010083</v>
       </c>
       <c r="H262" s="3">
         <v>1</v>
@@ -10609,21 +10617,21 @@
         <v>10000163</v>
       </c>
       <c r="J262" s="8">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="K262" s="2">
         <v>0</v>
       </c>
       <c r="M262" s="3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="263" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="263" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C263" s="3">
-        <v>80000004</v>
+        <v>80000002</v>
       </c>
       <c r="D263" s="3">
-        <v>80000005</v>
+        <v>80000003</v>
       </c>
       <c r="E263" s="3">
         <v>1</v>
@@ -10632,7 +10640,7 @@
         <v>100</v>
       </c>
       <c r="G263" s="9">
-        <v>10000139</v>
+        <v>10010086</v>
       </c>
       <c r="H263" s="3">
         <v>1</v>
@@ -10647,15 +10655,15 @@
         <v>0</v>
       </c>
       <c r="M263" s="3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="264" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="264" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C264" s="3">
-        <v>80000005</v>
+        <v>80000003</v>
       </c>
       <c r="D264" s="3">
-        <v>80000006</v>
+        <v>80000004</v>
       </c>
       <c r="E264" s="3">
         <v>1</v>
@@ -10664,7 +10672,7 @@
         <v>100</v>
       </c>
       <c r="G264" s="9">
-        <v>10000143</v>
+        <v>10010096</v>
       </c>
       <c r="H264" s="3">
         <v>1</v>
@@ -10673,21 +10681,21 @@
         <v>10000163</v>
       </c>
       <c r="J264" s="8">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="K264" s="2">
         <v>0</v>
       </c>
       <c r="M264" s="3" t="s">
-        <v>47</v>
+        <v>112</v>
       </c>
     </row>
     <row r="265" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C265" s="3">
-        <v>80000006</v>
+        <v>80000004</v>
       </c>
       <c r="D265" s="3">
-        <v>80000007</v>
+        <v>80000005</v>
       </c>
       <c r="E265" s="3">
         <v>1</v>
@@ -10696,7 +10704,7 @@
         <v>100</v>
       </c>
       <c r="G265" s="9">
-        <v>10000152</v>
+        <v>10000139</v>
       </c>
       <c r="H265" s="3">
         <v>1</v>
@@ -10705,21 +10713,21 @@
         <v>10000163</v>
       </c>
       <c r="J265" s="8">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="K265" s="2">
         <v>0</v>
       </c>
       <c r="M265" s="3" t="s">
-        <v>38</v>
+        <v>113</v>
       </c>
     </row>
     <row r="266" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C266" s="3">
-        <v>80000007</v>
+        <v>80000005</v>
       </c>
       <c r="D266" s="3">
-        <v>80000008</v>
+        <v>80000006</v>
       </c>
       <c r="E266" s="3">
         <v>1</v>
@@ -10728,7 +10736,7 @@
         <v>100</v>
       </c>
       <c r="G266" s="9">
-        <v>10000155</v>
+        <v>10000143</v>
       </c>
       <c r="H266" s="3">
         <v>1</v>
@@ -10737,21 +10745,21 @@
         <v>10000163</v>
       </c>
       <c r="J266" s="8">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K266" s="2">
         <v>0</v>
       </c>
       <c r="M266" s="3" t="s">
-        <v>114</v>
+        <v>47</v>
       </c>
     </row>
     <row r="267" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C267" s="3">
-        <v>80000008</v>
+        <v>80000006</v>
       </c>
       <c r="D267" s="3">
-        <v>80000009</v>
+        <v>80000007</v>
       </c>
       <c r="E267" s="3">
         <v>1</v>
@@ -10760,7 +10768,7 @@
         <v>100</v>
       </c>
       <c r="G267" s="9">
-        <v>10000158</v>
+        <v>10000152</v>
       </c>
       <c r="H267" s="3">
         <v>1</v>
@@ -10769,21 +10777,21 @@
         <v>10000163</v>
       </c>
       <c r="J267" s="8">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="K267" s="2">
         <v>0</v>
       </c>
       <c r="M267" s="3" t="s">
-        <v>106</v>
+        <v>38</v>
       </c>
     </row>
     <row r="268" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C268" s="3">
-        <v>80000009</v>
+        <v>80000007</v>
       </c>
       <c r="D268" s="3">
-        <v>0</v>
+        <v>80000008</v>
       </c>
       <c r="E268" s="3">
         <v>1</v>
@@ -10792,7 +10800,7 @@
         <v>100</v>
       </c>
       <c r="G268" s="9">
-        <v>10010093</v>
+        <v>10000155</v>
       </c>
       <c r="H268" s="3">
         <v>1</v>
@@ -10801,87 +10809,85 @@
         <v>10000163</v>
       </c>
       <c r="J268" s="8">
-        <v>35</v>
+        <v>5</v>
       </c>
       <c r="K268" s="2">
         <v>0</v>
       </c>
       <c r="M268" s="3" t="s">
-        <v>49</v>
+        <v>114</v>
       </c>
     </row>
     <row r="269" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C269" s="3">
-        <v>90000001</v>
+        <v>80000008</v>
       </c>
       <c r="D269" s="3">
-        <v>90000002</v>
-      </c>
-      <c r="E269" s="2">
+        <v>80000009</v>
+      </c>
+      <c r="E269" s="3">
         <v>1</v>
       </c>
       <c r="F269" s="3">
         <v>100</v>
       </c>
-      <c r="G269" s="3">
-        <v>10010093</v>
+      <c r="G269" s="9">
+        <v>10000158</v>
       </c>
       <c r="H269" s="3">
         <v>1</v>
       </c>
       <c r="I269" s="8">
-        <v>10000184</v>
+        <v>10000163</v>
       </c>
       <c r="J269" s="8">
-        <v>60</v>
+        <v>20</v>
       </c>
       <c r="K269" s="2">
         <v>0</v>
       </c>
-      <c r="L269" s="2"/>
-      <c r="M269" s="12" t="s">
-        <v>49</v>
+      <c r="M269" s="3" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="270" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C270" s="3">
-        <v>90000002</v>
+        <v>80000009</v>
       </c>
       <c r="D270" s="3">
-        <v>90000003</v>
-      </c>
-      <c r="E270" s="2">
+        <v>0</v>
+      </c>
+      <c r="E270" s="3">
         <v>1</v>
       </c>
       <c r="F270" s="3">
         <v>100</v>
       </c>
-      <c r="G270" s="3">
-        <v>10010083</v>
+      <c r="G270" s="9">
+        <v>10010093</v>
       </c>
       <c r="H270" s="3">
         <v>1</v>
       </c>
       <c r="I270" s="8">
-        <v>10000184</v>
+        <v>10000163</v>
       </c>
       <c r="J270" s="8">
-        <v>2</v>
+        <v>35</v>
       </c>
       <c r="K270" s="2">
         <v>0</v>
       </c>
-      <c r="L270" s="2"/>
-      <c r="M270" s="16" t="s">
-        <v>107</v>
+      <c r="M270" s="3" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="271" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C271" s="3">
-        <v>90000003</v>
+        <v>90000001</v>
       </c>
       <c r="D271" s="3">
-        <v>90000004</v>
+        <v>90000002</v>
       </c>
       <c r="E271" s="2">
         <v>1</v>
@@ -10890,7 +10896,7 @@
         <v>100</v>
       </c>
       <c r="G271" s="3">
-        <v>10010086</v>
+        <v>10010093</v>
       </c>
       <c r="H271" s="3">
         <v>1</v>
@@ -10899,22 +10905,22 @@
         <v>10000184</v>
       </c>
       <c r="J271" s="8">
-        <v>25</v>
+        <v>60</v>
       </c>
       <c r="K271" s="2">
         <v>0</v>
       </c>
       <c r="L271" s="2"/>
       <c r="M271" s="12" t="s">
-        <v>27</v>
+        <v>49</v>
       </c>
     </row>
     <row r="272" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C272" s="3">
-        <v>90000004</v>
+        <v>90000002</v>
       </c>
       <c r="D272" s="3">
-        <v>90000005</v>
+        <v>90000003</v>
       </c>
       <c r="E272" s="2">
         <v>1</v>
@@ -10923,7 +10929,7 @@
         <v>100</v>
       </c>
       <c r="G272" s="3">
-        <v>10000143</v>
+        <v>10010083</v>
       </c>
       <c r="H272" s="3">
         <v>1</v>
@@ -10932,22 +10938,22 @@
         <v>10000184</v>
       </c>
       <c r="J272" s="8">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="K272" s="2">
         <v>0</v>
       </c>
       <c r="L272" s="2"/>
-      <c r="M272" s="11" t="s">
-        <v>47</v>
+      <c r="M272" s="16" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="273" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C273" s="3">
-        <v>90000005</v>
+        <v>90000003</v>
       </c>
       <c r="D273" s="3">
-        <v>90000006</v>
+        <v>90000004</v>
       </c>
       <c r="E273" s="2">
         <v>1</v>
@@ -10956,7 +10962,7 @@
         <v>100</v>
       </c>
       <c r="G273" s="3">
-        <v>10000152</v>
+        <v>10010086</v>
       </c>
       <c r="H273" s="3">
         <v>1</v>
@@ -10965,22 +10971,22 @@
         <v>10000184</v>
       </c>
       <c r="J273" s="8">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="K273" s="2">
         <v>0</v>
       </c>
       <c r="L273" s="2"/>
-      <c r="M273" s="11" t="s">
-        <v>38</v>
+      <c r="M273" s="12" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="274" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C274" s="3">
-        <v>90000006</v>
+        <v>90000004</v>
       </c>
       <c r="D274" s="3">
-        <v>90000007</v>
+        <v>90000005</v>
       </c>
       <c r="E274" s="2">
         <v>1</v>
@@ -10989,7 +10995,7 @@
         <v>100</v>
       </c>
       <c r="G274" s="3">
-        <v>10000165</v>
+        <v>10000143</v>
       </c>
       <c r="H274" s="3">
         <v>1</v>
@@ -10998,22 +11004,22 @@
         <v>10000184</v>
       </c>
       <c r="J274" s="8">
-        <v>100</v>
+        <v>30</v>
       </c>
       <c r="K274" s="2">
         <v>0</v>
       </c>
       <c r="L274" s="2"/>
       <c r="M274" s="11" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="275" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C275" s="3">
-        <v>90000007</v>
+        <v>90000005</v>
       </c>
       <c r="D275" s="3">
-        <v>0</v>
+        <v>90000006</v>
       </c>
       <c r="E275" s="2">
         <v>1</v>
@@ -11022,7 +11028,7 @@
         <v>100</v>
       </c>
       <c r="G275" s="3">
-        <v>10010045</v>
+        <v>10000152</v>
       </c>
       <c r="H275" s="3">
         <v>1</v>
@@ -11031,22 +11037,22 @@
         <v>10000184</v>
       </c>
       <c r="J275" s="8">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="K275" s="2">
         <v>0</v>
       </c>
       <c r="L275" s="2"/>
       <c r="M275" s="11" t="s">
-        <v>105</v>
+        <v>38</v>
       </c>
     </row>
     <row r="276" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C276" s="3">
-        <v>91000001</v>
+        <v>90000006</v>
       </c>
       <c r="D276" s="3">
-        <v>91000002</v>
+        <v>90000007</v>
       </c>
       <c r="E276" s="2">
         <v>1</v>
@@ -11055,30 +11061,31 @@
         <v>100</v>
       </c>
       <c r="G276" s="3">
-        <v>10010086</v>
+        <v>10000165</v>
       </c>
       <c r="H276" s="3">
         <v>1</v>
       </c>
-      <c r="I276" s="19">
-        <v>36</v>
-      </c>
-      <c r="J276" s="20">
-        <v>8</v>
+      <c r="I276" s="8">
+        <v>10000184</v>
+      </c>
+      <c r="J276" s="8">
+        <v>100</v>
       </c>
       <c r="K276" s="2">
         <v>0</v>
       </c>
-      <c r="M276" s="3" t="s">
-        <v>27</v>
+      <c r="L276" s="2"/>
+      <c r="M276" s="11" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="277" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C277" s="3">
-        <v>91000002</v>
+        <v>90000007</v>
       </c>
       <c r="D277" s="3">
-        <v>91000003</v>
+        <v>0</v>
       </c>
       <c r="E277" s="2">
         <v>1</v>
@@ -11087,30 +11094,31 @@
         <v>100</v>
       </c>
       <c r="G277" s="3">
-        <v>10010096</v>
+        <v>10010045</v>
       </c>
       <c r="H277" s="3">
         <v>1</v>
       </c>
-      <c r="I277" s="19">
-        <v>36</v>
-      </c>
-      <c r="J277" s="20">
-        <v>20</v>
+      <c r="I277" s="8">
+        <v>10000184</v>
+      </c>
+      <c r="J277" s="8">
+        <v>45</v>
       </c>
       <c r="K277" s="2">
         <v>0</v>
       </c>
-      <c r="M277" s="3" t="s">
-        <v>112</v>
+      <c r="L277" s="2"/>
+      <c r="M277" s="11" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="278" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C278" s="3">
-        <v>91000003</v>
+        <v>91000001</v>
       </c>
       <c r="D278" s="3">
-        <v>91000004</v>
+        <v>91000002</v>
       </c>
       <c r="E278" s="2">
         <v>1</v>
@@ -11119,7 +11127,7 @@
         <v>100</v>
       </c>
       <c r="G278" s="3">
-        <v>10010074</v>
+        <v>10010086</v>
       </c>
       <c r="H278" s="3">
         <v>1</v>
@@ -11134,15 +11142,15 @@
         <v>0</v>
       </c>
       <c r="M278" s="3" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
     </row>
     <row r="279" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C279" s="3">
-        <v>91000004</v>
+        <v>91000002</v>
       </c>
       <c r="D279" s="3">
-        <v>91000005</v>
+        <v>91000003</v>
       </c>
       <c r="E279" s="2">
         <v>1</v>
@@ -11151,7 +11159,7 @@
         <v>100</v>
       </c>
       <c r="G279" s="3">
-        <v>10010075</v>
+        <v>10010096</v>
       </c>
       <c r="H279" s="3">
         <v>1</v>
@@ -11166,15 +11174,15 @@
         <v>0</v>
       </c>
       <c r="M279" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="280" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C280" s="3">
-        <v>91000005</v>
+        <v>91000003</v>
       </c>
       <c r="D280" s="3">
-        <v>91000006</v>
+        <v>91000004</v>
       </c>
       <c r="E280" s="2">
         <v>1</v>
@@ -11182,8 +11190,8 @@
       <c r="F280" s="3">
         <v>100</v>
       </c>
-      <c r="G280" s="2">
-        <v>10010083</v>
+      <c r="G280" s="3">
+        <v>10010074</v>
       </c>
       <c r="H280" s="3">
         <v>1</v>
@@ -11192,21 +11200,21 @@
         <v>36</v>
       </c>
       <c r="J280" s="20">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K280" s="2">
         <v>0</v>
       </c>
-      <c r="M280" s="15" t="s">
-        <v>118</v>
+      <c r="M280" s="3" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="281" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C281" s="3">
-        <v>91000006</v>
+        <v>91000004</v>
       </c>
       <c r="D281" s="3">
-        <v>91000007</v>
+        <v>91000005</v>
       </c>
       <c r="E281" s="2">
         <v>1</v>
@@ -11214,8 +11222,8 @@
       <c r="F281" s="3">
         <v>100</v>
       </c>
-      <c r="G281" s="2">
-        <v>10010098</v>
+      <c r="G281" s="3">
+        <v>10010075</v>
       </c>
       <c r="H281" s="3">
         <v>1</v>
@@ -11224,21 +11232,21 @@
         <v>36</v>
       </c>
       <c r="J281" s="20">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K281" s="2">
         <v>0</v>
       </c>
-      <c r="M281" s="15" t="s">
-        <v>117</v>
+      <c r="M281" s="3" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="282" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C282" s="3">
-        <v>91000007</v>
+        <v>91000005</v>
       </c>
       <c r="D282" s="3">
-        <v>0</v>
+        <v>91000006</v>
       </c>
       <c r="E282" s="2">
         <v>1</v>
@@ -11246,8 +11254,8 @@
       <c r="F282" s="3">
         <v>100</v>
       </c>
-      <c r="G282" s="9">
-        <v>10010040</v>
+      <c r="G282" s="2">
+        <v>10010083</v>
       </c>
       <c r="H282" s="3">
         <v>1</v>
@@ -11256,21 +11264,21 @@
         <v>36</v>
       </c>
       <c r="J282" s="20">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="K282" s="2">
-        <v>1</v>
-      </c>
-      <c r="M282" s="9" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="283" spans="3:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="M282" s="15" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="283" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C283" s="3">
-        <v>92000001</v>
+        <v>91000006</v>
       </c>
       <c r="D283" s="3">
-        <v>92000002</v>
+        <v>91000007</v>
       </c>
       <c r="E283" s="2">
         <v>1</v>
@@ -11278,65 +11286,64 @@
       <c r="F283" s="3">
         <v>100</v>
       </c>
-      <c r="G283" s="3">
-        <v>10060100</v>
+      <c r="G283" s="2">
+        <v>10010098</v>
       </c>
       <c r="H283" s="3">
         <v>1</v>
       </c>
-      <c r="I283" s="9">
-        <v>10000136</v>
-      </c>
-      <c r="J283" s="3">
-        <v>50</v>
+      <c r="I283" s="19">
+        <v>36</v>
+      </c>
+      <c r="J283" s="20">
+        <v>1</v>
       </c>
       <c r="K283" s="2">
         <v>0</v>
       </c>
-      <c r="M283" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q283" s="7"/>
+      <c r="M283" s="15" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="284" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C284" s="3">
+        <v>91000007</v>
+      </c>
+      <c r="D284" s="3">
+        <v>0</v>
+      </c>
+      <c r="E284" s="2">
+        <v>1</v>
+      </c>
+      <c r="F284" s="3">
+        <v>100</v>
+      </c>
+      <c r="G284" s="9">
+        <v>10010040</v>
+      </c>
+      <c r="H284" s="3">
+        <v>1</v>
+      </c>
+      <c r="I284" s="19">
+        <v>36</v>
+      </c>
+      <c r="J284" s="20">
+        <v>100</v>
+      </c>
+      <c r="K284" s="2">
+        <v>1</v>
+      </c>
+      <c r="M284" s="9" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="285" spans="3:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C285" s="3">
+        <v>92000001</v>
+      </c>
+      <c r="D285" s="3">
         <v>92000002</v>
       </c>
-      <c r="D284" s="3">
-        <v>92000003</v>
-      </c>
-      <c r="E284" s="2">
-        <v>1</v>
-      </c>
-      <c r="F284" s="3">
-        <v>100</v>
-      </c>
-      <c r="G284" s="3">
-        <v>10060200</v>
-      </c>
-      <c r="H284" s="3">
-        <v>1</v>
-      </c>
-      <c r="I284" s="9">
-        <v>10000136</v>
-      </c>
-      <c r="J284" s="3">
-        <v>50</v>
-      </c>
-      <c r="K284" s="2">
-        <v>0</v>
-      </c>
-      <c r="M284" s="22" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="285" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C285" s="3">
-        <v>92000003</v>
-      </c>
-      <c r="D285" s="3">
-        <v>92000004</v>
-      </c>
       <c r="E285" s="2">
         <v>1</v>
       </c>
@@ -11344,7 +11351,7 @@
         <v>100</v>
       </c>
       <c r="G285" s="3">
-        <v>10060300</v>
+        <v>10060100</v>
       </c>
       <c r="H285" s="3">
         <v>1</v>
@@ -11359,15 +11366,16 @@
         <v>0</v>
       </c>
       <c r="M285" s="22" t="s">
-        <v>125</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="Q285" s="7"/>
     </row>
     <row r="286" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C286" s="3">
-        <v>92000004</v>
+        <v>92000002</v>
       </c>
       <c r="D286" s="3">
-        <v>92000005</v>
+        <v>92000003</v>
       </c>
       <c r="E286" s="2">
         <v>1</v>
@@ -11376,7 +11384,7 @@
         <v>100</v>
       </c>
       <c r="G286" s="3">
-        <v>10060400</v>
+        <v>10060200</v>
       </c>
       <c r="H286" s="3">
         <v>1</v>
@@ -11391,15 +11399,15 @@
         <v>0</v>
       </c>
       <c r="M286" s="22" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="287" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C287" s="3">
-        <v>92000005</v>
+        <v>92000003</v>
       </c>
       <c r="D287" s="3">
-        <v>92000006</v>
+        <v>92000004</v>
       </c>
       <c r="E287" s="2">
         <v>1</v>
@@ -11408,7 +11416,7 @@
         <v>100</v>
       </c>
       <c r="G287" s="3">
-        <v>10060500</v>
+        <v>10060300</v>
       </c>
       <c r="H287" s="3">
         <v>1</v>
@@ -11423,15 +11431,15 @@
         <v>0</v>
       </c>
       <c r="M287" s="22" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="288" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C288" s="3">
-        <v>92000006</v>
+        <v>92000004</v>
       </c>
       <c r="D288" s="3">
-        <v>92000007</v>
+        <v>92000005</v>
       </c>
       <c r="E288" s="2">
         <v>1</v>
@@ -11440,7 +11448,7 @@
         <v>100</v>
       </c>
       <c r="G288" s="3">
-        <v>10060600</v>
+        <v>10060400</v>
       </c>
       <c r="H288" s="3">
         <v>1</v>
@@ -11455,15 +11463,15 @@
         <v>0</v>
       </c>
       <c r="M288" s="22" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="289" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C289" s="3">
-        <v>92000007</v>
+        <v>92000005</v>
       </c>
       <c r="D289" s="3">
-        <v>92000008</v>
+        <v>92000006</v>
       </c>
       <c r="E289" s="2">
         <v>1</v>
@@ -11472,7 +11480,7 @@
         <v>100</v>
       </c>
       <c r="G289" s="3">
-        <v>10060700</v>
+        <v>10060500</v>
       </c>
       <c r="H289" s="3">
         <v>1</v>
@@ -11487,15 +11495,15 @@
         <v>0</v>
       </c>
       <c r="M289" s="22" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="290" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C290" s="3">
-        <v>92000008</v>
+        <v>92000006</v>
       </c>
       <c r="D290" s="3">
-        <v>0</v>
+        <v>92000007</v>
       </c>
       <c r="E290" s="2">
         <v>1</v>
@@ -11504,7 +11512,7 @@
         <v>100</v>
       </c>
       <c r="G290" s="3">
-        <v>10000212</v>
+        <v>10060600</v>
       </c>
       <c r="H290" s="3">
         <v>1</v>
@@ -11513,18 +11521,82 @@
         <v>10000136</v>
       </c>
       <c r="J290" s="3">
-        <v>150</v>
+        <v>50</v>
       </c>
       <c r="K290" s="2">
         <v>0</v>
       </c>
-      <c r="M290" s="19" t="s">
+      <c r="M290" s="22" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="291" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C291" s="3">
+        <v>92000007</v>
+      </c>
+      <c r="D291" s="3">
+        <v>92000008</v>
+      </c>
+      <c r="E291" s="2">
+        <v>1</v>
+      </c>
+      <c r="F291" s="3">
+        <v>100</v>
+      </c>
+      <c r="G291" s="3">
+        <v>10060700</v>
+      </c>
+      <c r="H291" s="3">
+        <v>1</v>
+      </c>
+      <c r="I291" s="9">
+        <v>10000136</v>
+      </c>
+      <c r="J291" s="3">
+        <v>50</v>
+      </c>
+      <c r="K291" s="2">
+        <v>0</v>
+      </c>
+      <c r="M291" s="22" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="292" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C292" s="3">
+        <v>92000008</v>
+      </c>
+      <c r="D292" s="3">
+        <v>0</v>
+      </c>
+      <c r="E292" s="2">
+        <v>1</v>
+      </c>
+      <c r="F292" s="3">
+        <v>100</v>
+      </c>
+      <c r="G292" s="3">
+        <v>10000212</v>
+      </c>
+      <c r="H292" s="3">
+        <v>1</v>
+      </c>
+      <c r="I292" s="9">
+        <v>10000136</v>
+      </c>
+      <c r="J292" s="3">
+        <v>100</v>
+      </c>
+      <c r="K292" s="2">
+        <v>0</v>
+      </c>
+      <c r="M292" s="19" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="291" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="293" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="294" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="295" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StoreSellConfig.xlsx
+++ b/Excel/StoreSellConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9B8FF29C-8AEC-4A57-A949-84A161BBEE32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F57CA517-8E95-4D4A-B18B-31694B85C432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StoreSellProto" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="206" uniqueCount="165">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="166">
   <si>
     <t>Id</t>
   </si>
@@ -639,6 +639,10 @@
   </si>
   <si>
     <t>羚羊坐骑</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>无字之碑</t>
     <phoneticPr fontId="15" type="noConversion"/>
   </si>
 </sst>
@@ -1938,7 +1942,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2002,6 +2006,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2647,7 +2657,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q295"/>
+  <dimension ref="A1:Q296"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="5" width="14" customWidth="1"/>
@@ -7115,7 +7125,7 @@
         <v>1</v>
       </c>
       <c r="I153" s="9">
-        <v>10000167</v>
+        <v>10000151</v>
       </c>
       <c r="J153" s="3">
         <v>60</v>
@@ -7132,7 +7142,7 @@
         <v>50000020</v>
       </c>
       <c r="D154" s="3">
-        <v>0</v>
+        <v>50000021</v>
       </c>
       <c r="E154" s="2">
         <v>1</v>
@@ -7147,7 +7157,7 @@
         <v>1</v>
       </c>
       <c r="I154" s="9">
-        <v>10000167</v>
+        <v>10000151</v>
       </c>
       <c r="J154" s="3">
         <v>60</v>
@@ -7161,10 +7171,10 @@
     </row>
     <row r="155" spans="3:13" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C155" s="3">
-        <v>51000001</v>
+        <v>50000021</v>
       </c>
       <c r="D155" s="3">
-        <v>51000002</v>
+        <v>0</v>
       </c>
       <c r="E155" s="2">
         <v>1</v>
@@ -7172,32 +7182,32 @@
       <c r="F155" s="3">
         <v>100</v>
       </c>
-      <c r="G155" s="3">
-        <v>10010094</v>
-      </c>
-      <c r="H155" s="3">
+      <c r="G155" s="23">
+        <v>10010036</v>
+      </c>
+      <c r="H155" s="2">
         <v>1</v>
       </c>
       <c r="I155" s="9">
-        <v>10000167</v>
+        <v>10000151</v>
       </c>
       <c r="J155" s="3">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K155" s="2">
         <v>0</v>
       </c>
-      <c r="M155" s="12" t="s">
-        <v>30</v>
+      <c r="M155" s="24" t="s">
+        <v>165</v>
       </c>
     </row>
     <row r="156" spans="3:13" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C156" s="3">
+        <v>51000001</v>
+      </c>
+      <c r="D156" s="3">
         <v>51000002</v>
       </c>
-      <c r="D156" s="3">
-        <v>51000003</v>
-      </c>
       <c r="E156" s="2">
         <v>1</v>
       </c>
@@ -7205,31 +7215,31 @@
         <v>100</v>
       </c>
       <c r="G156" s="3">
-        <v>10000105</v>
-      </c>
-      <c r="H156" s="2">
+        <v>10010094</v>
+      </c>
+      <c r="H156" s="3">
         <v>1</v>
       </c>
       <c r="I156" s="9">
         <v>10000167</v>
       </c>
       <c r="J156" s="3">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K156" s="2">
         <v>0</v>
       </c>
-      <c r="M156" s="15" t="s">
-        <v>33</v>
+      <c r="M156" s="12" t="s">
+        <v>30</v>
       </c>
     </row>
     <row r="157" spans="3:13" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C157" s="3">
+        <v>51000002</v>
+      </c>
+      <c r="D157" s="3">
         <v>51000003</v>
       </c>
-      <c r="D157" s="3">
-        <v>51000004</v>
-      </c>
       <c r="E157" s="2">
         <v>1</v>
       </c>
@@ -7237,7 +7247,7 @@
         <v>100</v>
       </c>
       <c r="G157" s="3">
-        <v>10010026</v>
+        <v>10000105</v>
       </c>
       <c r="H157" s="2">
         <v>1</v>
@@ -7252,16 +7262,16 @@
         <v>0</v>
       </c>
       <c r="M157" s="15" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="158" spans="3:13" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C158" s="3">
+        <v>51000003</v>
+      </c>
+      <c r="D158" s="3">
         <v>51000004</v>
       </c>
-      <c r="D158" s="3">
-        <v>51000005</v>
-      </c>
       <c r="E158" s="2">
         <v>1</v>
       </c>
@@ -7269,7 +7279,7 @@
         <v>100</v>
       </c>
       <c r="G158" s="3">
-        <v>10000152</v>
+        <v>10010026</v>
       </c>
       <c r="H158" s="2">
         <v>1</v>
@@ -7278,22 +7288,22 @@
         <v>10000167</v>
       </c>
       <c r="J158" s="3">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="K158" s="2">
         <v>0</v>
       </c>
       <c r="M158" s="15" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="159" spans="3:13" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C159" s="3">
+        <v>51000004</v>
+      </c>
+      <c r="D159" s="3">
         <v>51000005</v>
       </c>
-      <c r="D159" s="3">
-        <v>51000006</v>
-      </c>
       <c r="E159" s="2">
         <v>1</v>
       </c>
@@ -7301,7 +7311,7 @@
         <v>100</v>
       </c>
       <c r="G159" s="3">
-        <v>10000157</v>
+        <v>10000152</v>
       </c>
       <c r="H159" s="2">
         <v>1</v>
@@ -7316,16 +7326,16 @@
         <v>0</v>
       </c>
       <c r="M159" s="15" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="160" spans="3:13" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C160" s="3">
+        <v>51000005</v>
+      </c>
+      <c r="D160" s="3">
         <v>51000006</v>
       </c>
-      <c r="D160" s="3">
-        <v>51000007</v>
-      </c>
       <c r="E160" s="2">
         <v>1</v>
       </c>
@@ -7333,7 +7343,7 @@
         <v>100</v>
       </c>
       <c r="G160" s="3">
-        <v>10000150</v>
+        <v>10000157</v>
       </c>
       <c r="H160" s="2">
         <v>1</v>
@@ -7342,22 +7352,22 @@
         <v>10000167</v>
       </c>
       <c r="J160" s="3">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K160" s="2">
         <v>0</v>
       </c>
       <c r="M160" s="15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="161" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C161" s="3">
+        <v>51000006</v>
+      </c>
+      <c r="D161" s="3">
         <v>51000007</v>
       </c>
-      <c r="D161" s="3">
-        <v>51000008</v>
-      </c>
       <c r="E161" s="2">
         <v>1</v>
       </c>
@@ -7365,7 +7375,7 @@
         <v>100</v>
       </c>
       <c r="G161" s="3">
-        <v>10010078</v>
+        <v>10000150</v>
       </c>
       <c r="H161" s="2">
         <v>1</v>
@@ -7374,22 +7384,22 @@
         <v>10000167</v>
       </c>
       <c r="J161" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K161" s="2">
         <v>0</v>
       </c>
-      <c r="M161" s="12" t="s">
-        <v>41</v>
+      <c r="M161" s="15" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="162" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C162" s="3">
+        <v>51000007</v>
+      </c>
+      <c r="D162" s="3">
         <v>51000008</v>
       </c>
-      <c r="D162" s="3">
-        <v>51000009</v>
-      </c>
       <c r="E162" s="2">
         <v>1</v>
       </c>
@@ -7397,7 +7407,7 @@
         <v>100</v>
       </c>
       <c r="G162" s="3">
-        <v>10010079</v>
+        <v>10010078</v>
       </c>
       <c r="H162" s="2">
         <v>1</v>
@@ -7411,25 +7421,25 @@
       <c r="K162" s="2">
         <v>0</v>
       </c>
-      <c r="M162" s="16" t="s">
-        <v>42</v>
+      <c r="M162" s="12" t="s">
+        <v>41</v>
       </c>
     </row>
     <row r="163" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C163" s="3">
+        <v>51000008</v>
+      </c>
+      <c r="D163" s="3">
         <v>51000009</v>
       </c>
-      <c r="D163" s="3">
-        <v>51000010</v>
-      </c>
       <c r="E163" s="2">
         <v>1</v>
       </c>
       <c r="F163" s="3">
         <v>100</v>
       </c>
-      <c r="G163" s="9">
-        <v>10000165</v>
+      <c r="G163" s="3">
+        <v>10010079</v>
       </c>
       <c r="H163" s="2">
         <v>1</v>
@@ -7438,22 +7448,22 @@
         <v>10000167</v>
       </c>
       <c r="J163" s="3">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="K163" s="2">
         <v>0</v>
       </c>
-      <c r="M163" s="11" t="s">
-        <v>45</v>
+      <c r="M163" s="16" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="164" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C164" s="3">
+        <v>51000009</v>
+      </c>
+      <c r="D164" s="3">
         <v>51000010</v>
       </c>
-      <c r="D164" s="3">
-        <v>51000011</v>
-      </c>
       <c r="E164" s="2">
         <v>1</v>
       </c>
@@ -7461,7 +7471,7 @@
         <v>100</v>
       </c>
       <c r="G164" s="9">
-        <v>10000183</v>
+        <v>10000165</v>
       </c>
       <c r="H164" s="2">
         <v>1</v>
@@ -7470,22 +7480,22 @@
         <v>10000167</v>
       </c>
       <c r="J164" s="3">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="K164" s="2">
         <v>0</v>
       </c>
       <c r="M164" s="11" t="s">
-        <v>132</v>
+        <v>45</v>
       </c>
     </row>
     <row r="165" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C165" s="3">
+        <v>51000010</v>
+      </c>
+      <c r="D165" s="3">
         <v>51000011</v>
       </c>
-      <c r="D165" s="3">
-        <v>0</v>
-      </c>
       <c r="E165" s="2">
         <v>1</v>
       </c>
@@ -7493,7 +7503,7 @@
         <v>100</v>
       </c>
       <c r="G165" s="9">
-        <v>10010060</v>
+        <v>10000183</v>
       </c>
       <c r="H165" s="2">
         <v>1</v>
@@ -7502,61 +7512,56 @@
         <v>10000167</v>
       </c>
       <c r="J165" s="3">
+        <v>5</v>
+      </c>
+      <c r="K165" s="2">
+        <v>0</v>
+      </c>
+      <c r="M165" s="11" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="166" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C166" s="3">
+        <v>51000011</v>
+      </c>
+      <c r="D166" s="3">
+        <v>0</v>
+      </c>
+      <c r="E166" s="2">
+        <v>1</v>
+      </c>
+      <c r="F166" s="3">
+        <v>100</v>
+      </c>
+      <c r="G166" s="9">
+        <v>10010060</v>
+      </c>
+      <c r="H166" s="2">
+        <v>1</v>
+      </c>
+      <c r="I166" s="9">
+        <v>10000167</v>
+      </c>
+      <c r="J166" s="3">
         <v>8</v>
       </c>
-      <c r="K165" s="2">
-        <v>0</v>
-      </c>
-      <c r="M165" s="11" t="s">
+      <c r="K166" s="2">
+        <v>0</v>
+      </c>
+      <c r="M166" s="11" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="166" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A166" s="3"/>
-      <c r="B166" s="3"/>
-      <c r="C166" s="3">
-        <v>60000001</v>
-      </c>
-      <c r="D166" s="3">
-        <v>60000002</v>
-      </c>
-      <c r="E166" s="3">
-        <v>1</v>
-      </c>
-      <c r="F166" s="3">
-        <v>100</v>
-      </c>
-      <c r="G166" s="3">
-        <v>10000143</v>
-      </c>
-      <c r="H166" s="11" t="s">
-        <v>46</v>
-      </c>
-      <c r="I166" s="9">
-        <v>10000157</v>
-      </c>
-      <c r="J166" s="3">
-        <v>1</v>
-      </c>
-      <c r="K166" s="2">
-        <v>0</v>
-      </c>
-      <c r="L166" s="3"/>
-      <c r="M166" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="N166" s="3"/>
-      <c r="P166" s="3"/>
     </row>
     <row r="167" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A167" s="3"/>
       <c r="B167" s="3"/>
       <c r="C167" s="3">
+        <v>60000001</v>
+      </c>
+      <c r="D167" s="3">
         <v>60000002</v>
       </c>
-      <c r="D167" s="3">
-        <v>60000003</v>
-      </c>
       <c r="E167" s="3">
         <v>1</v>
       </c>
@@ -7564,67 +7569,71 @@
         <v>100</v>
       </c>
       <c r="G167" s="3">
-        <v>10010093</v>
-      </c>
-      <c r="H167" s="12">
-        <v>1</v>
+        <v>10000143</v>
+      </c>
+      <c r="H167" s="11" t="s">
+        <v>46</v>
       </c>
       <c r="I167" s="9">
-        <v>10000143</v>
-      </c>
-      <c r="J167" s="11" t="s">
-        <v>48</v>
+        <v>10000157</v>
+      </c>
+      <c r="J167" s="3">
+        <v>1</v>
       </c>
       <c r="K167" s="2">
         <v>0</v>
       </c>
       <c r="L167" s="3"/>
-      <c r="M167" s="12" t="s">
-        <v>49</v>
+      <c r="M167" s="15" t="s">
+        <v>47</v>
       </c>
       <c r="N167" s="3"/>
       <c r="P167" s="3"/>
     </row>
-    <row r="168" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="168" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A168" s="3"/>
+      <c r="B168" s="3"/>
       <c r="C168" s="3">
+        <v>60000002</v>
+      </c>
+      <c r="D168" s="3">
         <v>60000003</v>
       </c>
-      <c r="D168" s="3">
-        <v>60000004</v>
-      </c>
       <c r="E168" s="3">
         <v>1</v>
       </c>
       <c r="F168" s="3">
         <v>100</v>
       </c>
-      <c r="G168" s="13">
-        <v>10012001</v>
-      </c>
-      <c r="H168" s="3">
-        <v>1</v>
-      </c>
-      <c r="I168" s="3">
-        <v>10010029</v>
-      </c>
-      <c r="J168" s="3">
-        <v>10</v>
+      <c r="G168" s="3">
+        <v>10010093</v>
+      </c>
+      <c r="H168" s="12">
+        <v>1</v>
+      </c>
+      <c r="I168" s="9">
+        <v>10000143</v>
+      </c>
+      <c r="J168" s="11" t="s">
+        <v>48</v>
       </c>
       <c r="K168" s="2">
         <v>0</v>
       </c>
-      <c r="M168" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="O168" s="2"/>
+      <c r="L168" s="3"/>
+      <c r="M168" s="12" t="s">
+        <v>49</v>
+      </c>
+      <c r="N168" s="3"/>
+      <c r="P168" s="3"/>
     </row>
     <row r="169" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C169" s="3">
+        <v>60000003</v>
+      </c>
+      <c r="D169" s="3">
         <v>60000004</v>
       </c>
-      <c r="D169" s="3">
-        <v>60000005</v>
-      </c>
       <c r="E169" s="3">
         <v>1</v>
       </c>
@@ -7632,7 +7641,7 @@
         <v>100</v>
       </c>
       <c r="G169" s="13">
-        <v>10012002</v>
+        <v>10012001</v>
       </c>
       <c r="H169" s="3">
         <v>1</v>
@@ -7647,16 +7656,17 @@
         <v>0</v>
       </c>
       <c r="M169" s="13" t="s">
-        <v>51</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="O169" s="2"/>
     </row>
     <row r="170" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C170" s="3">
+        <v>60000004</v>
+      </c>
+      <c r="D170" s="3">
         <v>60000005</v>
       </c>
-      <c r="D170" s="3">
-        <v>60000006</v>
-      </c>
       <c r="E170" s="3">
         <v>1</v>
       </c>
@@ -7664,7 +7674,7 @@
         <v>100</v>
       </c>
       <c r="G170" s="13">
-        <v>10012003</v>
+        <v>10012002</v>
       </c>
       <c r="H170" s="3">
         <v>1</v>
@@ -7679,16 +7689,16 @@
         <v>0</v>
       </c>
       <c r="M170" s="13" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="171" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C171" s="3">
+        <v>60000005</v>
+      </c>
+      <c r="D171" s="3">
         <v>60000006</v>
       </c>
-      <c r="D171" s="3">
-        <v>60000007</v>
-      </c>
       <c r="E171" s="3">
         <v>1</v>
       </c>
@@ -7696,7 +7706,7 @@
         <v>100</v>
       </c>
       <c r="G171" s="13">
-        <v>10012004</v>
+        <v>10012003</v>
       </c>
       <c r="H171" s="3">
         <v>1</v>
@@ -7711,16 +7721,16 @@
         <v>0</v>
       </c>
       <c r="M171" s="13" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="172" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C172" s="3">
+        <v>60000006</v>
+      </c>
+      <c r="D172" s="3">
         <v>60000007</v>
       </c>
-      <c r="D172" s="3">
-        <v>60000008</v>
-      </c>
       <c r="E172" s="3">
         <v>1</v>
       </c>
@@ -7728,7 +7738,7 @@
         <v>100</v>
       </c>
       <c r="G172" s="13">
-        <v>10012005</v>
+        <v>10012004</v>
       </c>
       <c r="H172" s="3">
         <v>1</v>
@@ -7743,16 +7753,16 @@
         <v>0</v>
       </c>
       <c r="M172" s="13" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="173" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C173" s="3">
+        <v>60000007</v>
+      </c>
+      <c r="D173" s="3">
         <v>60000008</v>
       </c>
-      <c r="D173" s="3">
-        <v>60000009</v>
-      </c>
       <c r="E173" s="3">
         <v>1</v>
       </c>
@@ -7760,7 +7770,7 @@
         <v>100</v>
       </c>
       <c r="G173" s="13">
-        <v>10012006</v>
+        <v>10012005</v>
       </c>
       <c r="H173" s="3">
         <v>1</v>
@@ -7775,16 +7785,16 @@
         <v>0</v>
       </c>
       <c r="M173" s="13" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
     </row>
     <row r="174" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C174" s="3">
+        <v>60000008</v>
+      </c>
+      <c r="D174" s="3">
         <v>60000009</v>
       </c>
-      <c r="D174" s="3">
-        <v>60000010</v>
-      </c>
       <c r="E174" s="3">
         <v>1</v>
       </c>
@@ -7792,7 +7802,7 @@
         <v>100</v>
       </c>
       <c r="G174" s="13">
-        <v>10012007</v>
+        <v>10012006</v>
       </c>
       <c r="H174" s="3">
         <v>1</v>
@@ -7807,16 +7817,16 @@
         <v>0</v>
       </c>
       <c r="M174" s="13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="175" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C175" s="3">
+        <v>60000009</v>
+      </c>
+      <c r="D175" s="3">
         <v>60000010</v>
       </c>
-      <c r="D175" s="3">
-        <v>60000011</v>
-      </c>
       <c r="E175" s="3">
         <v>1</v>
       </c>
@@ -7824,7 +7834,7 @@
         <v>100</v>
       </c>
       <c r="G175" s="13">
-        <v>10012008</v>
+        <v>10012007</v>
       </c>
       <c r="H175" s="3">
         <v>1</v>
@@ -7839,16 +7849,16 @@
         <v>0</v>
       </c>
       <c r="M175" s="13" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="176" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C176" s="3">
+        <v>60000010</v>
+      </c>
+      <c r="D176" s="3">
         <v>60000011</v>
       </c>
-      <c r="D176" s="3">
-        <v>60000012</v>
-      </c>
       <c r="E176" s="3">
         <v>1</v>
       </c>
@@ -7856,7 +7866,7 @@
         <v>100</v>
       </c>
       <c r="G176" s="13">
-        <v>10012009</v>
+        <v>10012008</v>
       </c>
       <c r="H176" s="3">
         <v>1</v>
@@ -7871,16 +7881,16 @@
         <v>0</v>
       </c>
       <c r="M176" s="13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="177" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C177" s="3">
+        <v>60000011</v>
+      </c>
+      <c r="D177" s="3">
         <v>60000012</v>
       </c>
-      <c r="D177" s="3">
-        <v>60000013</v>
-      </c>
       <c r="E177" s="3">
         <v>1</v>
       </c>
@@ -7888,7 +7898,7 @@
         <v>100</v>
       </c>
       <c r="G177" s="13">
-        <v>10012010</v>
+        <v>10012009</v>
       </c>
       <c r="H177" s="3">
         <v>1</v>
@@ -7903,16 +7913,16 @@
         <v>0</v>
       </c>
       <c r="M177" s="13" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="178" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C178" s="3">
+        <v>60000012</v>
+      </c>
+      <c r="D178" s="3">
         <v>60000013</v>
       </c>
-      <c r="D178" s="3">
-        <v>60000014</v>
-      </c>
       <c r="E178" s="3">
         <v>1</v>
       </c>
@@ -7920,7 +7930,7 @@
         <v>100</v>
       </c>
       <c r="G178" s="13">
-        <v>10012011</v>
+        <v>10012010</v>
       </c>
       <c r="H178" s="3">
         <v>1</v>
@@ -7935,16 +7945,16 @@
         <v>0</v>
       </c>
       <c r="M178" s="13" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="179" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C179" s="3">
+        <v>60000013</v>
+      </c>
+      <c r="D179" s="3">
         <v>60000014</v>
       </c>
-      <c r="D179" s="3">
-        <v>60000015</v>
-      </c>
       <c r="E179" s="3">
         <v>1</v>
       </c>
@@ -7952,7 +7962,7 @@
         <v>100</v>
       </c>
       <c r="G179" s="13">
-        <v>10012012</v>
+        <v>10012011</v>
       </c>
       <c r="H179" s="3">
         <v>1</v>
@@ -7967,16 +7977,16 @@
         <v>0</v>
       </c>
       <c r="M179" s="13" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="180" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C180" s="3">
+        <v>60000014</v>
+      </c>
+      <c r="D180" s="3">
         <v>60000015</v>
       </c>
-      <c r="D180" s="3">
-        <v>60000016</v>
-      </c>
       <c r="E180" s="3">
         <v>1</v>
       </c>
@@ -7984,7 +7994,7 @@
         <v>100</v>
       </c>
       <c r="G180" s="13">
-        <v>10012013</v>
+        <v>10012012</v>
       </c>
       <c r="H180" s="3">
         <v>1</v>
@@ -7999,16 +8009,16 @@
         <v>0</v>
       </c>
       <c r="M180" s="13" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="181" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C181" s="3">
+        <v>60000015</v>
+      </c>
+      <c r="D181" s="3">
         <v>60000016</v>
       </c>
-      <c r="D181" s="3">
-        <v>60000017</v>
-      </c>
       <c r="E181" s="3">
         <v>1</v>
       </c>
@@ -8016,7 +8026,7 @@
         <v>100</v>
       </c>
       <c r="G181" s="13">
-        <v>10012014</v>
+        <v>10012013</v>
       </c>
       <c r="H181" s="3">
         <v>1</v>
@@ -8031,16 +8041,16 @@
         <v>0</v>
       </c>
       <c r="M181" s="13" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="182" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C182" s="3">
+        <v>60000016</v>
+      </c>
+      <c r="D182" s="3">
         <v>60000017</v>
       </c>
-      <c r="D182" s="3">
-        <v>60000018</v>
-      </c>
       <c r="E182" s="3">
         <v>1</v>
       </c>
@@ -8048,7 +8058,7 @@
         <v>100</v>
       </c>
       <c r="G182" s="13">
-        <v>10012015</v>
+        <v>10012014</v>
       </c>
       <c r="H182" s="3">
         <v>1</v>
@@ -8063,16 +8073,16 @@
         <v>0</v>
       </c>
       <c r="M182" s="13" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="183" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C183" s="3">
+        <v>60000017</v>
+      </c>
+      <c r="D183" s="3">
         <v>60000018</v>
       </c>
-      <c r="D183" s="3">
-        <v>60000019</v>
-      </c>
       <c r="E183" s="3">
         <v>1</v>
       </c>
@@ -8080,7 +8090,7 @@
         <v>100</v>
       </c>
       <c r="G183" s="13">
-        <v>10012016</v>
+        <v>10012015</v>
       </c>
       <c r="H183" s="3">
         <v>1</v>
@@ -8095,16 +8105,16 @@
         <v>0</v>
       </c>
       <c r="M183" s="13" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="184" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C184" s="3">
+        <v>60000018</v>
+      </c>
+      <c r="D184" s="3">
         <v>60000019</v>
       </c>
-      <c r="D184" s="3">
-        <v>60000020</v>
-      </c>
       <c r="E184" s="3">
         <v>1</v>
       </c>
@@ -8112,7 +8122,7 @@
         <v>100</v>
       </c>
       <c r="G184" s="13">
-        <v>10012017</v>
+        <v>10012016</v>
       </c>
       <c r="H184" s="3">
         <v>1</v>
@@ -8127,16 +8137,16 @@
         <v>0</v>
       </c>
       <c r="M184" s="13" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="185" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C185" s="3">
+        <v>60000019</v>
+      </c>
+      <c r="D185" s="3">
         <v>60000020</v>
       </c>
-      <c r="D185" s="3">
-        <v>60000021</v>
-      </c>
       <c r="E185" s="3">
         <v>1</v>
       </c>
@@ -8144,7 +8154,7 @@
         <v>100</v>
       </c>
       <c r="G185" s="13">
-        <v>10012018</v>
+        <v>10012017</v>
       </c>
       <c r="H185" s="3">
         <v>1</v>
@@ -8159,16 +8169,16 @@
         <v>0</v>
       </c>
       <c r="M185" s="13" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="186" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C186" s="3">
+        <v>60000020</v>
+      </c>
+      <c r="D186" s="3">
         <v>60000021</v>
       </c>
-      <c r="D186" s="3">
-        <v>60000022</v>
-      </c>
       <c r="E186" s="3">
         <v>1</v>
       </c>
@@ -8176,7 +8186,7 @@
         <v>100</v>
       </c>
       <c r="G186" s="13">
-        <v>10012019</v>
+        <v>10012018</v>
       </c>
       <c r="H186" s="3">
         <v>1</v>
@@ -8191,16 +8201,16 @@
         <v>0</v>
       </c>
       <c r="M186" s="13" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="187" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C187" s="3">
+        <v>60000021</v>
+      </c>
+      <c r="D187" s="3">
         <v>60000022</v>
       </c>
-      <c r="D187" s="3">
-        <v>60000023</v>
-      </c>
       <c r="E187" s="3">
         <v>1</v>
       </c>
@@ -8208,7 +8218,7 @@
         <v>100</v>
       </c>
       <c r="G187" s="13">
-        <v>10012020</v>
+        <v>10012019</v>
       </c>
       <c r="H187" s="3">
         <v>1</v>
@@ -8217,22 +8227,22 @@
         <v>10010029</v>
       </c>
       <c r="J187" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K187" s="2">
         <v>0</v>
       </c>
       <c r="M187" s="13" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="188" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C188" s="3">
+        <v>60000022</v>
+      </c>
+      <c r="D188" s="3">
         <v>60000023</v>
       </c>
-      <c r="D188" s="3">
-        <v>60000024</v>
-      </c>
       <c r="E188" s="3">
         <v>1</v>
       </c>
@@ -8240,7 +8250,7 @@
         <v>100</v>
       </c>
       <c r="G188" s="13">
-        <v>10012021</v>
+        <v>10012020</v>
       </c>
       <c r="H188" s="3">
         <v>1</v>
@@ -8255,16 +8265,16 @@
         <v>0</v>
       </c>
       <c r="M188" s="13" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="189" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C189" s="3">
+        <v>60000023</v>
+      </c>
+      <c r="D189" s="3">
         <v>60000024</v>
       </c>
-      <c r="D189" s="3">
-        <v>60000025</v>
-      </c>
       <c r="E189" s="3">
         <v>1</v>
       </c>
@@ -8272,7 +8282,7 @@
         <v>100</v>
       </c>
       <c r="G189" s="13">
-        <v>10012022</v>
+        <v>10012021</v>
       </c>
       <c r="H189" s="3">
         <v>1</v>
@@ -8287,16 +8297,16 @@
         <v>0</v>
       </c>
       <c r="M189" s="13" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="190" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C190" s="3">
+        <v>60000024</v>
+      </c>
+      <c r="D190" s="3">
         <v>60000025</v>
       </c>
-      <c r="D190" s="3">
-        <v>60000026</v>
-      </c>
       <c r="E190" s="3">
         <v>1</v>
       </c>
@@ -8304,7 +8314,7 @@
         <v>100</v>
       </c>
       <c r="G190" s="13">
-        <v>10012023</v>
+        <v>10012022</v>
       </c>
       <c r="H190" s="3">
         <v>1</v>
@@ -8319,16 +8329,16 @@
         <v>0</v>
       </c>
       <c r="M190" s="13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="191" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C191" s="3">
+        <v>60000025</v>
+      </c>
+      <c r="D191" s="3">
         <v>60000026</v>
       </c>
-      <c r="D191" s="3">
-        <v>60000027</v>
-      </c>
       <c r="E191" s="3">
         <v>1</v>
       </c>
@@ -8336,7 +8346,7 @@
         <v>100</v>
       </c>
       <c r="G191" s="13">
-        <v>10012024</v>
+        <v>10012023</v>
       </c>
       <c r="H191" s="3">
         <v>1</v>
@@ -8351,16 +8361,16 @@
         <v>0</v>
       </c>
       <c r="M191" s="13" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="192" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C192" s="3">
+        <v>60000026</v>
+      </c>
+      <c r="D192" s="3">
         <v>60000027</v>
       </c>
-      <c r="D192" s="3">
-        <v>60000028</v>
-      </c>
       <c r="E192" s="3">
         <v>1</v>
       </c>
@@ -8368,7 +8378,7 @@
         <v>100</v>
       </c>
       <c r="G192" s="13">
-        <v>10012025</v>
+        <v>10012024</v>
       </c>
       <c r="H192" s="3">
         <v>1</v>
@@ -8383,16 +8393,16 @@
         <v>0</v>
       </c>
       <c r="M192" s="13" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="193" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C193" s="3">
+        <v>60000027</v>
+      </c>
+      <c r="D193" s="3">
         <v>60000028</v>
       </c>
-      <c r="D193" s="3">
-        <v>60000029</v>
-      </c>
       <c r="E193" s="3">
         <v>1</v>
       </c>
@@ -8400,7 +8410,7 @@
         <v>100</v>
       </c>
       <c r="G193" s="13">
-        <v>10012026</v>
+        <v>10012025</v>
       </c>
       <c r="H193" s="3">
         <v>1</v>
@@ -8415,16 +8425,16 @@
         <v>0</v>
       </c>
       <c r="M193" s="13" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="194" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C194" s="3">
+        <v>60000028</v>
+      </c>
+      <c r="D194" s="3">
         <v>60000029</v>
       </c>
-      <c r="D194" s="3">
-        <v>60000030</v>
-      </c>
       <c r="E194" s="3">
         <v>1</v>
       </c>
@@ -8432,7 +8442,7 @@
         <v>100</v>
       </c>
       <c r="G194" s="13">
-        <v>10012027</v>
+        <v>10012026</v>
       </c>
       <c r="H194" s="3">
         <v>1</v>
@@ -8447,16 +8457,16 @@
         <v>0</v>
       </c>
       <c r="M194" s="13" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="195" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C195" s="3">
+        <v>60000029</v>
+      </c>
+      <c r="D195" s="3">
         <v>60000030</v>
       </c>
-      <c r="D195" s="3">
-        <v>60000031</v>
-      </c>
       <c r="E195" s="3">
         <v>1</v>
       </c>
@@ -8464,13 +8474,13 @@
         <v>100</v>
       </c>
       <c r="G195" s="13">
-        <v>10013001</v>
+        <v>10012027</v>
       </c>
       <c r="H195" s="3">
         <v>1</v>
       </c>
       <c r="I195" s="3">
-        <v>10010030</v>
+        <v>10010029</v>
       </c>
       <c r="J195" s="3">
         <v>15</v>
@@ -8478,17 +8488,17 @@
       <c r="K195" s="2">
         <v>0</v>
       </c>
-      <c r="M195" s="17" t="s">
-        <v>77</v>
+      <c r="M195" s="13" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="196" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C196" s="3">
+        <v>60000030</v>
+      </c>
+      <c r="D196" s="3">
         <v>60000031</v>
       </c>
-      <c r="D196" s="3">
-        <v>60000032</v>
-      </c>
       <c r="E196" s="3">
         <v>1</v>
       </c>
@@ -8496,7 +8506,7 @@
         <v>100</v>
       </c>
       <c r="G196" s="13">
-        <v>10013002</v>
+        <v>10013001</v>
       </c>
       <c r="H196" s="3">
         <v>1</v>
@@ -8511,16 +8521,16 @@
         <v>0</v>
       </c>
       <c r="M196" s="17" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="197" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C197" s="3">
+        <v>60000031</v>
+      </c>
+      <c r="D197" s="3">
         <v>60000032</v>
       </c>
-      <c r="D197" s="3">
-        <v>60000033</v>
-      </c>
       <c r="E197" s="3">
         <v>1</v>
       </c>
@@ -8528,7 +8538,7 @@
         <v>100</v>
       </c>
       <c r="G197" s="13">
-        <v>10013003</v>
+        <v>10013002</v>
       </c>
       <c r="H197" s="3">
         <v>1</v>
@@ -8543,16 +8553,16 @@
         <v>0</v>
       </c>
       <c r="M197" s="17" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="198" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C198" s="3">
+        <v>60000032</v>
+      </c>
+      <c r="D198" s="3">
         <v>60000033</v>
       </c>
-      <c r="D198" s="3">
-        <v>60000034</v>
-      </c>
       <c r="E198" s="3">
         <v>1</v>
       </c>
@@ -8560,7 +8570,7 @@
         <v>100</v>
       </c>
       <c r="G198" s="13">
-        <v>10013004</v>
+        <v>10013003</v>
       </c>
       <c r="H198" s="3">
         <v>1</v>
@@ -8575,16 +8585,16 @@
         <v>0</v>
       </c>
       <c r="M198" s="17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="199" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C199" s="3">
+        <v>60000033</v>
+      </c>
+      <c r="D199" s="3">
         <v>60000034</v>
       </c>
-      <c r="D199" s="3">
-        <v>60000035</v>
-      </c>
       <c r="E199" s="3">
         <v>1</v>
       </c>
@@ -8592,7 +8602,7 @@
         <v>100</v>
       </c>
       <c r="G199" s="13">
-        <v>10013005</v>
+        <v>10013004</v>
       </c>
       <c r="H199" s="3">
         <v>1</v>
@@ -8607,16 +8617,16 @@
         <v>0</v>
       </c>
       <c r="M199" s="17" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="200" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C200" s="3">
+        <v>60000034</v>
+      </c>
+      <c r="D200" s="3">
         <v>60000035</v>
       </c>
-      <c r="D200" s="3">
-        <v>60000036</v>
-      </c>
       <c r="E200" s="3">
         <v>1</v>
       </c>
@@ -8624,7 +8634,7 @@
         <v>100</v>
       </c>
       <c r="G200" s="13">
-        <v>10013006</v>
+        <v>10013005</v>
       </c>
       <c r="H200" s="3">
         <v>1</v>
@@ -8639,16 +8649,16 @@
         <v>0</v>
       </c>
       <c r="M200" s="17" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="201" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C201" s="3">
+        <v>60000035</v>
+      </c>
+      <c r="D201" s="3">
         <v>60000036</v>
       </c>
-      <c r="D201" s="3">
-        <v>60000037</v>
-      </c>
       <c r="E201" s="3">
         <v>1</v>
       </c>
@@ -8656,7 +8666,7 @@
         <v>100</v>
       </c>
       <c r="G201" s="13">
-        <v>10013007</v>
+        <v>10013006</v>
       </c>
       <c r="H201" s="3">
         <v>1</v>
@@ -8671,16 +8681,16 @@
         <v>0</v>
       </c>
       <c r="M201" s="17" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="202" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C202" s="3">
+        <v>60000036</v>
+      </c>
+      <c r="D202" s="3">
         <v>60000037</v>
       </c>
-      <c r="D202" s="3">
-        <v>60000038</v>
-      </c>
       <c r="E202" s="3">
         <v>1</v>
       </c>
@@ -8688,7 +8698,7 @@
         <v>100</v>
       </c>
       <c r="G202" s="13">
-        <v>10013008</v>
+        <v>10013007</v>
       </c>
       <c r="H202" s="3">
         <v>1</v>
@@ -8703,16 +8713,16 @@
         <v>0</v>
       </c>
       <c r="M202" s="17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="203" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C203" s="3">
+        <v>60000037</v>
+      </c>
+      <c r="D203" s="3">
         <v>60000038</v>
       </c>
-      <c r="D203" s="3">
-        <v>60000039</v>
-      </c>
       <c r="E203" s="3">
         <v>1</v>
       </c>
@@ -8720,7 +8730,7 @@
         <v>100</v>
       </c>
       <c r="G203" s="13">
-        <v>10013009</v>
+        <v>10013008</v>
       </c>
       <c r="H203" s="3">
         <v>1</v>
@@ -8735,16 +8745,16 @@
         <v>0</v>
       </c>
       <c r="M203" s="17" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="204" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C204" s="3">
+        <v>60000038</v>
+      </c>
+      <c r="D204" s="3">
         <v>60000039</v>
       </c>
-      <c r="D204" s="3">
-        <v>60000040</v>
-      </c>
       <c r="E204" s="3">
         <v>1</v>
       </c>
@@ -8752,7 +8762,7 @@
         <v>100</v>
       </c>
       <c r="G204" s="13">
-        <v>10013010</v>
+        <v>10013009</v>
       </c>
       <c r="H204" s="3">
         <v>1</v>
@@ -8767,16 +8777,16 @@
         <v>0</v>
       </c>
       <c r="M204" s="17" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="205" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C205" s="3">
+        <v>60000039</v>
+      </c>
+      <c r="D205" s="3">
         <v>60000040</v>
       </c>
-      <c r="D205" s="3">
-        <v>60000041</v>
-      </c>
       <c r="E205" s="3">
         <v>1</v>
       </c>
@@ -8784,7 +8794,7 @@
         <v>100</v>
       </c>
       <c r="G205" s="13">
-        <v>10013011</v>
+        <v>10013010</v>
       </c>
       <c r="H205" s="3">
         <v>1</v>
@@ -8799,16 +8809,16 @@
         <v>0</v>
       </c>
       <c r="M205" s="17" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="206" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C206" s="3">
+        <v>60000040</v>
+      </c>
+      <c r="D206" s="3">
         <v>60000041</v>
       </c>
-      <c r="D206" s="3">
-        <v>60000042</v>
-      </c>
       <c r="E206" s="3">
         <v>1</v>
       </c>
@@ -8816,7 +8826,7 @@
         <v>100</v>
       </c>
       <c r="G206" s="13">
-        <v>10013012</v>
+        <v>10013011</v>
       </c>
       <c r="H206" s="3">
         <v>1</v>
@@ -8831,16 +8841,16 @@
         <v>0</v>
       </c>
       <c r="M206" s="17" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="207" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C207" s="3">
+        <v>60000041</v>
+      </c>
+      <c r="D207" s="3">
         <v>60000042</v>
       </c>
-      <c r="D207" s="3">
-        <v>60000043</v>
-      </c>
       <c r="E207" s="3">
         <v>1</v>
       </c>
@@ -8848,7 +8858,7 @@
         <v>100</v>
       </c>
       <c r="G207" s="13">
-        <v>10013013</v>
+        <v>10013012</v>
       </c>
       <c r="H207" s="3">
         <v>1</v>
@@ -8863,16 +8873,16 @@
         <v>0</v>
       </c>
       <c r="M207" s="17" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="208" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C208" s="3">
+        <v>60000042</v>
+      </c>
+      <c r="D208" s="3">
         <v>60000043</v>
       </c>
-      <c r="D208" s="3">
-        <v>60000044</v>
-      </c>
       <c r="E208" s="3">
         <v>1</v>
       </c>
@@ -8880,7 +8890,7 @@
         <v>100</v>
       </c>
       <c r="G208" s="13">
-        <v>10013014</v>
+        <v>10013013</v>
       </c>
       <c r="H208" s="3">
         <v>1</v>
@@ -8895,16 +8905,16 @@
         <v>0</v>
       </c>
       <c r="M208" s="17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="209" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C209" s="3">
+        <v>60000043</v>
+      </c>
+      <c r="D209" s="3">
         <v>60000044</v>
       </c>
-      <c r="D209" s="3">
-        <v>60000045</v>
-      </c>
       <c r="E209" s="3">
         <v>1</v>
       </c>
@@ -8912,7 +8922,7 @@
         <v>100</v>
       </c>
       <c r="G209" s="13">
-        <v>10013015</v>
+        <v>10013014</v>
       </c>
       <c r="H209" s="3">
         <v>1</v>
@@ -8927,16 +8937,16 @@
         <v>0</v>
       </c>
       <c r="M209" s="17" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="210" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C210" s="3">
+        <v>60000044</v>
+      </c>
+      <c r="D210" s="3">
         <v>60000045</v>
       </c>
-      <c r="D210" s="3">
-        <v>60000046</v>
-      </c>
       <c r="E210" s="3">
         <v>1</v>
       </c>
@@ -8944,7 +8954,7 @@
         <v>100</v>
       </c>
       <c r="G210" s="13">
-        <v>10013016</v>
+        <v>10013015</v>
       </c>
       <c r="H210" s="3">
         <v>1</v>
@@ -8959,16 +8969,16 @@
         <v>0</v>
       </c>
       <c r="M210" s="17" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="211" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C211" s="3">
+        <v>60000045</v>
+      </c>
+      <c r="D211" s="3">
         <v>60000046</v>
       </c>
-      <c r="D211" s="3">
-        <v>60000047</v>
-      </c>
       <c r="E211" s="3">
         <v>1</v>
       </c>
@@ -8976,7 +8986,7 @@
         <v>100</v>
       </c>
       <c r="G211" s="13">
-        <v>10013017</v>
+        <v>10013016</v>
       </c>
       <c r="H211" s="3">
         <v>1</v>
@@ -8991,16 +9001,16 @@
         <v>0</v>
       </c>
       <c r="M211" s="17" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="212" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C212" s="3">
+        <v>60000046</v>
+      </c>
+      <c r="D212" s="3">
         <v>60000047</v>
       </c>
-      <c r="D212" s="3">
-        <v>60000048</v>
-      </c>
       <c r="E212" s="3">
         <v>1</v>
       </c>
@@ -9008,7 +9018,7 @@
         <v>100</v>
       </c>
       <c r="G212" s="13">
-        <v>10013018</v>
+        <v>10013017</v>
       </c>
       <c r="H212" s="3">
         <v>1</v>
@@ -9023,16 +9033,16 @@
         <v>0</v>
       </c>
       <c r="M212" s="17" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="213" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C213" s="3">
+        <v>60000047</v>
+      </c>
+      <c r="D213" s="3">
         <v>60000048</v>
       </c>
-      <c r="D213" s="3">
-        <v>60000049</v>
-      </c>
       <c r="E213" s="3">
         <v>1</v>
       </c>
@@ -9040,7 +9050,7 @@
         <v>100</v>
       </c>
       <c r="G213" s="13">
-        <v>10013019</v>
+        <v>10013018</v>
       </c>
       <c r="H213" s="3">
         <v>1</v>
@@ -9055,16 +9065,16 @@
         <v>0</v>
       </c>
       <c r="M213" s="17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="214" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C214" s="3">
+        <v>60000048</v>
+      </c>
+      <c r="D214" s="3">
         <v>60000049</v>
       </c>
-      <c r="D214" s="3">
-        <v>60000050</v>
-      </c>
       <c r="E214" s="3">
         <v>1</v>
       </c>
@@ -9072,7 +9082,7 @@
         <v>100</v>
       </c>
       <c r="G214" s="13">
-        <v>10013020</v>
+        <v>10013019</v>
       </c>
       <c r="H214" s="3">
         <v>1</v>
@@ -9081,22 +9091,22 @@
         <v>10010030</v>
       </c>
       <c r="J214" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K214" s="2">
         <v>0</v>
       </c>
       <c r="M214" s="17" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="215" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C215" s="3">
+        <v>60000049</v>
+      </c>
+      <c r="D215" s="3">
         <v>60000050</v>
       </c>
-      <c r="D215" s="3">
-        <v>60000051</v>
-      </c>
       <c r="E215" s="3">
         <v>1</v>
       </c>
@@ -9104,7 +9114,7 @@
         <v>100</v>
       </c>
       <c r="G215" s="13">
-        <v>10013021</v>
+        <v>10013020</v>
       </c>
       <c r="H215" s="3">
         <v>1</v>
@@ -9119,16 +9129,16 @@
         <v>0</v>
       </c>
       <c r="M215" s="17" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="216" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C216" s="3">
+        <v>60000050</v>
+      </c>
+      <c r="D216" s="3">
         <v>60000051</v>
       </c>
-      <c r="D216" s="3">
-        <v>60000052</v>
-      </c>
       <c r="E216" s="3">
         <v>1</v>
       </c>
@@ -9136,7 +9146,7 @@
         <v>100</v>
       </c>
       <c r="G216" s="13">
-        <v>10013022</v>
+        <v>10013021</v>
       </c>
       <c r="H216" s="3">
         <v>1</v>
@@ -9151,16 +9161,16 @@
         <v>0</v>
       </c>
       <c r="M216" s="17" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="217" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C217" s="3">
+        <v>60000051</v>
+      </c>
+      <c r="D217" s="3">
         <v>60000052</v>
       </c>
-      <c r="D217" s="3">
-        <v>60000053</v>
-      </c>
       <c r="E217" s="3">
         <v>1</v>
       </c>
@@ -9168,7 +9178,7 @@
         <v>100</v>
       </c>
       <c r="G217" s="13">
-        <v>10013023</v>
+        <v>10013022</v>
       </c>
       <c r="H217" s="3">
         <v>1</v>
@@ -9183,16 +9193,16 @@
         <v>0</v>
       </c>
       <c r="M217" s="17" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="218" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C218" s="3">
+        <v>60000052</v>
+      </c>
+      <c r="D218" s="3">
         <v>60000053</v>
       </c>
-      <c r="D218" s="3">
-        <v>60000054</v>
-      </c>
       <c r="E218" s="3">
         <v>1</v>
       </c>
@@ -9200,7 +9210,7 @@
         <v>100</v>
       </c>
       <c r="G218" s="13">
-        <v>10013024</v>
+        <v>10013023</v>
       </c>
       <c r="H218" s="3">
         <v>1</v>
@@ -9215,16 +9225,16 @@
         <v>0</v>
       </c>
       <c r="M218" s="17" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="219" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C219" s="3">
+        <v>60000053</v>
+      </c>
+      <c r="D219" s="3">
         <v>60000054</v>
       </c>
-      <c r="D219" s="3">
-        <v>60000055</v>
-      </c>
       <c r="E219" s="3">
         <v>1</v>
       </c>
@@ -9232,7 +9242,7 @@
         <v>100</v>
       </c>
       <c r="G219" s="13">
-        <v>10013025</v>
+        <v>10013024</v>
       </c>
       <c r="H219" s="3">
         <v>1</v>
@@ -9247,16 +9257,16 @@
         <v>0</v>
       </c>
       <c r="M219" s="17" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="220" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C220" s="3">
+        <v>60000054</v>
+      </c>
+      <c r="D220" s="3">
         <v>60000055</v>
       </c>
-      <c r="D220" s="3">
-        <v>60000056</v>
-      </c>
       <c r="E220" s="3">
         <v>1</v>
       </c>
@@ -9264,7 +9274,7 @@
         <v>100</v>
       </c>
       <c r="G220" s="13">
-        <v>10013026</v>
+        <v>10013025</v>
       </c>
       <c r="H220" s="3">
         <v>1</v>
@@ -9279,16 +9289,16 @@
         <v>0</v>
       </c>
       <c r="M220" s="17" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="221" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C221" s="3">
+        <v>60000055</v>
+      </c>
+      <c r="D221" s="3">
         <v>60000056</v>
       </c>
-      <c r="D221" s="3">
-        <v>60000057</v>
-      </c>
       <c r="E221" s="3">
         <v>1</v>
       </c>
@@ -9296,7 +9306,7 @@
         <v>100</v>
       </c>
       <c r="G221" s="13">
-        <v>10013027</v>
+        <v>10013026</v>
       </c>
       <c r="H221" s="3">
         <v>1</v>
@@ -9311,16 +9321,16 @@
         <v>0</v>
       </c>
       <c r="M221" s="17" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="222" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C222" s="3">
+        <v>60000056</v>
+      </c>
+      <c r="D222" s="3">
         <v>60000057</v>
       </c>
-      <c r="D222" s="3">
-        <v>60000058</v>
-      </c>
       <c r="E222" s="3">
         <v>1</v>
       </c>
@@ -9328,13 +9338,13 @@
         <v>100</v>
       </c>
       <c r="G222" s="13">
-        <v>10014001</v>
+        <v>10013027</v>
       </c>
       <c r="H222" s="3">
         <v>1</v>
       </c>
       <c r="I222" s="3">
-        <v>10010031</v>
+        <v>10010030</v>
       </c>
       <c r="J222" s="3">
         <v>20</v>
@@ -9342,17 +9352,17 @@
       <c r="K222" s="2">
         <v>0</v>
       </c>
-      <c r="M222" s="3" t="s">
-        <v>134</v>
+      <c r="M222" s="17" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="223" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C223" s="3">
+        <v>60000057</v>
+      </c>
+      <c r="D223" s="3">
         <v>60000058</v>
       </c>
-      <c r="D223" s="3">
-        <v>60000059</v>
-      </c>
       <c r="E223" s="3">
         <v>1</v>
       </c>
@@ -9360,7 +9370,7 @@
         <v>100</v>
       </c>
       <c r="G223" s="13">
-        <v>10014002</v>
+        <v>10014001</v>
       </c>
       <c r="H223" s="3">
         <v>1</v>
@@ -9375,16 +9385,16 @@
         <v>0</v>
       </c>
       <c r="M223" s="3" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="224" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C224" s="3">
+        <v>60000058</v>
+      </c>
+      <c r="D224" s="3">
         <v>60000059</v>
       </c>
-      <c r="D224" s="3">
-        <v>60000060</v>
-      </c>
       <c r="E224" s="3">
         <v>1</v>
       </c>
@@ -9392,7 +9402,7 @@
         <v>100</v>
       </c>
       <c r="G224" s="13">
-        <v>10014003</v>
+        <v>10014002</v>
       </c>
       <c r="H224" s="3">
         <v>1</v>
@@ -9407,16 +9417,16 @@
         <v>0</v>
       </c>
       <c r="M224" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="225" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C225" s="3">
+        <v>60000059</v>
+      </c>
+      <c r="D225" s="3">
         <v>60000060</v>
       </c>
-      <c r="D225" s="3">
-        <v>60000061</v>
-      </c>
       <c r="E225" s="3">
         <v>1</v>
       </c>
@@ -9424,7 +9434,7 @@
         <v>100</v>
       </c>
       <c r="G225" s="13">
-        <v>10014004</v>
+        <v>10014003</v>
       </c>
       <c r="H225" s="3">
         <v>1</v>
@@ -9439,16 +9449,16 @@
         <v>0</v>
       </c>
       <c r="M225" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="226" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C226" s="3">
+        <v>60000060</v>
+      </c>
+      <c r="D226" s="3">
         <v>60000061</v>
       </c>
-      <c r="D226" s="3">
-        <v>60000062</v>
-      </c>
       <c r="E226" s="3">
         <v>1</v>
       </c>
@@ -9456,7 +9466,7 @@
         <v>100</v>
       </c>
       <c r="G226" s="13">
-        <v>10014005</v>
+        <v>10014004</v>
       </c>
       <c r="H226" s="3">
         <v>1</v>
@@ -9471,16 +9481,16 @@
         <v>0</v>
       </c>
       <c r="M226" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="227" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C227" s="3">
+        <v>60000061</v>
+      </c>
+      <c r="D227" s="3">
         <v>60000062</v>
       </c>
-      <c r="D227" s="3">
-        <v>60000063</v>
-      </c>
       <c r="E227" s="3">
         <v>1</v>
       </c>
@@ -9488,7 +9498,7 @@
         <v>100</v>
       </c>
       <c r="G227" s="13">
-        <v>10014006</v>
+        <v>10014005</v>
       </c>
       <c r="H227" s="3">
         <v>1</v>
@@ -9503,16 +9513,16 @@
         <v>0</v>
       </c>
       <c r="M227" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="228" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C228" s="3">
+        <v>60000062</v>
+      </c>
+      <c r="D228" s="3">
         <v>60000063</v>
       </c>
-      <c r="D228" s="3">
-        <v>60000064</v>
-      </c>
       <c r="E228" s="3">
         <v>1</v>
       </c>
@@ -9520,7 +9530,7 @@
         <v>100</v>
       </c>
       <c r="G228" s="13">
-        <v>10014007</v>
+        <v>10014006</v>
       </c>
       <c r="H228" s="3">
         <v>1</v>
@@ -9535,16 +9545,16 @@
         <v>0</v>
       </c>
       <c r="M228" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="229" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C229" s="3">
+        <v>60000063</v>
+      </c>
+      <c r="D229" s="3">
         <v>60000064</v>
       </c>
-      <c r="D229" s="3">
-        <v>60000065</v>
-      </c>
       <c r="E229" s="3">
         <v>1</v>
       </c>
@@ -9552,7 +9562,7 @@
         <v>100</v>
       </c>
       <c r="G229" s="13">
-        <v>10014008</v>
+        <v>10014007</v>
       </c>
       <c r="H229" s="3">
         <v>1</v>
@@ -9567,16 +9577,16 @@
         <v>0</v>
       </c>
       <c r="M229" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="230" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C230" s="3">
+        <v>60000064</v>
+      </c>
+      <c r="D230" s="3">
         <v>60000065</v>
       </c>
-      <c r="D230" s="3">
-        <v>60000066</v>
-      </c>
       <c r="E230" s="3">
         <v>1</v>
       </c>
@@ -9584,7 +9594,7 @@
         <v>100</v>
       </c>
       <c r="G230" s="13">
-        <v>10014009</v>
+        <v>10014008</v>
       </c>
       <c r="H230" s="3">
         <v>1</v>
@@ -9599,16 +9609,16 @@
         <v>0</v>
       </c>
       <c r="M230" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="231" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C231" s="3">
+        <v>60000065</v>
+      </c>
+      <c r="D231" s="3">
         <v>60000066</v>
       </c>
-      <c r="D231" s="3">
-        <v>60000067</v>
-      </c>
       <c r="E231" s="3">
         <v>1</v>
       </c>
@@ -9616,7 +9626,7 @@
         <v>100</v>
       </c>
       <c r="G231" s="13">
-        <v>10014010</v>
+        <v>10014009</v>
       </c>
       <c r="H231" s="3">
         <v>1</v>
@@ -9631,16 +9641,16 @@
         <v>0</v>
       </c>
       <c r="M231" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="232" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C232" s="3">
+        <v>60000066</v>
+      </c>
+      <c r="D232" s="3">
         <v>60000067</v>
       </c>
-      <c r="D232" s="3">
-        <v>60000068</v>
-      </c>
       <c r="E232" s="3">
         <v>1</v>
       </c>
@@ -9648,7 +9658,7 @@
         <v>100</v>
       </c>
       <c r="G232" s="13">
-        <v>10014011</v>
+        <v>10014010</v>
       </c>
       <c r="H232" s="3">
         <v>1</v>
@@ -9663,16 +9673,16 @@
         <v>0</v>
       </c>
       <c r="M232" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="233" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C233" s="3">
+        <v>60000067</v>
+      </c>
+      <c r="D233" s="3">
         <v>60000068</v>
       </c>
-      <c r="D233" s="3">
-        <v>60000069</v>
-      </c>
       <c r="E233" s="3">
         <v>1</v>
       </c>
@@ -9680,7 +9690,7 @@
         <v>100</v>
       </c>
       <c r="G233" s="13">
-        <v>10014012</v>
+        <v>10014011</v>
       </c>
       <c r="H233" s="3">
         <v>1</v>
@@ -9695,16 +9705,16 @@
         <v>0</v>
       </c>
       <c r="M233" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="234" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C234" s="3">
+        <v>60000068</v>
+      </c>
+      <c r="D234" s="3">
         <v>60000069</v>
       </c>
-      <c r="D234" s="3">
-        <v>60000070</v>
-      </c>
       <c r="E234" s="3">
         <v>1</v>
       </c>
@@ -9712,7 +9722,7 @@
         <v>100</v>
       </c>
       <c r="G234" s="13">
-        <v>10014013</v>
+        <v>10014012</v>
       </c>
       <c r="H234" s="3">
         <v>1</v>
@@ -9727,16 +9737,16 @@
         <v>0</v>
       </c>
       <c r="M234" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="235" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C235" s="3">
+        <v>60000069</v>
+      </c>
+      <c r="D235" s="3">
         <v>60000070</v>
       </c>
-      <c r="D235" s="3">
-        <v>60000071</v>
-      </c>
       <c r="E235" s="3">
         <v>1</v>
       </c>
@@ -9744,7 +9754,7 @@
         <v>100</v>
       </c>
       <c r="G235" s="13">
-        <v>10014014</v>
+        <v>10014013</v>
       </c>
       <c r="H235" s="3">
         <v>1</v>
@@ -9759,16 +9769,16 @@
         <v>0</v>
       </c>
       <c r="M235" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="236" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C236" s="3">
+        <v>60000070</v>
+      </c>
+      <c r="D236" s="3">
         <v>60000071</v>
       </c>
-      <c r="D236" s="3">
-        <v>60000072</v>
-      </c>
       <c r="E236" s="3">
         <v>1</v>
       </c>
@@ -9776,7 +9786,7 @@
         <v>100</v>
       </c>
       <c r="G236" s="13">
-        <v>10014015</v>
+        <v>10014014</v>
       </c>
       <c r="H236" s="3">
         <v>1</v>
@@ -9791,16 +9801,16 @@
         <v>0</v>
       </c>
       <c r="M236" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="237" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C237" s="3">
+        <v>60000071</v>
+      </c>
+      <c r="D237" s="3">
         <v>60000072</v>
       </c>
-      <c r="D237" s="3">
-        <v>60000073</v>
-      </c>
       <c r="E237" s="3">
         <v>1</v>
       </c>
@@ -9808,7 +9818,7 @@
         <v>100</v>
       </c>
       <c r="G237" s="13">
-        <v>10014016</v>
+        <v>10014015</v>
       </c>
       <c r="H237" s="3">
         <v>1</v>
@@ -9823,16 +9833,16 @@
         <v>0</v>
       </c>
       <c r="M237" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="238" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C238" s="3">
+        <v>60000072</v>
+      </c>
+      <c r="D238" s="3">
         <v>60000073</v>
       </c>
-      <c r="D238" s="3">
-        <v>60000074</v>
-      </c>
       <c r="E238" s="3">
         <v>1</v>
       </c>
@@ -9840,7 +9850,7 @@
         <v>100</v>
       </c>
       <c r="G238" s="13">
-        <v>10014017</v>
+        <v>10014016</v>
       </c>
       <c r="H238" s="3">
         <v>1</v>
@@ -9855,16 +9865,16 @@
         <v>0</v>
       </c>
       <c r="M238" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="239" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C239" s="3">
+        <v>60000073</v>
+      </c>
+      <c r="D239" s="3">
         <v>60000074</v>
       </c>
-      <c r="D239" s="3">
-        <v>60000075</v>
-      </c>
       <c r="E239" s="3">
         <v>1</v>
       </c>
@@ -9872,7 +9882,7 @@
         <v>100</v>
       </c>
       <c r="G239" s="13">
-        <v>10014018</v>
+        <v>10014017</v>
       </c>
       <c r="H239" s="3">
         <v>1</v>
@@ -9887,16 +9897,16 @@
         <v>0</v>
       </c>
       <c r="M239" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="240" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C240" s="3">
+        <v>60000074</v>
+      </c>
+      <c r="D240" s="3">
         <v>60000075</v>
       </c>
-      <c r="D240" s="3">
-        <v>60000076</v>
-      </c>
       <c r="E240" s="3">
         <v>1</v>
       </c>
@@ -9904,7 +9914,7 @@
         <v>100</v>
       </c>
       <c r="G240" s="13">
-        <v>10014019</v>
+        <v>10014018</v>
       </c>
       <c r="H240" s="3">
         <v>1</v>
@@ -9919,16 +9929,16 @@
         <v>0</v>
       </c>
       <c r="M240" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="241" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C241" s="3">
+        <v>60000075</v>
+      </c>
+      <c r="D241" s="3">
         <v>60000076</v>
       </c>
-      <c r="D241" s="3">
-        <v>60000077</v>
-      </c>
       <c r="E241" s="3">
         <v>1</v>
       </c>
@@ -9936,7 +9946,7 @@
         <v>100</v>
       </c>
       <c r="G241" s="13">
-        <v>10014020</v>
+        <v>10014019</v>
       </c>
       <c r="H241" s="3">
         <v>1</v>
@@ -9945,22 +9955,22 @@
         <v>10010031</v>
       </c>
       <c r="J241" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K241" s="2">
         <v>0</v>
       </c>
       <c r="M241" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="242" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C242" s="3">
+        <v>60000076</v>
+      </c>
+      <c r="D242" s="3">
         <v>60000077</v>
       </c>
-      <c r="D242" s="3">
-        <v>60000078</v>
-      </c>
       <c r="E242" s="3">
         <v>1</v>
       </c>
@@ -9968,7 +9978,7 @@
         <v>100</v>
       </c>
       <c r="G242" s="13">
-        <v>10014021</v>
+        <v>10014020</v>
       </c>
       <c r="H242" s="3">
         <v>1</v>
@@ -9983,16 +9993,16 @@
         <v>0</v>
       </c>
       <c r="M242" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="243" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C243" s="3">
+        <v>60000077</v>
+      </c>
+      <c r="D243" s="3">
         <v>60000078</v>
       </c>
-      <c r="D243" s="3">
-        <v>60000079</v>
-      </c>
       <c r="E243" s="3">
         <v>1</v>
       </c>
@@ -10000,7 +10010,7 @@
         <v>100</v>
       </c>
       <c r="G243" s="13">
-        <v>10014022</v>
+        <v>10014021</v>
       </c>
       <c r="H243" s="3">
         <v>1</v>
@@ -10015,16 +10025,16 @@
         <v>0</v>
       </c>
       <c r="M243" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="244" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C244" s="3">
+        <v>60000078</v>
+      </c>
+      <c r="D244" s="3">
         <v>60000079</v>
       </c>
-      <c r="D244" s="3">
-        <v>60000080</v>
-      </c>
       <c r="E244" s="3">
         <v>1</v>
       </c>
@@ -10032,7 +10042,7 @@
         <v>100</v>
       </c>
       <c r="G244" s="13">
-        <v>10014023</v>
+        <v>10014022</v>
       </c>
       <c r="H244" s="3">
         <v>1</v>
@@ -10047,16 +10057,16 @@
         <v>0</v>
       </c>
       <c r="M244" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="245" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C245" s="3">
+        <v>60000079</v>
+      </c>
+      <c r="D245" s="3">
         <v>60000080</v>
       </c>
-      <c r="D245" s="3">
-        <v>60000081</v>
-      </c>
       <c r="E245" s="3">
         <v>1</v>
       </c>
@@ -10064,7 +10074,7 @@
         <v>100</v>
       </c>
       <c r="G245" s="13">
-        <v>10014024</v>
+        <v>10014023</v>
       </c>
       <c r="H245" s="3">
         <v>1</v>
@@ -10079,16 +10089,16 @@
         <v>0</v>
       </c>
       <c r="M245" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="246" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C246" s="3">
+        <v>60000080</v>
+      </c>
+      <c r="D246" s="3">
         <v>60000081</v>
       </c>
-      <c r="D246" s="3">
-        <v>60000082</v>
-      </c>
       <c r="E246" s="3">
         <v>1</v>
       </c>
@@ -10096,7 +10106,7 @@
         <v>100</v>
       </c>
       <c r="G246" s="13">
-        <v>10014025</v>
+        <v>10014024</v>
       </c>
       <c r="H246" s="3">
         <v>1</v>
@@ -10111,16 +10121,16 @@
         <v>0</v>
       </c>
       <c r="M246" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="247" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C247" s="3">
+        <v>60000081</v>
+      </c>
+      <c r="D247" s="3">
         <v>60000082</v>
       </c>
-      <c r="D247" s="3">
-        <v>60000083</v>
-      </c>
       <c r="E247" s="3">
         <v>1</v>
       </c>
@@ -10128,7 +10138,7 @@
         <v>100</v>
       </c>
       <c r="G247" s="13">
-        <v>10014026</v>
+        <v>10014025</v>
       </c>
       <c r="H247" s="3">
         <v>1</v>
@@ -10143,16 +10153,16 @@
         <v>0</v>
       </c>
       <c r="M247" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="248" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C248" s="3">
+        <v>60000082</v>
+      </c>
+      <c r="D248" s="3">
         <v>60000083</v>
       </c>
-      <c r="D248" s="3">
-        <v>0</v>
-      </c>
       <c r="E248" s="3">
         <v>1</v>
       </c>
@@ -10160,7 +10170,7 @@
         <v>100</v>
       </c>
       <c r="G248" s="13">
-        <v>10014027</v>
+        <v>10014026</v>
       </c>
       <c r="H248" s="3">
         <v>1</v>
@@ -10175,15 +10185,15 @@
         <v>0</v>
       </c>
       <c r="M248" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="249" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C249" s="3">
-        <v>70000001</v>
+        <v>60000083</v>
       </c>
       <c r="D249" s="3">
-        <v>70000002</v>
+        <v>0</v>
       </c>
       <c r="E249" s="3">
         <v>1</v>
@@ -10191,32 +10201,32 @@
       <c r="F249" s="3">
         <v>100</v>
       </c>
-      <c r="G249" s="9">
-        <v>10010093</v>
+      <c r="G249" s="13">
+        <v>10014027</v>
       </c>
       <c r="H249" s="3">
         <v>1</v>
       </c>
-      <c r="I249" s="8">
-        <v>10000159</v>
-      </c>
-      <c r="J249" s="8">
+      <c r="I249" s="3">
+        <v>10010031</v>
+      </c>
+      <c r="J249" s="3">
         <v>30</v>
       </c>
       <c r="K249" s="2">
         <v>0</v>
       </c>
-      <c r="M249" s="12" t="s">
-        <v>49</v>
+      <c r="M249" s="3" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="250" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C250" s="3">
+        <v>70000001</v>
+      </c>
+      <c r="D250" s="3">
         <v>70000002</v>
       </c>
-      <c r="D250" s="3">
-        <v>70000003</v>
-      </c>
       <c r="E250" s="3">
         <v>1</v>
       </c>
@@ -10224,7 +10234,7 @@
         <v>100</v>
       </c>
       <c r="G250" s="9">
-        <v>10000162</v>
+        <v>10010093</v>
       </c>
       <c r="H250" s="3">
         <v>1</v>
@@ -10233,22 +10243,22 @@
         <v>10000159</v>
       </c>
       <c r="J250" s="8">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K250" s="2">
         <v>0</v>
       </c>
-      <c r="M250" s="11" t="s">
-        <v>104</v>
+      <c r="M250" s="12" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="251" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C251" s="3">
+        <v>70000002</v>
+      </c>
+      <c r="D251" s="3">
         <v>70000003</v>
       </c>
-      <c r="D251" s="3">
-        <v>70000004</v>
-      </c>
       <c r="E251" s="3">
         <v>1</v>
       </c>
@@ -10256,7 +10266,7 @@
         <v>100</v>
       </c>
       <c r="G251" s="9">
-        <v>10010045</v>
+        <v>10000162</v>
       </c>
       <c r="H251" s="3">
         <v>1</v>
@@ -10265,22 +10275,22 @@
         <v>10000159</v>
       </c>
       <c r="J251" s="8">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K251" s="2">
         <v>0</v>
       </c>
       <c r="M251" s="11" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="252" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="252" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C252" s="3">
+        <v>70000003</v>
+      </c>
+      <c r="D252" s="3">
         <v>70000004</v>
       </c>
-      <c r="D252" s="3">
-        <v>70000005</v>
-      </c>
       <c r="E252" s="3">
         <v>1</v>
       </c>
@@ -10288,7 +10298,7 @@
         <v>100</v>
       </c>
       <c r="G252" s="9">
-        <v>10000158</v>
+        <v>10010045</v>
       </c>
       <c r="H252" s="3">
         <v>1</v>
@@ -10297,22 +10307,22 @@
         <v>10000159</v>
       </c>
       <c r="J252" s="8">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K252" s="2">
         <v>0</v>
       </c>
-      <c r="M252" s="9" t="s">
-        <v>106</v>
+      <c r="M252" s="11" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="253" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C253" s="3">
+        <v>70000004</v>
+      </c>
+      <c r="D253" s="3">
         <v>70000005</v>
       </c>
-      <c r="D253" s="3">
-        <v>70000006</v>
-      </c>
       <c r="E253" s="3">
         <v>1</v>
       </c>
@@ -10320,7 +10330,7 @@
         <v>100</v>
       </c>
       <c r="G253" s="9">
-        <v>10010083</v>
+        <v>10000158</v>
       </c>
       <c r="H253" s="3">
         <v>1</v>
@@ -10329,22 +10339,22 @@
         <v>10000159</v>
       </c>
       <c r="J253" s="8">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="K253" s="2">
         <v>0</v>
       </c>
-      <c r="M253" s="16" t="s">
-        <v>107</v>
+      <c r="M253" s="9" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="254" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C254" s="3">
+        <v>70000005</v>
+      </c>
+      <c r="D254" s="3">
         <v>70000006</v>
       </c>
-      <c r="D254" s="3">
-        <v>70000007</v>
-      </c>
       <c r="E254" s="3">
         <v>1</v>
       </c>
@@ -10352,7 +10362,7 @@
         <v>100</v>
       </c>
       <c r="G254" s="9">
-        <v>10000143</v>
+        <v>10010083</v>
       </c>
       <c r="H254" s="3">
         <v>1</v>
@@ -10361,22 +10371,22 @@
         <v>10000159</v>
       </c>
       <c r="J254" s="8">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="K254" s="2">
         <v>0</v>
       </c>
       <c r="M254" s="16" t="s">
-        <v>47</v>
+        <v>107</v>
       </c>
     </row>
     <row r="255" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C255" s="3">
+        <v>70000006</v>
+      </c>
+      <c r="D255" s="3">
         <v>70000007</v>
       </c>
-      <c r="D255" s="3">
-        <v>70000008</v>
-      </c>
       <c r="E255" s="3">
         <v>1</v>
       </c>
@@ -10384,7 +10394,7 @@
         <v>100</v>
       </c>
       <c r="G255" s="9">
-        <v>10000152</v>
+        <v>10000143</v>
       </c>
       <c r="H255" s="3">
         <v>1</v>
@@ -10393,22 +10403,22 @@
         <v>10000159</v>
       </c>
       <c r="J255" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K255" s="2">
         <v>0</v>
       </c>
-      <c r="M255" s="11" t="s">
-        <v>38</v>
+      <c r="M255" s="16" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="256" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C256" s="3">
+        <v>70000007</v>
+      </c>
+      <c r="D256" s="3">
         <v>70000008</v>
       </c>
-      <c r="D256" s="3">
-        <v>70000009</v>
-      </c>
       <c r="E256" s="3">
         <v>1</v>
       </c>
@@ -10416,7 +10426,7 @@
         <v>100</v>
       </c>
       <c r="G256" s="9">
-        <v>10000157</v>
+        <v>10000152</v>
       </c>
       <c r="H256" s="3">
         <v>1</v>
@@ -10431,16 +10441,16 @@
         <v>0</v>
       </c>
       <c r="M256" s="11" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="257" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C257" s="3">
+        <v>70000008</v>
+      </c>
+      <c r="D257" s="3">
         <v>70000009</v>
       </c>
-      <c r="D257" s="3">
-        <v>70000010</v>
-      </c>
       <c r="E257" s="3">
         <v>1</v>
       </c>
@@ -10448,7 +10458,7 @@
         <v>100</v>
       </c>
       <c r="G257" s="9">
-        <v>10010029</v>
+        <v>10000157</v>
       </c>
       <c r="H257" s="3">
         <v>1</v>
@@ -10457,22 +10467,22 @@
         <v>10000159</v>
       </c>
       <c r="J257" s="8">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K257" s="2">
         <v>0</v>
       </c>
       <c r="M257" s="11" t="s">
-        <v>108</v>
+        <v>39</v>
       </c>
     </row>
     <row r="258" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C258" s="3">
+        <v>70000009</v>
+      </c>
+      <c r="D258" s="3">
         <v>70000010</v>
       </c>
-      <c r="D258" s="3">
-        <v>70000011</v>
-      </c>
       <c r="E258" s="3">
         <v>1</v>
       </c>
@@ -10480,7 +10490,7 @@
         <v>100</v>
       </c>
       <c r="G258" s="9">
-        <v>10010086</v>
+        <v>10010029</v>
       </c>
       <c r="H258" s="3">
         <v>1</v>
@@ -10489,30 +10499,30 @@
         <v>10000159</v>
       </c>
       <c r="J258" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K258" s="2">
         <v>0</v>
       </c>
-      <c r="M258" s="12" t="s">
-        <v>27</v>
+      <c r="M258" s="11" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="259" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C259" s="3">
+        <v>70000010</v>
+      </c>
+      <c r="D259" s="3">
         <v>70000011</v>
       </c>
-      <c r="D259" s="3">
-        <v>70000012</v>
-      </c>
       <c r="E259" s="3">
         <v>1</v>
       </c>
       <c r="F259" s="3">
         <v>100</v>
       </c>
-      <c r="G259" s="18">
-        <v>10010101</v>
+      <c r="G259" s="9">
+        <v>10010086</v>
       </c>
       <c r="H259" s="3">
         <v>1</v>
@@ -10521,22 +10531,22 @@
         <v>10000159</v>
       </c>
       <c r="J259" s="8">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K259" s="2">
         <v>0</v>
       </c>
-      <c r="M259" s="8" t="s">
-        <v>109</v>
+      <c r="M259" s="12" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="260" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C260" s="3">
+        <v>70000011</v>
+      </c>
+      <c r="D260" s="3">
         <v>70000012</v>
       </c>
-      <c r="D260" s="3">
-        <v>70000013</v>
-      </c>
       <c r="E260" s="3">
         <v>1</v>
       </c>
@@ -10544,7 +10554,7 @@
         <v>100</v>
       </c>
       <c r="G260" s="18">
-        <v>10010102</v>
+        <v>10010101</v>
       </c>
       <c r="H260" s="3">
         <v>1</v>
@@ -10553,22 +10563,22 @@
         <v>10000159</v>
       </c>
       <c r="J260" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K260" s="2">
         <v>0</v>
       </c>
-      <c r="M260" s="3" t="s">
-        <v>110</v>
+      <c r="M260" s="8" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="261" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C261" s="3">
+        <v>70000012</v>
+      </c>
+      <c r="D261" s="3">
         <v>70000013</v>
       </c>
-      <c r="D261" s="3">
-        <v>0</v>
-      </c>
       <c r="E261" s="3">
         <v>1</v>
       </c>
@@ -10576,7 +10586,7 @@
         <v>100</v>
       </c>
       <c r="G261" s="18">
-        <v>10010103</v>
+        <v>10010102</v>
       </c>
       <c r="H261" s="3">
         <v>1</v>
@@ -10585,54 +10595,54 @@
         <v>10000159</v>
       </c>
       <c r="J261" s="8">
+        <v>10</v>
+      </c>
+      <c r="K261" s="2">
+        <v>0</v>
+      </c>
+      <c r="M261" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="262" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C262" s="3">
+        <v>70000013</v>
+      </c>
+      <c r="D262" s="3">
+        <v>0</v>
+      </c>
+      <c r="E262" s="3">
+        <v>1</v>
+      </c>
+      <c r="F262" s="3">
+        <v>100</v>
+      </c>
+      <c r="G262" s="18">
+        <v>10010103</v>
+      </c>
+      <c r="H262" s="3">
+        <v>1</v>
+      </c>
+      <c r="I262" s="8">
+        <v>10000159</v>
+      </c>
+      <c r="J262" s="8">
         <v>20</v>
       </c>
-      <c r="K261" s="2">
-        <v>0</v>
-      </c>
-      <c r="M261" s="3" t="s">
+      <c r="K262" s="2">
+        <v>0</v>
+      </c>
+      <c r="M262" s="3" t="s">
         <v>111</v>
-      </c>
-    </row>
-    <row r="262" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C262" s="3">
-        <v>80000001</v>
-      </c>
-      <c r="D262" s="3">
-        <v>80000002</v>
-      </c>
-      <c r="E262" s="3">
-        <v>1</v>
-      </c>
-      <c r="F262" s="3">
-        <v>100</v>
-      </c>
-      <c r="G262" s="9">
-        <v>10010083</v>
-      </c>
-      <c r="H262" s="3">
-        <v>1</v>
-      </c>
-      <c r="I262" s="8">
-        <v>10000163</v>
-      </c>
-      <c r="J262" s="8">
-        <v>1</v>
-      </c>
-      <c r="K262" s="2">
-        <v>0</v>
-      </c>
-      <c r="M262" s="3" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="263" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C263" s="3">
+        <v>80000001</v>
+      </c>
+      <c r="D263" s="3">
         <v>80000002</v>
       </c>
-      <c r="D263" s="3">
-        <v>80000003</v>
-      </c>
       <c r="E263" s="3">
         <v>1</v>
       </c>
@@ -10640,7 +10650,7 @@
         <v>100</v>
       </c>
       <c r="G263" s="9">
-        <v>10010086</v>
+        <v>10010083</v>
       </c>
       <c r="H263" s="3">
         <v>1</v>
@@ -10649,22 +10659,22 @@
         <v>10000163</v>
       </c>
       <c r="J263" s="8">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K263" s="2">
         <v>0</v>
       </c>
       <c r="M263" s="3" t="s">
-        <v>27</v>
+        <v>107</v>
       </c>
     </row>
     <row r="264" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C264" s="3">
+        <v>80000002</v>
+      </c>
+      <c r="D264" s="3">
         <v>80000003</v>
       </c>
-      <c r="D264" s="3">
-        <v>80000004</v>
-      </c>
       <c r="E264" s="3">
         <v>1</v>
       </c>
@@ -10672,7 +10682,7 @@
         <v>100</v>
       </c>
       <c r="G264" s="9">
-        <v>10010096</v>
+        <v>10010086</v>
       </c>
       <c r="H264" s="3">
         <v>1</v>
@@ -10681,22 +10691,22 @@
         <v>10000163</v>
       </c>
       <c r="J264" s="8">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="K264" s="2">
         <v>0</v>
       </c>
       <c r="M264" s="3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="265" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="265" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C265" s="3">
+        <v>80000003</v>
+      </c>
+      <c r="D265" s="3">
         <v>80000004</v>
       </c>
-      <c r="D265" s="3">
-        <v>80000005</v>
-      </c>
       <c r="E265" s="3">
         <v>1</v>
       </c>
@@ -10704,7 +10714,7 @@
         <v>100</v>
       </c>
       <c r="G265" s="9">
-        <v>10000139</v>
+        <v>10010096</v>
       </c>
       <c r="H265" s="3">
         <v>1</v>
@@ -10713,22 +10723,22 @@
         <v>10000163</v>
       </c>
       <c r="J265" s="8">
-        <v>20</v>
+        <v>35</v>
       </c>
       <c r="K265" s="2">
         <v>0</v>
       </c>
       <c r="M265" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="266" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C266" s="3">
+        <v>80000004</v>
+      </c>
+      <c r="D266" s="3">
         <v>80000005</v>
       </c>
-      <c r="D266" s="3">
-        <v>80000006</v>
-      </c>
       <c r="E266" s="3">
         <v>1</v>
       </c>
@@ -10736,7 +10746,7 @@
         <v>100</v>
       </c>
       <c r="G266" s="9">
-        <v>10000143</v>
+        <v>10000139</v>
       </c>
       <c r="H266" s="3">
         <v>1</v>
@@ -10751,16 +10761,16 @@
         <v>0</v>
       </c>
       <c r="M266" s="3" t="s">
-        <v>47</v>
+        <v>113</v>
       </c>
     </row>
     <row r="267" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C267" s="3">
+        <v>80000005</v>
+      </c>
+      <c r="D267" s="3">
         <v>80000006</v>
       </c>
-      <c r="D267" s="3">
-        <v>80000007</v>
-      </c>
       <c r="E267" s="3">
         <v>1</v>
       </c>
@@ -10768,7 +10778,7 @@
         <v>100</v>
       </c>
       <c r="G267" s="9">
-        <v>10000152</v>
+        <v>10000143</v>
       </c>
       <c r="H267" s="3">
         <v>1</v>
@@ -10777,22 +10787,22 @@
         <v>10000163</v>
       </c>
       <c r="J267" s="8">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="K267" s="2">
         <v>0</v>
       </c>
       <c r="M267" s="3" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
     </row>
     <row r="268" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C268" s="3">
+        <v>80000006</v>
+      </c>
+      <c r="D268" s="3">
         <v>80000007</v>
       </c>
-      <c r="D268" s="3">
-        <v>80000008</v>
-      </c>
       <c r="E268" s="3">
         <v>1</v>
       </c>
@@ -10800,7 +10810,7 @@
         <v>100</v>
       </c>
       <c r="G268" s="9">
-        <v>10000155</v>
+        <v>10000152</v>
       </c>
       <c r="H268" s="3">
         <v>1</v>
@@ -10809,22 +10819,22 @@
         <v>10000163</v>
       </c>
       <c r="J268" s="8">
-        <v>5</v>
+        <v>35</v>
       </c>
       <c r="K268" s="2">
         <v>0</v>
       </c>
       <c r="M268" s="3" t="s">
-        <v>114</v>
+        <v>38</v>
       </c>
     </row>
     <row r="269" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C269" s="3">
+        <v>80000007</v>
+      </c>
+      <c r="D269" s="3">
         <v>80000008</v>
       </c>
-      <c r="D269" s="3">
-        <v>80000009</v>
-      </c>
       <c r="E269" s="3">
         <v>1</v>
       </c>
@@ -10832,7 +10842,7 @@
         <v>100</v>
       </c>
       <c r="G269" s="9">
-        <v>10000158</v>
+        <v>10000155</v>
       </c>
       <c r="H269" s="3">
         <v>1</v>
@@ -10841,22 +10851,22 @@
         <v>10000163</v>
       </c>
       <c r="J269" s="8">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="K269" s="2">
         <v>0</v>
       </c>
       <c r="M269" s="3" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
     </row>
     <row r="270" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C270" s="3">
+        <v>80000008</v>
+      </c>
+      <c r="D270" s="3">
         <v>80000009</v>
       </c>
-      <c r="D270" s="3">
-        <v>0</v>
-      </c>
       <c r="E270" s="3">
         <v>1</v>
       </c>
@@ -10864,7 +10874,7 @@
         <v>100</v>
       </c>
       <c r="G270" s="9">
-        <v>10010093</v>
+        <v>10000158</v>
       </c>
       <c r="H270" s="3">
         <v>1</v>
@@ -10873,55 +10883,54 @@
         <v>10000163</v>
       </c>
       <c r="J270" s="8">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="K270" s="2">
         <v>0</v>
       </c>
       <c r="M270" s="3" t="s">
-        <v>49</v>
+        <v>106</v>
       </c>
     </row>
     <row r="271" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C271" s="3">
-        <v>90000001</v>
+        <v>80000009</v>
       </c>
       <c r="D271" s="3">
-        <v>90000002</v>
-      </c>
-      <c r="E271" s="2">
+        <v>0</v>
+      </c>
+      <c r="E271" s="3">
         <v>1</v>
       </c>
       <c r="F271" s="3">
         <v>100</v>
       </c>
-      <c r="G271" s="3">
+      <c r="G271" s="9">
         <v>10010093</v>
       </c>
       <c r="H271" s="3">
         <v>1</v>
       </c>
       <c r="I271" s="8">
-        <v>10000184</v>
+        <v>10000163</v>
       </c>
       <c r="J271" s="8">
-        <v>60</v>
+        <v>35</v>
       </c>
       <c r="K271" s="2">
         <v>0</v>
       </c>
-      <c r="L271" s="2"/>
-      <c r="M271" s="12" t="s">
+      <c r="M271" s="3" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="272" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C272" s="3">
+        <v>90000001</v>
+      </c>
+      <c r="D272" s="3">
         <v>90000002</v>
       </c>
-      <c r="D272" s="3">
-        <v>90000003</v>
-      </c>
       <c r="E272" s="2">
         <v>1</v>
       </c>
@@ -10929,7 +10938,7 @@
         <v>100</v>
       </c>
       <c r="G272" s="3">
-        <v>10010083</v>
+        <v>10010093</v>
       </c>
       <c r="H272" s="3">
         <v>1</v>
@@ -10938,23 +10947,23 @@
         <v>10000184</v>
       </c>
       <c r="J272" s="8">
-        <v>2</v>
+        <v>60</v>
       </c>
       <c r="K272" s="2">
         <v>0</v>
       </c>
       <c r="L272" s="2"/>
-      <c r="M272" s="16" t="s">
-        <v>107</v>
+      <c r="M272" s="12" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="273" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C273" s="3">
+        <v>90000002</v>
+      </c>
+      <c r="D273" s="3">
         <v>90000003</v>
       </c>
-      <c r="D273" s="3">
-        <v>90000004</v>
-      </c>
       <c r="E273" s="2">
         <v>1</v>
       </c>
@@ -10962,7 +10971,7 @@
         <v>100</v>
       </c>
       <c r="G273" s="3">
-        <v>10010086</v>
+        <v>10010083</v>
       </c>
       <c r="H273" s="3">
         <v>1</v>
@@ -10971,23 +10980,23 @@
         <v>10000184</v>
       </c>
       <c r="J273" s="8">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="K273" s="2">
         <v>0</v>
       </c>
       <c r="L273" s="2"/>
-      <c r="M273" s="12" t="s">
-        <v>27</v>
+      <c r="M273" s="16" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="274" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C274" s="3">
+        <v>90000003</v>
+      </c>
+      <c r="D274" s="3">
         <v>90000004</v>
       </c>
-      <c r="D274" s="3">
-        <v>90000005</v>
-      </c>
       <c r="E274" s="2">
         <v>1</v>
       </c>
@@ -10995,7 +11004,7 @@
         <v>100</v>
       </c>
       <c r="G274" s="3">
-        <v>10000143</v>
+        <v>10010086</v>
       </c>
       <c r="H274" s="3">
         <v>1</v>
@@ -11004,23 +11013,23 @@
         <v>10000184</v>
       </c>
       <c r="J274" s="8">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="K274" s="2">
         <v>0</v>
       </c>
       <c r="L274" s="2"/>
-      <c r="M274" s="11" t="s">
-        <v>47</v>
+      <c r="M274" s="12" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="275" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C275" s="3">
+        <v>90000004</v>
+      </c>
+      <c r="D275" s="3">
         <v>90000005</v>
       </c>
-      <c r="D275" s="3">
-        <v>90000006</v>
-      </c>
       <c r="E275" s="2">
         <v>1</v>
       </c>
@@ -11028,7 +11037,7 @@
         <v>100</v>
       </c>
       <c r="G275" s="3">
-        <v>10000152</v>
+        <v>10000143</v>
       </c>
       <c r="H275" s="3">
         <v>1</v>
@@ -11037,23 +11046,23 @@
         <v>10000184</v>
       </c>
       <c r="J275" s="8">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="K275" s="2">
         <v>0</v>
       </c>
       <c r="L275" s="2"/>
       <c r="M275" s="11" t="s">
-        <v>38</v>
+        <v>47</v>
       </c>
     </row>
     <row r="276" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C276" s="3">
+        <v>90000005</v>
+      </c>
+      <c r="D276" s="3">
         <v>90000006</v>
       </c>
-      <c r="D276" s="3">
-        <v>90000007</v>
-      </c>
       <c r="E276" s="2">
         <v>1</v>
       </c>
@@ -11061,7 +11070,7 @@
         <v>100</v>
       </c>
       <c r="G276" s="3">
-        <v>10000165</v>
+        <v>10000152</v>
       </c>
       <c r="H276" s="3">
         <v>1</v>
@@ -11070,23 +11079,23 @@
         <v>10000184</v>
       </c>
       <c r="J276" s="8">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K276" s="2">
         <v>0</v>
       </c>
       <c r="L276" s="2"/>
       <c r="M276" s="11" t="s">
-        <v>45</v>
+        <v>38</v>
       </c>
     </row>
     <row r="277" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C277" s="3">
+        <v>90000006</v>
+      </c>
+      <c r="D277" s="3">
         <v>90000007</v>
       </c>
-      <c r="D277" s="3">
-        <v>0</v>
-      </c>
       <c r="E277" s="2">
         <v>1</v>
       </c>
@@ -11094,7 +11103,7 @@
         <v>100</v>
       </c>
       <c r="G277" s="3">
-        <v>10010045</v>
+        <v>10000165</v>
       </c>
       <c r="H277" s="3">
         <v>1</v>
@@ -11103,22 +11112,22 @@
         <v>10000184</v>
       </c>
       <c r="J277" s="8">
-        <v>45</v>
+        <v>100</v>
       </c>
       <c r="K277" s="2">
         <v>0</v>
       </c>
       <c r="L277" s="2"/>
       <c r="M277" s="11" t="s">
-        <v>105</v>
+        <v>45</v>
       </c>
     </row>
     <row r="278" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C278" s="3">
-        <v>91000001</v>
+        <v>90000007</v>
       </c>
       <c r="D278" s="3">
-        <v>91000002</v>
+        <v>0</v>
       </c>
       <c r="E278" s="2">
         <v>1</v>
@@ -11127,31 +11136,32 @@
         <v>100</v>
       </c>
       <c r="G278" s="3">
-        <v>10010086</v>
+        <v>10010045</v>
       </c>
       <c r="H278" s="3">
         <v>1</v>
       </c>
-      <c r="I278" s="19">
-        <v>36</v>
-      </c>
-      <c r="J278" s="20">
-        <v>8</v>
+      <c r="I278" s="8">
+        <v>10000184</v>
+      </c>
+      <c r="J278" s="8">
+        <v>45</v>
       </c>
       <c r="K278" s="2">
         <v>0</v>
       </c>
-      <c r="M278" s="3" t="s">
-        <v>27</v>
+      <c r="L278" s="2"/>
+      <c r="M278" s="11" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="279" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C279" s="3">
+        <v>91000001</v>
+      </c>
+      <c r="D279" s="3">
         <v>91000002</v>
       </c>
-      <c r="D279" s="3">
-        <v>91000003</v>
-      </c>
       <c r="E279" s="2">
         <v>1</v>
       </c>
@@ -11159,7 +11169,7 @@
         <v>100</v>
       </c>
       <c r="G279" s="3">
-        <v>10010096</v>
+        <v>10010086</v>
       </c>
       <c r="H279" s="3">
         <v>1</v>
@@ -11168,22 +11178,22 @@
         <v>36</v>
       </c>
       <c r="J279" s="20">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="K279" s="2">
         <v>0</v>
       </c>
       <c r="M279" s="3" t="s">
-        <v>112</v>
+        <v>27</v>
       </c>
     </row>
     <row r="280" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C280" s="3">
+        <v>91000002</v>
+      </c>
+      <c r="D280" s="3">
         <v>91000003</v>
       </c>
-      <c r="D280" s="3">
-        <v>91000004</v>
-      </c>
       <c r="E280" s="2">
         <v>1</v>
       </c>
@@ -11191,7 +11201,7 @@
         <v>100</v>
       </c>
       <c r="G280" s="3">
-        <v>10010074</v>
+        <v>10010096</v>
       </c>
       <c r="H280" s="3">
         <v>1</v>
@@ -11200,22 +11210,22 @@
         <v>36</v>
       </c>
       <c r="J280" s="20">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="K280" s="2">
         <v>0</v>
       </c>
       <c r="M280" s="3" t="s">
-        <v>115</v>
+        <v>112</v>
       </c>
     </row>
     <row r="281" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C281" s="3">
+        <v>91000003</v>
+      </c>
+      <c r="D281" s="3">
         <v>91000004</v>
       </c>
-      <c r="D281" s="3">
-        <v>91000005</v>
-      </c>
       <c r="E281" s="2">
         <v>1</v>
       </c>
@@ -11223,7 +11233,7 @@
         <v>100</v>
       </c>
       <c r="G281" s="3">
-        <v>10010075</v>
+        <v>10010074</v>
       </c>
       <c r="H281" s="3">
         <v>1</v>
@@ -11232,30 +11242,30 @@
         <v>36</v>
       </c>
       <c r="J281" s="20">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="K281" s="2">
         <v>0</v>
       </c>
       <c r="M281" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="282" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C282" s="3">
+        <v>91000004</v>
+      </c>
+      <c r="D282" s="3">
         <v>91000005</v>
       </c>
-      <c r="D282" s="3">
-        <v>91000006</v>
-      </c>
       <c r="E282" s="2">
         <v>1</v>
       </c>
       <c r="F282" s="3">
         <v>100</v>
       </c>
-      <c r="G282" s="2">
-        <v>10010083</v>
+      <c r="G282" s="3">
+        <v>10010075</v>
       </c>
       <c r="H282" s="3">
         <v>1</v>
@@ -11264,22 +11274,22 @@
         <v>36</v>
       </c>
       <c r="J282" s="20">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K282" s="2">
         <v>0</v>
       </c>
-      <c r="M282" s="15" t="s">
-        <v>118</v>
+      <c r="M282" s="3" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="283" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C283" s="3">
+        <v>91000005</v>
+      </c>
+      <c r="D283" s="3">
         <v>91000006</v>
       </c>
-      <c r="D283" s="3">
-        <v>91000007</v>
-      </c>
       <c r="E283" s="2">
         <v>1</v>
       </c>
@@ -11287,7 +11297,7 @@
         <v>100</v>
       </c>
       <c r="G283" s="2">
-        <v>10010098</v>
+        <v>10010083</v>
       </c>
       <c r="H283" s="3">
         <v>1</v>
@@ -11302,24 +11312,24 @@
         <v>0</v>
       </c>
       <c r="M283" s="15" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="284" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C284" s="3">
+        <v>91000006</v>
+      </c>
+      <c r="D284" s="3">
         <v>91000007</v>
       </c>
-      <c r="D284" s="3">
-        <v>0</v>
-      </c>
       <c r="E284" s="2">
         <v>1</v>
       </c>
       <c r="F284" s="3">
         <v>100</v>
       </c>
-      <c r="G284" s="9">
-        <v>10010040</v>
+      <c r="G284" s="2">
+        <v>10010098</v>
       </c>
       <c r="H284" s="3">
         <v>1</v>
@@ -11328,63 +11338,62 @@
         <v>36</v>
       </c>
       <c r="J284" s="20">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="K284" s="2">
-        <v>1</v>
-      </c>
-      <c r="M284" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="M284" s="15" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="285" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C285" s="3">
+        <v>91000007</v>
+      </c>
+      <c r="D285" s="3">
+        <v>0</v>
+      </c>
+      <c r="E285" s="2">
+        <v>1</v>
+      </c>
+      <c r="F285" s="3">
+        <v>100</v>
+      </c>
+      <c r="G285" s="9">
+        <v>10010040</v>
+      </c>
+      <c r="H285" s="3">
+        <v>1</v>
+      </c>
+      <c r="I285" s="19">
+        <v>36</v>
+      </c>
+      <c r="J285" s="20">
+        <v>100</v>
+      </c>
+      <c r="K285" s="2">
+        <v>1</v>
+      </c>
+      <c r="M285" s="9" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="285" spans="3:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C285" s="3">
+    <row r="286" spans="3:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C286" s="3">
         <v>92000001</v>
       </c>
-      <c r="D285" s="3">
+      <c r="D286" s="3">
         <v>92000002</v>
       </c>
-      <c r="E285" s="2">
-        <v>1</v>
-      </c>
-      <c r="F285" s="3">
-        <v>100</v>
-      </c>
-      <c r="G285" s="3">
+      <c r="E286" s="2">
+        <v>1</v>
+      </c>
+      <c r="F286" s="3">
+        <v>100</v>
+      </c>
+      <c r="G286" s="3">
         <v>10060100</v>
-      </c>
-      <c r="H285" s="3">
-        <v>1</v>
-      </c>
-      <c r="I285" s="9">
-        <v>10000136</v>
-      </c>
-      <c r="J285" s="3">
-        <v>50</v>
-      </c>
-      <c r="K285" s="2">
-        <v>0</v>
-      </c>
-      <c r="M285" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q285" s="7"/>
-    </row>
-    <row r="286" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C286" s="3">
-        <v>92000002</v>
-      </c>
-      <c r="D286" s="3">
-        <v>92000003</v>
-      </c>
-      <c r="E286" s="2">
-        <v>1</v>
-      </c>
-      <c r="F286" s="3">
-        <v>100</v>
-      </c>
-      <c r="G286" s="3">
-        <v>10060200</v>
       </c>
       <c r="H286" s="3">
         <v>1</v>
@@ -11399,16 +11408,17 @@
         <v>0</v>
       </c>
       <c r="M286" s="22" t="s">
-        <v>124</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="Q286" s="7"/>
     </row>
     <row r="287" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C287" s="3">
+        <v>92000002</v>
+      </c>
+      <c r="D287" s="3">
         <v>92000003</v>
       </c>
-      <c r="D287" s="3">
-        <v>92000004</v>
-      </c>
       <c r="E287" s="2">
         <v>1</v>
       </c>
@@ -11416,7 +11426,7 @@
         <v>100</v>
       </c>
       <c r="G287" s="3">
-        <v>10060300</v>
+        <v>10060200</v>
       </c>
       <c r="H287" s="3">
         <v>1</v>
@@ -11431,16 +11441,16 @@
         <v>0</v>
       </c>
       <c r="M287" s="22" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="288" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C288" s="3">
+        <v>92000003</v>
+      </c>
+      <c r="D288" s="3">
         <v>92000004</v>
       </c>
-      <c r="D288" s="3">
-        <v>92000005</v>
-      </c>
       <c r="E288" s="2">
         <v>1</v>
       </c>
@@ -11448,7 +11458,7 @@
         <v>100</v>
       </c>
       <c r="G288" s="3">
-        <v>10060400</v>
+        <v>10060300</v>
       </c>
       <c r="H288" s="3">
         <v>1</v>
@@ -11463,16 +11473,16 @@
         <v>0</v>
       </c>
       <c r="M288" s="22" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="289" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C289" s="3">
+        <v>92000004</v>
+      </c>
+      <c r="D289" s="3">
         <v>92000005</v>
       </c>
-      <c r="D289" s="3">
-        <v>92000006</v>
-      </c>
       <c r="E289" s="2">
         <v>1</v>
       </c>
@@ -11480,7 +11490,7 @@
         <v>100</v>
       </c>
       <c r="G289" s="3">
-        <v>10060500</v>
+        <v>10060400</v>
       </c>
       <c r="H289" s="3">
         <v>1</v>
@@ -11495,16 +11505,16 @@
         <v>0</v>
       </c>
       <c r="M289" s="22" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="290" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C290" s="3">
+        <v>92000005</v>
+      </c>
+      <c r="D290" s="3">
         <v>92000006</v>
       </c>
-      <c r="D290" s="3">
-        <v>92000007</v>
-      </c>
       <c r="E290" s="2">
         <v>1</v>
       </c>
@@ -11512,7 +11522,7 @@
         <v>100</v>
       </c>
       <c r="G290" s="3">
-        <v>10060600</v>
+        <v>10060500</v>
       </c>
       <c r="H290" s="3">
         <v>1</v>
@@ -11527,16 +11537,16 @@
         <v>0</v>
       </c>
       <c r="M290" s="22" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="291" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C291" s="3">
+        <v>92000006</v>
+      </c>
+      <c r="D291" s="3">
         <v>92000007</v>
       </c>
-      <c r="D291" s="3">
-        <v>92000008</v>
-      </c>
       <c r="E291" s="2">
         <v>1</v>
       </c>
@@ -11544,7 +11554,7 @@
         <v>100</v>
       </c>
       <c r="G291" s="3">
-        <v>10060700</v>
+        <v>10060600</v>
       </c>
       <c r="H291" s="3">
         <v>1</v>
@@ -11559,16 +11569,16 @@
         <v>0</v>
       </c>
       <c r="M291" s="22" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="292" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C292" s="3">
+        <v>92000007</v>
+      </c>
+      <c r="D292" s="3">
         <v>92000008</v>
       </c>
-      <c r="D292" s="3">
-        <v>0</v>
-      </c>
       <c r="E292" s="2">
         <v>1</v>
       </c>
@@ -11576,7 +11586,7 @@
         <v>100</v>
       </c>
       <c r="G292" s="3">
-        <v>10000212</v>
+        <v>10060700</v>
       </c>
       <c r="H292" s="3">
         <v>1</v>
@@ -11585,18 +11595,50 @@
         <v>10000136</v>
       </c>
       <c r="J292" s="3">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K292" s="2">
         <v>0</v>
       </c>
-      <c r="M292" s="19" t="s">
+      <c r="M292" s="22" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="293" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C293" s="3">
+        <v>92000008</v>
+      </c>
+      <c r="D293" s="3">
+        <v>0</v>
+      </c>
+      <c r="E293" s="2">
+        <v>1</v>
+      </c>
+      <c r="F293" s="3">
+        <v>100</v>
+      </c>
+      <c r="G293" s="3">
+        <v>10000212</v>
+      </c>
+      <c r="H293" s="3">
+        <v>1</v>
+      </c>
+      <c r="I293" s="9">
+        <v>10000136</v>
+      </c>
+      <c r="J293" s="3">
+        <v>100</v>
+      </c>
+      <c r="K293" s="2">
+        <v>0</v>
+      </c>
+      <c r="M293" s="19" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="293" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="294" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="295" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="296" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StoreSellConfig.xlsx
+++ b/Excel/StoreSellConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F57CA517-8E95-4D4A-B18B-31694B85C432}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BE4E64E-9674-4D9B-AC00-B995F93E7B64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="166">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="169">
   <si>
     <t>Id</t>
   </si>
@@ -643,6 +643,17 @@
   </si>
   <si>
     <t>无字之碑</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>生肖传承碎片</t>
+  </si>
+  <si>
+    <t>生肖之灵</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>梦境之核</t>
     <phoneticPr fontId="15" type="noConversion"/>
   </si>
 </sst>
@@ -1942,7 +1953,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2008,10 +2019,13 @@
     <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2657,7 +2671,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q296"/>
+  <dimension ref="A1:Q299"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="5" width="14" customWidth="1"/>
@@ -10957,7 +10971,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="273" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="273" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C273" s="3">
         <v>90000002</v>
       </c>
@@ -10990,7 +11004,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="274" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="274" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C274" s="3">
         <v>90000003</v>
       </c>
@@ -11023,7 +11037,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="275" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="275" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C275" s="3">
         <v>90000004</v>
       </c>
@@ -11056,7 +11070,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="276" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="276" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C276" s="3">
         <v>90000005</v>
       </c>
@@ -11089,7 +11103,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="277" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="277" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C277" s="3">
         <v>90000006</v>
       </c>
@@ -11122,12 +11136,12 @@
         <v>45</v>
       </c>
     </row>
-    <row r="278" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="278" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C278" s="3">
         <v>90000007</v>
       </c>
       <c r="D278" s="3">
-        <v>0</v>
+        <v>90000008</v>
       </c>
       <c r="E278" s="2">
         <v>1</v>
@@ -11155,117 +11169,120 @@
         <v>105</v>
       </c>
     </row>
-    <row r="279" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="279" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C279" s="3">
+        <v>90000008</v>
+      </c>
+      <c r="D279" s="3">
+        <v>90000009</v>
+      </c>
+      <c r="E279" s="2">
+        <v>1</v>
+      </c>
+      <c r="F279" s="3">
+        <v>100</v>
+      </c>
+      <c r="G279" s="3">
+        <v>10010090</v>
+      </c>
+      <c r="H279" s="3">
+        <v>1</v>
+      </c>
+      <c r="I279" s="8">
+        <v>10000184</v>
+      </c>
+      <c r="J279" s="8">
+        <v>80</v>
+      </c>
+      <c r="K279" s="2">
+        <v>0</v>
+      </c>
+      <c r="L279" s="2"/>
+      <c r="M279" s="11" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="280" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C280" s="3">
+        <v>90000009</v>
+      </c>
+      <c r="D280" s="3">
+        <v>90000010</v>
+      </c>
+      <c r="E280" s="2">
+        <v>1</v>
+      </c>
+      <c r="F280" s="3">
+        <v>100</v>
+      </c>
+      <c r="G280" s="3">
+        <v>10010037</v>
+      </c>
+      <c r="H280" s="3">
+        <v>1</v>
+      </c>
+      <c r="I280" s="8">
+        <v>10000184</v>
+      </c>
+      <c r="J280" s="8">
+        <v>2</v>
+      </c>
+      <c r="K280" s="2">
+        <v>0</v>
+      </c>
+      <c r="L280" s="2"/>
+      <c r="M280" s="25" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="281" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C281" s="3">
+        <v>90000010</v>
+      </c>
+      <c r="D281" s="3">
+        <v>0</v>
+      </c>
+      <c r="E281" s="2">
+        <v>1</v>
+      </c>
+      <c r="F281" s="3">
+        <v>100</v>
+      </c>
+      <c r="G281" s="3">
+        <v>10000179</v>
+      </c>
+      <c r="H281" s="3">
+        <v>1</v>
+      </c>
+      <c r="I281" s="8">
+        <v>10000184</v>
+      </c>
+      <c r="J281" s="8">
+        <v>35</v>
+      </c>
+      <c r="K281" s="2">
+        <v>0</v>
+      </c>
+      <c r="L281" s="2"/>
+      <c r="M281" s="25" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="282" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C282" s="3">
         <v>91000001</v>
       </c>
-      <c r="D279" s="3">
+      <c r="D282" s="3">
         <v>91000002</v>
       </c>
-      <c r="E279" s="2">
-        <v>1</v>
-      </c>
-      <c r="F279" s="3">
-        <v>100</v>
-      </c>
-      <c r="G279" s="3">
+      <c r="E282" s="2">
+        <v>1</v>
+      </c>
+      <c r="F282" s="3">
+        <v>100</v>
+      </c>
+      <c r="G282" s="3">
         <v>10010086</v>
-      </c>
-      <c r="H279" s="3">
-        <v>1</v>
-      </c>
-      <c r="I279" s="19">
-        <v>36</v>
-      </c>
-      <c r="J279" s="20">
-        <v>8</v>
-      </c>
-      <c r="K279" s="2">
-        <v>0</v>
-      </c>
-      <c r="M279" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="280" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C280" s="3">
-        <v>91000002</v>
-      </c>
-      <c r="D280" s="3">
-        <v>91000003</v>
-      </c>
-      <c r="E280" s="2">
-        <v>1</v>
-      </c>
-      <c r="F280" s="3">
-        <v>100</v>
-      </c>
-      <c r="G280" s="3">
-        <v>10010096</v>
-      </c>
-      <c r="H280" s="3">
-        <v>1</v>
-      </c>
-      <c r="I280" s="19">
-        <v>36</v>
-      </c>
-      <c r="J280" s="20">
-        <v>20</v>
-      </c>
-      <c r="K280" s="2">
-        <v>0</v>
-      </c>
-      <c r="M280" s="3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="281" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C281" s="3">
-        <v>91000003</v>
-      </c>
-      <c r="D281" s="3">
-        <v>91000004</v>
-      </c>
-      <c r="E281" s="2">
-        <v>1</v>
-      </c>
-      <c r="F281" s="3">
-        <v>100</v>
-      </c>
-      <c r="G281" s="3">
-        <v>10010074</v>
-      </c>
-      <c r="H281" s="3">
-        <v>1</v>
-      </c>
-      <c r="I281" s="19">
-        <v>36</v>
-      </c>
-      <c r="J281" s="20">
-        <v>8</v>
-      </c>
-      <c r="K281" s="2">
-        <v>0</v>
-      </c>
-      <c r="M281" s="3" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="282" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C282" s="3">
-        <v>91000004</v>
-      </c>
-      <c r="D282" s="3">
-        <v>91000005</v>
-      </c>
-      <c r="E282" s="2">
-        <v>1</v>
-      </c>
-      <c r="F282" s="3">
-        <v>100</v>
-      </c>
-      <c r="G282" s="3">
-        <v>10010075</v>
       </c>
       <c r="H282" s="3">
         <v>1</v>
@@ -11274,21 +11291,21 @@
         <v>36</v>
       </c>
       <c r="J282" s="20">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="K282" s="2">
         <v>0</v>
       </c>
       <c r="M282" s="3" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="283" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="283" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C283" s="3">
-        <v>91000005</v>
+        <v>91000002</v>
       </c>
       <c r="D283" s="3">
-        <v>91000006</v>
+        <v>91000003</v>
       </c>
       <c r="E283" s="2">
         <v>1</v>
@@ -11296,8 +11313,8 @@
       <c r="F283" s="3">
         <v>100</v>
       </c>
-      <c r="G283" s="2">
-        <v>10010083</v>
+      <c r="G283" s="3">
+        <v>10010096</v>
       </c>
       <c r="H283" s="3">
         <v>1</v>
@@ -11306,21 +11323,21 @@
         <v>36</v>
       </c>
       <c r="J283" s="20">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K283" s="2">
         <v>0</v>
       </c>
-      <c r="M283" s="15" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="284" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M283" s="3" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="284" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C284" s="3">
-        <v>91000006</v>
+        <v>91000003</v>
       </c>
       <c r="D284" s="3">
-        <v>91000007</v>
+        <v>91000004</v>
       </c>
       <c r="E284" s="2">
         <v>1</v>
@@ -11328,8 +11345,8 @@
       <c r="F284" s="3">
         <v>100</v>
       </c>
-      <c r="G284" s="2">
-        <v>10010098</v>
+      <c r="G284" s="3">
+        <v>10010074</v>
       </c>
       <c r="H284" s="3">
         <v>1</v>
@@ -11338,21 +11355,21 @@
         <v>36</v>
       </c>
       <c r="J284" s="20">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K284" s="2">
         <v>0</v>
       </c>
-      <c r="M284" s="15" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="285" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M284" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="285" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C285" s="3">
-        <v>91000007</v>
+        <v>91000004</v>
       </c>
       <c r="D285" s="3">
-        <v>0</v>
+        <v>91000005</v>
       </c>
       <c r="E285" s="2">
         <v>1</v>
@@ -11360,8 +11377,8 @@
       <c r="F285" s="3">
         <v>100</v>
       </c>
-      <c r="G285" s="9">
-        <v>10010040</v>
+      <c r="G285" s="3">
+        <v>10010075</v>
       </c>
       <c r="H285" s="3">
         <v>1</v>
@@ -11370,127 +11387,126 @@
         <v>36</v>
       </c>
       <c r="J285" s="20">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="K285" s="2">
-        <v>1</v>
-      </c>
-      <c r="M285" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="M285" s="3" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="286" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C286" s="3">
+        <v>91000005</v>
+      </c>
+      <c r="D286" s="3">
+        <v>91000006</v>
+      </c>
+      <c r="E286" s="2">
+        <v>1</v>
+      </c>
+      <c r="F286" s="3">
+        <v>100</v>
+      </c>
+      <c r="G286" s="2">
+        <v>10010083</v>
+      </c>
+      <c r="H286" s="3">
+        <v>1</v>
+      </c>
+      <c r="I286" s="19">
+        <v>36</v>
+      </c>
+      <c r="J286" s="20">
+        <v>1</v>
+      </c>
+      <c r="K286" s="2">
+        <v>0</v>
+      </c>
+      <c r="M286" s="15" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="287" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C287" s="3">
+        <v>91000006</v>
+      </c>
+      <c r="D287" s="3">
+        <v>91000007</v>
+      </c>
+      <c r="E287" s="2">
+        <v>1</v>
+      </c>
+      <c r="F287" s="3">
+        <v>100</v>
+      </c>
+      <c r="G287" s="2">
+        <v>10010098</v>
+      </c>
+      <c r="H287" s="3">
+        <v>1</v>
+      </c>
+      <c r="I287" s="19">
+        <v>36</v>
+      </c>
+      <c r="J287" s="20">
+        <v>1</v>
+      </c>
+      <c r="K287" s="2">
+        <v>0</v>
+      </c>
+      <c r="M287" s="15" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="288" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C288" s="3">
+        <v>91000007</v>
+      </c>
+      <c r="D288" s="3">
+        <v>0</v>
+      </c>
+      <c r="E288" s="2">
+        <v>1</v>
+      </c>
+      <c r="F288" s="3">
+        <v>100</v>
+      </c>
+      <c r="G288" s="9">
+        <v>10010040</v>
+      </c>
+      <c r="H288" s="3">
+        <v>1</v>
+      </c>
+      <c r="I288" s="19">
+        <v>36</v>
+      </c>
+      <c r="J288" s="20">
+        <v>100</v>
+      </c>
+      <c r="K288" s="2">
+        <v>1</v>
+      </c>
+      <c r="M288" s="9" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="286" spans="3:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C286" s="3">
+    <row r="289" spans="3:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C289" s="3">
         <v>92000001</v>
       </c>
-      <c r="D286" s="3">
+      <c r="D289" s="3">
         <v>92000002</v>
       </c>
-      <c r="E286" s="2">
-        <v>1</v>
-      </c>
-      <c r="F286" s="3">
-        <v>100</v>
-      </c>
-      <c r="G286" s="3">
+      <c r="E289" s="2">
+        <v>1</v>
+      </c>
+      <c r="F289" s="3">
+        <v>100</v>
+      </c>
+      <c r="G289" s="3">
         <v>10060100</v>
-      </c>
-      <c r="H286" s="3">
-        <v>1</v>
-      </c>
-      <c r="I286" s="9">
-        <v>10000136</v>
-      </c>
-      <c r="J286" s="3">
-        <v>50</v>
-      </c>
-      <c r="K286" s="2">
-        <v>0</v>
-      </c>
-      <c r="M286" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q286" s="7"/>
-    </row>
-    <row r="287" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C287" s="3">
-        <v>92000002</v>
-      </c>
-      <c r="D287" s="3">
-        <v>92000003</v>
-      </c>
-      <c r="E287" s="2">
-        <v>1</v>
-      </c>
-      <c r="F287" s="3">
-        <v>100</v>
-      </c>
-      <c r="G287" s="3">
-        <v>10060200</v>
-      </c>
-      <c r="H287" s="3">
-        <v>1</v>
-      </c>
-      <c r="I287" s="9">
-        <v>10000136</v>
-      </c>
-      <c r="J287" s="3">
-        <v>50</v>
-      </c>
-      <c r="K287" s="2">
-        <v>0</v>
-      </c>
-      <c r="M287" s="22" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="288" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C288" s="3">
-        <v>92000003</v>
-      </c>
-      <c r="D288" s="3">
-        <v>92000004</v>
-      </c>
-      <c r="E288" s="2">
-        <v>1</v>
-      </c>
-      <c r="F288" s="3">
-        <v>100</v>
-      </c>
-      <c r="G288" s="3">
-        <v>10060300</v>
-      </c>
-      <c r="H288" s="3">
-        <v>1</v>
-      </c>
-      <c r="I288" s="9">
-        <v>10000136</v>
-      </c>
-      <c r="J288" s="3">
-        <v>50</v>
-      </c>
-      <c r="K288" s="2">
-        <v>0</v>
-      </c>
-      <c r="M288" s="22" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="289" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C289" s="3">
-        <v>92000004</v>
-      </c>
-      <c r="D289" s="3">
-        <v>92000005</v>
-      </c>
-      <c r="E289" s="2">
-        <v>1</v>
-      </c>
-      <c r="F289" s="3">
-        <v>100</v>
-      </c>
-      <c r="G289" s="3">
-        <v>10060400</v>
       </c>
       <c r="H289" s="3">
         <v>1</v>
@@ -11505,15 +11521,16 @@
         <v>0</v>
       </c>
       <c r="M289" s="22" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="290" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>123</v>
+      </c>
+      <c r="Q289" s="7"/>
+    </row>
+    <row r="290" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C290" s="3">
-        <v>92000005</v>
+        <v>92000002</v>
       </c>
       <c r="D290" s="3">
-        <v>92000006</v>
+        <v>92000003</v>
       </c>
       <c r="E290" s="2">
         <v>1</v>
@@ -11522,7 +11539,7 @@
         <v>100</v>
       </c>
       <c r="G290" s="3">
-        <v>10060500</v>
+        <v>10060200</v>
       </c>
       <c r="H290" s="3">
         <v>1</v>
@@ -11537,15 +11554,15 @@
         <v>0</v>
       </c>
       <c r="M290" s="22" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="291" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="291" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C291" s="3">
-        <v>92000006</v>
+        <v>92000003</v>
       </c>
       <c r="D291" s="3">
-        <v>92000007</v>
+        <v>92000004</v>
       </c>
       <c r="E291" s="2">
         <v>1</v>
@@ -11554,7 +11571,7 @@
         <v>100</v>
       </c>
       <c r="G291" s="3">
-        <v>10060600</v>
+        <v>10060300</v>
       </c>
       <c r="H291" s="3">
         <v>1</v>
@@ -11569,15 +11586,15 @@
         <v>0</v>
       </c>
       <c r="M291" s="22" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="292" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="292" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C292" s="3">
-        <v>92000007</v>
+        <v>92000004</v>
       </c>
       <c r="D292" s="3">
-        <v>92000008</v>
+        <v>92000005</v>
       </c>
       <c r="E292" s="2">
         <v>1</v>
@@ -11586,7 +11603,7 @@
         <v>100</v>
       </c>
       <c r="G292" s="3">
-        <v>10060700</v>
+        <v>10060400</v>
       </c>
       <c r="H292" s="3">
         <v>1</v>
@@ -11601,15 +11618,15 @@
         <v>0</v>
       </c>
       <c r="M292" s="22" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="293" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="293" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C293" s="3">
-        <v>92000008</v>
+        <v>92000005</v>
       </c>
       <c r="D293" s="3">
-        <v>0</v>
+        <v>92000006</v>
       </c>
       <c r="E293" s="2">
         <v>1</v>
@@ -11618,7 +11635,7 @@
         <v>100</v>
       </c>
       <c r="G293" s="3">
-        <v>10000212</v>
+        <v>10060500</v>
       </c>
       <c r="H293" s="3">
         <v>1</v>
@@ -11627,18 +11644,114 @@
         <v>10000136</v>
       </c>
       <c r="J293" s="3">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K293" s="2">
         <v>0</v>
       </c>
-      <c r="M293" s="19" t="s">
+      <c r="M293" s="22" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="294" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C294" s="3">
+        <v>92000006</v>
+      </c>
+      <c r="D294" s="3">
+        <v>92000007</v>
+      </c>
+      <c r="E294" s="2">
+        <v>1</v>
+      </c>
+      <c r="F294" s="3">
+        <v>100</v>
+      </c>
+      <c r="G294" s="3">
+        <v>10060600</v>
+      </c>
+      <c r="H294" s="3">
+        <v>1</v>
+      </c>
+      <c r="I294" s="9">
+        <v>10000136</v>
+      </c>
+      <c r="J294" s="3">
+        <v>50</v>
+      </c>
+      <c r="K294" s="2">
+        <v>0</v>
+      </c>
+      <c r="M294" s="22" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="295" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C295" s="3">
+        <v>92000007</v>
+      </c>
+      <c r="D295" s="3">
+        <v>92000008</v>
+      </c>
+      <c r="E295" s="2">
+        <v>1</v>
+      </c>
+      <c r="F295" s="3">
+        <v>100</v>
+      </c>
+      <c r="G295" s="3">
+        <v>10060700</v>
+      </c>
+      <c r="H295" s="3">
+        <v>1</v>
+      </c>
+      <c r="I295" s="9">
+        <v>10000136</v>
+      </c>
+      <c r="J295" s="3">
+        <v>50</v>
+      </c>
+      <c r="K295" s="2">
+        <v>0</v>
+      </c>
+      <c r="M295" s="22" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="296" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C296" s="3">
+        <v>92000008</v>
+      </c>
+      <c r="D296" s="3">
+        <v>0</v>
+      </c>
+      <c r="E296" s="2">
+        <v>1</v>
+      </c>
+      <c r="F296" s="3">
+        <v>100</v>
+      </c>
+      <c r="G296" s="3">
+        <v>10000212</v>
+      </c>
+      <c r="H296" s="3">
+        <v>1</v>
+      </c>
+      <c r="I296" s="9">
+        <v>10000136</v>
+      </c>
+      <c r="J296" s="3">
+        <v>100</v>
+      </c>
+      <c r="K296" s="2">
+        <v>0</v>
+      </c>
+      <c r="M296" s="19" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="294" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="297" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="298" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="299" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Excel/StoreSellConfig.xlsx
+++ b/Excel/StoreSellConfig.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3BE4E64E-9674-4D9B-AC00-B995F93E7B64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E562987-A13C-4E05-8D52-06B854D35BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2025,7 +2025,7 @@
     <xf numFmtId="49" fontId="5" fillId="5" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -11258,7 +11258,7 @@
         <v>10000184</v>
       </c>
       <c r="J281" s="8">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="K281" s="2">
         <v>0</v>

--- a/Excel/StoreSellConfig.xlsx
+++ b/Excel/StoreSellConfig.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E562987-A13C-4E05-8D52-06B854D35BAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18B6D978-DC6F-47B5-ACF2-246888D27DDC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="StoreSellProto" sheetId="1" r:id="rId1"/>
@@ -54,7 +54,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="210" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="171">
   <si>
     <t>Id</t>
   </si>
@@ -646,14 +646,23 @@
     <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
-    <t>生肖传承碎片</t>
-  </si>
-  <si>
     <t>生肖之灵</t>
     <phoneticPr fontId="15" type="noConversion"/>
   </si>
   <si>
     <t>梦境之核</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>宠之印记</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>生肖传承粉末</t>
+    <phoneticPr fontId="15" type="noConversion"/>
+  </si>
+  <si>
+    <t>宠之冰核</t>
     <phoneticPr fontId="15" type="noConversion"/>
   </si>
 </sst>
@@ -1953,7 +1962,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="28">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -2026,6 +2035,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2671,7 +2686,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Q299"/>
+  <dimension ref="A1:Q301"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="3" max="5" width="14" customWidth="1"/>
@@ -7110,7 +7125,7 @@
         <v>10000151</v>
       </c>
       <c r="J152" s="3">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="K152" s="2">
         <v>0</v>
@@ -7540,7 +7555,7 @@
         <v>51000011</v>
       </c>
       <c r="D166" s="3">
-        <v>0</v>
+        <v>51000012</v>
       </c>
       <c r="E166" s="2">
         <v>1</v>
@@ -7568,182 +7583,181 @@
       </c>
     </row>
     <row r="167" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A167" s="3"/>
-      <c r="B167" s="3"/>
       <c r="C167" s="3">
+        <v>51000012</v>
+      </c>
+      <c r="D167" s="3">
+        <v>51000013</v>
+      </c>
+      <c r="E167" s="2">
+        <v>1</v>
+      </c>
+      <c r="F167" s="3">
+        <v>100</v>
+      </c>
+      <c r="G167" s="3">
+        <v>10000179</v>
+      </c>
+      <c r="H167" s="3">
+        <v>15</v>
+      </c>
+      <c r="I167" s="9">
+        <v>10000167</v>
+      </c>
+      <c r="J167" s="3">
+        <v>10</v>
+      </c>
+      <c r="K167" s="2">
+        <v>0</v>
+      </c>
+      <c r="M167" s="27" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="168" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C168" s="3">
+        <v>51000013</v>
+      </c>
+      <c r="D168" s="3">
+        <v>51000014</v>
+      </c>
+      <c r="E168" s="2">
+        <v>1</v>
+      </c>
+      <c r="F168" s="3">
+        <v>100</v>
+      </c>
+      <c r="G168" s="9">
+        <v>10000169</v>
+      </c>
+      <c r="H168" s="3">
+        <v>1</v>
+      </c>
+      <c r="I168" s="9">
+        <v>10000167</v>
+      </c>
+      <c r="J168" s="3">
+        <v>1</v>
+      </c>
+      <c r="K168" s="2">
+        <v>0</v>
+      </c>
+      <c r="M168" s="27" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="169" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C169" s="3">
+        <v>51000014</v>
+      </c>
+      <c r="D169" s="3">
+        <v>0</v>
+      </c>
+      <c r="E169" s="2">
+        <v>1</v>
+      </c>
+      <c r="F169" s="3">
+        <v>100</v>
+      </c>
+      <c r="G169" s="26">
+        <v>10010090</v>
+      </c>
+      <c r="H169" s="3">
+        <v>1</v>
+      </c>
+      <c r="I169" s="9">
+        <v>10000167</v>
+      </c>
+      <c r="J169" s="3">
+        <v>1</v>
+      </c>
+      <c r="K169" s="2">
+        <v>0</v>
+      </c>
+      <c r="M169" s="27" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="170" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A170" s="3"/>
+      <c r="B170" s="3"/>
+      <c r="C170" s="3">
         <v>60000001</v>
       </c>
-      <c r="D167" s="3">
+      <c r="D170" s="3">
         <v>60000002</v>
       </c>
-      <c r="E167" s="3">
-        <v>1</v>
-      </c>
-      <c r="F167" s="3">
-        <v>100</v>
-      </c>
-      <c r="G167" s="3">
+      <c r="E170" s="3">
+        <v>1</v>
+      </c>
+      <c r="F170" s="3">
+        <v>100</v>
+      </c>
+      <c r="G170" s="3">
         <v>10000143</v>
       </c>
-      <c r="H167" s="11" t="s">
+      <c r="H170" s="11" t="s">
         <v>46</v>
       </c>
-      <c r="I167" s="9">
+      <c r="I170" s="9">
         <v>10000157</v>
       </c>
-      <c r="J167" s="3">
-        <v>1</v>
-      </c>
-      <c r="K167" s="2">
-        <v>0</v>
-      </c>
-      <c r="L167" s="3"/>
-      <c r="M167" s="15" t="s">
+      <c r="J170" s="3">
+        <v>1</v>
+      </c>
+      <c r="K170" s="2">
+        <v>0</v>
+      </c>
+      <c r="L170" s="3"/>
+      <c r="M170" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="N167" s="3"/>
-      <c r="P167" s="3"/>
-    </row>
-    <row r="168" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A168" s="3"/>
-      <c r="B168" s="3"/>
-      <c r="C168" s="3">
+      <c r="N170" s="3"/>
+      <c r="P170" s="3"/>
+    </row>
+    <row r="171" spans="1:16" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A171" s="3"/>
+      <c r="B171" s="3"/>
+      <c r="C171" s="3">
         <v>60000002</v>
       </c>
-      <c r="D168" s="3">
+      <c r="D171" s="3">
         <v>60000003</v>
       </c>
-      <c r="E168" s="3">
-        <v>1</v>
-      </c>
-      <c r="F168" s="3">
-        <v>100</v>
-      </c>
-      <c r="G168" s="3">
+      <c r="E171" s="3">
+        <v>1</v>
+      </c>
+      <c r="F171" s="3">
+        <v>100</v>
+      </c>
+      <c r="G171" s="3">
         <v>10010093</v>
       </c>
-      <c r="H168" s="12">
-        <v>1</v>
-      </c>
-      <c r="I168" s="9">
+      <c r="H171" s="12">
+        <v>1</v>
+      </c>
+      <c r="I171" s="9">
         <v>10000143</v>
       </c>
-      <c r="J168" s="11" t="s">
+      <c r="J171" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="K168" s="2">
-        <v>0</v>
-      </c>
-      <c r="L168" s="3"/>
-      <c r="M168" s="12" t="s">
+      <c r="K171" s="2">
+        <v>0</v>
+      </c>
+      <c r="L171" s="3"/>
+      <c r="M171" s="12" t="s">
         <v>49</v>
       </c>
-      <c r="N168" s="3"/>
-      <c r="P168" s="3"/>
-    </row>
-    <row r="169" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C169" s="3">
-        <v>60000003</v>
-      </c>
-      <c r="D169" s="3">
-        <v>60000004</v>
-      </c>
-      <c r="E169" s="3">
-        <v>1</v>
-      </c>
-      <c r="F169" s="3">
-        <v>100</v>
-      </c>
-      <c r="G169" s="13">
-        <v>10012001</v>
-      </c>
-      <c r="H169" s="3">
-        <v>1</v>
-      </c>
-      <c r="I169" s="3">
-        <v>10010029</v>
-      </c>
-      <c r="J169" s="3">
-        <v>10</v>
-      </c>
-      <c r="K169" s="2">
-        <v>0</v>
-      </c>
-      <c r="M169" s="13" t="s">
-        <v>50</v>
-      </c>
-      <c r="O169" s="2"/>
-    </row>
-    <row r="170" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C170" s="3">
-        <v>60000004</v>
-      </c>
-      <c r="D170" s="3">
-        <v>60000005</v>
-      </c>
-      <c r="E170" s="3">
-        <v>1</v>
-      </c>
-      <c r="F170" s="3">
-        <v>100</v>
-      </c>
-      <c r="G170" s="13">
-        <v>10012002</v>
-      </c>
-      <c r="H170" s="3">
-        <v>1</v>
-      </c>
-      <c r="I170" s="3">
-        <v>10010029</v>
-      </c>
-      <c r="J170" s="3">
-        <v>10</v>
-      </c>
-      <c r="K170" s="2">
-        <v>0</v>
-      </c>
-      <c r="M170" s="13" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="171" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C171" s="3">
-        <v>60000005</v>
-      </c>
-      <c r="D171" s="3">
-        <v>60000006</v>
-      </c>
-      <c r="E171" s="3">
-        <v>1</v>
-      </c>
-      <c r="F171" s="3">
-        <v>100</v>
-      </c>
-      <c r="G171" s="13">
-        <v>10012003</v>
-      </c>
-      <c r="H171" s="3">
-        <v>1</v>
-      </c>
-      <c r="I171" s="3">
-        <v>10010029</v>
-      </c>
-      <c r="J171" s="3">
-        <v>10</v>
-      </c>
-      <c r="K171" s="2">
-        <v>0</v>
-      </c>
-      <c r="M171" s="13" t="s">
-        <v>52</v>
-      </c>
+      <c r="N171" s="3"/>
+      <c r="P171" s="3"/>
     </row>
     <row r="172" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C172" s="3">
-        <v>60000006</v>
+        <v>60000003</v>
       </c>
       <c r="D172" s="3">
-        <v>60000007</v>
+        <v>60000004</v>
       </c>
       <c r="E172" s="3">
         <v>1</v>
@@ -7752,7 +7766,7 @@
         <v>100</v>
       </c>
       <c r="G172" s="13">
-        <v>10012004</v>
+        <v>10012001</v>
       </c>
       <c r="H172" s="3">
         <v>1</v>
@@ -7767,15 +7781,16 @@
         <v>0</v>
       </c>
       <c r="M172" s="13" t="s">
-        <v>53</v>
-      </c>
+        <v>50</v>
+      </c>
+      <c r="O172" s="2"/>
     </row>
     <row r="173" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C173" s="3">
-        <v>60000007</v>
+        <v>60000004</v>
       </c>
       <c r="D173" s="3">
-        <v>60000008</v>
+        <v>60000005</v>
       </c>
       <c r="E173" s="3">
         <v>1</v>
@@ -7784,7 +7799,7 @@
         <v>100</v>
       </c>
       <c r="G173" s="13">
-        <v>10012005</v>
+        <v>10012002</v>
       </c>
       <c r="H173" s="3">
         <v>1</v>
@@ -7799,15 +7814,15 @@
         <v>0</v>
       </c>
       <c r="M173" s="13" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
     </row>
     <row r="174" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C174" s="3">
-        <v>60000008</v>
+        <v>60000005</v>
       </c>
       <c r="D174" s="3">
-        <v>60000009</v>
+        <v>60000006</v>
       </c>
       <c r="E174" s="3">
         <v>1</v>
@@ -7816,7 +7831,7 @@
         <v>100</v>
       </c>
       <c r="G174" s="13">
-        <v>10012006</v>
+        <v>10012003</v>
       </c>
       <c r="H174" s="3">
         <v>1</v>
@@ -7831,15 +7846,15 @@
         <v>0</v>
       </c>
       <c r="M174" s="13" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
     </row>
     <row r="175" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C175" s="3">
-        <v>60000009</v>
+        <v>60000006</v>
       </c>
       <c r="D175" s="3">
-        <v>60000010</v>
+        <v>60000007</v>
       </c>
       <c r="E175" s="3">
         <v>1</v>
@@ -7848,7 +7863,7 @@
         <v>100</v>
       </c>
       <c r="G175" s="13">
-        <v>10012007</v>
+        <v>10012004</v>
       </c>
       <c r="H175" s="3">
         <v>1</v>
@@ -7863,15 +7878,15 @@
         <v>0</v>
       </c>
       <c r="M175" s="13" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
     </row>
     <row r="176" spans="1:16" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C176" s="3">
-        <v>60000010</v>
+        <v>60000007</v>
       </c>
       <c r="D176" s="3">
-        <v>60000011</v>
+        <v>60000008</v>
       </c>
       <c r="E176" s="3">
         <v>1</v>
@@ -7880,7 +7895,7 @@
         <v>100</v>
       </c>
       <c r="G176" s="13">
-        <v>10012008</v>
+        <v>10012005</v>
       </c>
       <c r="H176" s="3">
         <v>1</v>
@@ -7895,15 +7910,15 @@
         <v>0</v>
       </c>
       <c r="M176" s="13" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="177" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C177" s="3">
-        <v>60000011</v>
+        <v>60000008</v>
       </c>
       <c r="D177" s="3">
-        <v>60000012</v>
+        <v>60000009</v>
       </c>
       <c r="E177" s="3">
         <v>1</v>
@@ -7912,7 +7927,7 @@
         <v>100</v>
       </c>
       <c r="G177" s="13">
-        <v>10012009</v>
+        <v>10012006</v>
       </c>
       <c r="H177" s="3">
         <v>1</v>
@@ -7927,15 +7942,15 @@
         <v>0</v>
       </c>
       <c r="M177" s="13" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="178" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C178" s="3">
-        <v>60000012</v>
+        <v>60000009</v>
       </c>
       <c r="D178" s="3">
-        <v>60000013</v>
+        <v>60000010</v>
       </c>
       <c r="E178" s="3">
         <v>1</v>
@@ -7944,7 +7959,7 @@
         <v>100</v>
       </c>
       <c r="G178" s="13">
-        <v>10012010</v>
+        <v>10012007</v>
       </c>
       <c r="H178" s="3">
         <v>1</v>
@@ -7959,15 +7974,15 @@
         <v>0</v>
       </c>
       <c r="M178" s="13" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="179" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C179" s="3">
-        <v>60000013</v>
+        <v>60000010</v>
       </c>
       <c r="D179" s="3">
-        <v>60000014</v>
+        <v>60000011</v>
       </c>
       <c r="E179" s="3">
         <v>1</v>
@@ -7976,7 +7991,7 @@
         <v>100</v>
       </c>
       <c r="G179" s="13">
-        <v>10012011</v>
+        <v>10012008</v>
       </c>
       <c r="H179" s="3">
         <v>1</v>
@@ -7991,15 +8006,15 @@
         <v>0</v>
       </c>
       <c r="M179" s="13" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="180" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C180" s="3">
-        <v>60000014</v>
+        <v>60000011</v>
       </c>
       <c r="D180" s="3">
-        <v>60000015</v>
+        <v>60000012</v>
       </c>
       <c r="E180" s="3">
         <v>1</v>
@@ -8008,7 +8023,7 @@
         <v>100</v>
       </c>
       <c r="G180" s="13">
-        <v>10012012</v>
+        <v>10012009</v>
       </c>
       <c r="H180" s="3">
         <v>1</v>
@@ -8023,15 +8038,15 @@
         <v>0</v>
       </c>
       <c r="M180" s="13" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="181" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C181" s="3">
-        <v>60000015</v>
+        <v>60000012</v>
       </c>
       <c r="D181" s="3">
-        <v>60000016</v>
+        <v>60000013</v>
       </c>
       <c r="E181" s="3">
         <v>1</v>
@@ -8040,7 +8055,7 @@
         <v>100</v>
       </c>
       <c r="G181" s="13">
-        <v>10012013</v>
+        <v>10012010</v>
       </c>
       <c r="H181" s="3">
         <v>1</v>
@@ -8055,15 +8070,15 @@
         <v>0</v>
       </c>
       <c r="M181" s="13" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="182" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C182" s="3">
-        <v>60000016</v>
+        <v>60000013</v>
       </c>
       <c r="D182" s="3">
-        <v>60000017</v>
+        <v>60000014</v>
       </c>
       <c r="E182" s="3">
         <v>1</v>
@@ -8072,7 +8087,7 @@
         <v>100</v>
       </c>
       <c r="G182" s="13">
-        <v>10012014</v>
+        <v>10012011</v>
       </c>
       <c r="H182" s="3">
         <v>1</v>
@@ -8087,15 +8102,15 @@
         <v>0</v>
       </c>
       <c r="M182" s="13" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="183" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C183" s="3">
-        <v>60000017</v>
+        <v>60000014</v>
       </c>
       <c r="D183" s="3">
-        <v>60000018</v>
+        <v>60000015</v>
       </c>
       <c r="E183" s="3">
         <v>1</v>
@@ -8104,7 +8119,7 @@
         <v>100</v>
       </c>
       <c r="G183" s="13">
-        <v>10012015</v>
+        <v>10012012</v>
       </c>
       <c r="H183" s="3">
         <v>1</v>
@@ -8119,15 +8134,15 @@
         <v>0</v>
       </c>
       <c r="M183" s="13" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="184" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C184" s="3">
-        <v>60000018</v>
+        <v>60000015</v>
       </c>
       <c r="D184" s="3">
-        <v>60000019</v>
+        <v>60000016</v>
       </c>
       <c r="E184" s="3">
         <v>1</v>
@@ -8136,7 +8151,7 @@
         <v>100</v>
       </c>
       <c r="G184" s="13">
-        <v>10012016</v>
+        <v>10012013</v>
       </c>
       <c r="H184" s="3">
         <v>1</v>
@@ -8151,15 +8166,15 @@
         <v>0</v>
       </c>
       <c r="M184" s="13" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="185" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C185" s="3">
-        <v>60000019</v>
+        <v>60000016</v>
       </c>
       <c r="D185" s="3">
-        <v>60000020</v>
+        <v>60000017</v>
       </c>
       <c r="E185" s="3">
         <v>1</v>
@@ -8168,7 +8183,7 @@
         <v>100</v>
       </c>
       <c r="G185" s="13">
-        <v>10012017</v>
+        <v>10012014</v>
       </c>
       <c r="H185" s="3">
         <v>1</v>
@@ -8183,15 +8198,15 @@
         <v>0</v>
       </c>
       <c r="M185" s="13" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="186" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C186" s="3">
-        <v>60000020</v>
+        <v>60000017</v>
       </c>
       <c r="D186" s="3">
-        <v>60000021</v>
+        <v>60000018</v>
       </c>
       <c r="E186" s="3">
         <v>1</v>
@@ -8200,7 +8215,7 @@
         <v>100</v>
       </c>
       <c r="G186" s="13">
-        <v>10012018</v>
+        <v>10012015</v>
       </c>
       <c r="H186" s="3">
         <v>1</v>
@@ -8215,15 +8230,15 @@
         <v>0</v>
       </c>
       <c r="M186" s="13" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
     </row>
     <row r="187" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C187" s="3">
-        <v>60000021</v>
+        <v>60000018</v>
       </c>
       <c r="D187" s="3">
-        <v>60000022</v>
+        <v>60000019</v>
       </c>
       <c r="E187" s="3">
         <v>1</v>
@@ -8232,7 +8247,7 @@
         <v>100</v>
       </c>
       <c r="G187" s="13">
-        <v>10012019</v>
+        <v>10012016</v>
       </c>
       <c r="H187" s="3">
         <v>1</v>
@@ -8247,15 +8262,15 @@
         <v>0</v>
       </c>
       <c r="M187" s="13" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
     </row>
     <row r="188" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C188" s="3">
-        <v>60000022</v>
+        <v>60000019</v>
       </c>
       <c r="D188" s="3">
-        <v>60000023</v>
+        <v>60000020</v>
       </c>
       <c r="E188" s="3">
         <v>1</v>
@@ -8264,7 +8279,7 @@
         <v>100</v>
       </c>
       <c r="G188" s="13">
-        <v>10012020</v>
+        <v>10012017</v>
       </c>
       <c r="H188" s="3">
         <v>1</v>
@@ -8273,21 +8288,21 @@
         <v>10010029</v>
       </c>
       <c r="J188" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K188" s="2">
         <v>0</v>
       </c>
       <c r="M188" s="13" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
     </row>
     <row r="189" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C189" s="3">
-        <v>60000023</v>
+        <v>60000020</v>
       </c>
       <c r="D189" s="3">
-        <v>60000024</v>
+        <v>60000021</v>
       </c>
       <c r="E189" s="3">
         <v>1</v>
@@ -8296,7 +8311,7 @@
         <v>100</v>
       </c>
       <c r="G189" s="13">
-        <v>10012021</v>
+        <v>10012018</v>
       </c>
       <c r="H189" s="3">
         <v>1</v>
@@ -8305,21 +8320,21 @@
         <v>10010029</v>
       </c>
       <c r="J189" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K189" s="2">
         <v>0</v>
       </c>
       <c r="M189" s="13" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="190" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C190" s="3">
-        <v>60000024</v>
+        <v>60000021</v>
       </c>
       <c r="D190" s="3">
-        <v>60000025</v>
+        <v>60000022</v>
       </c>
       <c r="E190" s="3">
         <v>1</v>
@@ -8328,7 +8343,7 @@
         <v>100</v>
       </c>
       <c r="G190" s="13">
-        <v>10012022</v>
+        <v>10012019</v>
       </c>
       <c r="H190" s="3">
         <v>1</v>
@@ -8337,21 +8352,21 @@
         <v>10010029</v>
       </c>
       <c r="J190" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="K190" s="2">
         <v>0</v>
       </c>
       <c r="M190" s="13" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="191" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C191" s="3">
-        <v>60000025</v>
+        <v>60000022</v>
       </c>
       <c r="D191" s="3">
-        <v>60000026</v>
+        <v>60000023</v>
       </c>
       <c r="E191" s="3">
         <v>1</v>
@@ -8360,7 +8375,7 @@
         <v>100</v>
       </c>
       <c r="G191" s="13">
-        <v>10012023</v>
+        <v>10012020</v>
       </c>
       <c r="H191" s="3">
         <v>1</v>
@@ -8375,15 +8390,15 @@
         <v>0</v>
       </c>
       <c r="M191" s="13" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="192" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C192" s="3">
-        <v>60000026</v>
+        <v>60000023</v>
       </c>
       <c r="D192" s="3">
-        <v>60000027</v>
+        <v>60000024</v>
       </c>
       <c r="E192" s="3">
         <v>1</v>
@@ -8392,7 +8407,7 @@
         <v>100</v>
       </c>
       <c r="G192" s="13">
-        <v>10012024</v>
+        <v>10012021</v>
       </c>
       <c r="H192" s="3">
         <v>1</v>
@@ -8407,15 +8422,15 @@
         <v>0</v>
       </c>
       <c r="M192" s="13" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="193" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C193" s="3">
-        <v>60000027</v>
+        <v>60000024</v>
       </c>
       <c r="D193" s="3">
-        <v>60000028</v>
+        <v>60000025</v>
       </c>
       <c r="E193" s="3">
         <v>1</v>
@@ -8424,7 +8439,7 @@
         <v>100</v>
       </c>
       <c r="G193" s="13">
-        <v>10012025</v>
+        <v>10012022</v>
       </c>
       <c r="H193" s="3">
         <v>1</v>
@@ -8439,15 +8454,15 @@
         <v>0</v>
       </c>
       <c r="M193" s="13" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
     </row>
     <row r="194" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C194" s="3">
-        <v>60000028</v>
+        <v>60000025</v>
       </c>
       <c r="D194" s="3">
-        <v>60000029</v>
+        <v>60000026</v>
       </c>
       <c r="E194" s="3">
         <v>1</v>
@@ -8456,7 +8471,7 @@
         <v>100</v>
       </c>
       <c r="G194" s="13">
-        <v>10012026</v>
+        <v>10012023</v>
       </c>
       <c r="H194" s="3">
         <v>1</v>
@@ -8471,15 +8486,15 @@
         <v>0</v>
       </c>
       <c r="M194" s="13" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
     </row>
     <row r="195" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C195" s="3">
-        <v>60000029</v>
+        <v>60000026</v>
       </c>
       <c r="D195" s="3">
-        <v>60000030</v>
+        <v>60000027</v>
       </c>
       <c r="E195" s="3">
         <v>1</v>
@@ -8488,7 +8503,7 @@
         <v>100</v>
       </c>
       <c r="G195" s="13">
-        <v>10012027</v>
+        <v>10012024</v>
       </c>
       <c r="H195" s="3">
         <v>1</v>
@@ -8503,15 +8518,15 @@
         <v>0</v>
       </c>
       <c r="M195" s="13" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="196" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C196" s="3">
-        <v>60000030</v>
+        <v>60000027</v>
       </c>
       <c r="D196" s="3">
-        <v>60000031</v>
+        <v>60000028</v>
       </c>
       <c r="E196" s="3">
         <v>1</v>
@@ -8520,13 +8535,13 @@
         <v>100</v>
       </c>
       <c r="G196" s="13">
-        <v>10013001</v>
+        <v>10012025</v>
       </c>
       <c r="H196" s="3">
         <v>1</v>
       </c>
       <c r="I196" s="3">
-        <v>10010030</v>
+        <v>10010029</v>
       </c>
       <c r="J196" s="3">
         <v>15</v>
@@ -8534,16 +8549,16 @@
       <c r="K196" s="2">
         <v>0</v>
       </c>
-      <c r="M196" s="17" t="s">
-        <v>77</v>
+      <c r="M196" s="13" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="197" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C197" s="3">
-        <v>60000031</v>
+        <v>60000028</v>
       </c>
       <c r="D197" s="3">
-        <v>60000032</v>
+        <v>60000029</v>
       </c>
       <c r="E197" s="3">
         <v>1</v>
@@ -8552,13 +8567,13 @@
         <v>100</v>
       </c>
       <c r="G197" s="13">
-        <v>10013002</v>
+        <v>10012026</v>
       </c>
       <c r="H197" s="3">
         <v>1</v>
       </c>
       <c r="I197" s="3">
-        <v>10010030</v>
+        <v>10010029</v>
       </c>
       <c r="J197" s="3">
         <v>15</v>
@@ -8566,16 +8581,16 @@
       <c r="K197" s="2">
         <v>0</v>
       </c>
-      <c r="M197" s="17" t="s">
-        <v>78</v>
+      <c r="M197" s="13" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="198" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C198" s="3">
-        <v>60000032</v>
+        <v>60000029</v>
       </c>
       <c r="D198" s="3">
-        <v>60000033</v>
+        <v>60000030</v>
       </c>
       <c r="E198" s="3">
         <v>1</v>
@@ -8584,13 +8599,13 @@
         <v>100</v>
       </c>
       <c r="G198" s="13">
-        <v>10013003</v>
+        <v>10012027</v>
       </c>
       <c r="H198" s="3">
         <v>1</v>
       </c>
       <c r="I198" s="3">
-        <v>10010030</v>
+        <v>10010029</v>
       </c>
       <c r="J198" s="3">
         <v>15</v>
@@ -8598,16 +8613,16 @@
       <c r="K198" s="2">
         <v>0</v>
       </c>
-      <c r="M198" s="17" t="s">
-        <v>79</v>
+      <c r="M198" s="13" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="199" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C199" s="3">
-        <v>60000033</v>
+        <v>60000030</v>
       </c>
       <c r="D199" s="3">
-        <v>60000034</v>
+        <v>60000031</v>
       </c>
       <c r="E199" s="3">
         <v>1</v>
@@ -8616,7 +8631,7 @@
         <v>100</v>
       </c>
       <c r="G199" s="13">
-        <v>10013004</v>
+        <v>10013001</v>
       </c>
       <c r="H199" s="3">
         <v>1</v>
@@ -8631,15 +8646,15 @@
         <v>0</v>
       </c>
       <c r="M199" s="17" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
     </row>
     <row r="200" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C200" s="3">
-        <v>60000034</v>
+        <v>60000031</v>
       </c>
       <c r="D200" s="3">
-        <v>60000035</v>
+        <v>60000032</v>
       </c>
       <c r="E200" s="3">
         <v>1</v>
@@ -8648,7 +8663,7 @@
         <v>100</v>
       </c>
       <c r="G200" s="13">
-        <v>10013005</v>
+        <v>10013002</v>
       </c>
       <c r="H200" s="3">
         <v>1</v>
@@ -8663,15 +8678,15 @@
         <v>0</v>
       </c>
       <c r="M200" s="17" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="201" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C201" s="3">
-        <v>60000035</v>
+        <v>60000032</v>
       </c>
       <c r="D201" s="3">
-        <v>60000036</v>
+        <v>60000033</v>
       </c>
       <c r="E201" s="3">
         <v>1</v>
@@ -8680,7 +8695,7 @@
         <v>100</v>
       </c>
       <c r="G201" s="13">
-        <v>10013006</v>
+        <v>10013003</v>
       </c>
       <c r="H201" s="3">
         <v>1</v>
@@ -8695,15 +8710,15 @@
         <v>0</v>
       </c>
       <c r="M201" s="17" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
     </row>
     <row r="202" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C202" s="3">
-        <v>60000036</v>
+        <v>60000033</v>
       </c>
       <c r="D202" s="3">
-        <v>60000037</v>
+        <v>60000034</v>
       </c>
       <c r="E202" s="3">
         <v>1</v>
@@ -8712,7 +8727,7 @@
         <v>100</v>
       </c>
       <c r="G202" s="13">
-        <v>10013007</v>
+        <v>10013004</v>
       </c>
       <c r="H202" s="3">
         <v>1</v>
@@ -8727,15 +8742,15 @@
         <v>0</v>
       </c>
       <c r="M202" s="17" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
     </row>
     <row r="203" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C203" s="3">
-        <v>60000037</v>
+        <v>60000034</v>
       </c>
       <c r="D203" s="3">
-        <v>60000038</v>
+        <v>60000035</v>
       </c>
       <c r="E203" s="3">
         <v>1</v>
@@ -8744,7 +8759,7 @@
         <v>100</v>
       </c>
       <c r="G203" s="13">
-        <v>10013008</v>
+        <v>10013005</v>
       </c>
       <c r="H203" s="3">
         <v>1</v>
@@ -8759,15 +8774,15 @@
         <v>0</v>
       </c>
       <c r="M203" s="17" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="204" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C204" s="3">
-        <v>60000038</v>
+        <v>60000035</v>
       </c>
       <c r="D204" s="3">
-        <v>60000039</v>
+        <v>60000036</v>
       </c>
       <c r="E204" s="3">
         <v>1</v>
@@ -8776,7 +8791,7 @@
         <v>100</v>
       </c>
       <c r="G204" s="13">
-        <v>10013009</v>
+        <v>10013006</v>
       </c>
       <c r="H204" s="3">
         <v>1</v>
@@ -8791,15 +8806,15 @@
         <v>0</v>
       </c>
       <c r="M204" s="17" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="205" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C205" s="3">
-        <v>60000039</v>
+        <v>60000036</v>
       </c>
       <c r="D205" s="3">
-        <v>60000040</v>
+        <v>60000037</v>
       </c>
       <c r="E205" s="3">
         <v>1</v>
@@ -8808,7 +8823,7 @@
         <v>100</v>
       </c>
       <c r="G205" s="13">
-        <v>10013010</v>
+        <v>10013007</v>
       </c>
       <c r="H205" s="3">
         <v>1</v>
@@ -8823,15 +8838,15 @@
         <v>0</v>
       </c>
       <c r="M205" s="17" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
     </row>
     <row r="206" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C206" s="3">
-        <v>60000040</v>
+        <v>60000037</v>
       </c>
       <c r="D206" s="3">
-        <v>60000041</v>
+        <v>60000038</v>
       </c>
       <c r="E206" s="3">
         <v>1</v>
@@ -8840,7 +8855,7 @@
         <v>100</v>
       </c>
       <c r="G206" s="13">
-        <v>10013011</v>
+        <v>10013008</v>
       </c>
       <c r="H206" s="3">
         <v>1</v>
@@ -8855,15 +8870,15 @@
         <v>0</v>
       </c>
       <c r="M206" s="17" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="207" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C207" s="3">
-        <v>60000041</v>
+        <v>60000038</v>
       </c>
       <c r="D207" s="3">
-        <v>60000042</v>
+        <v>60000039</v>
       </c>
       <c r="E207" s="3">
         <v>1</v>
@@ -8872,7 +8887,7 @@
         <v>100</v>
       </c>
       <c r="G207" s="13">
-        <v>10013012</v>
+        <v>10013009</v>
       </c>
       <c r="H207" s="3">
         <v>1</v>
@@ -8887,15 +8902,15 @@
         <v>0</v>
       </c>
       <c r="M207" s="17" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="208" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C208" s="3">
-        <v>60000042</v>
+        <v>60000039</v>
       </c>
       <c r="D208" s="3">
-        <v>60000043</v>
+        <v>60000040</v>
       </c>
       <c r="E208" s="3">
         <v>1</v>
@@ -8904,7 +8919,7 @@
         <v>100</v>
       </c>
       <c r="G208" s="13">
-        <v>10013013</v>
+        <v>10013010</v>
       </c>
       <c r="H208" s="3">
         <v>1</v>
@@ -8919,15 +8934,15 @@
         <v>0</v>
       </c>
       <c r="M208" s="17" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="209" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C209" s="3">
-        <v>60000043</v>
+        <v>60000040</v>
       </c>
       <c r="D209" s="3">
-        <v>60000044</v>
+        <v>60000041</v>
       </c>
       <c r="E209" s="3">
         <v>1</v>
@@ -8936,7 +8951,7 @@
         <v>100</v>
       </c>
       <c r="G209" s="13">
-        <v>10013014</v>
+        <v>10013011</v>
       </c>
       <c r="H209" s="3">
         <v>1</v>
@@ -8951,15 +8966,15 @@
         <v>0</v>
       </c>
       <c r="M209" s="17" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
     </row>
     <row r="210" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C210" s="3">
-        <v>60000044</v>
+        <v>60000041</v>
       </c>
       <c r="D210" s="3">
-        <v>60000045</v>
+        <v>60000042</v>
       </c>
       <c r="E210" s="3">
         <v>1</v>
@@ -8968,7 +8983,7 @@
         <v>100</v>
       </c>
       <c r="G210" s="13">
-        <v>10013015</v>
+        <v>10013012</v>
       </c>
       <c r="H210" s="3">
         <v>1</v>
@@ -8983,15 +8998,15 @@
         <v>0</v>
       </c>
       <c r="M210" s="17" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
     </row>
     <row r="211" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C211" s="3">
-        <v>60000045</v>
+        <v>60000042</v>
       </c>
       <c r="D211" s="3">
-        <v>60000046</v>
+        <v>60000043</v>
       </c>
       <c r="E211" s="3">
         <v>1</v>
@@ -9000,7 +9015,7 @@
         <v>100</v>
       </c>
       <c r="G211" s="13">
-        <v>10013016</v>
+        <v>10013013</v>
       </c>
       <c r="H211" s="3">
         <v>1</v>
@@ -9015,15 +9030,15 @@
         <v>0</v>
       </c>
       <c r="M211" s="17" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
     </row>
     <row r="212" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C212" s="3">
-        <v>60000046</v>
+        <v>60000043</v>
       </c>
       <c r="D212" s="3">
-        <v>60000047</v>
+        <v>60000044</v>
       </c>
       <c r="E212" s="3">
         <v>1</v>
@@ -9032,7 +9047,7 @@
         <v>100</v>
       </c>
       <c r="G212" s="13">
-        <v>10013017</v>
+        <v>10013014</v>
       </c>
       <c r="H212" s="3">
         <v>1</v>
@@ -9047,15 +9062,15 @@
         <v>0</v>
       </c>
       <c r="M212" s="17" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
     </row>
     <row r="213" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C213" s="3">
-        <v>60000047</v>
+        <v>60000044</v>
       </c>
       <c r="D213" s="3">
-        <v>60000048</v>
+        <v>60000045</v>
       </c>
       <c r="E213" s="3">
         <v>1</v>
@@ -9064,7 +9079,7 @@
         <v>100</v>
       </c>
       <c r="G213" s="13">
-        <v>10013018</v>
+        <v>10013015</v>
       </c>
       <c r="H213" s="3">
         <v>1</v>
@@ -9079,15 +9094,15 @@
         <v>0</v>
       </c>
       <c r="M213" s="17" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
     </row>
     <row r="214" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C214" s="3">
-        <v>60000048</v>
+        <v>60000045</v>
       </c>
       <c r="D214" s="3">
-        <v>60000049</v>
+        <v>60000046</v>
       </c>
       <c r="E214" s="3">
         <v>1</v>
@@ -9096,7 +9111,7 @@
         <v>100</v>
       </c>
       <c r="G214" s="13">
-        <v>10013019</v>
+        <v>10013016</v>
       </c>
       <c r="H214" s="3">
         <v>1</v>
@@ -9111,15 +9126,15 @@
         <v>0</v>
       </c>
       <c r="M214" s="17" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
     <row r="215" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C215" s="3">
-        <v>60000049</v>
+        <v>60000046</v>
       </c>
       <c r="D215" s="3">
-        <v>60000050</v>
+        <v>60000047</v>
       </c>
       <c r="E215" s="3">
         <v>1</v>
@@ -9128,7 +9143,7 @@
         <v>100</v>
       </c>
       <c r="G215" s="13">
-        <v>10013020</v>
+        <v>10013017</v>
       </c>
       <c r="H215" s="3">
         <v>1</v>
@@ -9137,21 +9152,21 @@
         <v>10010030</v>
       </c>
       <c r="J215" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K215" s="2">
         <v>0</v>
       </c>
       <c r="M215" s="17" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
     </row>
     <row r="216" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C216" s="3">
-        <v>60000050</v>
+        <v>60000047</v>
       </c>
       <c r="D216" s="3">
-        <v>60000051</v>
+        <v>60000048</v>
       </c>
       <c r="E216" s="3">
         <v>1</v>
@@ -9160,7 +9175,7 @@
         <v>100</v>
       </c>
       <c r="G216" s="13">
-        <v>10013021</v>
+        <v>10013018</v>
       </c>
       <c r="H216" s="3">
         <v>1</v>
@@ -9169,21 +9184,21 @@
         <v>10010030</v>
       </c>
       <c r="J216" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K216" s="2">
         <v>0</v>
       </c>
       <c r="M216" s="17" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
     </row>
     <row r="217" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C217" s="3">
-        <v>60000051</v>
+        <v>60000048</v>
       </c>
       <c r="D217" s="3">
-        <v>60000052</v>
+        <v>60000049</v>
       </c>
       <c r="E217" s="3">
         <v>1</v>
@@ -9192,7 +9207,7 @@
         <v>100</v>
       </c>
       <c r="G217" s="13">
-        <v>10013022</v>
+        <v>10013019</v>
       </c>
       <c r="H217" s="3">
         <v>1</v>
@@ -9201,21 +9216,21 @@
         <v>10010030</v>
       </c>
       <c r="J217" s="3">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="K217" s="2">
         <v>0</v>
       </c>
       <c r="M217" s="17" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
     </row>
     <row r="218" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C218" s="3">
-        <v>60000052</v>
+        <v>60000049</v>
       </c>
       <c r="D218" s="3">
-        <v>60000053</v>
+        <v>60000050</v>
       </c>
       <c r="E218" s="3">
         <v>1</v>
@@ -9224,7 +9239,7 @@
         <v>100</v>
       </c>
       <c r="G218" s="13">
-        <v>10013023</v>
+        <v>10013020</v>
       </c>
       <c r="H218" s="3">
         <v>1</v>
@@ -9239,15 +9254,15 @@
         <v>0</v>
       </c>
       <c r="M218" s="17" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
     </row>
     <row r="219" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C219" s="3">
-        <v>60000053</v>
+        <v>60000050</v>
       </c>
       <c r="D219" s="3">
-        <v>60000054</v>
+        <v>60000051</v>
       </c>
       <c r="E219" s="3">
         <v>1</v>
@@ -9256,7 +9271,7 @@
         <v>100</v>
       </c>
       <c r="G219" s="13">
-        <v>10013024</v>
+        <v>10013021</v>
       </c>
       <c r="H219" s="3">
         <v>1</v>
@@ -9271,15 +9286,15 @@
         <v>0</v>
       </c>
       <c r="M219" s="17" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
     </row>
     <row r="220" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C220" s="3">
-        <v>60000054</v>
+        <v>60000051</v>
       </c>
       <c r="D220" s="3">
-        <v>60000055</v>
+        <v>60000052</v>
       </c>
       <c r="E220" s="3">
         <v>1</v>
@@ -9288,7 +9303,7 @@
         <v>100</v>
       </c>
       <c r="G220" s="13">
-        <v>10013025</v>
+        <v>10013022</v>
       </c>
       <c r="H220" s="3">
         <v>1</v>
@@ -9303,15 +9318,15 @@
         <v>0</v>
       </c>
       <c r="M220" s="17" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
     </row>
     <row r="221" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C221" s="3">
-        <v>60000055</v>
+        <v>60000052</v>
       </c>
       <c r="D221" s="3">
-        <v>60000056</v>
+        <v>60000053</v>
       </c>
       <c r="E221" s="3">
         <v>1</v>
@@ -9320,7 +9335,7 @@
         <v>100</v>
       </c>
       <c r="G221" s="13">
-        <v>10013026</v>
+        <v>10013023</v>
       </c>
       <c r="H221" s="3">
         <v>1</v>
@@ -9335,15 +9350,15 @@
         <v>0</v>
       </c>
       <c r="M221" s="17" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="222" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C222" s="3">
-        <v>60000056</v>
+        <v>60000053</v>
       </c>
       <c r="D222" s="3">
-        <v>60000057</v>
+        <v>60000054</v>
       </c>
       <c r="E222" s="3">
         <v>1</v>
@@ -9352,7 +9367,7 @@
         <v>100</v>
       </c>
       <c r="G222" s="13">
-        <v>10013027</v>
+        <v>10013024</v>
       </c>
       <c r="H222" s="3">
         <v>1</v>
@@ -9367,15 +9382,15 @@
         <v>0</v>
       </c>
       <c r="M222" s="17" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
     </row>
     <row r="223" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C223" s="3">
-        <v>60000057</v>
+        <v>60000054</v>
       </c>
       <c r="D223" s="3">
-        <v>60000058</v>
+        <v>60000055</v>
       </c>
       <c r="E223" s="3">
         <v>1</v>
@@ -9384,13 +9399,13 @@
         <v>100</v>
       </c>
       <c r="G223" s="13">
-        <v>10014001</v>
+        <v>10013025</v>
       </c>
       <c r="H223" s="3">
         <v>1</v>
       </c>
       <c r="I223" s="3">
-        <v>10010031</v>
+        <v>10010030</v>
       </c>
       <c r="J223" s="3">
         <v>20</v>
@@ -9398,16 +9413,16 @@
       <c r="K223" s="2">
         <v>0</v>
       </c>
-      <c r="M223" s="3" t="s">
-        <v>134</v>
+      <c r="M223" s="17" t="s">
+        <v>101</v>
       </c>
     </row>
     <row r="224" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C224" s="3">
-        <v>60000058</v>
+        <v>60000055</v>
       </c>
       <c r="D224" s="3">
-        <v>60000059</v>
+        <v>60000056</v>
       </c>
       <c r="E224" s="3">
         <v>1</v>
@@ -9416,13 +9431,13 @@
         <v>100</v>
       </c>
       <c r="G224" s="13">
-        <v>10014002</v>
+        <v>10013026</v>
       </c>
       <c r="H224" s="3">
         <v>1</v>
       </c>
       <c r="I224" s="3">
-        <v>10010031</v>
+        <v>10010030</v>
       </c>
       <c r="J224" s="3">
         <v>20</v>
@@ -9430,16 +9445,16 @@
       <c r="K224" s="2">
         <v>0</v>
       </c>
-      <c r="M224" s="3" t="s">
-        <v>135</v>
+      <c r="M224" s="17" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="225" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C225" s="3">
-        <v>60000059</v>
+        <v>60000056</v>
       </c>
       <c r="D225" s="3">
-        <v>60000060</v>
+        <v>60000057</v>
       </c>
       <c r="E225" s="3">
         <v>1</v>
@@ -9448,13 +9463,13 @@
         <v>100</v>
       </c>
       <c r="G225" s="13">
-        <v>10014003</v>
+        <v>10013027</v>
       </c>
       <c r="H225" s="3">
         <v>1</v>
       </c>
       <c r="I225" s="3">
-        <v>10010031</v>
+        <v>10010030</v>
       </c>
       <c r="J225" s="3">
         <v>20</v>
@@ -9462,16 +9477,16 @@
       <c r="K225" s="2">
         <v>0</v>
       </c>
-      <c r="M225" s="3" t="s">
-        <v>136</v>
+      <c r="M225" s="17" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="226" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C226" s="3">
-        <v>60000060</v>
+        <v>60000057</v>
       </c>
       <c r="D226" s="3">
-        <v>60000061</v>
+        <v>60000058</v>
       </c>
       <c r="E226" s="3">
         <v>1</v>
@@ -9480,7 +9495,7 @@
         <v>100</v>
       </c>
       <c r="G226" s="13">
-        <v>10014004</v>
+        <v>10014001</v>
       </c>
       <c r="H226" s="3">
         <v>1</v>
@@ -9495,15 +9510,15 @@
         <v>0</v>
       </c>
       <c r="M226" s="3" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
     </row>
     <row r="227" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C227" s="3">
-        <v>60000061</v>
+        <v>60000058</v>
       </c>
       <c r="D227" s="3">
-        <v>60000062</v>
+        <v>60000059</v>
       </c>
       <c r="E227" s="3">
         <v>1</v>
@@ -9512,7 +9527,7 @@
         <v>100</v>
       </c>
       <c r="G227" s="13">
-        <v>10014005</v>
+        <v>10014002</v>
       </c>
       <c r="H227" s="3">
         <v>1</v>
@@ -9527,15 +9542,15 @@
         <v>0</v>
       </c>
       <c r="M227" s="3" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
     </row>
     <row r="228" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C228" s="3">
-        <v>60000062</v>
+        <v>60000059</v>
       </c>
       <c r="D228" s="3">
-        <v>60000063</v>
+        <v>60000060</v>
       </c>
       <c r="E228" s="3">
         <v>1</v>
@@ -9544,7 +9559,7 @@
         <v>100</v>
       </c>
       <c r="G228" s="13">
-        <v>10014006</v>
+        <v>10014003</v>
       </c>
       <c r="H228" s="3">
         <v>1</v>
@@ -9559,15 +9574,15 @@
         <v>0</v>
       </c>
       <c r="M228" s="3" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
     </row>
     <row r="229" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C229" s="3">
-        <v>60000063</v>
+        <v>60000060</v>
       </c>
       <c r="D229" s="3">
-        <v>60000064</v>
+        <v>60000061</v>
       </c>
       <c r="E229" s="3">
         <v>1</v>
@@ -9576,7 +9591,7 @@
         <v>100</v>
       </c>
       <c r="G229" s="13">
-        <v>10014007</v>
+        <v>10014004</v>
       </c>
       <c r="H229" s="3">
         <v>1</v>
@@ -9591,15 +9606,15 @@
         <v>0</v>
       </c>
       <c r="M229" s="3" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
     </row>
     <row r="230" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C230" s="3">
-        <v>60000064</v>
+        <v>60000061</v>
       </c>
       <c r="D230" s="3">
-        <v>60000065</v>
+        <v>60000062</v>
       </c>
       <c r="E230" s="3">
         <v>1</v>
@@ -9608,7 +9623,7 @@
         <v>100</v>
       </c>
       <c r="G230" s="13">
-        <v>10014008</v>
+        <v>10014005</v>
       </c>
       <c r="H230" s="3">
         <v>1</v>
@@ -9623,15 +9638,15 @@
         <v>0</v>
       </c>
       <c r="M230" s="3" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
     </row>
     <row r="231" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C231" s="3">
-        <v>60000065</v>
+        <v>60000062</v>
       </c>
       <c r="D231" s="3">
-        <v>60000066</v>
+        <v>60000063</v>
       </c>
       <c r="E231" s="3">
         <v>1</v>
@@ -9640,7 +9655,7 @@
         <v>100</v>
       </c>
       <c r="G231" s="13">
-        <v>10014009</v>
+        <v>10014006</v>
       </c>
       <c r="H231" s="3">
         <v>1</v>
@@ -9655,15 +9670,15 @@
         <v>0</v>
       </c>
       <c r="M231" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="232" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C232" s="3">
-        <v>60000066</v>
+        <v>60000063</v>
       </c>
       <c r="D232" s="3">
-        <v>60000067</v>
+        <v>60000064</v>
       </c>
       <c r="E232" s="3">
         <v>1</v>
@@ -9672,7 +9687,7 @@
         <v>100</v>
       </c>
       <c r="G232" s="13">
-        <v>10014010</v>
+        <v>10014007</v>
       </c>
       <c r="H232" s="3">
         <v>1</v>
@@ -9687,15 +9702,15 @@
         <v>0</v>
       </c>
       <c r="M232" s="3" t="s">
-        <v>143</v>
+        <v>140</v>
       </c>
     </row>
     <row r="233" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C233" s="3">
-        <v>60000067</v>
+        <v>60000064</v>
       </c>
       <c r="D233" s="3">
-        <v>60000068</v>
+        <v>60000065</v>
       </c>
       <c r="E233" s="3">
         <v>1</v>
@@ -9704,7 +9719,7 @@
         <v>100</v>
       </c>
       <c r="G233" s="13">
-        <v>10014011</v>
+        <v>10014008</v>
       </c>
       <c r="H233" s="3">
         <v>1</v>
@@ -9719,15 +9734,15 @@
         <v>0</v>
       </c>
       <c r="M233" s="3" t="s">
-        <v>144</v>
+        <v>141</v>
       </c>
     </row>
     <row r="234" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C234" s="3">
-        <v>60000068</v>
+        <v>60000065</v>
       </c>
       <c r="D234" s="3">
-        <v>60000069</v>
+        <v>60000066</v>
       </c>
       <c r="E234" s="3">
         <v>1</v>
@@ -9736,7 +9751,7 @@
         <v>100</v>
       </c>
       <c r="G234" s="13">
-        <v>10014012</v>
+        <v>10014009</v>
       </c>
       <c r="H234" s="3">
         <v>1</v>
@@ -9751,15 +9766,15 @@
         <v>0</v>
       </c>
       <c r="M234" s="3" t="s">
-        <v>145</v>
+        <v>142</v>
       </c>
     </row>
     <row r="235" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C235" s="3">
-        <v>60000069</v>
+        <v>60000066</v>
       </c>
       <c r="D235" s="3">
-        <v>60000070</v>
+        <v>60000067</v>
       </c>
       <c r="E235" s="3">
         <v>1</v>
@@ -9768,7 +9783,7 @@
         <v>100</v>
       </c>
       <c r="G235" s="13">
-        <v>10014013</v>
+        <v>10014010</v>
       </c>
       <c r="H235" s="3">
         <v>1</v>
@@ -9783,15 +9798,15 @@
         <v>0</v>
       </c>
       <c r="M235" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
     </row>
     <row r="236" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C236" s="3">
-        <v>60000070</v>
+        <v>60000067</v>
       </c>
       <c r="D236" s="3">
-        <v>60000071</v>
+        <v>60000068</v>
       </c>
       <c r="E236" s="3">
         <v>1</v>
@@ -9800,7 +9815,7 @@
         <v>100</v>
       </c>
       <c r="G236" s="13">
-        <v>10014014</v>
+        <v>10014011</v>
       </c>
       <c r="H236" s="3">
         <v>1</v>
@@ -9815,15 +9830,15 @@
         <v>0</v>
       </c>
       <c r="M236" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
     </row>
     <row r="237" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C237" s="3">
-        <v>60000071</v>
+        <v>60000068</v>
       </c>
       <c r="D237" s="3">
-        <v>60000072</v>
+        <v>60000069</v>
       </c>
       <c r="E237" s="3">
         <v>1</v>
@@ -9832,7 +9847,7 @@
         <v>100</v>
       </c>
       <c r="G237" s="13">
-        <v>10014015</v>
+        <v>10014012</v>
       </c>
       <c r="H237" s="3">
         <v>1</v>
@@ -9847,15 +9862,15 @@
         <v>0</v>
       </c>
       <c r="M237" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="238" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C238" s="3">
-        <v>60000072</v>
+        <v>60000069</v>
       </c>
       <c r="D238" s="3">
-        <v>60000073</v>
+        <v>60000070</v>
       </c>
       <c r="E238" s="3">
         <v>1</v>
@@ -9864,7 +9879,7 @@
         <v>100</v>
       </c>
       <c r="G238" s="13">
-        <v>10014016</v>
+        <v>10014013</v>
       </c>
       <c r="H238" s="3">
         <v>1</v>
@@ -9879,15 +9894,15 @@
         <v>0</v>
       </c>
       <c r="M238" s="3" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
     </row>
     <row r="239" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C239" s="3">
-        <v>60000073</v>
+        <v>60000070</v>
       </c>
       <c r="D239" s="3">
-        <v>60000074</v>
+        <v>60000071</v>
       </c>
       <c r="E239" s="3">
         <v>1</v>
@@ -9896,7 +9911,7 @@
         <v>100</v>
       </c>
       <c r="G239" s="13">
-        <v>10014017</v>
+        <v>10014014</v>
       </c>
       <c r="H239" s="3">
         <v>1</v>
@@ -9911,15 +9926,15 @@
         <v>0</v>
       </c>
       <c r="M239" s="3" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
     </row>
     <row r="240" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C240" s="3">
-        <v>60000074</v>
+        <v>60000071</v>
       </c>
       <c r="D240" s="3">
-        <v>60000075</v>
+        <v>60000072</v>
       </c>
       <c r="E240" s="3">
         <v>1</v>
@@ -9928,7 +9943,7 @@
         <v>100</v>
       </c>
       <c r="G240" s="13">
-        <v>10014018</v>
+        <v>10014015</v>
       </c>
       <c r="H240" s="3">
         <v>1</v>
@@ -9943,15 +9958,15 @@
         <v>0</v>
       </c>
       <c r="M240" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="241" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C241" s="3">
-        <v>60000075</v>
+        <v>60000072</v>
       </c>
       <c r="D241" s="3">
-        <v>60000076</v>
+        <v>60000073</v>
       </c>
       <c r="E241" s="3">
         <v>1</v>
@@ -9960,7 +9975,7 @@
         <v>100</v>
       </c>
       <c r="G241" s="13">
-        <v>10014019</v>
+        <v>10014016</v>
       </c>
       <c r="H241" s="3">
         <v>1</v>
@@ -9975,15 +9990,15 @@
         <v>0</v>
       </c>
       <c r="M241" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
     </row>
     <row r="242" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C242" s="3">
-        <v>60000076</v>
+        <v>60000073</v>
       </c>
       <c r="D242" s="3">
-        <v>60000077</v>
+        <v>60000074</v>
       </c>
       <c r="E242" s="3">
         <v>1</v>
@@ -9992,7 +10007,7 @@
         <v>100</v>
       </c>
       <c r="G242" s="13">
-        <v>10014020</v>
+        <v>10014017</v>
       </c>
       <c r="H242" s="3">
         <v>1</v>
@@ -10001,21 +10016,21 @@
         <v>10010031</v>
       </c>
       <c r="J242" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K242" s="2">
         <v>0</v>
       </c>
       <c r="M242" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="243" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C243" s="3">
-        <v>60000077</v>
+        <v>60000074</v>
       </c>
       <c r="D243" s="3">
-        <v>60000078</v>
+        <v>60000075</v>
       </c>
       <c r="E243" s="3">
         <v>1</v>
@@ -10024,7 +10039,7 @@
         <v>100</v>
       </c>
       <c r="G243" s="13">
-        <v>10014021</v>
+        <v>10014018</v>
       </c>
       <c r="H243" s="3">
         <v>1</v>
@@ -10033,21 +10048,21 @@
         <v>10010031</v>
       </c>
       <c r="J243" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K243" s="2">
         <v>0</v>
       </c>
       <c r="M243" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="244" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C244" s="3">
-        <v>60000078</v>
+        <v>60000075</v>
       </c>
       <c r="D244" s="3">
-        <v>60000079</v>
+        <v>60000076</v>
       </c>
       <c r="E244" s="3">
         <v>1</v>
@@ -10056,7 +10071,7 @@
         <v>100</v>
       </c>
       <c r="G244" s="13">
-        <v>10014022</v>
+        <v>10014019</v>
       </c>
       <c r="H244" s="3">
         <v>1</v>
@@ -10065,21 +10080,21 @@
         <v>10010031</v>
       </c>
       <c r="J244" s="3">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="K244" s="2">
         <v>0</v>
       </c>
       <c r="M244" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="245" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C245" s="3">
-        <v>60000079</v>
+        <v>60000076</v>
       </c>
       <c r="D245" s="3">
-        <v>60000080</v>
+        <v>60000077</v>
       </c>
       <c r="E245" s="3">
         <v>1</v>
@@ -10088,7 +10103,7 @@
         <v>100</v>
       </c>
       <c r="G245" s="13">
-        <v>10014023</v>
+        <v>10014020</v>
       </c>
       <c r="H245" s="3">
         <v>1</v>
@@ -10103,15 +10118,15 @@
         <v>0</v>
       </c>
       <c r="M245" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="246" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C246" s="3">
-        <v>60000080</v>
+        <v>60000077</v>
       </c>
       <c r="D246" s="3">
-        <v>60000081</v>
+        <v>60000078</v>
       </c>
       <c r="E246" s="3">
         <v>1</v>
@@ -10120,7 +10135,7 @@
         <v>100</v>
       </c>
       <c r="G246" s="13">
-        <v>10014024</v>
+        <v>10014021</v>
       </c>
       <c r="H246" s="3">
         <v>1</v>
@@ -10135,15 +10150,15 @@
         <v>0</v>
       </c>
       <c r="M246" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="247" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C247" s="3">
-        <v>60000081</v>
+        <v>60000078</v>
       </c>
       <c r="D247" s="3">
-        <v>60000082</v>
+        <v>60000079</v>
       </c>
       <c r="E247" s="3">
         <v>1</v>
@@ -10152,7 +10167,7 @@
         <v>100</v>
       </c>
       <c r="G247" s="13">
-        <v>10014025</v>
+        <v>10014022</v>
       </c>
       <c r="H247" s="3">
         <v>1</v>
@@ -10167,15 +10182,15 @@
         <v>0</v>
       </c>
       <c r="M247" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
     </row>
     <row r="248" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C248" s="3">
-        <v>60000082</v>
+        <v>60000079</v>
       </c>
       <c r="D248" s="3">
-        <v>60000083</v>
+        <v>60000080</v>
       </c>
       <c r="E248" s="3">
         <v>1</v>
@@ -10184,7 +10199,7 @@
         <v>100</v>
       </c>
       <c r="G248" s="13">
-        <v>10014026</v>
+        <v>10014023</v>
       </c>
       <c r="H248" s="3">
         <v>1</v>
@@ -10199,15 +10214,15 @@
         <v>0</v>
       </c>
       <c r="M248" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="249" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C249" s="3">
-        <v>60000083</v>
+        <v>60000080</v>
       </c>
       <c r="D249" s="3">
-        <v>0</v>
+        <v>60000081</v>
       </c>
       <c r="E249" s="3">
         <v>1</v>
@@ -10216,7 +10231,7 @@
         <v>100</v>
       </c>
       <c r="G249" s="13">
-        <v>10014027</v>
+        <v>10014024</v>
       </c>
       <c r="H249" s="3">
         <v>1</v>
@@ -10231,15 +10246,15 @@
         <v>0</v>
       </c>
       <c r="M249" s="3" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="250" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C250" s="3">
-        <v>70000001</v>
+        <v>60000081</v>
       </c>
       <c r="D250" s="3">
-        <v>70000002</v>
+        <v>60000082</v>
       </c>
       <c r="E250" s="3">
         <v>1</v>
@@ -10247,31 +10262,31 @@
       <c r="F250" s="3">
         <v>100</v>
       </c>
-      <c r="G250" s="9">
-        <v>10010093</v>
+      <c r="G250" s="13">
+        <v>10014025</v>
       </c>
       <c r="H250" s="3">
         <v>1</v>
       </c>
-      <c r="I250" s="8">
-        <v>10000159</v>
-      </c>
-      <c r="J250" s="8">
+      <c r="I250" s="3">
+        <v>10010031</v>
+      </c>
+      <c r="J250" s="3">
         <v>30</v>
       </c>
       <c r="K250" s="2">
         <v>0</v>
       </c>
-      <c r="M250" s="12" t="s">
-        <v>49</v>
+      <c r="M250" s="3" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="251" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C251" s="3">
-        <v>70000002</v>
+        <v>60000082</v>
       </c>
       <c r="D251" s="3">
-        <v>70000003</v>
+        <v>60000083</v>
       </c>
       <c r="E251" s="3">
         <v>1</v>
@@ -10279,31 +10294,31 @@
       <c r="F251" s="3">
         <v>100</v>
       </c>
-      <c r="G251" s="9">
-        <v>10000162</v>
+      <c r="G251" s="13">
+        <v>10014026</v>
       </c>
       <c r="H251" s="3">
         <v>1</v>
       </c>
-      <c r="I251" s="8">
-        <v>10000159</v>
-      </c>
-      <c r="J251" s="8">
-        <v>20</v>
+      <c r="I251" s="3">
+        <v>10010031</v>
+      </c>
+      <c r="J251" s="3">
+        <v>30</v>
       </c>
       <c r="K251" s="2">
         <v>0</v>
       </c>
-      <c r="M251" s="11" t="s">
-        <v>104</v>
+      <c r="M251" s="3" t="s">
+        <v>159</v>
       </c>
     </row>
     <row r="252" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C252" s="3">
-        <v>70000003</v>
+        <v>60000083</v>
       </c>
       <c r="D252" s="3">
-        <v>70000004</v>
+        <v>0</v>
       </c>
       <c r="E252" s="3">
         <v>1</v>
@@ -10311,31 +10326,31 @@
       <c r="F252" s="3">
         <v>100</v>
       </c>
-      <c r="G252" s="9">
-        <v>10010045</v>
+      <c r="G252" s="13">
+        <v>10014027</v>
       </c>
       <c r="H252" s="3">
         <v>1</v>
       </c>
-      <c r="I252" s="8">
-        <v>10000159</v>
-      </c>
-      <c r="J252" s="8">
+      <c r="I252" s="3">
+        <v>10010031</v>
+      </c>
+      <c r="J252" s="3">
         <v>30</v>
       </c>
       <c r="K252" s="2">
         <v>0</v>
       </c>
-      <c r="M252" s="11" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="253" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M252" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="253" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C253" s="3">
-        <v>70000004</v>
+        <v>70000001</v>
       </c>
       <c r="D253" s="3">
-        <v>70000005</v>
+        <v>70000002</v>
       </c>
       <c r="E253" s="3">
         <v>1</v>
@@ -10344,7 +10359,7 @@
         <v>100</v>
       </c>
       <c r="G253" s="9">
-        <v>10000158</v>
+        <v>10010093</v>
       </c>
       <c r="H253" s="3">
         <v>1</v>
@@ -10353,21 +10368,21 @@
         <v>10000159</v>
       </c>
       <c r="J253" s="8">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="K253" s="2">
         <v>0</v>
       </c>
-      <c r="M253" s="9" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="254" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M253" s="12" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="254" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C254" s="3">
-        <v>70000005</v>
+        <v>70000002</v>
       </c>
       <c r="D254" s="3">
-        <v>70000006</v>
+        <v>70000003</v>
       </c>
       <c r="E254" s="3">
         <v>1</v>
@@ -10376,7 +10391,7 @@
         <v>100</v>
       </c>
       <c r="G254" s="9">
-        <v>10010083</v>
+        <v>10000162</v>
       </c>
       <c r="H254" s="3">
         <v>1</v>
@@ -10385,21 +10400,21 @@
         <v>10000159</v>
       </c>
       <c r="J254" s="8">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="K254" s="2">
         <v>0</v>
       </c>
-      <c r="M254" s="16" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="255" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="M254" s="11" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="255" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C255" s="3">
-        <v>70000006</v>
+        <v>70000003</v>
       </c>
       <c r="D255" s="3">
-        <v>70000007</v>
+        <v>70000004</v>
       </c>
       <c r="E255" s="3">
         <v>1</v>
@@ -10408,7 +10423,7 @@
         <v>100</v>
       </c>
       <c r="G255" s="9">
-        <v>10000143</v>
+        <v>10010045</v>
       </c>
       <c r="H255" s="3">
         <v>1</v>
@@ -10417,21 +10432,21 @@
         <v>10000159</v>
       </c>
       <c r="J255" s="8">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="K255" s="2">
         <v>0</v>
       </c>
-      <c r="M255" s="16" t="s">
-        <v>47</v>
+      <c r="M255" s="11" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="256" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C256" s="3">
-        <v>70000007</v>
+        <v>70000004</v>
       </c>
       <c r="D256" s="3">
-        <v>70000008</v>
+        <v>70000005</v>
       </c>
       <c r="E256" s="3">
         <v>1</v>
@@ -10440,7 +10455,7 @@
         <v>100</v>
       </c>
       <c r="G256" s="9">
-        <v>10000152</v>
+        <v>10000158</v>
       </c>
       <c r="H256" s="3">
         <v>1</v>
@@ -10449,21 +10464,21 @@
         <v>10000159</v>
       </c>
       <c r="J256" s="8">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K256" s="2">
         <v>0</v>
       </c>
-      <c r="M256" s="11" t="s">
-        <v>38</v>
+      <c r="M256" s="9" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="257" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C257" s="3">
-        <v>70000008</v>
+        <v>70000005</v>
       </c>
       <c r="D257" s="3">
-        <v>70000009</v>
+        <v>70000006</v>
       </c>
       <c r="E257" s="3">
         <v>1</v>
@@ -10472,7 +10487,7 @@
         <v>100</v>
       </c>
       <c r="G257" s="9">
-        <v>10000157</v>
+        <v>10010083</v>
       </c>
       <c r="H257" s="3">
         <v>1</v>
@@ -10481,21 +10496,21 @@
         <v>10000159</v>
       </c>
       <c r="J257" s="8">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="K257" s="2">
         <v>0</v>
       </c>
-      <c r="M257" s="11" t="s">
-        <v>39</v>
+      <c r="M257" s="16" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="258" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C258" s="3">
-        <v>70000009</v>
+        <v>70000006</v>
       </c>
       <c r="D258" s="3">
-        <v>70000010</v>
+        <v>70000007</v>
       </c>
       <c r="E258" s="3">
         <v>1</v>
@@ -10504,7 +10519,7 @@
         <v>100</v>
       </c>
       <c r="G258" s="9">
-        <v>10010029</v>
+        <v>10000143</v>
       </c>
       <c r="H258" s="3">
         <v>1</v>
@@ -10518,16 +10533,16 @@
       <c r="K258" s="2">
         <v>0</v>
       </c>
-      <c r="M258" s="11" t="s">
-        <v>108</v>
+      <c r="M258" s="16" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="259" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C259" s="3">
-        <v>70000010</v>
+        <v>70000007</v>
       </c>
       <c r="D259" s="3">
-        <v>70000011</v>
+        <v>70000008</v>
       </c>
       <c r="E259" s="3">
         <v>1</v>
@@ -10536,7 +10551,7 @@
         <v>100</v>
       </c>
       <c r="G259" s="9">
-        <v>10010086</v>
+        <v>10000152</v>
       </c>
       <c r="H259" s="3">
         <v>1</v>
@@ -10550,16 +10565,16 @@
       <c r="K259" s="2">
         <v>0</v>
       </c>
-      <c r="M259" s="12" t="s">
-        <v>27</v>
+      <c r="M259" s="11" t="s">
+        <v>38</v>
       </c>
     </row>
     <row r="260" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C260" s="3">
-        <v>70000011</v>
+        <v>70000008</v>
       </c>
       <c r="D260" s="3">
-        <v>70000012</v>
+        <v>70000009</v>
       </c>
       <c r="E260" s="3">
         <v>1</v>
@@ -10567,8 +10582,8 @@
       <c r="F260" s="3">
         <v>100</v>
       </c>
-      <c r="G260" s="18">
-        <v>10010101</v>
+      <c r="G260" s="9">
+        <v>10000157</v>
       </c>
       <c r="H260" s="3">
         <v>1</v>
@@ -10577,21 +10592,21 @@
         <v>10000159</v>
       </c>
       <c r="J260" s="8">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="K260" s="2">
         <v>0</v>
       </c>
-      <c r="M260" s="8" t="s">
-        <v>109</v>
+      <c r="M260" s="11" t="s">
+        <v>39</v>
       </c>
     </row>
     <row r="261" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C261" s="3">
-        <v>70000012</v>
+        <v>70000009</v>
       </c>
       <c r="D261" s="3">
-        <v>70000013</v>
+        <v>70000010</v>
       </c>
       <c r="E261" s="3">
         <v>1</v>
@@ -10599,8 +10614,8 @@
       <c r="F261" s="3">
         <v>100</v>
       </c>
-      <c r="G261" s="18">
-        <v>10010102</v>
+      <c r="G261" s="9">
+        <v>10010029</v>
       </c>
       <c r="H261" s="3">
         <v>1</v>
@@ -10609,21 +10624,21 @@
         <v>10000159</v>
       </c>
       <c r="J261" s="8">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K261" s="2">
         <v>0</v>
       </c>
-      <c r="M261" s="3" t="s">
-        <v>110</v>
+      <c r="M261" s="11" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="262" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C262" s="3">
-        <v>70000013</v>
+        <v>70000010</v>
       </c>
       <c r="D262" s="3">
-        <v>0</v>
+        <v>70000011</v>
       </c>
       <c r="E262" s="3">
         <v>1</v>
@@ -10631,8 +10646,8 @@
       <c r="F262" s="3">
         <v>100</v>
       </c>
-      <c r="G262" s="18">
-        <v>10010103</v>
+      <c r="G262" s="9">
+        <v>10010086</v>
       </c>
       <c r="H262" s="3">
         <v>1</v>
@@ -10641,126 +10656,126 @@
         <v>10000159</v>
       </c>
       <c r="J262" s="8">
+        <v>10</v>
+      </c>
+      <c r="K262" s="2">
+        <v>0</v>
+      </c>
+      <c r="M262" s="12" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="263" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C263" s="3">
+        <v>70000011</v>
+      </c>
+      <c r="D263" s="3">
+        <v>70000012</v>
+      </c>
+      <c r="E263" s="3">
+        <v>1</v>
+      </c>
+      <c r="F263" s="3">
+        <v>100</v>
+      </c>
+      <c r="G263" s="18">
+        <v>10010101</v>
+      </c>
+      <c r="H263" s="3">
+        <v>1</v>
+      </c>
+      <c r="I263" s="8">
+        <v>10000159</v>
+      </c>
+      <c r="J263" s="8">
+        <v>5</v>
+      </c>
+      <c r="K263" s="2">
+        <v>0</v>
+      </c>
+      <c r="M263" s="8" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="264" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C264" s="3">
+        <v>70000012</v>
+      </c>
+      <c r="D264" s="3">
+        <v>70000013</v>
+      </c>
+      <c r="E264" s="3">
+        <v>1</v>
+      </c>
+      <c r="F264" s="3">
+        <v>100</v>
+      </c>
+      <c r="G264" s="18">
+        <v>10010102</v>
+      </c>
+      <c r="H264" s="3">
+        <v>1</v>
+      </c>
+      <c r="I264" s="8">
+        <v>10000159</v>
+      </c>
+      <c r="J264" s="8">
+        <v>10</v>
+      </c>
+      <c r="K264" s="2">
+        <v>0</v>
+      </c>
+      <c r="M264" s="3" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="265" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C265" s="3">
+        <v>70000013</v>
+      </c>
+      <c r="D265" s="3">
+        <v>0</v>
+      </c>
+      <c r="E265" s="3">
+        <v>1</v>
+      </c>
+      <c r="F265" s="3">
+        <v>100</v>
+      </c>
+      <c r="G265" s="18">
+        <v>10010103</v>
+      </c>
+      <c r="H265" s="3">
+        <v>1</v>
+      </c>
+      <c r="I265" s="8">
+        <v>10000159</v>
+      </c>
+      <c r="J265" s="8">
         <v>20</v>
       </c>
-      <c r="K262" s="2">
-        <v>0</v>
-      </c>
-      <c r="M262" s="3" t="s">
+      <c r="K265" s="2">
+        <v>0</v>
+      </c>
+      <c r="M265" s="3" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="263" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C263" s="3">
+    <row r="266" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C266" s="3">
         <v>80000001</v>
       </c>
-      <c r="D263" s="3">
+      <c r="D266" s="3">
         <v>80000002</v>
       </c>
-      <c r="E263" s="3">
-        <v>1</v>
-      </c>
-      <c r="F263" s="3">
-        <v>100</v>
-      </c>
-      <c r="G263" s="9">
+      <c r="E266" s="3">
+        <v>1</v>
+      </c>
+      <c r="F266" s="3">
+        <v>100</v>
+      </c>
+      <c r="G266" s="9">
         <v>10010083</v>
-      </c>
-      <c r="H263" s="3">
-        <v>1</v>
-      </c>
-      <c r="I263" s="8">
-        <v>10000163</v>
-      </c>
-      <c r="J263" s="8">
-        <v>1</v>
-      </c>
-      <c r="K263" s="2">
-        <v>0</v>
-      </c>
-      <c r="M263" s="3" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="264" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C264" s="3">
-        <v>80000002</v>
-      </c>
-      <c r="D264" s="3">
-        <v>80000003</v>
-      </c>
-      <c r="E264" s="3">
-        <v>1</v>
-      </c>
-      <c r="F264" s="3">
-        <v>100</v>
-      </c>
-      <c r="G264" s="9">
-        <v>10010086</v>
-      </c>
-      <c r="H264" s="3">
-        <v>1</v>
-      </c>
-      <c r="I264" s="8">
-        <v>10000163</v>
-      </c>
-      <c r="J264" s="8">
-        <v>20</v>
-      </c>
-      <c r="K264" s="2">
-        <v>0</v>
-      </c>
-      <c r="M264" s="3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="265" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C265" s="3">
-        <v>80000003</v>
-      </c>
-      <c r="D265" s="3">
-        <v>80000004</v>
-      </c>
-      <c r="E265" s="3">
-        <v>1</v>
-      </c>
-      <c r="F265" s="3">
-        <v>100</v>
-      </c>
-      <c r="G265" s="9">
-        <v>10010096</v>
-      </c>
-      <c r="H265" s="3">
-        <v>1</v>
-      </c>
-      <c r="I265" s="8">
-        <v>10000163</v>
-      </c>
-      <c r="J265" s="8">
-        <v>35</v>
-      </c>
-      <c r="K265" s="2">
-        <v>0</v>
-      </c>
-      <c r="M265" s="3" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="266" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C266" s="3">
-        <v>80000004</v>
-      </c>
-      <c r="D266" s="3">
-        <v>80000005</v>
-      </c>
-      <c r="E266" s="3">
-        <v>1</v>
-      </c>
-      <c r="F266" s="3">
-        <v>100</v>
-      </c>
-      <c r="G266" s="9">
-        <v>10000139</v>
       </c>
       <c r="H266" s="3">
         <v>1</v>
@@ -10769,21 +10784,21 @@
         <v>10000163</v>
       </c>
       <c r="J266" s="8">
-        <v>20</v>
+        <v>1</v>
       </c>
       <c r="K266" s="2">
         <v>0</v>
       </c>
       <c r="M266" s="3" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="267" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="267" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C267" s="3">
-        <v>80000005</v>
+        <v>80000002</v>
       </c>
       <c r="D267" s="3">
-        <v>80000006</v>
+        <v>80000003</v>
       </c>
       <c r="E267" s="3">
         <v>1</v>
@@ -10792,7 +10807,7 @@
         <v>100</v>
       </c>
       <c r="G267" s="9">
-        <v>10000143</v>
+        <v>10010086</v>
       </c>
       <c r="H267" s="3">
         <v>1</v>
@@ -10807,15 +10822,15 @@
         <v>0</v>
       </c>
       <c r="M267" s="3" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="268" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="268" spans="3:13" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C268" s="3">
-        <v>80000006</v>
+        <v>80000003</v>
       </c>
       <c r="D268" s="3">
-        <v>80000007</v>
+        <v>80000004</v>
       </c>
       <c r="E268" s="3">
         <v>1</v>
@@ -10824,7 +10839,7 @@
         <v>100</v>
       </c>
       <c r="G268" s="9">
-        <v>10000152</v>
+        <v>10010096</v>
       </c>
       <c r="H268" s="3">
         <v>1</v>
@@ -10839,15 +10854,15 @@
         <v>0</v>
       </c>
       <c r="M268" s="3" t="s">
-        <v>38</v>
+        <v>112</v>
       </c>
     </row>
     <row r="269" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C269" s="3">
-        <v>80000007</v>
+        <v>80000004</v>
       </c>
       <c r="D269" s="3">
-        <v>80000008</v>
+        <v>80000005</v>
       </c>
       <c r="E269" s="3">
         <v>1</v>
@@ -10856,7 +10871,7 @@
         <v>100</v>
       </c>
       <c r="G269" s="9">
-        <v>10000155</v>
+        <v>10000139</v>
       </c>
       <c r="H269" s="3">
         <v>1</v>
@@ -10865,21 +10880,21 @@
         <v>10000163</v>
       </c>
       <c r="J269" s="8">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="K269" s="2">
         <v>0</v>
       </c>
       <c r="M269" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="270" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C270" s="3">
-        <v>80000008</v>
+        <v>80000005</v>
       </c>
       <c r="D270" s="3">
-        <v>80000009</v>
+        <v>80000006</v>
       </c>
       <c r="E270" s="3">
         <v>1</v>
@@ -10888,7 +10903,7 @@
         <v>100</v>
       </c>
       <c r="G270" s="9">
-        <v>10000158</v>
+        <v>10000143</v>
       </c>
       <c r="H270" s="3">
         <v>1</v>
@@ -10903,15 +10918,15 @@
         <v>0</v>
       </c>
       <c r="M270" s="3" t="s">
-        <v>106</v>
+        <v>47</v>
       </c>
     </row>
     <row r="271" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C271" s="3">
-        <v>80000009</v>
+        <v>80000006</v>
       </c>
       <c r="D271" s="3">
-        <v>0</v>
+        <v>80000007</v>
       </c>
       <c r="E271" s="3">
         <v>1</v>
@@ -10920,7 +10935,7 @@
         <v>100</v>
       </c>
       <c r="G271" s="9">
-        <v>10010093</v>
+        <v>10000152</v>
       </c>
       <c r="H271" s="3">
         <v>1</v>
@@ -10935,114 +10950,111 @@
         <v>0</v>
       </c>
       <c r="M271" s="3" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
     </row>
     <row r="272" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C272" s="3">
-        <v>90000001</v>
+        <v>80000007</v>
       </c>
       <c r="D272" s="3">
-        <v>90000002</v>
-      </c>
-      <c r="E272" s="2">
+        <v>80000008</v>
+      </c>
+      <c r="E272" s="3">
         <v>1</v>
       </c>
       <c r="F272" s="3">
         <v>100</v>
       </c>
-      <c r="G272" s="3">
-        <v>10010093</v>
+      <c r="G272" s="9">
+        <v>10000155</v>
       </c>
       <c r="H272" s="3">
         <v>1</v>
       </c>
       <c r="I272" s="8">
-        <v>10000184</v>
+        <v>10000163</v>
       </c>
       <c r="J272" s="8">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="K272" s="2">
         <v>0</v>
       </c>
-      <c r="L272" s="2"/>
-      <c r="M272" s="12" t="s">
-        <v>49</v>
+      <c r="M272" s="3" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="273" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C273" s="3">
-        <v>90000002</v>
+        <v>80000008</v>
       </c>
       <c r="D273" s="3">
-        <v>90000003</v>
-      </c>
-      <c r="E273" s="2">
+        <v>80000009</v>
+      </c>
+      <c r="E273" s="3">
         <v>1</v>
       </c>
       <c r="F273" s="3">
         <v>100</v>
       </c>
-      <c r="G273" s="3">
-        <v>10010083</v>
+      <c r="G273" s="9">
+        <v>10000158</v>
       </c>
       <c r="H273" s="3">
         <v>1</v>
       </c>
       <c r="I273" s="8">
-        <v>10000184</v>
+        <v>10000163</v>
       </c>
       <c r="J273" s="8">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="K273" s="2">
         <v>0</v>
       </c>
-      <c r="L273" s="2"/>
-      <c r="M273" s="16" t="s">
-        <v>107</v>
+      <c r="M273" s="3" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="274" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C274" s="3">
-        <v>90000003</v>
+        <v>80000009</v>
       </c>
       <c r="D274" s="3">
-        <v>90000004</v>
-      </c>
-      <c r="E274" s="2">
+        <v>0</v>
+      </c>
+      <c r="E274" s="3">
         <v>1</v>
       </c>
       <c r="F274" s="3">
         <v>100</v>
       </c>
-      <c r="G274" s="3">
-        <v>10010086</v>
+      <c r="G274" s="9">
+        <v>10010093</v>
       </c>
       <c r="H274" s="3">
         <v>1</v>
       </c>
       <c r="I274" s="8">
-        <v>10000184</v>
+        <v>10000163</v>
       </c>
       <c r="J274" s="8">
-        <v>25</v>
+        <v>35</v>
       </c>
       <c r="K274" s="2">
         <v>0</v>
       </c>
-      <c r="L274" s="2"/>
-      <c r="M274" s="12" t="s">
-        <v>27</v>
+      <c r="M274" s="3" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="275" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C275" s="3">
-        <v>90000004</v>
+        <v>90000001</v>
       </c>
       <c r="D275" s="3">
-        <v>90000005</v>
+        <v>90000002</v>
       </c>
       <c r="E275" s="2">
         <v>1</v>
@@ -11051,7 +11063,7 @@
         <v>100</v>
       </c>
       <c r="G275" s="3">
-        <v>10000143</v>
+        <v>10010093</v>
       </c>
       <c r="H275" s="3">
         <v>1</v>
@@ -11060,22 +11072,22 @@
         <v>10000184</v>
       </c>
       <c r="J275" s="8">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="K275" s="2">
         <v>0</v>
       </c>
       <c r="L275" s="2"/>
-      <c r="M275" s="11" t="s">
-        <v>47</v>
+      <c r="M275" s="12" t="s">
+        <v>49</v>
       </c>
     </row>
     <row r="276" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C276" s="3">
-        <v>90000005</v>
+        <v>90000002</v>
       </c>
       <c r="D276" s="3">
-        <v>90000006</v>
+        <v>90000003</v>
       </c>
       <c r="E276" s="2">
         <v>1</v>
@@ -11084,7 +11096,7 @@
         <v>100</v>
       </c>
       <c r="G276" s="3">
-        <v>10000152</v>
+        <v>10010083</v>
       </c>
       <c r="H276" s="3">
         <v>1</v>
@@ -11093,22 +11105,22 @@
         <v>10000184</v>
       </c>
       <c r="J276" s="8">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="K276" s="2">
         <v>0</v>
       </c>
       <c r="L276" s="2"/>
-      <c r="M276" s="11" t="s">
-        <v>38</v>
+      <c r="M276" s="16" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="277" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C277" s="3">
-        <v>90000006</v>
+        <v>90000003</v>
       </c>
       <c r="D277" s="3">
-        <v>90000007</v>
+        <v>90000004</v>
       </c>
       <c r="E277" s="2">
         <v>1</v>
@@ -11117,7 +11129,7 @@
         <v>100</v>
       </c>
       <c r="G277" s="3">
-        <v>10000165</v>
+        <v>10010086</v>
       </c>
       <c r="H277" s="3">
         <v>1</v>
@@ -11126,22 +11138,22 @@
         <v>10000184</v>
       </c>
       <c r="J277" s="8">
-        <v>100</v>
+        <v>25</v>
       </c>
       <c r="K277" s="2">
         <v>0</v>
       </c>
       <c r="L277" s="2"/>
-      <c r="M277" s="11" t="s">
-        <v>45</v>
+      <c r="M277" s="12" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="278" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C278" s="3">
-        <v>90000007</v>
+        <v>90000004</v>
       </c>
       <c r="D278" s="3">
-        <v>90000008</v>
+        <v>90000005</v>
       </c>
       <c r="E278" s="2">
         <v>1</v>
@@ -11150,7 +11162,7 @@
         <v>100</v>
       </c>
       <c r="G278" s="3">
-        <v>10010045</v>
+        <v>10000143</v>
       </c>
       <c r="H278" s="3">
         <v>1</v>
@@ -11159,22 +11171,22 @@
         <v>10000184</v>
       </c>
       <c r="J278" s="8">
-        <v>45</v>
+        <v>30</v>
       </c>
       <c r="K278" s="2">
         <v>0</v>
       </c>
       <c r="L278" s="2"/>
       <c r="M278" s="11" t="s">
-        <v>105</v>
+        <v>47</v>
       </c>
     </row>
     <row r="279" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C279" s="3">
-        <v>90000008</v>
+        <v>90000005</v>
       </c>
       <c r="D279" s="3">
-        <v>90000009</v>
+        <v>90000006</v>
       </c>
       <c r="E279" s="2">
         <v>1</v>
@@ -11183,7 +11195,7 @@
         <v>100</v>
       </c>
       <c r="G279" s="3">
-        <v>10010090</v>
+        <v>10000152</v>
       </c>
       <c r="H279" s="3">
         <v>1</v>
@@ -11192,22 +11204,22 @@
         <v>10000184</v>
       </c>
       <c r="J279" s="8">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="K279" s="2">
         <v>0</v>
       </c>
       <c r="L279" s="2"/>
       <c r="M279" s="11" t="s">
-        <v>166</v>
+        <v>38</v>
       </c>
     </row>
     <row r="280" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C280" s="3">
-        <v>90000009</v>
+        <v>90000006</v>
       </c>
       <c r="D280" s="3">
-        <v>90000010</v>
+        <v>90000007</v>
       </c>
       <c r="E280" s="2">
         <v>1</v>
@@ -11216,7 +11228,7 @@
         <v>100</v>
       </c>
       <c r="G280" s="3">
-        <v>10010037</v>
+        <v>10000165</v>
       </c>
       <c r="H280" s="3">
         <v>1</v>
@@ -11225,22 +11237,22 @@
         <v>10000184</v>
       </c>
       <c r="J280" s="8">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="K280" s="2">
         <v>0</v>
       </c>
       <c r="L280" s="2"/>
-      <c r="M280" s="25" t="s">
-        <v>167</v>
+      <c r="M280" s="11" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="281" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C281" s="3">
-        <v>90000010</v>
+        <v>90000007</v>
       </c>
       <c r="D281" s="3">
-        <v>0</v>
+        <v>90000008</v>
       </c>
       <c r="E281" s="2">
         <v>1</v>
@@ -11249,7 +11261,7 @@
         <v>100</v>
       </c>
       <c r="G281" s="3">
-        <v>10000179</v>
+        <v>10010045</v>
       </c>
       <c r="H281" s="3">
         <v>1</v>
@@ -11258,22 +11270,22 @@
         <v>10000184</v>
       </c>
       <c r="J281" s="8">
-        <v>30</v>
+        <v>45</v>
       </c>
       <c r="K281" s="2">
         <v>0</v>
       </c>
       <c r="L281" s="2"/>
-      <c r="M281" s="25" t="s">
-        <v>168</v>
+      <c r="M281" s="11" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="282" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C282" s="3">
-        <v>91000001</v>
+        <v>90000008</v>
       </c>
       <c r="D282" s="3">
-        <v>91000002</v>
+        <v>90000009</v>
       </c>
       <c r="E282" s="2">
         <v>1</v>
@@ -11282,30 +11294,31 @@
         <v>100</v>
       </c>
       <c r="G282" s="3">
-        <v>10010086</v>
+        <v>10010037</v>
       </c>
       <c r="H282" s="3">
-        <v>1</v>
-      </c>
-      <c r="I282" s="19">
-        <v>36</v>
-      </c>
-      <c r="J282" s="20">
-        <v>8</v>
+        <v>3</v>
+      </c>
+      <c r="I282" s="8">
+        <v>10000184</v>
+      </c>
+      <c r="J282" s="8">
+        <v>1</v>
       </c>
       <c r="K282" s="2">
         <v>0</v>
       </c>
-      <c r="M282" s="3" t="s">
-        <v>27</v>
+      <c r="L282" s="2"/>
+      <c r="M282" s="25" t="s">
+        <v>166</v>
       </c>
     </row>
     <row r="283" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C283" s="3">
-        <v>91000002</v>
+        <v>90000009</v>
       </c>
       <c r="D283" s="3">
-        <v>91000003</v>
+        <v>0</v>
       </c>
       <c r="E283" s="2">
         <v>1</v>
@@ -11314,30 +11327,31 @@
         <v>100</v>
       </c>
       <c r="G283" s="3">
-        <v>10010096</v>
+        <v>10000168</v>
       </c>
       <c r="H283" s="3">
         <v>1</v>
       </c>
-      <c r="I283" s="19">
-        <v>36</v>
-      </c>
-      <c r="J283" s="20">
-        <v>20</v>
+      <c r="I283" s="8">
+        <v>10000184</v>
+      </c>
+      <c r="J283" s="8">
+        <v>5</v>
       </c>
       <c r="K283" s="2">
         <v>0</v>
       </c>
-      <c r="M283" s="3" t="s">
-        <v>112</v>
+      <c r="L283" s="2"/>
+      <c r="M283" s="25" t="s">
+        <v>170</v>
       </c>
     </row>
     <row r="284" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C284" s="3">
-        <v>91000003</v>
+        <v>91000001</v>
       </c>
       <c r="D284" s="3">
-        <v>91000004</v>
+        <v>91000002</v>
       </c>
       <c r="E284" s="2">
         <v>1</v>
@@ -11346,7 +11360,7 @@
         <v>100</v>
       </c>
       <c r="G284" s="3">
-        <v>10010074</v>
+        <v>10010086</v>
       </c>
       <c r="H284" s="3">
         <v>1</v>
@@ -11361,15 +11375,15 @@
         <v>0</v>
       </c>
       <c r="M284" s="3" t="s">
-        <v>115</v>
+        <v>27</v>
       </c>
     </row>
     <row r="285" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C285" s="3">
-        <v>91000004</v>
+        <v>91000002</v>
       </c>
       <c r="D285" s="3">
-        <v>91000005</v>
+        <v>91000003</v>
       </c>
       <c r="E285" s="2">
         <v>1</v>
@@ -11378,7 +11392,7 @@
         <v>100</v>
       </c>
       <c r="G285" s="3">
-        <v>10010075</v>
+        <v>10010096</v>
       </c>
       <c r="H285" s="3">
         <v>1</v>
@@ -11393,15 +11407,15 @@
         <v>0</v>
       </c>
       <c r="M285" s="3" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="286" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C286" s="3">
-        <v>91000005</v>
+        <v>91000003</v>
       </c>
       <c r="D286" s="3">
-        <v>91000006</v>
+        <v>91000004</v>
       </c>
       <c r="E286" s="2">
         <v>1</v>
@@ -11409,8 +11423,8 @@
       <c r="F286" s="3">
         <v>100</v>
       </c>
-      <c r="G286" s="2">
-        <v>10010083</v>
+      <c r="G286" s="3">
+        <v>10010074</v>
       </c>
       <c r="H286" s="3">
         <v>1</v>
@@ -11419,21 +11433,21 @@
         <v>36</v>
       </c>
       <c r="J286" s="20">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K286" s="2">
         <v>0</v>
       </c>
-      <c r="M286" s="15" t="s">
-        <v>118</v>
+      <c r="M286" s="3" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="287" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C287" s="3">
-        <v>91000006</v>
+        <v>91000004</v>
       </c>
       <c r="D287" s="3">
-        <v>91000007</v>
+        <v>91000005</v>
       </c>
       <c r="E287" s="2">
         <v>1</v>
@@ -11441,8 +11455,8 @@
       <c r="F287" s="3">
         <v>100</v>
       </c>
-      <c r="G287" s="2">
-        <v>10010098</v>
+      <c r="G287" s="3">
+        <v>10010075</v>
       </c>
       <c r="H287" s="3">
         <v>1</v>
@@ -11451,21 +11465,21 @@
         <v>36</v>
       </c>
       <c r="J287" s="20">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="K287" s="2">
         <v>0</v>
       </c>
-      <c r="M287" s="15" t="s">
-        <v>117</v>
+      <c r="M287" s="3" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="288" spans="3:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C288" s="3">
-        <v>91000007</v>
+        <v>91000005</v>
       </c>
       <c r="D288" s="3">
-        <v>0</v>
+        <v>91000006</v>
       </c>
       <c r="E288" s="2">
         <v>1</v>
@@ -11473,8 +11487,8 @@
       <c r="F288" s="3">
         <v>100</v>
       </c>
-      <c r="G288" s="9">
-        <v>10010040</v>
+      <c r="G288" s="2">
+        <v>10010083</v>
       </c>
       <c r="H288" s="3">
         <v>1</v>
@@ -11483,21 +11497,21 @@
         <v>36</v>
       </c>
       <c r="J288" s="20">
-        <v>100</v>
+        <v>1</v>
       </c>
       <c r="K288" s="2">
-        <v>1</v>
-      </c>
-      <c r="M288" s="9" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="289" spans="3:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+      <c r="M288" s="15" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="289" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C289" s="3">
-        <v>92000001</v>
+        <v>91000006</v>
       </c>
       <c r="D289" s="3">
-        <v>92000002</v>
+        <v>91000007</v>
       </c>
       <c r="E289" s="2">
         <v>1</v>
@@ -11505,65 +11519,64 @@
       <c r="F289" s="3">
         <v>100</v>
       </c>
-      <c r="G289" s="3">
-        <v>10060100</v>
+      <c r="G289" s="2">
+        <v>10010098</v>
       </c>
       <c r="H289" s="3">
         <v>1</v>
       </c>
-      <c r="I289" s="9">
-        <v>10000136</v>
-      </c>
-      <c r="J289" s="3">
-        <v>50</v>
+      <c r="I289" s="19">
+        <v>36</v>
+      </c>
+      <c r="J289" s="20">
+        <v>1</v>
       </c>
       <c r="K289" s="2">
         <v>0</v>
       </c>
-      <c r="M289" s="22" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q289" s="7"/>
+      <c r="M289" s="15" t="s">
+        <v>117</v>
+      </c>
     </row>
     <row r="290" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C290" s="3">
+        <v>91000007</v>
+      </c>
+      <c r="D290" s="3">
+        <v>0</v>
+      </c>
+      <c r="E290" s="2">
+        <v>1</v>
+      </c>
+      <c r="F290" s="3">
+        <v>100</v>
+      </c>
+      <c r="G290" s="9">
+        <v>10010040</v>
+      </c>
+      <c r="H290" s="3">
+        <v>1</v>
+      </c>
+      <c r="I290" s="19">
+        <v>36</v>
+      </c>
+      <c r="J290" s="20">
+        <v>100</v>
+      </c>
+      <c r="K290" s="2">
+        <v>1</v>
+      </c>
+      <c r="M290" s="9" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="291" spans="3:17" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C291" s="3">
+        <v>92000001</v>
+      </c>
+      <c r="D291" s="3">
         <v>92000002</v>
       </c>
-      <c r="D290" s="3">
-        <v>92000003</v>
-      </c>
-      <c r="E290" s="2">
-        <v>1</v>
-      </c>
-      <c r="F290" s="3">
-        <v>100</v>
-      </c>
-      <c r="G290" s="3">
-        <v>10060200</v>
-      </c>
-      <c r="H290" s="3">
-        <v>1</v>
-      </c>
-      <c r="I290" s="9">
-        <v>10000136</v>
-      </c>
-      <c r="J290" s="3">
-        <v>50</v>
-      </c>
-      <c r="K290" s="2">
-        <v>0</v>
-      </c>
-      <c r="M290" s="22" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="291" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C291" s="3">
-        <v>92000003</v>
-      </c>
-      <c r="D291" s="3">
-        <v>92000004</v>
-      </c>
       <c r="E291" s="2">
         <v>1</v>
       </c>
@@ -11571,7 +11584,7 @@
         <v>100</v>
       </c>
       <c r="G291" s="3">
-        <v>10060300</v>
+        <v>10060100</v>
       </c>
       <c r="H291" s="3">
         <v>1</v>
@@ -11586,15 +11599,16 @@
         <v>0</v>
       </c>
       <c r="M291" s="22" t="s">
-        <v>125</v>
-      </c>
+        <v>123</v>
+      </c>
+      <c r="Q291" s="7"/>
     </row>
     <row r="292" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C292" s="3">
-        <v>92000004</v>
+        <v>92000002</v>
       </c>
       <c r="D292" s="3">
-        <v>92000005</v>
+        <v>92000003</v>
       </c>
       <c r="E292" s="2">
         <v>1</v>
@@ -11603,7 +11617,7 @@
         <v>100</v>
       </c>
       <c r="G292" s="3">
-        <v>10060400</v>
+        <v>10060200</v>
       </c>
       <c r="H292" s="3">
         <v>1</v>
@@ -11618,15 +11632,15 @@
         <v>0</v>
       </c>
       <c r="M292" s="22" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
     </row>
     <row r="293" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C293" s="3">
-        <v>92000005</v>
+        <v>92000003</v>
       </c>
       <c r="D293" s="3">
-        <v>92000006</v>
+        <v>92000004</v>
       </c>
       <c r="E293" s="2">
         <v>1</v>
@@ -11635,7 +11649,7 @@
         <v>100</v>
       </c>
       <c r="G293" s="3">
-        <v>10060500</v>
+        <v>10060300</v>
       </c>
       <c r="H293" s="3">
         <v>1</v>
@@ -11650,15 +11664,15 @@
         <v>0</v>
       </c>
       <c r="M293" s="22" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
     </row>
     <row r="294" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C294" s="3">
-        <v>92000006</v>
+        <v>92000004</v>
       </c>
       <c r="D294" s="3">
-        <v>92000007</v>
+        <v>92000005</v>
       </c>
       <c r="E294" s="2">
         <v>1</v>
@@ -11667,7 +11681,7 @@
         <v>100</v>
       </c>
       <c r="G294" s="3">
-        <v>10060600</v>
+        <v>10060400</v>
       </c>
       <c r="H294" s="3">
         <v>1</v>
@@ -11682,15 +11696,15 @@
         <v>0</v>
       </c>
       <c r="M294" s="22" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
     </row>
     <row r="295" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C295" s="3">
-        <v>92000007</v>
+        <v>92000005</v>
       </c>
       <c r="D295" s="3">
-        <v>92000008</v>
+        <v>92000006</v>
       </c>
       <c r="E295" s="2">
         <v>1</v>
@@ -11699,7 +11713,7 @@
         <v>100</v>
       </c>
       <c r="G295" s="3">
-        <v>10060700</v>
+        <v>10060500</v>
       </c>
       <c r="H295" s="3">
         <v>1</v>
@@ -11714,15 +11728,15 @@
         <v>0</v>
       </c>
       <c r="M295" s="22" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
     </row>
     <row r="296" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C296" s="3">
-        <v>92000008</v>
+        <v>92000006</v>
       </c>
       <c r="D296" s="3">
-        <v>0</v>
+        <v>92000007</v>
       </c>
       <c r="E296" s="2">
         <v>1</v>
@@ -11731,7 +11745,7 @@
         <v>100</v>
       </c>
       <c r="G296" s="3">
-        <v>10000212</v>
+        <v>10060600</v>
       </c>
       <c r="H296" s="3">
         <v>1</v>
@@ -11740,18 +11754,82 @@
         <v>10000136</v>
       </c>
       <c r="J296" s="3">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="K296" s="2">
         <v>0</v>
       </c>
-      <c r="M296" s="19" t="s">
+      <c r="M296" s="22" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="297" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C297" s="3">
+        <v>92000007</v>
+      </c>
+      <c r="D297" s="3">
+        <v>92000008</v>
+      </c>
+      <c r="E297" s="2">
+        <v>1</v>
+      </c>
+      <c r="F297" s="3">
+        <v>100</v>
+      </c>
+      <c r="G297" s="3">
+        <v>10060700</v>
+      </c>
+      <c r="H297" s="3">
+        <v>1</v>
+      </c>
+      <c r="I297" s="9">
+        <v>10000136</v>
+      </c>
+      <c r="J297" s="3">
+        <v>50</v>
+      </c>
+      <c r="K297" s="2">
+        <v>0</v>
+      </c>
+      <c r="M297" s="22" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="298" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C298" s="3">
+        <v>92000008</v>
+      </c>
+      <c r="D298" s="3">
+        <v>0</v>
+      </c>
+      <c r="E298" s="2">
+        <v>1</v>
+      </c>
+      <c r="F298" s="3">
+        <v>100</v>
+      </c>
+      <c r="G298" s="3">
+        <v>10000212</v>
+      </c>
+      <c r="H298" s="3">
+        <v>1</v>
+      </c>
+      <c r="I298" s="9">
+        <v>10000136</v>
+      </c>
+      <c r="J298" s="3">
+        <v>100</v>
+      </c>
+      <c r="K298" s="2">
+        <v>0</v>
+      </c>
+      <c r="M298" s="19" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="297" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="299" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="300" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="301" spans="3:17" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="15" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
